--- a/data/Template_Resmi_Database_SIRUMAH.xlsx
+++ b/data/Template_Resmi_Database_SIRUMAH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5F8931-08E5-4FEC-A79C-477D3A1DA17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665B7BBB-0F10-469B-AA5A-D173EB610DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12990" yWindow="190" windowWidth="12540" windowHeight="14870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PERUMAHAN" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3552" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="912">
   <si>
     <t>TEMPLATE RESMI DATABASE SIRUMAH — DATA PERUMAHAN</t>
   </si>
@@ -2734,6 +2734,45 @@
   </si>
   <si>
     <t>Jl. Sungai Liat</t>
+  </si>
+  <si>
+    <t>Kecamatan</t>
+  </si>
+  <si>
+    <t>BKKBN</t>
+  </si>
+  <si>
+    <t>Terverifikasi</t>
+  </si>
+  <si>
+    <t>Taman Sari</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Kota</t>
   </si>
 </sst>
 </file>
@@ -24374,105 +24413,215 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A6" s="31"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="16"/>
+      <c r="A6" s="31" t="s">
+        <v>903</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>899</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="16">
+        <v>1977</v>
+      </c>
       <c r="E6" s="16"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="F6" s="19">
+        <v>2023</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>900</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>901</v>
+      </c>
       <c r="I6" s="13"/>
       <c r="J6" s="10"/>
       <c r="K6" s="5"/>
     </row>
     <row r="7" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A7" s="32"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="17"/>
+      <c r="A7" s="32" t="s">
+        <v>905</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>899</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" s="17">
+        <v>1420</v>
+      </c>
       <c r="E7" s="17"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
+      <c r="F7" s="20">
+        <v>2023</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>901</v>
+      </c>
       <c r="I7" s="14"/>
       <c r="J7" s="11"/>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A8" s="32"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="17"/>
+      <c r="A8" s="32" t="s">
+        <v>904</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>899</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>902</v>
+      </c>
+      <c r="D8" s="17">
+        <v>1571</v>
+      </c>
       <c r="E8" s="17"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
+      <c r="F8" s="20">
+        <v>2023</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>901</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="11"/>
       <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A9" s="32"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="17"/>
+      <c r="A9" s="32" t="s">
+        <v>908</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>899</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="17">
+        <v>1322</v>
+      </c>
       <c r="E9" s="17"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
+      <c r="F9" s="20">
+        <v>2023</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>901</v>
+      </c>
       <c r="I9" s="14"/>
       <c r="J9" s="11"/>
       <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A10" s="32"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="17"/>
+      <c r="A10" s="32" t="s">
+        <v>907</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>899</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="D10" s="17">
+        <v>3084</v>
+      </c>
       <c r="E10" s="17"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
+      <c r="F10" s="20">
+        <v>2023</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>901</v>
+      </c>
       <c r="I10" s="14"/>
       <c r="J10" s="11"/>
       <c r="K10" s="7"/>
     </row>
     <row r="11" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A11" s="32"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="17"/>
+      <c r="A11" s="32" t="s">
+        <v>909</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>899</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="17">
+        <v>1450</v>
+      </c>
       <c r="E11" s="17"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
+      <c r="F11" s="20">
+        <v>2023</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>901</v>
+      </c>
       <c r="I11" s="14"/>
       <c r="J11" s="11"/>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A12" s="32"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="17"/>
+      <c r="A12" s="32" t="s">
+        <v>906</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>899</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="D12" s="17">
+        <v>1338</v>
+      </c>
       <c r="E12" s="17"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
+      <c r="F12" s="20">
+        <v>2023</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>901</v>
+      </c>
       <c r="I12" s="14"/>
       <c r="J12" s="11"/>
       <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A13" s="32"/>
-      <c r="B13" s="11"/>
+      <c r="A13" s="32" t="s">
+        <v>910</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>911</v>
+      </c>
       <c r="C13" s="11"/>
       <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+      <c r="E13" s="17">
+        <v>13921</v>
+      </c>
+      <c r="F13" s="20">
+        <v>2023</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>901</v>
+      </c>
       <c r="I13" s="14"/>
       <c r="J13" s="11"/>
       <c r="K13" s="7"/>
@@ -25796,7 +25945,7 @@
       <c r="C38" s="20"/>
       <c r="D38" s="20"/>
       <c r="E38" s="38" t="str">
-        <f t="shared" ref="E38:E69" si="2">IF(A38="","",MAX(C38-D38,0))</f>
+        <f t="shared" ref="E38:E55" si="2">IF(A38="","",MAX(C38-D38,0))</f>
         <v/>
       </c>
       <c r="F38" s="26" t="str">
@@ -38052,7 +38201,7 @@
       <c r="E102" s="50"/>
       <c r="F102" s="50"/>
       <c r="G102" s="26" t="str">
-        <f t="shared" ref="G102:G133" si="3">IF(A102="","",IFERROR(F102/E102,0))</f>
+        <f t="shared" ref="G102:G105" si="3">IF(A102="","",IFERROR(F102/E102,0))</f>
         <v/>
       </c>
       <c r="H102" s="11"/>

--- a/data/Template_Resmi_Database_SIRUMAH.xlsx
+++ b/data/Template_Resmi_Database_SIRUMAH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665B7BBB-0F10-469B-AA5A-D173EB610DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DBD919C-909F-4606-B558-96A6128716CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PERUMAHAN" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3619" uniqueCount="912">
   <si>
     <t>TEMPLATE RESMI DATABASE SIRUMAH — DATA PERUMAHAN</t>
   </si>
@@ -25332,135 +25332,233 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A6" s="31"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="37" t="str">
+      <c r="A6" s="31" t="s">
+        <v>903</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="19">
+        <v>12049</v>
+      </c>
+      <c r="D6" s="19">
+        <v>424</v>
+      </c>
+      <c r="E6" s="37">
         <f t="shared" ref="E6:E37" si="0">IF(A6="","",MAX(C6-D6,0))</f>
-        <v/>
-      </c>
-      <c r="F6" s="25" t="str">
+        <v>11625</v>
+      </c>
+      <c r="F6" s="25">
         <f t="shared" ref="F6:F37" si="1">IF(A6="","",IFERROR(D6/C6,0))</f>
-        <v/>
-      </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
+        <v>3.5189642293966303E-2</v>
+      </c>
+      <c r="G6" s="19">
+        <v>2023</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>900</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>901</v>
+      </c>
       <c r="J6" s="13"/>
       <c r="K6" s="34"/>
     </row>
     <row r="7" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A7" s="32"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="38" t="str">
+      <c r="A7" s="32" t="s">
+        <v>905</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="20">
+        <v>9500</v>
+      </c>
+      <c r="D7" s="20">
+        <v>655</v>
+      </c>
+      <c r="E7" s="38">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F7" s="26" t="str">
+        <v>8845</v>
+      </c>
+      <c r="F7" s="26">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G7" s="20"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
+        <v>6.8947368421052632E-2</v>
+      </c>
+      <c r="G7" s="20">
+        <v>2023</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>901</v>
+      </c>
       <c r="J7" s="14"/>
       <c r="K7" s="35"/>
     </row>
     <row r="8" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A8" s="32"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="38" t="str">
+      <c r="A8" s="32" t="s">
+        <v>904</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>902</v>
+      </c>
+      <c r="C8" s="20">
+        <v>4805</v>
+      </c>
+      <c r="D8" s="20">
+        <v>183</v>
+      </c>
+      <c r="E8" s="38">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F8" s="26" t="str">
+        <v>4622</v>
+      </c>
+      <c r="F8" s="26">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
+        <v>3.8085327783558796E-2</v>
+      </c>
+      <c r="G8" s="20">
+        <v>2023</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>901</v>
+      </c>
       <c r="J8" s="14"/>
       <c r="K8" s="35"/>
     </row>
     <row r="9" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A9" s="32"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="38" t="str">
+      <c r="A9" s="32" t="s">
+        <v>908</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="20">
+        <v>8982</v>
+      </c>
+      <c r="D9" s="20">
+        <v>568</v>
+      </c>
+      <c r="E9" s="38">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F9" s="26" t="str">
+        <v>8414</v>
+      </c>
+      <c r="F9" s="26">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G9" s="20"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+        <v>6.3237586283678468E-2</v>
+      </c>
+      <c r="G9" s="20">
+        <v>2023</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>901</v>
+      </c>
       <c r="J9" s="14"/>
       <c r="K9" s="35"/>
     </row>
     <row r="10" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A10" s="32"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="38" t="str">
+      <c r="A10" s="32" t="s">
+        <v>907</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="C10" s="20">
+        <v>9679</v>
+      </c>
+      <c r="D10" s="20">
+        <v>362</v>
+      </c>
+      <c r="E10" s="38">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F10" s="26" t="str">
+        <v>9317</v>
+      </c>
+      <c r="F10" s="26">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
+        <v>3.7400557908874886E-2</v>
+      </c>
+      <c r="G10" s="20">
+        <v>2023</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>901</v>
+      </c>
       <c r="J10" s="14"/>
       <c r="K10" s="35"/>
     </row>
     <row r="11" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A11" s="32"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="38" t="str">
+      <c r="A11" s="32" t="s">
+        <v>909</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" s="20">
+        <v>5789</v>
+      </c>
+      <c r="D11" s="20">
+        <v>757</v>
+      </c>
+      <c r="E11" s="38">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F11" s="26" t="str">
+        <v>5032</v>
+      </c>
+      <c r="F11" s="26">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G11" s="20"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
+        <v>0.13076524442908966</v>
+      </c>
+      <c r="G11" s="20">
+        <v>2023</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>901</v>
+      </c>
       <c r="J11" s="14"/>
       <c r="K11" s="35"/>
     </row>
     <row r="12" spans="1:11" ht="14.65" customHeight="1">
-      <c r="A12" s="32"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="38" t="str">
+      <c r="A12" s="32" t="s">
+        <v>906</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="C12" s="20">
+        <v>4979</v>
+      </c>
+      <c r="D12" s="20">
+        <v>49</v>
+      </c>
+      <c r="E12" s="38">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F12" s="26" t="str">
+        <v>4930</v>
+      </c>
+      <c r="F12" s="26">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G12" s="20"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
+        <v>9.8413336011247236E-3</v>
+      </c>
+      <c r="G12" s="20">
+        <v>2023</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>900</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>901</v>
+      </c>
       <c r="J12" s="14"/>
       <c r="K12" s="35"/>
     </row>

--- a/data/Template_Resmi_Database_SIRUMAH.xlsx
+++ b/data/Template_Resmi_Database_SIRUMAH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE038FE9-55D6-4530-BADC-F19F5498757E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C3AECB-5E11-41C1-BF8E-DC96B7406620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26241,12 +26241,8 @@
       <c r="S308" s="67"/>
       <c r="T308" s="67"/>
       <c r="U308" s="67"/>
-      <c r="V308" s="75">
-        <v>-2.1093229999999998</v>
-      </c>
-      <c r="W308" s="67">
-        <v>109.067087</v>
-      </c>
+      <c r="V308" s="75"/>
+      <c r="W308" s="67"/>
       <c r="X308" s="69"/>
       <c r="Y308" s="69"/>
       <c r="Z308" s="67"/>

--- a/data/Template_Resmi_Database_SIRUMAH.xlsx
+++ b/data/Template_Resmi_Database_SIRUMAH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179712A2-930A-43AE-B77D-34794AE5054C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCB6C92-CA41-431A-8E82-A2B4793FFEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4126" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4134" uniqueCount="921">
   <si>
     <t>TEMPLATE RESMI DATABASE SIRUMAH — DATA PERUMAHAN</t>
   </si>
@@ -3075,7 +3075,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3261,28 +3261,40 @@
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="8" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -3320,7 +3332,7 @@
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PENGEMBANG"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="DIREKTUR/PELAKSANA"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="ASOSIASI"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="TAHUN_SITEPLAN" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="TAHUN_SITEPLAN" dataDxfId="2"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="JUMLAH_SITEPLAN"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="JUMLAH_TERBANGUN"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="JUMLAH_TERHUNI"/>
@@ -3332,9 +3344,9 @@
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="STATUS_PENGEMBANG"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="STATUS_RAWAN_BANJIR"/>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="CATATAN"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="LATITUDE" dataDxfId="0"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="LATITUDE" dataDxfId="1"/>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="LONGITUDE"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="TAHUN_DATA*"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="TAHUN_DATA*" dataDxfId="0"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="SUMBER_DATA*"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="STATUS_VERIFIKASI*"/>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="TANGGAL_UPDATE*"/>
@@ -3654,106 +3666,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="20" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="66"/>
-      <c r="AA1" s="66"/>
-      <c r="AB1" s="66"/>
-      <c r="AC1" s="66"/>
-      <c r="AD1" s="66"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="70"/>
+      <c r="S1" s="70"/>
+      <c r="T1" s="70"/>
+      <c r="U1" s="70"/>
+      <c r="V1" s="70"/>
+      <c r="W1" s="70"/>
+      <c r="X1" s="70"/>
+      <c r="Y1" s="70"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
     </row>
     <row r="2" spans="1:30" ht="17.399999999999999" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="66"/>
-      <c r="AA2" s="66"/>
-      <c r="AB2" s="66"/>
-      <c r="AC2" s="66"/>
-      <c r="AD2" s="66"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="71"/>
+      <c r="V2" s="71"/>
+      <c r="W2" s="71"/>
+      <c r="X2" s="71"/>
+      <c r="Y2" s="71"/>
+      <c r="Z2" s="73"/>
+      <c r="AA2" s="73"/>
+      <c r="AB2" s="73"/>
+      <c r="AC2" s="73"/>
+      <c r="AD2" s="73"/>
     </row>
     <row r="3" spans="1:30" ht="25.4" customHeight="1">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
-      <c r="V3" s="68"/>
-      <c r="W3" s="68"/>
-      <c r="X3" s="68"/>
-      <c r="Y3" s="68"/>
-      <c r="Z3" s="69"/>
-      <c r="AA3" s="69"/>
-      <c r="AB3" s="69"/>
-      <c r="AC3" s="69"/>
-      <c r="AD3" s="69"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="72"/>
+      <c r="U3" s="72"/>
+      <c r="V3" s="72"/>
+      <c r="W3" s="72"/>
+      <c r="X3" s="72"/>
+      <c r="Y3" s="72"/>
+      <c r="Z3" s="74"/>
+      <c r="AA3" s="74"/>
+      <c r="AB3" s="74"/>
+      <c r="AC3" s="74"/>
+      <c r="AD3" s="74"/>
     </row>
     <row r="5" spans="1:30" ht="24" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -3909,7 +3921,9 @@
       <c r="W6" s="10">
         <v>106.0769433</v>
       </c>
-      <c r="X6" s="25"/>
+      <c r="X6" s="67">
+        <v>2025</v>
+      </c>
       <c r="Y6" s="28"/>
       <c r="Z6" s="53"/>
       <c r="AA6" s="55"/>
@@ -3983,7 +3997,7 @@
       <c r="W7" s="11">
         <v>106.06782029999999</v>
       </c>
-      <c r="X7" s="26"/>
+      <c r="X7" s="68"/>
       <c r="Y7" s="29"/>
       <c r="Z7" s="54"/>
       <c r="AA7" s="56"/>
@@ -4057,7 +4071,7 @@
       <c r="W8" s="11">
         <v>106.065597</v>
       </c>
-      <c r="X8" s="26"/>
+      <c r="X8" s="68"/>
       <c r="Y8" s="29"/>
       <c r="Z8" s="54"/>
       <c r="AA8" s="56"/>
@@ -4131,7 +4145,7 @@
       <c r="W9" s="11">
         <v>106.07257199999999</v>
       </c>
-      <c r="X9" s="26"/>
+      <c r="X9" s="68"/>
       <c r="Y9" s="29"/>
       <c r="Z9" s="54"/>
       <c r="AA9" s="56"/>
@@ -4195,7 +4209,9 @@
       <c r="Q10" s="23" t="s">
         <v>912</v>
       </c>
-      <c r="R10" s="23"/>
+      <c r="R10" s="23" t="s">
+        <v>919</v>
+      </c>
       <c r="S10" s="20"/>
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
@@ -4205,7 +4221,7 @@
       <c r="W10" s="11">
         <v>106.0800655</v>
       </c>
-      <c r="X10" s="26"/>
+      <c r="X10" s="68"/>
       <c r="Y10" s="29"/>
       <c r="Z10" s="54"/>
       <c r="AA10" s="56"/>
@@ -4279,7 +4295,7 @@
       <c r="W11" s="11">
         <v>106.0637443</v>
       </c>
-      <c r="X11" s="26"/>
+      <c r="X11" s="68"/>
       <c r="Y11" s="29"/>
       <c r="Z11" s="54"/>
       <c r="AA11" s="56"/>
@@ -4343,7 +4359,9 @@
       <c r="Q12" s="23" t="s">
         <v>912</v>
       </c>
-      <c r="R12" s="23"/>
+      <c r="R12" s="23" t="s">
+        <v>919</v>
+      </c>
       <c r="S12" s="20"/>
       <c r="T12" s="11"/>
       <c r="U12" s="11"/>
@@ -4353,7 +4371,7 @@
       <c r="W12" s="11">
         <v>106.0958978</v>
       </c>
-      <c r="X12" s="26"/>
+      <c r="X12" s="68"/>
       <c r="Y12" s="29"/>
       <c r="Z12" s="54"/>
       <c r="AA12" s="56"/>
@@ -4427,7 +4445,7 @@
       <c r="W13" s="11">
         <v>106.10589899999999</v>
       </c>
-      <c r="X13" s="26"/>
+      <c r="X13" s="68"/>
       <c r="Y13" s="29"/>
       <c r="Z13" s="54"/>
       <c r="AA13" s="56"/>
@@ -4501,7 +4519,7 @@
       <c r="W14" s="11">
         <v>106.09290710000001</v>
       </c>
-      <c r="X14" s="26"/>
+      <c r="X14" s="68"/>
       <c r="Y14" s="29"/>
       <c r="Z14" s="54"/>
       <c r="AA14" s="56"/>
@@ -4563,9 +4581,11 @@
       </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="23" t="s">
-        <v>914</v>
-      </c>
-      <c r="R15" s="23"/>
+        <v>917</v>
+      </c>
+      <c r="R15" s="23" t="s">
+        <v>919</v>
+      </c>
       <c r="S15" s="20"/>
       <c r="T15" s="11" t="s">
         <v>913</v>
@@ -4577,7 +4597,7 @@
       <c r="W15" s="11">
         <v>106.07501499999999</v>
       </c>
-      <c r="X15" s="26"/>
+      <c r="X15" s="68"/>
       <c r="Y15" s="29"/>
       <c r="Z15" s="54"/>
       <c r="AA15" s="56"/>
@@ -4651,7 +4671,7 @@
       <c r="W16" s="11">
         <v>106.0656738</v>
       </c>
-      <c r="X16" s="26"/>
+      <c r="X16" s="68"/>
       <c r="Y16" s="29"/>
       <c r="Z16" s="54"/>
       <c r="AA16" s="56"/>
@@ -4727,7 +4747,7 @@
       <c r="W17" s="11">
         <v>106.09608110000001</v>
       </c>
-      <c r="X17" s="26"/>
+      <c r="X17" s="68"/>
       <c r="Y17" s="29"/>
       <c r="Z17" s="54"/>
       <c r="AA17" s="56"/>
@@ -4803,7 +4823,7 @@
       <c r="W18" s="11">
         <v>106.14707799999999</v>
       </c>
-      <c r="X18" s="26"/>
+      <c r="X18" s="68"/>
       <c r="Y18" s="29"/>
       <c r="Z18" s="54"/>
       <c r="AA18" s="56"/>
@@ -4881,7 +4901,7 @@
       <c r="W19" s="11">
         <v>106.14707900000001</v>
       </c>
-      <c r="X19" s="26"/>
+      <c r="X19" s="68"/>
       <c r="Y19" s="29"/>
       <c r="Z19" s="54"/>
       <c r="AA19" s="56"/>
@@ -4959,7 +4979,7 @@
       <c r="W20" s="11">
         <v>106.1168948</v>
       </c>
-      <c r="X20" s="26"/>
+      <c r="X20" s="68"/>
       <c r="Y20" s="29"/>
       <c r="Z20" s="54"/>
       <c r="AA20" s="56"/>
@@ -5037,7 +5057,7 @@
       <c r="W21" s="11">
         <v>106.11689490000001</v>
       </c>
-      <c r="X21" s="26"/>
+      <c r="X21" s="68"/>
       <c r="Y21" s="29"/>
       <c r="Z21" s="54"/>
       <c r="AA21" s="56"/>
@@ -5113,7 +5133,7 @@
       <c r="W22" s="11">
         <v>106.1741657</v>
       </c>
-      <c r="X22" s="26"/>
+      <c r="X22" s="68"/>
       <c r="Y22" s="29"/>
       <c r="Z22" s="54"/>
       <c r="AA22" s="56"/>
@@ -5189,7 +5209,7 @@
       <c r="W23" s="11">
         <v>106.1741657</v>
       </c>
-      <c r="X23" s="26"/>
+      <c r="X23" s="68"/>
       <c r="Y23" s="29"/>
       <c r="Z23" s="54"/>
       <c r="AA23" s="56"/>
@@ -5263,7 +5283,7 @@
       <c r="W24" s="11">
         <v>106.13135629999999</v>
       </c>
-      <c r="X24" s="26"/>
+      <c r="X24" s="68"/>
       <c r="Y24" s="29"/>
       <c r="Z24" s="54"/>
       <c r="AA24" s="56"/>
@@ -5337,7 +5357,7 @@
       <c r="W25" s="11">
         <v>106.0581504</v>
       </c>
-      <c r="X25" s="26"/>
+      <c r="X25" s="68"/>
       <c r="Y25" s="29"/>
       <c r="Z25" s="54"/>
       <c r="AA25" s="56"/>
@@ -5411,7 +5431,7 @@
       <c r="W26" s="11">
         <v>106.0581504</v>
       </c>
-      <c r="X26" s="26"/>
+      <c r="X26" s="68"/>
       <c r="Y26" s="29"/>
       <c r="Z26" s="54"/>
       <c r="AA26" s="56"/>
@@ -5475,7 +5495,9 @@
       <c r="Q27" s="23" t="s">
         <v>912</v>
       </c>
-      <c r="R27" s="23"/>
+      <c r="R27" s="23" t="s">
+        <v>920</v>
+      </c>
       <c r="S27" s="20"/>
       <c r="T27" s="11"/>
       <c r="U27" s="11"/>
@@ -5485,7 +5507,7 @@
       <c r="W27" s="11">
         <v>106.08262999999999</v>
       </c>
-      <c r="X27" s="26"/>
+      <c r="X27" s="68"/>
       <c r="Y27" s="29"/>
       <c r="Z27" s="54"/>
       <c r="AA27" s="56"/>
@@ -5559,7 +5581,7 @@
       <c r="W28" s="11">
         <v>106.068039</v>
       </c>
-      <c r="X28" s="26"/>
+      <c r="X28" s="68"/>
       <c r="Y28" s="29"/>
       <c r="Z28" s="54"/>
       <c r="AA28" s="56"/>
@@ -5633,7 +5655,7 @@
       <c r="W29" s="11">
         <v>106.0855923</v>
       </c>
-      <c r="X29" s="26"/>
+      <c r="X29" s="68"/>
       <c r="Y29" s="29"/>
       <c r="Z29" s="54"/>
       <c r="AA29" s="56"/>
@@ -5707,7 +5729,7 @@
       <c r="W30" s="11">
         <v>106.09478319999999</v>
       </c>
-      <c r="X30" s="26"/>
+      <c r="X30" s="68"/>
       <c r="Y30" s="29"/>
       <c r="Z30" s="54"/>
       <c r="AA30" s="56"/>
@@ -5777,7 +5799,7 @@
       <c r="U31" s="11"/>
       <c r="V31" s="11"/>
       <c r="W31" s="11"/>
-      <c r="X31" s="26"/>
+      <c r="X31" s="68"/>
       <c r="Y31" s="29"/>
       <c r="Z31" s="54"/>
       <c r="AA31" s="56"/>
@@ -5853,7 +5875,7 @@
       <c r="W32" s="11">
         <v>106.16171900000001</v>
       </c>
-      <c r="X32" s="26"/>
+      <c r="X32" s="68"/>
       <c r="Y32" s="29"/>
       <c r="Z32" s="54"/>
       <c r="AA32" s="56"/>
@@ -5929,7 +5951,7 @@
       <c r="W33" s="11">
         <v>106.162347</v>
       </c>
-      <c r="X33" s="26"/>
+      <c r="X33" s="68"/>
       <c r="Y33" s="29"/>
       <c r="Z33" s="54"/>
       <c r="AA33" s="56"/>
@@ -6005,7 +6027,7 @@
       <c r="W34" s="11">
         <v>106.163877</v>
       </c>
-      <c r="X34" s="26"/>
+      <c r="X34" s="68"/>
       <c r="Y34" s="29"/>
       <c r="Z34" s="54"/>
       <c r="AA34" s="56"/>
@@ -6079,7 +6101,7 @@
       <c r="W35" s="11">
         <v>106.1647957</v>
       </c>
-      <c r="X35" s="26"/>
+      <c r="X35" s="68"/>
       <c r="Y35" s="29"/>
       <c r="Z35" s="54"/>
       <c r="AA35" s="56"/>
@@ -6155,7 +6177,7 @@
       <c r="W36" s="11">
         <v>106.07701280000001</v>
       </c>
-      <c r="X36" s="26"/>
+      <c r="X36" s="68"/>
       <c r="Y36" s="29"/>
       <c r="Z36" s="54"/>
       <c r="AA36" s="56"/>
@@ -6229,7 +6251,7 @@
       <c r="W37" s="11">
         <v>106.09184</v>
       </c>
-      <c r="X37" s="26"/>
+      <c r="X37" s="68"/>
       <c r="Y37" s="29"/>
       <c r="Z37" s="54"/>
       <c r="AA37" s="56"/>
@@ -6303,7 +6325,7 @@
       <c r="W38" s="11">
         <v>106.0869773</v>
       </c>
-      <c r="X38" s="26"/>
+      <c r="X38" s="68"/>
       <c r="Y38" s="29"/>
       <c r="Z38" s="54"/>
       <c r="AA38" s="56"/>
@@ -6377,7 +6399,7 @@
       <c r="W39" s="11">
         <v>106.078391</v>
       </c>
-      <c r="X39" s="26"/>
+      <c r="X39" s="68"/>
       <c r="Y39" s="29"/>
       <c r="Z39" s="54"/>
       <c r="AA39" s="56"/>
@@ -6451,7 +6473,7 @@
       <c r="W40" s="11">
         <v>106.07858899999999</v>
       </c>
-      <c r="X40" s="26"/>
+      <c r="X40" s="68"/>
       <c r="Y40" s="29"/>
       <c r="Z40" s="54"/>
       <c r="AA40" s="56"/>
@@ -6525,7 +6547,7 @@
       <c r="W41" s="11">
         <v>106.0729504</v>
       </c>
-      <c r="X41" s="26"/>
+      <c r="X41" s="68"/>
       <c r="Y41" s="29"/>
       <c r="Z41" s="54"/>
       <c r="AA41" s="56"/>
@@ -6599,7 +6621,7 @@
       <c r="W42" s="11">
         <v>106.0734587</v>
       </c>
-      <c r="X42" s="26"/>
+      <c r="X42" s="68"/>
       <c r="Y42" s="29"/>
       <c r="Z42" s="54"/>
       <c r="AA42" s="56"/>
@@ -6673,7 +6695,7 @@
       <c r="W43" s="11">
         <v>106.0597731</v>
       </c>
-      <c r="X43" s="26"/>
+      <c r="X43" s="68"/>
       <c r="Y43" s="29"/>
       <c r="Z43" s="54"/>
       <c r="AA43" s="56"/>
@@ -6747,7 +6769,7 @@
       <c r="W44" s="11">
         <v>106.0597731</v>
       </c>
-      <c r="X44" s="26"/>
+      <c r="X44" s="68"/>
       <c r="Y44" s="29"/>
       <c r="Z44" s="54"/>
       <c r="AA44" s="56"/>
@@ -6823,7 +6845,7 @@
       <c r="W45" s="11">
         <v>106.10564100000001</v>
       </c>
-      <c r="X45" s="26"/>
+      <c r="X45" s="68"/>
       <c r="Y45" s="29"/>
       <c r="Z45" s="54"/>
       <c r="AA45" s="56"/>
@@ -6897,7 +6919,7 @@
       <c r="W46" s="11">
         <v>106.09772599999999</v>
       </c>
-      <c r="X46" s="26"/>
+      <c r="X46" s="68"/>
       <c r="Y46" s="29"/>
       <c r="Z46" s="54"/>
       <c r="AA46" s="56"/>
@@ -6971,7 +6993,7 @@
       <c r="W47" s="11">
         <v>106.1672731</v>
       </c>
-      <c r="X47" s="26"/>
+      <c r="X47" s="68"/>
       <c r="Y47" s="29"/>
       <c r="Z47" s="54"/>
       <c r="AA47" s="56"/>
@@ -7045,7 +7067,7 @@
       <c r="W48" s="11">
         <v>106.167591</v>
       </c>
-      <c r="X48" s="26"/>
+      <c r="X48" s="68"/>
       <c r="Y48" s="29"/>
       <c r="Z48" s="54"/>
       <c r="AA48" s="56"/>
@@ -7115,7 +7137,7 @@
       <c r="U49" s="11"/>
       <c r="V49" s="11"/>
       <c r="W49" s="11"/>
-      <c r="X49" s="26"/>
+      <c r="X49" s="68"/>
       <c r="Y49" s="29"/>
       <c r="Z49" s="54"/>
       <c r="AA49" s="56"/>
@@ -7189,7 +7211,7 @@
       <c r="W50" s="11">
         <v>106.0769555</v>
       </c>
-      <c r="X50" s="26"/>
+      <c r="X50" s="68"/>
       <c r="Y50" s="29"/>
       <c r="Z50" s="54"/>
       <c r="AA50" s="56"/>
@@ -7263,7 +7285,7 @@
       <c r="W51" s="11">
         <v>106.1002032</v>
       </c>
-      <c r="X51" s="26"/>
+      <c r="X51" s="68"/>
       <c r="Y51" s="29"/>
       <c r="Z51" s="54"/>
       <c r="AA51" s="56"/>
@@ -7339,7 +7361,7 @@
       <c r="W52" s="11">
         <v>106.09541299999999</v>
       </c>
-      <c r="X52" s="26"/>
+      <c r="X52" s="68"/>
       <c r="Y52" s="29"/>
       <c r="Z52" s="54"/>
       <c r="AA52" s="56"/>
@@ -7415,7 +7437,7 @@
       <c r="W53" s="11">
         <v>106.09485599999999</v>
       </c>
-      <c r="X53" s="26"/>
+      <c r="X53" s="68"/>
       <c r="Y53" s="29"/>
       <c r="Z53" s="54"/>
       <c r="AA53" s="56"/>
@@ -7491,7 +7513,7 @@
       <c r="W54" s="11">
         <v>106.092901</v>
       </c>
-      <c r="X54" s="26"/>
+      <c r="X54" s="68"/>
       <c r="Y54" s="29"/>
       <c r="Z54" s="54"/>
       <c r="AA54" s="56"/>
@@ -7567,7 +7589,7 @@
       <c r="W55" s="11">
         <v>106.089313</v>
       </c>
-      <c r="X55" s="26"/>
+      <c r="X55" s="68"/>
       <c r="Y55" s="29"/>
       <c r="Z55" s="54"/>
       <c r="AA55" s="56"/>
@@ -7641,7 +7663,7 @@
       <c r="W56" s="11">
         <v>106.135379</v>
       </c>
-      <c r="X56" s="26"/>
+      <c r="X56" s="68"/>
       <c r="Y56" s="29"/>
       <c r="Z56" s="54"/>
       <c r="AA56" s="56"/>
@@ -7715,7 +7737,7 @@
       <c r="W57" s="11">
         <v>106.089422</v>
       </c>
-      <c r="X57" s="26"/>
+      <c r="X57" s="68"/>
       <c r="Y57" s="29"/>
       <c r="Z57" s="54"/>
       <c r="AA57" s="56"/>
@@ -7789,7 +7811,7 @@
       <c r="W58" s="11">
         <v>106.0891817</v>
       </c>
-      <c r="X58" s="26"/>
+      <c r="X58" s="68"/>
       <c r="Y58" s="29"/>
       <c r="Z58" s="54"/>
       <c r="AA58" s="56"/>
@@ -7863,7 +7885,7 @@
       <c r="W59" s="11">
         <v>106.088959</v>
       </c>
-      <c r="X59" s="26"/>
+      <c r="X59" s="68"/>
       <c r="Y59" s="29"/>
       <c r="Z59" s="54"/>
       <c r="AA59" s="56"/>
@@ -7937,7 +7959,7 @@
       <c r="W60" s="11">
         <v>106.04731630000001</v>
       </c>
-      <c r="X60" s="26"/>
+      <c r="X60" s="68"/>
       <c r="Y60" s="29"/>
       <c r="Z60" s="54"/>
       <c r="AA60" s="56"/>
@@ -8011,7 +8033,7 @@
       <c r="W61" s="11">
         <v>106.0473164</v>
       </c>
-      <c r="X61" s="26"/>
+      <c r="X61" s="68"/>
       <c r="Y61" s="29"/>
       <c r="Z61" s="54"/>
       <c r="AA61" s="56"/>
@@ -8081,7 +8103,7 @@
       <c r="U62" s="11"/>
       <c r="V62" s="11"/>
       <c r="W62" s="11"/>
-      <c r="X62" s="26"/>
+      <c r="X62" s="68"/>
       <c r="Y62" s="29"/>
       <c r="Z62" s="54"/>
       <c r="AA62" s="56"/>
@@ -8157,7 +8179,7 @@
       <c r="W63" s="11">
         <v>106.0806498</v>
       </c>
-      <c r="X63" s="26"/>
+      <c r="X63" s="68"/>
       <c r="Y63" s="29"/>
       <c r="Z63" s="54"/>
       <c r="AA63" s="56"/>
@@ -8231,7 +8253,7 @@
       <c r="W64" s="11">
         <v>106.1239751</v>
       </c>
-      <c r="X64" s="26"/>
+      <c r="X64" s="68"/>
       <c r="Y64" s="29"/>
       <c r="Z64" s="54"/>
       <c r="AA64" s="56"/>
@@ -8305,7 +8327,7 @@
       <c r="W65" s="11">
         <v>106.12235029999999</v>
       </c>
-      <c r="X65" s="26"/>
+      <c r="X65" s="68"/>
       <c r="Y65" s="29"/>
       <c r="Z65" s="54"/>
       <c r="AA65" s="56"/>
@@ -8379,7 +8401,7 @@
       <c r="W66" s="11">
         <v>106.16664129999999</v>
       </c>
-      <c r="X66" s="26"/>
+      <c r="X66" s="68"/>
       <c r="Y66" s="29"/>
       <c r="Z66" s="54"/>
       <c r="AA66" s="56"/>
@@ -8455,7 +8477,7 @@
       <c r="W67" s="11">
         <v>106.084007</v>
       </c>
-      <c r="X67" s="26"/>
+      <c r="X67" s="68"/>
       <c r="Y67" s="29"/>
       <c r="Z67" s="54"/>
       <c r="AA67" s="56"/>
@@ -8531,7 +8553,7 @@
       <c r="W68" s="11">
         <v>106.080001</v>
       </c>
-      <c r="X68" s="26"/>
+      <c r="X68" s="68"/>
       <c r="Y68" s="29"/>
       <c r="Z68" s="54"/>
       <c r="AA68" s="56"/>
@@ -8607,7 +8629,7 @@
       <c r="W69" s="11">
         <v>106.0800362</v>
       </c>
-      <c r="X69" s="26"/>
+      <c r="X69" s="68"/>
       <c r="Y69" s="29"/>
       <c r="Z69" s="54"/>
       <c r="AA69" s="56"/>
@@ -8683,7 +8705,7 @@
       <c r="W70" s="11">
         <v>106.080805</v>
       </c>
-      <c r="X70" s="26"/>
+      <c r="X70" s="68"/>
       <c r="Y70" s="29"/>
       <c r="Z70" s="54"/>
       <c r="AA70" s="56"/>
@@ -8759,7 +8781,7 @@
       <c r="W71" s="11">
         <v>106.088167</v>
       </c>
-      <c r="X71" s="26"/>
+      <c r="X71" s="68"/>
       <c r="Y71" s="29"/>
       <c r="Z71" s="54"/>
       <c r="AA71" s="56"/>
@@ -8835,7 +8857,7 @@
       <c r="W72" s="11">
         <v>106.0873139</v>
       </c>
-      <c r="X72" s="26"/>
+      <c r="X72" s="68"/>
       <c r="Y72" s="29"/>
       <c r="Z72" s="54"/>
       <c r="AA72" s="56"/>
@@ -8911,7 +8933,7 @@
       <c r="W73" s="11">
         <v>106.0932651</v>
       </c>
-      <c r="X73" s="26"/>
+      <c r="X73" s="68"/>
       <c r="Y73" s="29"/>
       <c r="Z73" s="54"/>
       <c r="AA73" s="56"/>
@@ -8985,7 +9007,7 @@
       <c r="W74" s="11">
         <v>106.098916</v>
       </c>
-      <c r="X74" s="26"/>
+      <c r="X74" s="68"/>
       <c r="Y74" s="29"/>
       <c r="Z74" s="54"/>
       <c r="AA74" s="56"/>
@@ -9059,7 +9081,7 @@
       <c r="W75" s="11">
         <v>106.096616</v>
       </c>
-      <c r="X75" s="26"/>
+      <c r="X75" s="68"/>
       <c r="Y75" s="29"/>
       <c r="Z75" s="54"/>
       <c r="AA75" s="56"/>
@@ -9133,7 +9155,7 @@
       <c r="W76" s="11">
         <v>106.0948856</v>
       </c>
-      <c r="X76" s="26"/>
+      <c r="X76" s="68"/>
       <c r="Y76" s="29"/>
       <c r="Z76" s="54"/>
       <c r="AA76" s="56"/>
@@ -9207,7 +9229,7 @@
       <c r="W77" s="11">
         <v>106.08195600000001</v>
       </c>
-      <c r="X77" s="26"/>
+      <c r="X77" s="68"/>
       <c r="Y77" s="29"/>
       <c r="Z77" s="54"/>
       <c r="AA77" s="56"/>
@@ -9281,7 +9303,7 @@
       <c r="W78" s="11">
         <v>106.095277</v>
       </c>
-      <c r="X78" s="26"/>
+      <c r="X78" s="68"/>
       <c r="Y78" s="29"/>
       <c r="Z78" s="54"/>
       <c r="AA78" s="56"/>
@@ -9355,7 +9377,7 @@
       <c r="W79" s="11">
         <v>106.094336</v>
       </c>
-      <c r="X79" s="26"/>
+      <c r="X79" s="68"/>
       <c r="Y79" s="29"/>
       <c r="Z79" s="54"/>
       <c r="AA79" s="56"/>
@@ -9429,7 +9451,7 @@
       <c r="W80" s="11">
         <v>106.08377350000001</v>
       </c>
-      <c r="X80" s="26"/>
+      <c r="X80" s="68"/>
       <c r="Y80" s="29"/>
       <c r="Z80" s="54"/>
       <c r="AA80" s="56"/>
@@ -9503,7 +9525,7 @@
       <c r="W81" s="11">
         <v>106.083372</v>
       </c>
-      <c r="X81" s="26"/>
+      <c r="X81" s="68"/>
       <c r="Y81" s="29"/>
       <c r="Z81" s="54"/>
       <c r="AA81" s="56"/>
@@ -9577,7 +9599,7 @@
       <c r="W82" s="11">
         <v>106.08407010000001</v>
       </c>
-      <c r="X82" s="26"/>
+      <c r="X82" s="68"/>
       <c r="Y82" s="29"/>
       <c r="Z82" s="54"/>
       <c r="AA82" s="56"/>
@@ -9641,7 +9663,9 @@
       <c r="Q83" s="23" t="s">
         <v>912</v>
       </c>
-      <c r="R83" s="23"/>
+      <c r="R83" s="23" t="s">
+        <v>918</v>
+      </c>
       <c r="S83" s="20"/>
       <c r="T83" s="11"/>
       <c r="U83" s="11"/>
@@ -9651,7 +9675,7 @@
       <c r="W83" s="11">
         <v>106.08517500000001</v>
       </c>
-      <c r="X83" s="26"/>
+      <c r="X83" s="68"/>
       <c r="Y83" s="29"/>
       <c r="Z83" s="54"/>
       <c r="AA83" s="56"/>
@@ -9725,7 +9749,7 @@
       <c r="W84" s="11">
         <v>106.0750427</v>
       </c>
-      <c r="X84" s="26"/>
+      <c r="X84" s="68"/>
       <c r="Y84" s="29"/>
       <c r="Z84" s="54"/>
       <c r="AA84" s="56"/>
@@ -9799,7 +9823,7 @@
       <c r="W85" s="11">
         <v>106.09328499999999</v>
       </c>
-      <c r="X85" s="26"/>
+      <c r="X85" s="68"/>
       <c r="Y85" s="29"/>
       <c r="Z85" s="54"/>
       <c r="AA85" s="56"/>
@@ -9875,7 +9899,7 @@
       <c r="W86" s="11">
         <v>106.09471600000001</v>
       </c>
-      <c r="X86" s="26"/>
+      <c r="X86" s="68"/>
       <c r="Y86" s="29"/>
       <c r="Z86" s="54"/>
       <c r="AA86" s="56"/>
@@ -9945,7 +9969,7 @@
       <c r="U87" s="11"/>
       <c r="V87" s="11"/>
       <c r="W87" s="11"/>
-      <c r="X87" s="26"/>
+      <c r="X87" s="68"/>
       <c r="Y87" s="29"/>
       <c r="Z87" s="54"/>
       <c r="AA87" s="56"/>
@@ -10019,7 +10043,7 @@
       <c r="W88" s="11">
         <v>106.092079</v>
       </c>
-      <c r="X88" s="26"/>
+      <c r="X88" s="68"/>
       <c r="Y88" s="29"/>
       <c r="Z88" s="54"/>
       <c r="AA88" s="56"/>
@@ -10093,7 +10117,7 @@
       <c r="W89" s="11">
         <v>106.1520824</v>
       </c>
-      <c r="X89" s="26"/>
+      <c r="X89" s="68"/>
       <c r="Y89" s="29"/>
       <c r="Z89" s="54"/>
       <c r="AA89" s="56"/>
@@ -10167,7 +10191,7 @@
       <c r="W90" s="11">
         <v>106.08923830000001</v>
       </c>
-      <c r="X90" s="26"/>
+      <c r="X90" s="68"/>
       <c r="Y90" s="29"/>
       <c r="Z90" s="54"/>
       <c r="AA90" s="56"/>
@@ -10241,7 +10265,7 @@
       <c r="W91" s="11">
         <v>106.1375556</v>
       </c>
-      <c r="X91" s="26"/>
+      <c r="X91" s="68"/>
       <c r="Y91" s="29"/>
       <c r="Z91" s="54"/>
       <c r="AA91" s="56"/>
@@ -10317,7 +10341,7 @@
       <c r="W92" s="11">
         <v>106.165569</v>
       </c>
-      <c r="X92" s="26"/>
+      <c r="X92" s="68"/>
       <c r="Y92" s="29"/>
       <c r="Z92" s="54"/>
       <c r="AA92" s="56"/>
@@ -10395,7 +10419,7 @@
       <c r="W93" s="11">
         <v>106.1655691</v>
       </c>
-      <c r="X93" s="26"/>
+      <c r="X93" s="68"/>
       <c r="Y93" s="29"/>
       <c r="Z93" s="54"/>
       <c r="AA93" s="56"/>
@@ -10471,7 +10495,7 @@
       <c r="W94" s="11">
         <v>106.11421300000001</v>
       </c>
-      <c r="X94" s="26"/>
+      <c r="X94" s="68"/>
       <c r="Y94" s="29"/>
       <c r="Z94" s="54"/>
       <c r="AA94" s="56"/>
@@ -10545,7 +10569,7 @@
       <c r="W95" s="11">
         <v>106.115123</v>
       </c>
-      <c r="X95" s="26"/>
+      <c r="X95" s="68"/>
       <c r="Y95" s="29"/>
       <c r="Z95" s="54"/>
       <c r="AA95" s="56"/>
@@ -10619,7 +10643,7 @@
       <c r="W96" s="11">
         <v>106.16383949999999</v>
       </c>
-      <c r="X96" s="26"/>
+      <c r="X96" s="68"/>
       <c r="Y96" s="29"/>
       <c r="Z96" s="54"/>
       <c r="AA96" s="56"/>
@@ -10693,7 +10717,7 @@
       <c r="W97" s="11">
         <v>106.1638396</v>
       </c>
-      <c r="X97" s="26"/>
+      <c r="X97" s="68"/>
       <c r="Y97" s="29"/>
       <c r="Z97" s="54"/>
       <c r="AA97" s="56"/>
@@ -10771,7 +10795,7 @@
       <c r="W98" s="11">
         <v>106.0753648</v>
       </c>
-      <c r="X98" s="26"/>
+      <c r="X98" s="68"/>
       <c r="Y98" s="29"/>
       <c r="Z98" s="54"/>
       <c r="AA98" s="56"/>
@@ -10849,7 +10873,7 @@
       <c r="W99" s="11">
         <v>106.07502890000001</v>
       </c>
-      <c r="X99" s="26"/>
+      <c r="X99" s="68"/>
       <c r="Y99" s="29"/>
       <c r="Z99" s="54"/>
       <c r="AA99" s="56"/>
@@ -10925,7 +10949,7 @@
       <c r="W100" s="11">
         <v>106.1668955</v>
       </c>
-      <c r="X100" s="26"/>
+      <c r="X100" s="68"/>
       <c r="Y100" s="29"/>
       <c r="Z100" s="54"/>
       <c r="AA100" s="56"/>
@@ -11001,7 +11025,7 @@
       <c r="W101" s="11">
         <v>106.1668955</v>
       </c>
-      <c r="X101" s="26"/>
+      <c r="X101" s="68"/>
       <c r="Y101" s="29"/>
       <c r="Z101" s="54"/>
       <c r="AA101" s="56"/>
@@ -11075,7 +11099,7 @@
       <c r="W102" s="11">
         <v>106.07392950000001</v>
       </c>
-      <c r="X102" s="26"/>
+      <c r="X102" s="68"/>
       <c r="Y102" s="29"/>
       <c r="Z102" s="54"/>
       <c r="AA102" s="56"/>
@@ -11149,7 +11173,7 @@
       <c r="W103" s="11">
         <v>106.07577000000001</v>
       </c>
-      <c r="X103" s="26"/>
+      <c r="X103" s="68"/>
       <c r="Y103" s="29"/>
       <c r="Z103" s="54"/>
       <c r="AA103" s="56"/>
@@ -11223,7 +11247,7 @@
       <c r="W104" s="11">
         <v>106.07570800000001</v>
       </c>
-      <c r="X104" s="26"/>
+      <c r="X104" s="68"/>
       <c r="Y104" s="29"/>
       <c r="Z104" s="54"/>
       <c r="AA104" s="56"/>
@@ -11287,7 +11311,9 @@
       <c r="Q105" s="23" t="s">
         <v>912</v>
       </c>
-      <c r="R105" s="23"/>
+      <c r="R105" s="23" t="s">
+        <v>920</v>
+      </c>
       <c r="S105" s="20"/>
       <c r="T105" s="11"/>
       <c r="U105" s="11"/>
@@ -11297,7 +11323,7 @@
       <c r="W105" s="11">
         <v>106.093493</v>
       </c>
-      <c r="X105" s="26"/>
+      <c r="X105" s="68"/>
       <c r="Y105" s="29"/>
       <c r="Z105" s="54"/>
       <c r="AA105" s="56"/>
@@ -11373,7 +11399,7 @@
       <c r="W106" s="11">
         <v>106.1419678</v>
       </c>
-      <c r="X106" s="26"/>
+      <c r="X106" s="68"/>
       <c r="Y106" s="29"/>
       <c r="Z106" s="54"/>
       <c r="AA106" s="56"/>
@@ -11447,7 +11473,7 @@
       <c r="W107" s="11">
         <v>106.1503439</v>
       </c>
-      <c r="X107" s="26"/>
+      <c r="X107" s="68"/>
       <c r="Y107" s="29"/>
       <c r="Z107" s="54"/>
       <c r="AA107" s="56"/>
@@ -11521,7 +11547,7 @@
       <c r="W108" s="11">
         <v>106.09747900000001</v>
       </c>
-      <c r="X108" s="26"/>
+      <c r="X108" s="68"/>
       <c r="Y108" s="29"/>
       <c r="Z108" s="54"/>
       <c r="AA108" s="56"/>
@@ -11595,7 +11621,7 @@
       <c r="W109" s="11">
         <v>106.083653</v>
       </c>
-      <c r="X109" s="26"/>
+      <c r="X109" s="68"/>
       <c r="Y109" s="29"/>
       <c r="Z109" s="54"/>
       <c r="AA109" s="56"/>
@@ -11669,7 +11695,7 @@
       <c r="W110" s="11">
         <v>106.0965628</v>
       </c>
-      <c r="X110" s="26"/>
+      <c r="X110" s="68"/>
       <c r="Y110" s="29"/>
       <c r="Z110" s="54"/>
       <c r="AA110" s="56"/>
@@ -11745,7 +11771,7 @@
       <c r="W111" s="11">
         <v>106.10645599999999</v>
       </c>
-      <c r="X111" s="26"/>
+      <c r="X111" s="68"/>
       <c r="Y111" s="29"/>
       <c r="Z111" s="54"/>
       <c r="AA111" s="56"/>
@@ -11819,7 +11845,7 @@
       <c r="W112" s="11">
         <v>106.08669140000001</v>
       </c>
-      <c r="X112" s="26"/>
+      <c r="X112" s="68"/>
       <c r="Y112" s="29"/>
       <c r="Z112" s="54"/>
       <c r="AA112" s="56"/>
@@ -11895,7 +11921,7 @@
       <c r="W113" s="11">
         <v>106.118709</v>
       </c>
-      <c r="X113" s="26"/>
+      <c r="X113" s="68"/>
       <c r="Y113" s="29"/>
       <c r="Z113" s="54"/>
       <c r="AA113" s="56"/>
@@ -11971,7 +11997,7 @@
       <c r="W114" s="11">
         <v>106.118709</v>
       </c>
-      <c r="X114" s="26"/>
+      <c r="X114" s="68"/>
       <c r="Y114" s="29"/>
       <c r="Z114" s="54"/>
       <c r="AA114" s="56"/>
@@ -12045,7 +12071,7 @@
       <c r="W115" s="11">
         <v>106.0815047</v>
       </c>
-      <c r="X115" s="26"/>
+      <c r="X115" s="68"/>
       <c r="Y115" s="29"/>
       <c r="Z115" s="54"/>
       <c r="AA115" s="56"/>
@@ -12119,7 +12145,7 @@
       <c r="W116" s="11">
         <v>106.0839</v>
       </c>
-      <c r="X116" s="26"/>
+      <c r="X116" s="68"/>
       <c r="Y116" s="29"/>
       <c r="Z116" s="54"/>
       <c r="AA116" s="56"/>
@@ -12193,7 +12219,7 @@
       <c r="W117" s="11">
         <v>106.1543704</v>
       </c>
-      <c r="X117" s="26"/>
+      <c r="X117" s="68"/>
       <c r="Y117" s="29"/>
       <c r="Z117" s="54"/>
       <c r="AA117" s="56"/>
@@ -12267,7 +12293,7 @@
       <c r="W118" s="11">
         <v>106.1576383</v>
       </c>
-      <c r="X118" s="26"/>
+      <c r="X118" s="68"/>
       <c r="Y118" s="29"/>
       <c r="Z118" s="54"/>
       <c r="AA118" s="56"/>
@@ -12341,7 +12367,7 @@
       <c r="W119" s="11">
         <v>106.085612</v>
       </c>
-      <c r="X119" s="26"/>
+      <c r="X119" s="68"/>
       <c r="Y119" s="29"/>
       <c r="Z119" s="54"/>
       <c r="AA119" s="56"/>
@@ -12415,7 +12441,7 @@
       <c r="W120" s="11">
         <v>106.080567</v>
       </c>
-      <c r="X120" s="26"/>
+      <c r="X120" s="68"/>
       <c r="Y120" s="29"/>
       <c r="Z120" s="54"/>
       <c r="AA120" s="56"/>
@@ -12491,7 +12517,7 @@
       <c r="W121" s="11">
         <v>106.090628</v>
       </c>
-      <c r="X121" s="26"/>
+      <c r="X121" s="68"/>
       <c r="Y121" s="29"/>
       <c r="Z121" s="54"/>
       <c r="AA121" s="56"/>
@@ -12567,7 +12593,7 @@
       <c r="W122" s="11">
         <v>106.07904379999999</v>
       </c>
-      <c r="X122" s="26"/>
+      <c r="X122" s="68"/>
       <c r="Y122" s="29"/>
       <c r="Z122" s="54"/>
       <c r="AA122" s="56"/>
@@ -12643,7 +12669,7 @@
       <c r="W123" s="11">
         <v>106.086156</v>
       </c>
-      <c r="X123" s="26"/>
+      <c r="X123" s="68"/>
       <c r="Y123" s="29"/>
       <c r="Z123" s="54"/>
       <c r="AA123" s="56"/>
@@ -12719,7 +12745,7 @@
       <c r="W124" s="11">
         <v>106.0764578</v>
       </c>
-      <c r="X124" s="26"/>
+      <c r="X124" s="68"/>
       <c r="Y124" s="29"/>
       <c r="Z124" s="54"/>
       <c r="AA124" s="56"/>
@@ -12789,7 +12815,7 @@
       <c r="U125" s="11"/>
       <c r="V125" s="11"/>
       <c r="W125" s="11"/>
-      <c r="X125" s="26"/>
+      <c r="X125" s="68"/>
       <c r="Y125" s="29"/>
       <c r="Z125" s="54"/>
       <c r="AA125" s="56"/>
@@ -12863,7 +12889,7 @@
       <c r="W126" s="11">
         <v>106.0873765</v>
       </c>
-      <c r="X126" s="26"/>
+      <c r="X126" s="68"/>
       <c r="Y126" s="29"/>
       <c r="Z126" s="54"/>
       <c r="AA126" s="56"/>
@@ -12937,7 +12963,7 @@
       <c r="W127" s="11">
         <v>106.07832500000001</v>
       </c>
-      <c r="X127" s="26"/>
+      <c r="X127" s="68"/>
       <c r="Y127" s="29"/>
       <c r="Z127" s="54"/>
       <c r="AA127" s="56"/>
@@ -13001,7 +13027,9 @@
       <c r="Q128" s="23" t="s">
         <v>912</v>
       </c>
-      <c r="R128" s="23"/>
+      <c r="R128" s="23" t="s">
+        <v>920</v>
+      </c>
       <c r="S128" s="20"/>
       <c r="T128" s="11"/>
       <c r="U128" s="11"/>
@@ -13011,7 +13039,7 @@
       <c r="W128" s="11">
         <v>106.0747703</v>
       </c>
-      <c r="X128" s="26"/>
+      <c r="X128" s="68"/>
       <c r="Y128" s="29"/>
       <c r="Z128" s="54"/>
       <c r="AA128" s="56"/>
@@ -13085,7 +13113,7 @@
       <c r="W129" s="11">
         <v>106.096946</v>
       </c>
-      <c r="X129" s="26"/>
+      <c r="X129" s="68"/>
       <c r="Y129" s="29"/>
       <c r="Z129" s="54"/>
       <c r="AA129" s="56"/>
@@ -13159,7 +13187,7 @@
       <c r="W130" s="11">
         <v>106.0729011</v>
       </c>
-      <c r="X130" s="26"/>
+      <c r="X130" s="68"/>
       <c r="Y130" s="29"/>
       <c r="Z130" s="54"/>
       <c r="AA130" s="56"/>
@@ -13233,7 +13261,7 @@
       <c r="W131" s="11">
         <v>106.0727887</v>
       </c>
-      <c r="X131" s="26"/>
+      <c r="X131" s="68"/>
       <c r="Y131" s="29"/>
       <c r="Z131" s="54"/>
       <c r="AA131" s="56"/>
@@ -13305,7 +13333,7 @@
       <c r="U132" s="11"/>
       <c r="V132" s="11"/>
       <c r="W132" s="11"/>
-      <c r="X132" s="26"/>
+      <c r="X132" s="68"/>
       <c r="Y132" s="29"/>
       <c r="Z132" s="54"/>
       <c r="AA132" s="56"/>
@@ -13381,7 +13409,7 @@
       <c r="W133" s="11">
         <v>106.116671</v>
       </c>
-      <c r="X133" s="26"/>
+      <c r="X133" s="68"/>
       <c r="Y133" s="29"/>
       <c r="Z133" s="54"/>
       <c r="AA133" s="56"/>
@@ -13457,7 +13485,7 @@
       <c r="W134" s="11">
         <v>106.11780299999999</v>
       </c>
-      <c r="X134" s="26"/>
+      <c r="X134" s="68"/>
       <c r="Y134" s="29"/>
       <c r="Z134" s="54"/>
       <c r="AA134" s="56"/>
@@ -13535,7 +13563,7 @@
       <c r="W135" s="11">
         <v>106.0761523</v>
       </c>
-      <c r="X135" s="26"/>
+      <c r="X135" s="68"/>
       <c r="Y135" s="29"/>
       <c r="Z135" s="54"/>
       <c r="AA135" s="56"/>
@@ -13613,7 +13641,7 @@
       <c r="W136" s="11">
         <v>106.07432350000001</v>
       </c>
-      <c r="X136" s="26"/>
+      <c r="X136" s="68"/>
       <c r="Y136" s="29"/>
       <c r="Z136" s="54"/>
       <c r="AA136" s="56"/>
@@ -13689,7 +13717,7 @@
       <c r="W137" s="11">
         <v>106.092822</v>
       </c>
-      <c r="X137" s="26"/>
+      <c r="X137" s="68"/>
       <c r="Y137" s="29"/>
       <c r="Z137" s="54"/>
       <c r="AA137" s="56"/>
@@ -13763,7 +13791,7 @@
       <c r="W138" s="11">
         <v>106.159896</v>
       </c>
-      <c r="X138" s="26"/>
+      <c r="X138" s="68"/>
       <c r="Y138" s="29"/>
       <c r="Z138" s="54"/>
       <c r="AA138" s="56"/>
@@ -13837,7 +13865,7 @@
       <c r="W139" s="11">
         <v>106.159896</v>
       </c>
-      <c r="X139" s="26"/>
+      <c r="X139" s="68"/>
       <c r="Y139" s="29"/>
       <c r="Z139" s="54"/>
       <c r="AA139" s="56"/>
@@ -13911,7 +13939,7 @@
       <c r="W140" s="11">
         <v>106.15365199999999</v>
       </c>
-      <c r="X140" s="26"/>
+      <c r="X140" s="68"/>
       <c r="Y140" s="29"/>
       <c r="Z140" s="54"/>
       <c r="AA140" s="56"/>
@@ -13985,7 +14013,7 @@
       <c r="W141" s="11">
         <v>106.0614738</v>
       </c>
-      <c r="X141" s="26"/>
+      <c r="X141" s="68"/>
       <c r="Y141" s="29"/>
       <c r="Z141" s="54"/>
       <c r="AA141" s="56"/>
@@ -14059,7 +14087,7 @@
       <c r="W142" s="11">
         <v>106.11130199999999</v>
       </c>
-      <c r="X142" s="26"/>
+      <c r="X142" s="68"/>
       <c r="Y142" s="29"/>
       <c r="Z142" s="54"/>
       <c r="AA142" s="56"/>
@@ -14131,7 +14159,7 @@
       <c r="U143" s="11"/>
       <c r="V143" s="11"/>
       <c r="W143" s="11"/>
-      <c r="X143" s="26"/>
+      <c r="X143" s="68"/>
       <c r="Y143" s="29"/>
       <c r="Z143" s="54"/>
       <c r="AA143" s="56"/>
@@ -14205,7 +14233,7 @@
       <c r="W144" s="11">
         <v>106.078397</v>
       </c>
-      <c r="X144" s="26"/>
+      <c r="X144" s="68"/>
       <c r="Y144" s="29"/>
       <c r="Z144" s="54"/>
       <c r="AA144" s="56"/>
@@ -14279,7 +14307,7 @@
       <c r="W145" s="11">
         <v>106.113918</v>
       </c>
-      <c r="X145" s="26"/>
+      <c r="X145" s="68"/>
       <c r="Y145" s="29"/>
       <c r="Z145" s="54"/>
       <c r="AA145" s="56"/>
@@ -14353,7 +14381,7 @@
       <c r="W146" s="11">
         <v>106.1247745</v>
       </c>
-      <c r="X146" s="26"/>
+      <c r="X146" s="68"/>
       <c r="Y146" s="29"/>
       <c r="Z146" s="54"/>
       <c r="AA146" s="56"/>
@@ -14423,7 +14451,7 @@
       <c r="U147" s="11"/>
       <c r="V147" s="11"/>
       <c r="W147" s="11"/>
-      <c r="X147" s="26"/>
+      <c r="X147" s="68"/>
       <c r="Y147" s="29"/>
       <c r="Z147" s="54"/>
       <c r="AA147" s="56"/>
@@ -14497,7 +14525,7 @@
       <c r="W148" s="11">
         <v>106.081965</v>
       </c>
-      <c r="X148" s="26"/>
+      <c r="X148" s="68"/>
       <c r="Y148" s="29"/>
       <c r="Z148" s="54"/>
       <c r="AA148" s="56"/>
@@ -14573,7 +14601,7 @@
       <c r="W149" s="11">
         <v>106.0816123</v>
       </c>
-      <c r="X149" s="26"/>
+      <c r="X149" s="68"/>
       <c r="Y149" s="29"/>
       <c r="Z149" s="54"/>
       <c r="AA149" s="56"/>
@@ -14647,7 +14675,7 @@
       <c r="W150" s="11">
         <v>106.08137979999999</v>
       </c>
-      <c r="X150" s="26"/>
+      <c r="X150" s="68"/>
       <c r="Y150" s="29"/>
       <c r="Z150" s="54"/>
       <c r="AA150" s="56"/>
@@ -14721,7 +14749,7 @@
       <c r="W151" s="11">
         <v>106.157115</v>
       </c>
-      <c r="X151" s="26"/>
+      <c r="X151" s="68"/>
       <c r="Y151" s="29"/>
       <c r="Z151" s="54"/>
       <c r="AA151" s="56"/>
@@ -14795,7 +14823,7 @@
       <c r="W152" s="11">
         <v>106.1604487</v>
       </c>
-      <c r="X152" s="26"/>
+      <c r="X152" s="68"/>
       <c r="Y152" s="29"/>
       <c r="Z152" s="54"/>
       <c r="AA152" s="56"/>
@@ -14869,7 +14897,7 @@
       <c r="W153" s="11">
         <v>106.15998329999999</v>
       </c>
-      <c r="X153" s="26"/>
+      <c r="X153" s="68"/>
       <c r="Y153" s="29"/>
       <c r="Z153" s="54"/>
       <c r="AA153" s="56"/>
@@ -14945,7 +14973,7 @@
       <c r="W154" s="11">
         <v>106.16054800000001</v>
       </c>
-      <c r="X154" s="26"/>
+      <c r="X154" s="68"/>
       <c r="Y154" s="29"/>
       <c r="Z154" s="54"/>
       <c r="AA154" s="56"/>
@@ -15021,7 +15049,7 @@
       <c r="W155" s="11">
         <v>106.06042100000001</v>
       </c>
-      <c r="X155" s="26"/>
+      <c r="X155" s="68"/>
       <c r="Y155" s="29"/>
       <c r="Z155" s="54"/>
       <c r="AA155" s="56"/>
@@ -15097,7 +15125,7 @@
       <c r="W156" s="11">
         <v>106.07043590000001</v>
       </c>
-      <c r="X156" s="26"/>
+      <c r="X156" s="68"/>
       <c r="Y156" s="29"/>
       <c r="Z156" s="54"/>
       <c r="AA156" s="56"/>
@@ -15173,7 +15201,7 @@
       <c r="W157" s="11">
         <v>106.062211</v>
       </c>
-      <c r="X157" s="26"/>
+      <c r="X157" s="68"/>
       <c r="Y157" s="29"/>
       <c r="Z157" s="54"/>
       <c r="AA157" s="56"/>
@@ -15249,7 +15277,7 @@
       <c r="W158" s="11">
         <v>106.113224</v>
       </c>
-      <c r="X158" s="26"/>
+      <c r="X158" s="68"/>
       <c r="Y158" s="29"/>
       <c r="Z158" s="54"/>
       <c r="AA158" s="56"/>
@@ -15325,7 +15353,7 @@
       <c r="W159" s="11">
         <v>106.0760401</v>
       </c>
-      <c r="X159" s="26"/>
+      <c r="X159" s="68"/>
       <c r="Y159" s="29"/>
       <c r="Z159" s="54"/>
       <c r="AA159" s="56"/>
@@ -15395,7 +15423,7 @@
       <c r="U160" s="11"/>
       <c r="V160" s="11"/>
       <c r="W160" s="11"/>
-      <c r="X160" s="26"/>
+      <c r="X160" s="68"/>
       <c r="Y160" s="29"/>
       <c r="Z160" s="54"/>
       <c r="AA160" s="56"/>
@@ -15471,7 +15499,7 @@
       <c r="W161" s="11">
         <v>106.1042964</v>
       </c>
-      <c r="X161" s="26"/>
+      <c r="X161" s="68"/>
       <c r="Y161" s="29"/>
       <c r="Z161" s="54"/>
       <c r="AA161" s="56"/>
@@ -15545,7 +15573,7 @@
       <c r="W162" s="11">
         <v>106.162803</v>
       </c>
-      <c r="X162" s="26"/>
+      <c r="X162" s="68"/>
       <c r="Y162" s="29"/>
       <c r="Z162" s="54"/>
       <c r="AA162" s="56"/>
@@ -15621,7 +15649,7 @@
       <c r="W163" s="11">
         <v>106.118658</v>
       </c>
-      <c r="X163" s="26"/>
+      <c r="X163" s="68"/>
       <c r="Y163" s="29"/>
       <c r="Z163" s="54"/>
       <c r="AA163" s="56"/>
@@ -15697,7 +15725,7 @@
       <c r="W164" s="11">
         <v>106.07646699999999</v>
       </c>
-      <c r="X164" s="26"/>
+      <c r="X164" s="68"/>
       <c r="Y164" s="29"/>
       <c r="Z164" s="54"/>
       <c r="AA164" s="56"/>
@@ -15771,7 +15799,7 @@
       <c r="W165" s="11">
         <v>106.07139979999999</v>
       </c>
-      <c r="X165" s="26"/>
+      <c r="X165" s="68"/>
       <c r="Y165" s="29"/>
       <c r="Z165" s="54"/>
       <c r="AA165" s="56"/>
@@ -15847,7 +15875,7 @@
       <c r="W166" s="11">
         <v>106.11813600000001</v>
       </c>
-      <c r="X166" s="26"/>
+      <c r="X166" s="68"/>
       <c r="Y166" s="29"/>
       <c r="Z166" s="54"/>
       <c r="AA166" s="56"/>
@@ -15921,7 +15949,7 @@
       <c r="W167" s="11">
         <v>106.078672</v>
       </c>
-      <c r="X167" s="26"/>
+      <c r="X167" s="68"/>
       <c r="Y167" s="29"/>
       <c r="Z167" s="54"/>
       <c r="AA167" s="56"/>
@@ -15997,7 +16025,7 @@
       <c r="W168" s="11">
         <v>106.15588889999999</v>
       </c>
-      <c r="X168" s="26"/>
+      <c r="X168" s="68"/>
       <c r="Y168" s="29"/>
       <c r="Z168" s="54"/>
       <c r="AA168" s="56"/>
@@ -16077,7 +16105,7 @@
       <c r="W169" s="11">
         <v>106.096322</v>
       </c>
-      <c r="X169" s="26"/>
+      <c r="X169" s="68"/>
       <c r="Y169" s="29"/>
       <c r="Z169" s="54"/>
       <c r="AA169" s="56"/>
@@ -16153,7 +16181,7 @@
       <c r="W170" s="11">
         <v>106.1528338</v>
       </c>
-      <c r="X170" s="26"/>
+      <c r="X170" s="68"/>
       <c r="Y170" s="29"/>
       <c r="Z170" s="54"/>
       <c r="AA170" s="56"/>
@@ -16229,7 +16257,7 @@
       <c r="W171" s="11">
         <v>106.116389</v>
       </c>
-      <c r="X171" s="26"/>
+      <c r="X171" s="68"/>
       <c r="Y171" s="29"/>
       <c r="Z171" s="54"/>
       <c r="AA171" s="56"/>
@@ -16305,7 +16333,7 @@
       <c r="W172" s="11">
         <v>106.096075</v>
       </c>
-      <c r="X172" s="26"/>
+      <c r="X172" s="68"/>
       <c r="Y172" s="29"/>
       <c r="Z172" s="54"/>
       <c r="AA172" s="56"/>
@@ -16381,7 +16409,7 @@
       <c r="W173" s="11">
         <v>106.094559</v>
       </c>
-      <c r="X173" s="26"/>
+      <c r="X173" s="68"/>
       <c r="Y173" s="29"/>
       <c r="Z173" s="54"/>
       <c r="AA173" s="56"/>
@@ -16457,7 +16485,7 @@
       <c r="W174" s="11">
         <v>106.1040895</v>
       </c>
-      <c r="X174" s="26"/>
+      <c r="X174" s="68"/>
       <c r="Y174" s="29"/>
       <c r="Z174" s="54"/>
       <c r="AA174" s="56"/>
@@ -16533,7 +16561,7 @@
       <c r="W175" s="11">
         <v>106.12316300000001</v>
       </c>
-      <c r="X175" s="26"/>
+      <c r="X175" s="68"/>
       <c r="Y175" s="29"/>
       <c r="Z175" s="54"/>
       <c r="AA175" s="56"/>
@@ -16607,7 +16635,7 @@
       <c r="W176" s="11">
         <v>106.117035</v>
       </c>
-      <c r="X176" s="26"/>
+      <c r="X176" s="68"/>
       <c r="Y176" s="29"/>
       <c r="Z176" s="54"/>
       <c r="AA176" s="56"/>
@@ -16683,7 +16711,7 @@
       <c r="W177" s="11">
         <v>106.0923793</v>
       </c>
-      <c r="X177" s="26"/>
+      <c r="X177" s="68"/>
       <c r="Y177" s="29"/>
       <c r="Z177" s="54"/>
       <c r="AA177" s="56"/>
@@ -16757,7 +16785,7 @@
       <c r="W178" s="11">
         <v>106.1508</v>
       </c>
-      <c r="X178" s="26"/>
+      <c r="X178" s="68"/>
       <c r="Y178" s="29"/>
       <c r="Z178" s="54"/>
       <c r="AA178" s="56"/>
@@ -16831,7 +16859,7 @@
       <c r="W179" s="11">
         <v>106.1074424</v>
       </c>
-      <c r="X179" s="26"/>
+      <c r="X179" s="68"/>
       <c r="Y179" s="29"/>
       <c r="Z179" s="54"/>
       <c r="AA179" s="56"/>
@@ -16907,7 +16935,7 @@
       <c r="W180" s="11">
         <v>106.0942</v>
       </c>
-      <c r="X180" s="26"/>
+      <c r="X180" s="68"/>
       <c r="Y180" s="29"/>
       <c r="Z180" s="54"/>
       <c r="AA180" s="56"/>
@@ -16983,7 +17011,7 @@
       <c r="W181" s="11">
         <v>106.0888344</v>
       </c>
-      <c r="X181" s="26"/>
+      <c r="X181" s="68"/>
       <c r="Y181" s="29"/>
       <c r="Z181" s="54"/>
       <c r="AA181" s="56"/>
@@ -17059,7 +17087,7 @@
       <c r="W182" s="11">
         <v>106.10247200000001</v>
       </c>
-      <c r="X182" s="26"/>
+      <c r="X182" s="68"/>
       <c r="Y182" s="29"/>
       <c r="Z182" s="54"/>
       <c r="AA182" s="56"/>
@@ -17133,7 +17161,7 @@
       <c r="W183" s="11">
         <v>106.09792659999999</v>
       </c>
-      <c r="X183" s="26"/>
+      <c r="X183" s="68"/>
       <c r="Y183" s="29"/>
       <c r="Z183" s="54"/>
       <c r="AA183" s="56"/>
@@ -17207,7 +17235,7 @@
       <c r="W184" s="11">
         <v>106.13170340000001</v>
       </c>
-      <c r="X184" s="26"/>
+      <c r="X184" s="68"/>
       <c r="Y184" s="29"/>
       <c r="Z184" s="54"/>
       <c r="AA184" s="56"/>
@@ -17281,7 +17309,7 @@
       <c r="W185" s="11">
         <v>106.0862723</v>
       </c>
-      <c r="X185" s="26"/>
+      <c r="X185" s="68"/>
       <c r="Y185" s="29"/>
       <c r="Z185" s="54"/>
       <c r="AA185" s="56"/>
@@ -17357,7 +17385,7 @@
       <c r="W186" s="11">
         <v>106.091736</v>
       </c>
-      <c r="X186" s="26"/>
+      <c r="X186" s="68"/>
       <c r="Y186" s="29"/>
       <c r="Z186" s="54"/>
       <c r="AA186" s="56"/>
@@ -17431,7 +17459,7 @@
       <c r="W187" s="11">
         <v>106.0856861</v>
       </c>
-      <c r="X187" s="26"/>
+      <c r="X187" s="68"/>
       <c r="Y187" s="29"/>
       <c r="Z187" s="54"/>
       <c r="AA187" s="56"/>
@@ -17505,7 +17533,7 @@
       <c r="W188" s="11">
         <v>106.0848124</v>
       </c>
-      <c r="X188" s="26"/>
+      <c r="X188" s="68"/>
       <c r="Y188" s="29"/>
       <c r="Z188" s="54"/>
       <c r="AA188" s="56"/>
@@ -17581,7 +17609,7 @@
       <c r="W189" s="11">
         <v>106.090225</v>
       </c>
-      <c r="X189" s="26"/>
+      <c r="X189" s="68"/>
       <c r="Y189" s="29"/>
       <c r="Z189" s="54"/>
       <c r="AA189" s="56"/>
@@ -17655,7 +17683,7 @@
       <c r="W190" s="11">
         <v>106.0875205</v>
       </c>
-      <c r="X190" s="26"/>
+      <c r="X190" s="68"/>
       <c r="Y190" s="29"/>
       <c r="Z190" s="54"/>
       <c r="AA190" s="56"/>
@@ -17729,7 +17757,7 @@
       <c r="W191" s="11">
         <v>106.0795565</v>
       </c>
-      <c r="X191" s="26"/>
+      <c r="X191" s="68"/>
       <c r="Y191" s="29"/>
       <c r="Z191" s="54"/>
       <c r="AA191" s="56"/>
@@ -17803,7 +17831,7 @@
       <c r="W192" s="11">
         <v>106.103634</v>
       </c>
-      <c r="X192" s="26"/>
+      <c r="X192" s="68"/>
       <c r="Y192" s="29"/>
       <c r="Z192" s="54"/>
       <c r="AA192" s="56"/>
@@ -17879,7 +17907,7 @@
       <c r="W193" s="11">
         <v>106.10897799999999</v>
       </c>
-      <c r="X193" s="26"/>
+      <c r="X193" s="68"/>
       <c r="Y193" s="29"/>
       <c r="Z193" s="54"/>
       <c r="AA193" s="56"/>
@@ -17957,7 +17985,7 @@
       <c r="W194" s="11">
         <v>106.15800900000001</v>
       </c>
-      <c r="X194" s="26"/>
+      <c r="X194" s="68"/>
       <c r="Y194" s="29"/>
       <c r="Z194" s="54"/>
       <c r="AA194" s="56"/>
@@ -18031,7 +18059,7 @@
       <c r="U195" s="11"/>
       <c r="V195" s="11"/>
       <c r="W195" s="11"/>
-      <c r="X195" s="26"/>
+      <c r="X195" s="68"/>
       <c r="Y195" s="29"/>
       <c r="Z195" s="54"/>
       <c r="AA195" s="56"/>
@@ -18105,7 +18133,7 @@
       <c r="U196" s="11"/>
       <c r="V196" s="11"/>
       <c r="W196" s="11"/>
-      <c r="X196" s="26"/>
+      <c r="X196" s="68"/>
       <c r="Y196" s="29"/>
       <c r="Z196" s="54"/>
       <c r="AA196" s="56"/>
@@ -18183,7 +18211,7 @@
       <c r="W197" s="11">
         <v>106.15800900000001</v>
       </c>
-      <c r="X197" s="26"/>
+      <c r="X197" s="68"/>
       <c r="Y197" s="29"/>
       <c r="Z197" s="54"/>
       <c r="AA197" s="56"/>
@@ -18261,7 +18289,7 @@
       <c r="W198" s="11">
         <v>106.1568065</v>
       </c>
-      <c r="X198" s="26"/>
+      <c r="X198" s="68"/>
       <c r="Y198" s="29"/>
       <c r="Z198" s="54"/>
       <c r="AA198" s="56"/>
@@ -18335,7 +18363,7 @@
       <c r="W199" s="11">
         <v>106.09867819999999</v>
       </c>
-      <c r="X199" s="26"/>
+      <c r="X199" s="68"/>
       <c r="Y199" s="29"/>
       <c r="Z199" s="54"/>
       <c r="AA199" s="56"/>
@@ -18411,7 +18439,7 @@
       <c r="W200" s="11">
         <v>106.12775739999999</v>
       </c>
-      <c r="X200" s="26"/>
+      <c r="X200" s="68"/>
       <c r="Y200" s="29"/>
       <c r="Z200" s="54"/>
       <c r="AA200" s="56"/>
@@ -18485,7 +18513,7 @@
       <c r="W201" s="11">
         <v>106.0945468</v>
       </c>
-      <c r="X201" s="26"/>
+      <c r="X201" s="68"/>
       <c r="Y201" s="29"/>
       <c r="Z201" s="54"/>
       <c r="AA201" s="56"/>
@@ -18559,7 +18587,7 @@
       <c r="W202" s="11">
         <v>106.16425479999999</v>
       </c>
-      <c r="X202" s="26"/>
+      <c r="X202" s="68"/>
       <c r="Y202" s="29"/>
       <c r="Z202" s="54"/>
       <c r="AA202" s="56"/>
@@ -18633,7 +18661,7 @@
       <c r="W203" s="11">
         <v>106.0662955</v>
       </c>
-      <c r="X203" s="26"/>
+      <c r="X203" s="68"/>
       <c r="Y203" s="29"/>
       <c r="Z203" s="54"/>
       <c r="AA203" s="56"/>
@@ -18709,7 +18737,7 @@
       <c r="W204" s="11">
         <v>106.092687</v>
       </c>
-      <c r="X204" s="26"/>
+      <c r="X204" s="68"/>
       <c r="Y204" s="29"/>
       <c r="Z204" s="54"/>
       <c r="AA204" s="56"/>
@@ -18785,7 +18813,7 @@
       <c r="W205" s="12">
         <v>106.09254</v>
       </c>
-      <c r="X205" s="27"/>
+      <c r="X205" s="69"/>
       <c r="Y205" s="30"/>
       <c r="Z205" s="54"/>
       <c r="AA205" s="56"/>
@@ -18800,7 +18828,7 @@
       </c>
     </row>
     <row r="206" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A206" s="70">
+      <c r="A206" s="65">
         <v>201</v>
       </c>
       <c r="B206" s="61" t="s">
@@ -18874,7 +18902,7 @@
       </c>
     </row>
     <row r="207" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A207" s="71">
+      <c r="A207" s="66">
         <v>202</v>
       </c>
       <c r="B207" s="61" t="s">
@@ -18946,7 +18974,7 @@
       </c>
     </row>
     <row r="208" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A208" s="71">
+      <c r="A208" s="66">
         <v>203</v>
       </c>
       <c r="B208" s="61" t="s">
@@ -19018,7 +19046,7 @@
       </c>
     </row>
     <row r="209" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A209" s="71">
+      <c r="A209" s="66">
         <v>204</v>
       </c>
       <c r="B209" s="61" t="s">
@@ -19093,7 +19121,7 @@
       </c>
     </row>
     <row r="210" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A210" s="71">
+      <c r="A210" s="66">
         <v>205</v>
       </c>
       <c r="B210" s="61" t="s">
@@ -19168,7 +19196,7 @@
       </c>
     </row>
     <row r="211" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A211" s="71">
+      <c r="A211" s="66">
         <v>206</v>
       </c>
       <c r="B211" s="61" t="s">
@@ -19240,7 +19268,7 @@
       </c>
     </row>
     <row r="212" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A212" s="71">
+      <c r="A212" s="66">
         <v>207</v>
       </c>
       <c r="B212" s="61" t="s">
@@ -19312,7 +19340,7 @@
       </c>
     </row>
     <row r="213" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A213" s="71">
+      <c r="A213" s="66">
         <v>208</v>
       </c>
       <c r="B213" s="61" t="s">
@@ -19384,7 +19412,7 @@
       </c>
     </row>
     <row r="214" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A214" s="71">
+      <c r="A214" s="66">
         <v>209</v>
       </c>
       <c r="B214" s="61" t="s">
@@ -19458,7 +19486,7 @@
       </c>
     </row>
     <row r="215" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A215" s="71">
+      <c r="A215" s="66">
         <v>210</v>
       </c>
       <c r="B215" s="61" t="s">
@@ -19530,7 +19558,7 @@
       </c>
     </row>
     <row r="216" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A216" s="71">
+      <c r="A216" s="66">
         <v>211</v>
       </c>
       <c r="B216" s="61" t="s">
@@ -19605,7 +19633,7 @@
       </c>
     </row>
     <row r="217" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A217" s="71">
+      <c r="A217" s="66">
         <v>212</v>
       </c>
       <c r="B217" s="61" t="s">
@@ -19680,7 +19708,7 @@
       </c>
     </row>
     <row r="218" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A218" s="71">
+      <c r="A218" s="66">
         <v>213</v>
       </c>
       <c r="B218" s="61" t="s">
@@ -19752,7 +19780,7 @@
       </c>
     </row>
     <row r="219" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A219" s="71">
+      <c r="A219" s="66">
         <v>214</v>
       </c>
       <c r="B219" s="61" t="s">
@@ -19824,7 +19852,7 @@
       </c>
     </row>
     <row r="220" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A220" s="71">
+      <c r="A220" s="66">
         <v>215</v>
       </c>
       <c r="B220" s="61" t="s">
@@ -19896,7 +19924,7 @@
       </c>
     </row>
     <row r="221" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A221" s="71">
+      <c r="A221" s="66">
         <v>216</v>
       </c>
       <c r="B221" s="61" t="s">
@@ -19971,7 +19999,7 @@
       </c>
     </row>
     <row r="222" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A222" s="71">
+      <c r="A222" s="66">
         <v>217</v>
       </c>
       <c r="B222" s="61" t="s">
@@ -20043,7 +20071,7 @@
       </c>
     </row>
     <row r="223" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A223" s="71">
+      <c r="A223" s="66">
         <v>218</v>
       </c>
       <c r="B223" s="61" t="s">
@@ -20115,7 +20143,7 @@
       </c>
     </row>
     <row r="224" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A224" s="71">
+      <c r="A224" s="66">
         <v>219</v>
       </c>
       <c r="B224" s="61" t="s">
@@ -20187,7 +20215,7 @@
       </c>
     </row>
     <row r="225" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A225" s="71">
+      <c r="A225" s="66">
         <v>220</v>
       </c>
       <c r="B225" s="61" t="s">
@@ -20255,7 +20283,7 @@
       </c>
     </row>
     <row r="226" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A226" s="71">
+      <c r="A226" s="66">
         <v>221</v>
       </c>
       <c r="B226" s="61" t="s">
@@ -20326,7 +20354,7 @@
       </c>
     </row>
     <row r="227" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A227" s="71">
+      <c r="A227" s="66">
         <v>222</v>
       </c>
       <c r="B227" s="61" t="s">
@@ -20398,7 +20426,7 @@
       </c>
     </row>
     <row r="228" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A228" s="71">
+      <c r="A228" s="66">
         <v>223</v>
       </c>
       <c r="B228" s="61" t="s">
@@ -20470,7 +20498,7 @@
       </c>
     </row>
     <row r="229" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A229" s="71">
+      <c r="A229" s="66">
         <v>224</v>
       </c>
       <c r="B229" s="61" t="s">
@@ -20542,7 +20570,7 @@
       </c>
     </row>
     <row r="230" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A230" s="71">
+      <c r="A230" s="66">
         <v>225</v>
       </c>
       <c r="B230" s="61" t="s">
@@ -20617,7 +20645,7 @@
       </c>
     </row>
     <row r="231" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A231" s="71">
+      <c r="A231" s="66">
         <v>226</v>
       </c>
       <c r="B231" s="61" t="s">
@@ -20692,7 +20720,7 @@
       </c>
     </row>
     <row r="232" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A232" s="71">
+      <c r="A232" s="66">
         <v>227</v>
       </c>
       <c r="B232" s="61" t="s">
@@ -20764,7 +20792,7 @@
       </c>
     </row>
     <row r="233" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A233" s="71">
+      <c r="A233" s="66">
         <v>228</v>
       </c>
       <c r="B233" s="61" t="s">
@@ -20839,7 +20867,7 @@
       </c>
     </row>
     <row r="234" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A234" s="71">
+      <c r="A234" s="66">
         <v>229</v>
       </c>
       <c r="B234" s="61" t="s">
@@ -20911,7 +20939,7 @@
       </c>
     </row>
     <row r="235" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A235" s="71">
+      <c r="A235" s="66">
         <v>230</v>
       </c>
       <c r="B235" s="61" t="s">
@@ -20958,6 +20986,9 @@
       </c>
       <c r="Q235" s="23" t="s">
         <v>912</v>
+      </c>
+      <c r="R235" s="62" t="s">
+        <v>920</v>
       </c>
       <c r="S235" s="61"/>
       <c r="T235" s="61"/>
@@ -20983,7 +21014,7 @@
       </c>
     </row>
     <row r="236" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A236" s="71">
+      <c r="A236" s="66">
         <v>231</v>
       </c>
       <c r="B236" s="61" t="s">
@@ -21058,7 +21089,7 @@
       </c>
     </row>
     <row r="237" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A237" s="71">
+      <c r="A237" s="66">
         <v>232</v>
       </c>
       <c r="B237" s="61" t="s">
@@ -21130,7 +21161,7 @@
       </c>
     </row>
     <row r="238" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A238" s="71">
+      <c r="A238" s="66">
         <v>233</v>
       </c>
       <c r="B238" s="61" t="s">
@@ -21205,7 +21236,7 @@
       </c>
     </row>
     <row r="239" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A239" s="71">
+      <c r="A239" s="66">
         <v>234</v>
       </c>
       <c r="B239" s="61" t="s">
@@ -21280,7 +21311,7 @@
       </c>
     </row>
     <row r="240" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A240" s="71">
+      <c r="A240" s="66">
         <v>235</v>
       </c>
       <c r="B240" s="61" t="s">
@@ -21355,7 +21386,7 @@
       </c>
     </row>
     <row r="241" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A241" s="71">
+      <c r="A241" s="66">
         <v>236</v>
       </c>
       <c r="B241" s="61" t="s">
@@ -21427,7 +21458,7 @@
       </c>
     </row>
     <row r="242" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A242" s="71">
+      <c r="A242" s="66">
         <v>237</v>
       </c>
       <c r="B242" s="61" t="s">
@@ -21499,7 +21530,7 @@
       </c>
     </row>
     <row r="243" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A243" s="71">
+      <c r="A243" s="66">
         <v>238</v>
       </c>
       <c r="B243" s="61" t="s">
@@ -21574,7 +21605,7 @@
       </c>
     </row>
     <row r="244" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A244" s="71">
+      <c r="A244" s="66">
         <v>239</v>
       </c>
       <c r="B244" s="61" t="s">
@@ -21649,7 +21680,7 @@
       </c>
     </row>
     <row r="245" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A245" s="71">
+      <c r="A245" s="66">
         <v>240</v>
       </c>
       <c r="B245" s="61" t="s">
@@ -21724,7 +21755,7 @@
       </c>
     </row>
     <row r="246" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A246" s="71">
+      <c r="A246" s="66">
         <v>241</v>
       </c>
       <c r="B246" s="61" t="s">
@@ -21796,7 +21827,7 @@
       </c>
     </row>
     <row r="247" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A247" s="71">
+      <c r="A247" s="66">
         <v>242</v>
       </c>
       <c r="B247" s="61" t="s">
@@ -21871,7 +21902,7 @@
       </c>
     </row>
     <row r="248" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A248" s="71">
+      <c r="A248" s="66">
         <v>243</v>
       </c>
       <c r="B248" s="61" t="s">
@@ -21946,7 +21977,7 @@
       </c>
     </row>
     <row r="249" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A249" s="71">
+      <c r="A249" s="66">
         <v>244</v>
       </c>
       <c r="B249" s="61" t="s">
@@ -22020,7 +22051,7 @@
       </c>
     </row>
     <row r="250" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A250" s="71">
+      <c r="A250" s="66">
         <v>245</v>
       </c>
       <c r="B250" s="61" t="s">
@@ -22092,7 +22123,7 @@
       </c>
     </row>
     <row r="251" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A251" s="71">
+      <c r="A251" s="66">
         <v>246</v>
       </c>
       <c r="B251" s="61" t="s">
@@ -22169,7 +22200,7 @@
       </c>
     </row>
     <row r="252" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A252" s="71">
+      <c r="A252" s="66">
         <v>247</v>
       </c>
       <c r="B252" s="61" t="s">
@@ -22241,7 +22272,7 @@
       </c>
     </row>
     <row r="253" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A253" s="71">
+      <c r="A253" s="66">
         <v>248</v>
       </c>
       <c r="B253" s="61" t="s">
@@ -22316,7 +22347,7 @@
       </c>
     </row>
     <row r="254" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A254" s="71">
+      <c r="A254" s="66">
         <v>249</v>
       </c>
       <c r="B254" s="61" t="s">
@@ -22388,7 +22419,7 @@
       </c>
     </row>
     <row r="255" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A255" s="71">
+      <c r="A255" s="66">
         <v>250</v>
       </c>
       <c r="B255" s="61" t="s">
@@ -22460,7 +22491,7 @@
       </c>
     </row>
     <row r="256" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A256" s="71">
+      <c r="A256" s="66">
         <v>251</v>
       </c>
       <c r="B256" s="61" t="s">
@@ -22534,7 +22565,7 @@
       </c>
     </row>
     <row r="257" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A257" s="71">
+      <c r="A257" s="66">
         <v>252</v>
       </c>
       <c r="B257" s="61" t="s">
@@ -22602,7 +22633,7 @@
       </c>
     </row>
     <row r="258" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A258" s="71">
+      <c r="A258" s="66">
         <v>253</v>
       </c>
       <c r="B258" s="61" t="s">
@@ -22674,7 +22705,7 @@
       </c>
     </row>
     <row r="259" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A259" s="71">
+      <c r="A259" s="66">
         <v>254</v>
       </c>
       <c r="B259" s="61" t="s">
@@ -22746,7 +22777,7 @@
       </c>
     </row>
     <row r="260" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A260" s="71">
+      <c r="A260" s="66">
         <v>255</v>
       </c>
       <c r="B260" s="61" t="s">
@@ -22818,7 +22849,7 @@
       </c>
     </row>
     <row r="261" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A261" s="71">
+      <c r="A261" s="66">
         <v>256</v>
       </c>
       <c r="B261" s="61" t="s">
@@ -22890,7 +22921,7 @@
       </c>
     </row>
     <row r="262" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A262" s="71">
+      <c r="A262" s="66">
         <v>257</v>
       </c>
       <c r="B262" s="61" t="s">
@@ -22962,7 +22993,7 @@
       </c>
     </row>
     <row r="263" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A263" s="71">
+      <c r="A263" s="66">
         <v>258</v>
       </c>
       <c r="B263" s="61" t="s">
@@ -23034,7 +23065,7 @@
       </c>
     </row>
     <row r="264" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A264" s="71">
+      <c r="A264" s="66">
         <v>259</v>
       </c>
       <c r="B264" s="61" t="s">
@@ -23106,7 +23137,7 @@
       </c>
     </row>
     <row r="265" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A265" s="71">
+      <c r="A265" s="66">
         <v>260</v>
       </c>
       <c r="B265" s="61" t="s">
@@ -23178,7 +23209,7 @@
       </c>
     </row>
     <row r="266" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A266" s="71">
+      <c r="A266" s="66">
         <v>261</v>
       </c>
       <c r="B266" s="61" t="s">
@@ -23250,7 +23281,7 @@
       </c>
     </row>
     <row r="267" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A267" s="71">
+      <c r="A267" s="66">
         <v>262</v>
       </c>
       <c r="B267" s="61" t="s">
@@ -23322,7 +23353,7 @@
       </c>
     </row>
     <row r="268" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A268" s="71">
+      <c r="A268" s="66">
         <v>263</v>
       </c>
       <c r="B268" s="61" t="s">
@@ -23394,7 +23425,7 @@
       </c>
     </row>
     <row r="269" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A269" s="71">
+      <c r="A269" s="66">
         <v>264</v>
       </c>
       <c r="B269" s="61" t="s">
@@ -23466,7 +23497,7 @@
       </c>
     </row>
     <row r="270" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A270" s="71">
+      <c r="A270" s="66">
         <v>265</v>
       </c>
       <c r="B270" s="61" t="s">
@@ -23538,7 +23569,7 @@
       </c>
     </row>
     <row r="271" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A271" s="71">
+      <c r="A271" s="66">
         <v>266</v>
       </c>
       <c r="B271" s="61" t="s">
@@ -23610,7 +23641,7 @@
       </c>
     </row>
     <row r="272" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A272" s="71">
+      <c r="A272" s="66">
         <v>267</v>
       </c>
       <c r="B272" s="61" t="s">
@@ -23685,7 +23716,7 @@
       </c>
     </row>
     <row r="273" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A273" s="71">
+      <c r="A273" s="66">
         <v>268</v>
       </c>
       <c r="B273" s="61" t="s">
@@ -23757,7 +23788,7 @@
       </c>
     </row>
     <row r="274" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A274" s="71">
+      <c r="A274" s="66">
         <v>269</v>
       </c>
       <c r="B274" s="61" t="s">
@@ -23829,7 +23860,7 @@
       </c>
     </row>
     <row r="275" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A275" s="71">
+      <c r="A275" s="66">
         <v>270</v>
       </c>
       <c r="B275" s="61" t="s">
@@ -23901,7 +23932,7 @@
       </c>
     </row>
     <row r="276" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A276" s="71">
+      <c r="A276" s="66">
         <v>271</v>
       </c>
       <c r="B276" s="61" t="s">
@@ -23973,7 +24004,7 @@
       </c>
     </row>
     <row r="277" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A277" s="71">
+      <c r="A277" s="66">
         <v>272</v>
       </c>
       <c r="B277" s="61" t="s">
@@ -24046,7 +24077,7 @@
       </c>
     </row>
     <row r="278" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A278" s="71">
+      <c r="A278" s="66">
         <v>273</v>
       </c>
       <c r="B278" s="61" t="s">
@@ -24114,7 +24145,7 @@
       </c>
     </row>
     <row r="279" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A279" s="71">
+      <c r="A279" s="66">
         <v>274</v>
       </c>
       <c r="B279" s="61" t="s">
@@ -24186,7 +24217,7 @@
       </c>
     </row>
     <row r="280" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A280" s="71">
+      <c r="A280" s="66">
         <v>275</v>
       </c>
       <c r="B280" s="61" t="s">
@@ -24254,7 +24285,7 @@
       </c>
     </row>
     <row r="281" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A281" s="71">
+      <c r="A281" s="66">
         <v>276</v>
       </c>
       <c r="B281" s="61" t="s">
@@ -24329,7 +24360,7 @@
       </c>
     </row>
     <row r="282" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A282" s="71">
+      <c r="A282" s="66">
         <v>277</v>
       </c>
       <c r="B282" s="61" t="s">
@@ -24404,7 +24435,7 @@
       </c>
     </row>
     <row r="283" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A283" s="71">
+      <c r="A283" s="66">
         <v>278</v>
       </c>
       <c r="B283" s="61" t="s">
@@ -24476,7 +24507,7 @@
       </c>
     </row>
     <row r="284" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A284" s="71">
+      <c r="A284" s="66">
         <v>279</v>
       </c>
       <c r="B284" s="61" t="s">
@@ -24548,7 +24579,7 @@
       </c>
     </row>
     <row r="285" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A285" s="71">
+      <c r="A285" s="66">
         <v>280</v>
       </c>
       <c r="B285" s="61" t="s">
@@ -24623,7 +24654,7 @@
       </c>
     </row>
     <row r="286" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A286" s="71">
+      <c r="A286" s="66">
         <v>281</v>
       </c>
       <c r="B286" s="61" t="s">
@@ -24695,7 +24726,7 @@
       </c>
     </row>
     <row r="287" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A287" s="71">
+      <c r="A287" s="66">
         <v>282</v>
       </c>
       <c r="B287" s="61" t="s">
@@ -24767,7 +24798,7 @@
       </c>
     </row>
     <row r="288" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A288" s="71">
+      <c r="A288" s="66">
         <v>283</v>
       </c>
       <c r="B288" s="61" t="s">
@@ -24842,7 +24873,7 @@
       </c>
     </row>
     <row r="289" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A289" s="71">
+      <c r="A289" s="66">
         <v>284</v>
       </c>
       <c r="B289" s="61" t="s">
@@ -24917,7 +24948,7 @@
       </c>
     </row>
     <row r="290" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A290" s="71">
+      <c r="A290" s="66">
         <v>285</v>
       </c>
       <c r="B290" s="61" t="s">
@@ -24992,7 +25023,7 @@
       </c>
     </row>
     <row r="291" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A291" s="71">
+      <c r="A291" s="66">
         <v>286</v>
       </c>
       <c r="B291" s="61" t="s">
@@ -25067,7 +25098,7 @@
       </c>
     </row>
     <row r="292" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A292" s="71">
+      <c r="A292" s="66">
         <v>287</v>
       </c>
       <c r="B292" s="61" t="s">
@@ -25142,7 +25173,7 @@
       </c>
     </row>
     <row r="293" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A293" s="71">
+      <c r="A293" s="66">
         <v>288</v>
       </c>
       <c r="B293" s="61" t="s">
@@ -25217,7 +25248,7 @@
       </c>
     </row>
     <row r="294" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A294" s="71">
+      <c r="A294" s="66">
         <v>289</v>
       </c>
       <c r="B294" s="61" t="s">
@@ -25292,7 +25323,7 @@
       </c>
     </row>
     <row r="295" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A295" s="71">
+      <c r="A295" s="66">
         <v>290</v>
       </c>
       <c r="B295" s="61" t="s">
@@ -25367,7 +25398,7 @@
       </c>
     </row>
     <row r="296" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A296" s="71">
+      <c r="A296" s="66">
         <v>291</v>
       </c>
       <c r="B296" s="61" t="s">
@@ -25442,7 +25473,7 @@
       </c>
     </row>
     <row r="297" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A297" s="71">
+      <c r="A297" s="66">
         <v>292</v>
       </c>
       <c r="B297" s="61" t="s">
@@ -25514,7 +25545,7 @@
       </c>
     </row>
     <row r="298" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A298" s="71">
+      <c r="A298" s="66">
         <v>293</v>
       </c>
       <c r="B298" s="61" t="s">
@@ -25589,7 +25620,7 @@
       </c>
     </row>
     <row r="299" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A299" s="71">
+      <c r="A299" s="66">
         <v>294</v>
       </c>
       <c r="B299" s="61" t="s">
@@ -25661,7 +25692,7 @@
       </c>
     </row>
     <row r="300" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A300" s="71">
+      <c r="A300" s="66">
         <v>295</v>
       </c>
       <c r="B300" s="61" t="s">
@@ -25732,7 +25763,7 @@
       </c>
     </row>
     <row r="301" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A301" s="71">
+      <c r="A301" s="66">
         <v>296</v>
       </c>
       <c r="B301" s="61" t="s">
@@ -25804,7 +25835,7 @@
       </c>
     </row>
     <row r="302" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A302" s="71">
+      <c r="A302" s="66">
         <v>297</v>
       </c>
       <c r="B302" s="61" t="s">
@@ -25876,7 +25907,7 @@
       </c>
     </row>
     <row r="303" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A303" s="71">
+      <c r="A303" s="66">
         <v>298</v>
       </c>
       <c r="B303" s="61" t="s">
@@ -25951,7 +25982,7 @@
       </c>
     </row>
     <row r="304" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A304" s="71">
+      <c r="A304" s="66">
         <v>299</v>
       </c>
       <c r="B304" s="61" t="s">
@@ -26023,7 +26054,7 @@
       </c>
     </row>
     <row r="305" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A305" s="71">
+      <c r="A305" s="66">
         <v>300</v>
       </c>
       <c r="B305" s="61" t="s">
@@ -26095,7 +26126,7 @@
       </c>
     </row>
     <row r="306" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A306" s="71">
+      <c r="A306" s="66">
         <v>301</v>
       </c>
       <c r="B306" s="61" t="s">
@@ -26167,7 +26198,7 @@
       </c>
     </row>
     <row r="307" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A307" s="71">
+      <c r="A307" s="66">
         <v>302</v>
       </c>
       <c r="B307" s="61" t="s">
@@ -26235,7 +26266,7 @@
       </c>
     </row>
     <row r="308" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A308" s="71">
+      <c r="A308" s="66">
         <v>303</v>
       </c>
       <c r="B308" s="61" t="s">
@@ -26306,7 +26337,7 @@
       </c>
     </row>
     <row r="309" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A309" s="71">
+      <c r="A309" s="66">
         <v>304</v>
       </c>
       <c r="B309" s="61" t="s">
@@ -26378,7 +26409,7 @@
       </c>
     </row>
     <row r="310" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A310" s="71">
+      <c r="A310" s="66">
         <v>305</v>
       </c>
       <c r="B310" s="61" t="s">
@@ -26450,7 +26481,7 @@
       </c>
     </row>
     <row r="311" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A311" s="71">
+      <c r="A311" s="66">
         <v>306</v>
       </c>
       <c r="B311" s="61" t="s">
@@ -26525,7 +26556,7 @@
       </c>
     </row>
     <row r="312" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A312" s="71">
+      <c r="A312" s="66">
         <v>307</v>
       </c>
       <c r="B312" s="61" t="s">
@@ -26593,7 +26624,7 @@
       </c>
     </row>
     <row r="313" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A313" s="71">
+      <c r="A313" s="66">
         <v>308</v>
       </c>
       <c r="B313" s="61" t="s">
@@ -26668,7 +26699,7 @@
       </c>
     </row>
     <row r="314" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A314" s="71">
+      <c r="A314" s="66">
         <v>309</v>
       </c>
       <c r="B314" s="61" t="s">
@@ -26739,7 +26770,7 @@
       </c>
     </row>
     <row r="315" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A315" s="71">
+      <c r="A315" s="66">
         <v>310</v>
       </c>
       <c r="B315" s="61" t="s">
@@ -26811,7 +26842,7 @@
       </c>
     </row>
     <row r="316" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A316" s="71">
+      <c r="A316" s="66">
         <v>311</v>
       </c>
       <c r="B316" s="61" t="s">
@@ -26885,7 +26916,7 @@
       </c>
     </row>
     <row r="317" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A317" s="71">
+      <c r="A317" s="66">
         <v>312</v>
       </c>
       <c r="B317" s="61" t="s">
@@ -26957,7 +26988,7 @@
       </c>
     </row>
     <row r="318" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A318" s="71">
+      <c r="A318" s="66">
         <v>313</v>
       </c>
       <c r="B318" s="61" t="s">
@@ -27029,7 +27060,7 @@
       </c>
     </row>
     <row r="319" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A319" s="71">
+      <c r="A319" s="66">
         <v>314</v>
       </c>
       <c r="B319" s="61" t="s">
@@ -27100,7 +27131,7 @@
       </c>
     </row>
     <row r="320" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A320" s="71">
+      <c r="A320" s="66">
         <v>315</v>
       </c>
       <c r="B320" s="61" t="s">
@@ -27175,7 +27206,7 @@
       </c>
     </row>
     <row r="321" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A321" s="71">
+      <c r="A321" s="66">
         <v>316</v>
       </c>
       <c r="B321" s="61" t="s">
@@ -27250,7 +27281,7 @@
       </c>
     </row>
     <row r="322" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A322" s="71">
+      <c r="A322" s="66">
         <v>317</v>
       </c>
       <c r="B322" s="61" t="s">
@@ -27318,7 +27349,7 @@
       </c>
     </row>
     <row r="323" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A323" s="71">
+      <c r="A323" s="66">
         <v>318</v>
       </c>
       <c r="B323" s="61" t="s">
@@ -27389,7 +27420,7 @@
       </c>
     </row>
     <row r="324" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A324" s="71">
+      <c r="A324" s="66">
         <v>319</v>
       </c>
       <c r="B324" s="61" t="s">
@@ -27460,7 +27491,7 @@
       </c>
     </row>
     <row r="325" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A325" s="71">
+      <c r="A325" s="66">
         <v>320</v>
       </c>
       <c r="B325" s="61" t="s">
@@ -27535,7 +27566,7 @@
       </c>
     </row>
     <row r="326" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A326" s="71">
+      <c r="A326" s="66">
         <v>321</v>
       </c>
       <c r="B326" s="61" t="s">
@@ -27610,7 +27641,7 @@
       </c>
     </row>
     <row r="327" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A327" s="71">
+      <c r="A327" s="66">
         <v>322</v>
       </c>
       <c r="B327" s="61" t="s">
@@ -27678,7 +27709,7 @@
       </c>
     </row>
     <row r="328" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A328" s="71">
+      <c r="A328" s="66">
         <v>323</v>
       </c>
       <c r="B328" s="61" t="s">
@@ -27753,7 +27784,7 @@
       </c>
     </row>
     <row r="329" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A329" s="71">
+      <c r="A329" s="66">
         <v>324</v>
       </c>
       <c r="B329" s="61" t="s">
@@ -27825,7 +27856,7 @@
       </c>
     </row>
     <row r="330" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A330" s="71">
+      <c r="A330" s="66">
         <v>325</v>
       </c>
       <c r="B330" s="61" t="s">
@@ -27900,7 +27931,7 @@
       </c>
     </row>
     <row r="331" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A331" s="71">
+      <c r="A331" s="66">
         <v>326</v>
       </c>
       <c r="B331" s="61" t="s">
@@ -27972,7 +28003,7 @@
       </c>
     </row>
     <row r="332" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A332" s="71">
+      <c r="A332" s="66">
         <v>327</v>
       </c>
       <c r="B332" s="61" t="s">
@@ -28044,7 +28075,7 @@
       </c>
     </row>
     <row r="333" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A333" s="71">
+      <c r="A333" s="66">
         <v>328</v>
       </c>
       <c r="B333" s="61" t="s">
@@ -28116,7 +28147,7 @@
       </c>
     </row>
     <row r="334" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A334" s="71">
+      <c r="A334" s="66">
         <v>329</v>
       </c>
       <c r="B334" s="61" t="s">
@@ -28188,7 +28219,7 @@
       </c>
     </row>
     <row r="335" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A335" s="71">
+      <c r="A335" s="66">
         <v>330</v>
       </c>
       <c r="B335" s="61" t="s">
@@ -28260,7 +28291,7 @@
       </c>
     </row>
     <row r="336" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A336" s="71">
+      <c r="A336" s="66">
         <v>331</v>
       </c>
       <c r="B336" s="61" t="s">
@@ -28328,7 +28359,7 @@
       </c>
     </row>
     <row r="337" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A337" s="71">
+      <c r="A337" s="66">
         <v>332</v>
       </c>
       <c r="B337" s="61" t="s">
@@ -28400,7 +28431,7 @@
       </c>
     </row>
     <row r="338" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A338" s="71">
+      <c r="A338" s="66">
         <v>333</v>
       </c>
       <c r="B338" s="61" t="s">
@@ -28472,7 +28503,7 @@
       </c>
     </row>
     <row r="339" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A339" s="71">
+      <c r="A339" s="66">
         <v>334</v>
       </c>
       <c r="B339" s="61" t="s">
@@ -28547,7 +28578,7 @@
       </c>
     </row>
     <row r="340" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A340" s="71">
+      <c r="A340" s="66">
         <v>335</v>
       </c>
       <c r="B340" s="61" t="s">
@@ -28622,7 +28653,7 @@
       </c>
     </row>
     <row r="341" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A341" s="71">
+      <c r="A341" s="66">
         <v>336</v>
       </c>
       <c r="B341" s="61" t="s">
@@ -28697,7 +28728,7 @@
       </c>
     </row>
     <row r="342" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A342" s="71">
+      <c r="A342" s="66">
         <v>337</v>
       </c>
       <c r="B342" s="61" t="s">
@@ -28772,7 +28803,7 @@
       </c>
     </row>
     <row r="343" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A343" s="71">
+      <c r="A343" s="66">
         <v>338</v>
       </c>
       <c r="B343" s="61" t="s">
@@ -28844,7 +28875,7 @@
       </c>
     </row>
     <row r="344" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A344" s="71">
+      <c r="A344" s="66">
         <v>339</v>
       </c>
       <c r="B344" s="61" t="s">
@@ -28919,7 +28950,7 @@
       </c>
     </row>
     <row r="345" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A345" s="71">
+      <c r="A345" s="66">
         <v>340</v>
       </c>
       <c r="B345" s="61" t="s">
@@ -28991,7 +29022,7 @@
       </c>
     </row>
     <row r="346" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A346" s="71">
+      <c r="A346" s="66">
         <v>341</v>
       </c>
       <c r="B346" s="61" t="s">
@@ -29066,7 +29097,7 @@
       </c>
     </row>
     <row r="347" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A347" s="71">
+      <c r="A347" s="66">
         <v>342</v>
       </c>
       <c r="B347" s="61" t="s">
@@ -29138,7 +29169,7 @@
       </c>
     </row>
     <row r="348" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A348" s="71">
+      <c r="A348" s="66">
         <v>343</v>
       </c>
       <c r="B348" s="61" t="s">
@@ -29210,7 +29241,7 @@
       </c>
     </row>
     <row r="349" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A349" s="71">
+      <c r="A349" s="66">
         <v>344</v>
       </c>
       <c r="B349" s="61" t="s">
@@ -29282,7 +29313,7 @@
       </c>
     </row>
     <row r="350" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A350" s="71">
+      <c r="A350" s="66">
         <v>345</v>
       </c>
       <c r="B350" s="61" t="s">
@@ -29354,7 +29385,7 @@
       </c>
     </row>
     <row r="351" spans="1:30" s="62" customFormat="1" ht="12.5">
-      <c r="A351" s="71">
+      <c r="A351" s="66">
         <v>346</v>
       </c>
       <c r="B351" s="61" t="s">
@@ -29520,49 +29551,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:11" ht="17.399999999999999" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
     </row>
     <row r="3" spans="1:11" ht="20" customHeight="1">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="5" spans="1:11" ht="28" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -30439,49 +30470,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="20" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:11" ht="17.399999999999999" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
     </row>
     <row r="3" spans="1:11" ht="20" customHeight="1">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="5" spans="1:11" ht="28" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -31625,76 +31656,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="70"/>
+      <c r="S1" s="70"/>
+      <c r="T1" s="70"/>
     </row>
     <row r="2" spans="1:20" ht="17.399999999999999" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="71"/>
     </row>
     <row r="3" spans="1:20" ht="20" customHeight="1">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="72"/>
     </row>
     <row r="5" spans="1:20" ht="28" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -38422,58 +38453,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
     </row>
     <row r="2" spans="1:14" ht="17.399999999999999" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
     </row>
     <row r="3" spans="1:14" ht="20" customHeight="1">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
     </row>
     <row r="5" spans="1:14" ht="28" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -41761,52 +41792,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="20" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
     </row>
     <row r="2" spans="1:12" ht="17.399999999999999" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
     </row>
     <row r="3" spans="1:12" ht="20" customHeight="1">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
     </row>
     <row r="5" spans="1:12" ht="28" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -43626,58 +43657,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
     </row>
     <row r="2" spans="1:14" ht="17.399999999999999" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
     </row>
     <row r="3" spans="1:14" ht="20" customHeight="1">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
     </row>
     <row r="5" spans="1:14" ht="28" customHeight="1">
       <c r="A5" s="1" t="s">

--- a/data/Template_Resmi_Database_SIRUMAH.xlsx
+++ b/data/Template_Resmi_Database_SIRUMAH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCB6C92-CA41-431A-8E82-A2B4793FFEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CB6B0F-9FAD-4678-B11B-54C031659249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PERUMAHAN" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4134" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4139" uniqueCount="926">
   <si>
     <t>TEMPLATE RESMI DATABASE SIRUMAH — DATA PERUMAHAN</t>
   </si>
@@ -2800,6 +2800,21 @@
   </si>
   <si>
     <t>Jalan rusak berat</t>
+  </si>
+  <si>
+    <t>Januari</t>
+  </si>
+  <si>
+    <t>Februari</t>
+  </si>
+  <si>
+    <t>Maret</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>Mei</t>
   </si>
 </sst>
 </file>
@@ -3075,7 +3090,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3277,21 +3292,37 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -3332,7 +3363,7 @@
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PENGEMBANG"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="DIREKTUR/PELAKSANA"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="ASOSIASI"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="TAHUN_SITEPLAN" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="TAHUN_SITEPLAN" dataDxfId="3"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="JUMLAH_SITEPLAN"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="JUMLAH_TERBANGUN"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="JUMLAH_TERHUNI"/>
@@ -3344,9 +3375,9 @@
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="STATUS_PENGEMBANG"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="STATUS_RAWAN_BANJIR"/>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="CATATAN"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="LATITUDE" dataDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="LATITUDE" dataDxfId="2"/>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="LONGITUDE"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="TAHUN_DATA*" dataDxfId="0"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="TAHUN_DATA*" dataDxfId="1"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="SUMBER_DATA*"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="STATUS_VERIFIKASI*"/>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="TANGGAL_UPDATE*"/>
@@ -3451,7 +3482,7 @@
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="ID_RETRIBUSI*"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="NAMA_RUSUNAWA*"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="TAHUN*"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="TAHUN*" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="BULAN*"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="TARGET*"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="REALISASI*"/>
@@ -3693,74 +3724,74 @@
       <c r="W1" s="70"/>
       <c r="X1" s="70"/>
       <c r="Y1" s="70"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-      <c r="AD1" s="73"/>
+      <c r="Z1" s="71"/>
+      <c r="AA1" s="71"/>
+      <c r="AB1" s="71"/>
+      <c r="AC1" s="71"/>
+      <c r="AD1" s="71"/>
     </row>
     <row r="2" spans="1:30" ht="17.399999999999999" customHeight="1">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71"/>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71"/>
-      <c r="V2" s="71"/>
-      <c r="W2" s="71"/>
-      <c r="X2" s="71"/>
-      <c r="Y2" s="71"/>
-      <c r="Z2" s="73"/>
-      <c r="AA2" s="73"/>
-      <c r="AB2" s="73"/>
-      <c r="AC2" s="73"/>
-      <c r="AD2" s="73"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="72"/>
+      <c r="V2" s="72"/>
+      <c r="W2" s="72"/>
+      <c r="X2" s="72"/>
+      <c r="Y2" s="72"/>
+      <c r="Z2" s="71"/>
+      <c r="AA2" s="71"/>
+      <c r="AB2" s="71"/>
+      <c r="AC2" s="71"/>
+      <c r="AD2" s="71"/>
     </row>
     <row r="3" spans="1:30" ht="25.4" customHeight="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="72"/>
-      <c r="T3" s="72"/>
-      <c r="U3" s="72"/>
-      <c r="V3" s="72"/>
-      <c r="W3" s="72"/>
-      <c r="X3" s="72"/>
-      <c r="Y3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="W3" s="73"/>
+      <c r="X3" s="73"/>
+      <c r="Y3" s="73"/>
       <c r="Z3" s="74"/>
       <c r="AA3" s="74"/>
       <c r="AB3" s="74"/>
@@ -29566,34 +29597,34 @@
       <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:11" ht="17.399999999999999" customHeight="1">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
     </row>
     <row r="3" spans="1:11" ht="20" customHeight="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
     </row>
     <row r="5" spans="1:11" ht="28" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -30485,34 +30516,34 @@
       <c r="K1" s="70"/>
     </row>
     <row r="2" spans="1:11" ht="17.399999999999999" customHeight="1">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
     </row>
     <row r="3" spans="1:11" ht="20" customHeight="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
     </row>
     <row r="5" spans="1:11" ht="28" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -31680,52 +31711,52 @@
       <c r="T1" s="70"/>
     </row>
     <row r="2" spans="1:20" ht="17.399999999999999" customHeight="1">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71"/>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
     </row>
     <row r="3" spans="1:20" ht="20" customHeight="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="72"/>
-      <c r="T3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
     </row>
     <row r="5" spans="1:20" ht="28" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -38471,40 +38502,40 @@
       <c r="N1" s="70"/>
     </row>
     <row r="2" spans="1:14" ht="17.399999999999999" customHeight="1">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
     </row>
     <row r="3" spans="1:14" ht="20" customHeight="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
     </row>
     <row r="5" spans="1:14" ht="28" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -41781,7 +41812,7 @@
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="3" max="3" width="12" style="79" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
@@ -41808,36 +41839,36 @@
       <c r="L1" s="70"/>
     </row>
     <row r="2" spans="1:12" ht="17.399999999999999" customHeight="1">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
     </row>
     <row r="3" spans="1:12" ht="20" customHeight="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
     </row>
     <row r="5" spans="1:12" ht="28" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -41846,7 +41877,7 @@
       <c r="B5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="75" t="s">
         <v>77</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -41880,10 +41911,16 @@
     <row r="6" spans="1:12" ht="14.65" customHeight="1">
       <c r="A6" s="31"/>
       <c r="B6" s="10"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="10"/>
+      <c r="C6" s="76">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>921</v>
+      </c>
       <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
+      <c r="F6" s="49">
+        <v>15850000</v>
+      </c>
       <c r="G6" s="25" t="str">
         <f t="shared" ref="G6:G37" si="0">IF(A6="","",IFERROR(F6/E6,0))</f>
         <v/>
@@ -41897,10 +41934,14 @@
     <row r="7" spans="1:12" ht="14.65" customHeight="1">
       <c r="A7" s="32"/>
       <c r="B7" s="11"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="11"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="11" t="s">
+        <v>922</v>
+      </c>
       <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
+      <c r="F7" s="50">
+        <v>13675000</v>
+      </c>
       <c r="G7" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -41914,10 +41955,14 @@
     <row r="8" spans="1:12" ht="14.65" customHeight="1">
       <c r="A8" s="32"/>
       <c r="B8" s="11"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="11" t="s">
+        <v>923</v>
+      </c>
       <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
+      <c r="F8" s="50">
+        <v>24950000</v>
+      </c>
       <c r="G8" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -41931,10 +41976,14 @@
     <row r="9" spans="1:12" ht="14.65" customHeight="1">
       <c r="A9" s="32"/>
       <c r="B9" s="11"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="11"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="11" t="s">
+        <v>924</v>
+      </c>
       <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
+      <c r="F9" s="50">
+        <v>32950000</v>
+      </c>
       <c r="G9" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -41948,10 +41997,14 @@
     <row r="10" spans="1:12" ht="14.65" customHeight="1">
       <c r="A10" s="32"/>
       <c r="B10" s="11"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="11"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="11" t="s">
+        <v>925</v>
+      </c>
       <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
+      <c r="F10" s="50">
+        <v>32950000</v>
+      </c>
       <c r="G10" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -41965,7 +42018,7 @@
     <row r="11" spans="1:12" ht="14.65" customHeight="1">
       <c r="A11" s="32"/>
       <c r="B11" s="11"/>
-      <c r="C11" s="20"/>
+      <c r="C11" s="77"/>
       <c r="D11" s="11"/>
       <c r="E11" s="50"/>
       <c r="F11" s="50"/>
@@ -41982,7 +42035,7 @@
     <row r="12" spans="1:12" ht="14.65" customHeight="1">
       <c r="A12" s="32"/>
       <c r="B12" s="11"/>
-      <c r="C12" s="20"/>
+      <c r="C12" s="77"/>
       <c r="D12" s="11"/>
       <c r="E12" s="50"/>
       <c r="F12" s="50"/>
@@ -41999,7 +42052,7 @@
     <row r="13" spans="1:12" ht="14.65" customHeight="1">
       <c r="A13" s="32"/>
       <c r="B13" s="11"/>
-      <c r="C13" s="20"/>
+      <c r="C13" s="77"/>
       <c r="D13" s="11"/>
       <c r="E13" s="50"/>
       <c r="F13" s="50"/>
@@ -42016,7 +42069,7 @@
     <row r="14" spans="1:12" ht="14.65" customHeight="1">
       <c r="A14" s="32"/>
       <c r="B14" s="11"/>
-      <c r="C14" s="20"/>
+      <c r="C14" s="77"/>
       <c r="D14" s="11"/>
       <c r="E14" s="50"/>
       <c r="F14" s="50"/>
@@ -42033,7 +42086,7 @@
     <row r="15" spans="1:12" ht="14.65" customHeight="1">
       <c r="A15" s="32"/>
       <c r="B15" s="11"/>
-      <c r="C15" s="20"/>
+      <c r="C15" s="77"/>
       <c r="D15" s="11"/>
       <c r="E15" s="50"/>
       <c r="F15" s="50"/>
@@ -42050,7 +42103,7 @@
     <row r="16" spans="1:12" ht="14.65" customHeight="1">
       <c r="A16" s="32"/>
       <c r="B16" s="11"/>
-      <c r="C16" s="20"/>
+      <c r="C16" s="77"/>
       <c r="D16" s="11"/>
       <c r="E16" s="50"/>
       <c r="F16" s="50"/>
@@ -42067,7 +42120,7 @@
     <row r="17" spans="1:12" ht="14.65" customHeight="1">
       <c r="A17" s="32"/>
       <c r="B17" s="11"/>
-      <c r="C17" s="20"/>
+      <c r="C17" s="77"/>
       <c r="D17" s="11"/>
       <c r="E17" s="50"/>
       <c r="F17" s="50"/>
@@ -42084,7 +42137,7 @@
     <row r="18" spans="1:12" ht="14.65" customHeight="1">
       <c r="A18" s="32"/>
       <c r="B18" s="11"/>
-      <c r="C18" s="20"/>
+      <c r="C18" s="77"/>
       <c r="D18" s="11"/>
       <c r="E18" s="50"/>
       <c r="F18" s="50"/>
@@ -42101,7 +42154,7 @@
     <row r="19" spans="1:12" ht="14.65" customHeight="1">
       <c r="A19" s="32"/>
       <c r="B19" s="11"/>
-      <c r="C19" s="20"/>
+      <c r="C19" s="77"/>
       <c r="D19" s="11"/>
       <c r="E19" s="50"/>
       <c r="F19" s="50"/>
@@ -42118,7 +42171,7 @@
     <row r="20" spans="1:12" ht="14.65" customHeight="1">
       <c r="A20" s="32"/>
       <c r="B20" s="11"/>
-      <c r="C20" s="20"/>
+      <c r="C20" s="77"/>
       <c r="D20" s="11"/>
       <c r="E20" s="50"/>
       <c r="F20" s="50"/>
@@ -42135,7 +42188,7 @@
     <row r="21" spans="1:12" ht="14.65" customHeight="1">
       <c r="A21" s="32"/>
       <c r="B21" s="11"/>
-      <c r="C21" s="20"/>
+      <c r="C21" s="77"/>
       <c r="D21" s="11"/>
       <c r="E21" s="50"/>
       <c r="F21" s="50"/>
@@ -42152,7 +42205,7 @@
     <row r="22" spans="1:12" ht="14.65" customHeight="1">
       <c r="A22" s="32"/>
       <c r="B22" s="11"/>
-      <c r="C22" s="20"/>
+      <c r="C22" s="77"/>
       <c r="D22" s="11"/>
       <c r="E22" s="50"/>
       <c r="F22" s="50"/>
@@ -42169,7 +42222,7 @@
     <row r="23" spans="1:12" ht="14.65" customHeight="1">
       <c r="A23" s="32"/>
       <c r="B23" s="11"/>
-      <c r="C23" s="20"/>
+      <c r="C23" s="77"/>
       <c r="D23" s="11"/>
       <c r="E23" s="50"/>
       <c r="F23" s="50"/>
@@ -42186,7 +42239,7 @@
     <row r="24" spans="1:12" ht="14.65" customHeight="1">
       <c r="A24" s="32"/>
       <c r="B24" s="11"/>
-      <c r="C24" s="20"/>
+      <c r="C24" s="77"/>
       <c r="D24" s="11"/>
       <c r="E24" s="50"/>
       <c r="F24" s="50"/>
@@ -42203,7 +42256,7 @@
     <row r="25" spans="1:12" ht="14.65" customHeight="1">
       <c r="A25" s="32"/>
       <c r="B25" s="11"/>
-      <c r="C25" s="20"/>
+      <c r="C25" s="77"/>
       <c r="D25" s="11"/>
       <c r="E25" s="50"/>
       <c r="F25" s="50"/>
@@ -42220,7 +42273,7 @@
     <row r="26" spans="1:12" ht="14.65" customHeight="1">
       <c r="A26" s="32"/>
       <c r="B26" s="11"/>
-      <c r="C26" s="20"/>
+      <c r="C26" s="77"/>
       <c r="D26" s="11"/>
       <c r="E26" s="50"/>
       <c r="F26" s="50"/>
@@ -42237,7 +42290,7 @@
     <row r="27" spans="1:12" ht="14.65" customHeight="1">
       <c r="A27" s="32"/>
       <c r="B27" s="11"/>
-      <c r="C27" s="20"/>
+      <c r="C27" s="77"/>
       <c r="D27" s="11"/>
       <c r="E27" s="50"/>
       <c r="F27" s="50"/>
@@ -42254,7 +42307,7 @@
     <row r="28" spans="1:12" ht="14.65" customHeight="1">
       <c r="A28" s="32"/>
       <c r="B28" s="11"/>
-      <c r="C28" s="20"/>
+      <c r="C28" s="77"/>
       <c r="D28" s="11"/>
       <c r="E28" s="50"/>
       <c r="F28" s="50"/>
@@ -42271,7 +42324,7 @@
     <row r="29" spans="1:12" ht="14.65" customHeight="1">
       <c r="A29" s="32"/>
       <c r="B29" s="11"/>
-      <c r="C29" s="20"/>
+      <c r="C29" s="77"/>
       <c r="D29" s="11"/>
       <c r="E29" s="50"/>
       <c r="F29" s="50"/>
@@ -42288,7 +42341,7 @@
     <row r="30" spans="1:12" ht="14.65" customHeight="1">
       <c r="A30" s="32"/>
       <c r="B30" s="11"/>
-      <c r="C30" s="20"/>
+      <c r="C30" s="77"/>
       <c r="D30" s="11"/>
       <c r="E30" s="50"/>
       <c r="F30" s="50"/>
@@ -42305,7 +42358,7 @@
     <row r="31" spans="1:12" ht="14.65" customHeight="1">
       <c r="A31" s="32"/>
       <c r="B31" s="11"/>
-      <c r="C31" s="20"/>
+      <c r="C31" s="77"/>
       <c r="D31" s="11"/>
       <c r="E31" s="50"/>
       <c r="F31" s="50"/>
@@ -42322,7 +42375,7 @@
     <row r="32" spans="1:12" ht="14.65" customHeight="1">
       <c r="A32" s="32"/>
       <c r="B32" s="11"/>
-      <c r="C32" s="20"/>
+      <c r="C32" s="77"/>
       <c r="D32" s="11"/>
       <c r="E32" s="50"/>
       <c r="F32" s="50"/>
@@ -42339,7 +42392,7 @@
     <row r="33" spans="1:12" ht="14.65" customHeight="1">
       <c r="A33" s="32"/>
       <c r="B33" s="11"/>
-      <c r="C33" s="20"/>
+      <c r="C33" s="77"/>
       <c r="D33" s="11"/>
       <c r="E33" s="50"/>
       <c r="F33" s="50"/>
@@ -42356,7 +42409,7 @@
     <row r="34" spans="1:12" ht="14.65" customHeight="1">
       <c r="A34" s="32"/>
       <c r="B34" s="11"/>
-      <c r="C34" s="20"/>
+      <c r="C34" s="77"/>
       <c r="D34" s="11"/>
       <c r="E34" s="50"/>
       <c r="F34" s="50"/>
@@ -42373,7 +42426,7 @@
     <row r="35" spans="1:12" ht="14.65" customHeight="1">
       <c r="A35" s="32"/>
       <c r="B35" s="11"/>
-      <c r="C35" s="20"/>
+      <c r="C35" s="77"/>
       <c r="D35" s="11"/>
       <c r="E35" s="50"/>
       <c r="F35" s="50"/>
@@ -42390,7 +42443,7 @@
     <row r="36" spans="1:12" ht="14.65" customHeight="1">
       <c r="A36" s="32"/>
       <c r="B36" s="11"/>
-      <c r="C36" s="20"/>
+      <c r="C36" s="77"/>
       <c r="D36" s="11"/>
       <c r="E36" s="50"/>
       <c r="F36" s="50"/>
@@ -42407,7 +42460,7 @@
     <row r="37" spans="1:12" ht="14.65" customHeight="1">
       <c r="A37" s="32"/>
       <c r="B37" s="11"/>
-      <c r="C37" s="20"/>
+      <c r="C37" s="77"/>
       <c r="D37" s="11"/>
       <c r="E37" s="50"/>
       <c r="F37" s="50"/>
@@ -42424,7 +42477,7 @@
     <row r="38" spans="1:12" ht="14.65" customHeight="1">
       <c r="A38" s="32"/>
       <c r="B38" s="11"/>
-      <c r="C38" s="20"/>
+      <c r="C38" s="77"/>
       <c r="D38" s="11"/>
       <c r="E38" s="50"/>
       <c r="F38" s="50"/>
@@ -42441,7 +42494,7 @@
     <row r="39" spans="1:12" ht="14.65" customHeight="1">
       <c r="A39" s="32"/>
       <c r="B39" s="11"/>
-      <c r="C39" s="20"/>
+      <c r="C39" s="77"/>
       <c r="D39" s="11"/>
       <c r="E39" s="50"/>
       <c r="F39" s="50"/>
@@ -42458,7 +42511,7 @@
     <row r="40" spans="1:12" ht="14.65" customHeight="1">
       <c r="A40" s="32"/>
       <c r="B40" s="11"/>
-      <c r="C40" s="20"/>
+      <c r="C40" s="77"/>
       <c r="D40" s="11"/>
       <c r="E40" s="50"/>
       <c r="F40" s="50"/>
@@ -42475,7 +42528,7 @@
     <row r="41" spans="1:12" ht="14.65" customHeight="1">
       <c r="A41" s="32"/>
       <c r="B41" s="11"/>
-      <c r="C41" s="20"/>
+      <c r="C41" s="77"/>
       <c r="D41" s="11"/>
       <c r="E41" s="50"/>
       <c r="F41" s="50"/>
@@ -42492,7 +42545,7 @@
     <row r="42" spans="1:12" ht="14.65" customHeight="1">
       <c r="A42" s="32"/>
       <c r="B42" s="11"/>
-      <c r="C42" s="20"/>
+      <c r="C42" s="77"/>
       <c r="D42" s="11"/>
       <c r="E42" s="50"/>
       <c r="F42" s="50"/>
@@ -42509,7 +42562,7 @@
     <row r="43" spans="1:12" ht="14.65" customHeight="1">
       <c r="A43" s="32"/>
       <c r="B43" s="11"/>
-      <c r="C43" s="20"/>
+      <c r="C43" s="77"/>
       <c r="D43" s="11"/>
       <c r="E43" s="50"/>
       <c r="F43" s="50"/>
@@ -42526,7 +42579,7 @@
     <row r="44" spans="1:12" ht="14.65" customHeight="1">
       <c r="A44" s="32"/>
       <c r="B44" s="11"/>
-      <c r="C44" s="20"/>
+      <c r="C44" s="77"/>
       <c r="D44" s="11"/>
       <c r="E44" s="50"/>
       <c r="F44" s="50"/>
@@ -42543,7 +42596,7 @@
     <row r="45" spans="1:12" ht="14.65" customHeight="1">
       <c r="A45" s="32"/>
       <c r="B45" s="11"/>
-      <c r="C45" s="20"/>
+      <c r="C45" s="77"/>
       <c r="D45" s="11"/>
       <c r="E45" s="50"/>
       <c r="F45" s="50"/>
@@ -42560,7 +42613,7 @@
     <row r="46" spans="1:12" ht="14.65" customHeight="1">
       <c r="A46" s="32"/>
       <c r="B46" s="11"/>
-      <c r="C46" s="20"/>
+      <c r="C46" s="77"/>
       <c r="D46" s="11"/>
       <c r="E46" s="50"/>
       <c r="F46" s="50"/>
@@ -42577,7 +42630,7 @@
     <row r="47" spans="1:12" ht="14.65" customHeight="1">
       <c r="A47" s="32"/>
       <c r="B47" s="11"/>
-      <c r="C47" s="20"/>
+      <c r="C47" s="77"/>
       <c r="D47" s="11"/>
       <c r="E47" s="50"/>
       <c r="F47" s="50"/>
@@ -42594,7 +42647,7 @@
     <row r="48" spans="1:12" ht="14.65" customHeight="1">
       <c r="A48" s="32"/>
       <c r="B48" s="11"/>
-      <c r="C48" s="20"/>
+      <c r="C48" s="77"/>
       <c r="D48" s="11"/>
       <c r="E48" s="50"/>
       <c r="F48" s="50"/>
@@ -42611,7 +42664,7 @@
     <row r="49" spans="1:12" ht="14.65" customHeight="1">
       <c r="A49" s="32"/>
       <c r="B49" s="11"/>
-      <c r="C49" s="20"/>
+      <c r="C49" s="77"/>
       <c r="D49" s="11"/>
       <c r="E49" s="50"/>
       <c r="F49" s="50"/>
@@ -42628,7 +42681,7 @@
     <row r="50" spans="1:12" ht="14.65" customHeight="1">
       <c r="A50" s="32"/>
       <c r="B50" s="11"/>
-      <c r="C50" s="20"/>
+      <c r="C50" s="77"/>
       <c r="D50" s="11"/>
       <c r="E50" s="50"/>
       <c r="F50" s="50"/>
@@ -42645,7 +42698,7 @@
     <row r="51" spans="1:12" ht="14.65" customHeight="1">
       <c r="A51" s="32"/>
       <c r="B51" s="11"/>
-      <c r="C51" s="20"/>
+      <c r="C51" s="77"/>
       <c r="D51" s="11"/>
       <c r="E51" s="50"/>
       <c r="F51" s="50"/>
@@ -42662,7 +42715,7 @@
     <row r="52" spans="1:12" ht="14.65" customHeight="1">
       <c r="A52" s="32"/>
       <c r="B52" s="11"/>
-      <c r="C52" s="20"/>
+      <c r="C52" s="77"/>
       <c r="D52" s="11"/>
       <c r="E52" s="50"/>
       <c r="F52" s="50"/>
@@ -42679,7 +42732,7 @@
     <row r="53" spans="1:12" ht="14.65" customHeight="1">
       <c r="A53" s="32"/>
       <c r="B53" s="11"/>
-      <c r="C53" s="20"/>
+      <c r="C53" s="77"/>
       <c r="D53" s="11"/>
       <c r="E53" s="50"/>
       <c r="F53" s="50"/>
@@ -42696,7 +42749,7 @@
     <row r="54" spans="1:12" ht="14.65" customHeight="1">
       <c r="A54" s="32"/>
       <c r="B54" s="11"/>
-      <c r="C54" s="20"/>
+      <c r="C54" s="77"/>
       <c r="D54" s="11"/>
       <c r="E54" s="50"/>
       <c r="F54" s="50"/>
@@ -42713,7 +42766,7 @@
     <row r="55" spans="1:12" ht="14.65" customHeight="1">
       <c r="A55" s="32"/>
       <c r="B55" s="11"/>
-      <c r="C55" s="20"/>
+      <c r="C55" s="77"/>
       <c r="D55" s="11"/>
       <c r="E55" s="50"/>
       <c r="F55" s="50"/>
@@ -42730,7 +42783,7 @@
     <row r="56" spans="1:12" ht="14.65" customHeight="1">
       <c r="A56" s="32"/>
       <c r="B56" s="11"/>
-      <c r="C56" s="20"/>
+      <c r="C56" s="77"/>
       <c r="D56" s="11"/>
       <c r="E56" s="50"/>
       <c r="F56" s="50"/>
@@ -42747,7 +42800,7 @@
     <row r="57" spans="1:12" ht="14.65" customHeight="1">
       <c r="A57" s="32"/>
       <c r="B57" s="11"/>
-      <c r="C57" s="20"/>
+      <c r="C57" s="77"/>
       <c r="D57" s="11"/>
       <c r="E57" s="50"/>
       <c r="F57" s="50"/>
@@ -42764,7 +42817,7 @@
     <row r="58" spans="1:12" ht="14.65" customHeight="1">
       <c r="A58" s="32"/>
       <c r="B58" s="11"/>
-      <c r="C58" s="20"/>
+      <c r="C58" s="77"/>
       <c r="D58" s="11"/>
       <c r="E58" s="50"/>
       <c r="F58" s="50"/>
@@ -42781,7 +42834,7 @@
     <row r="59" spans="1:12" ht="14.65" customHeight="1">
       <c r="A59" s="32"/>
       <c r="B59" s="11"/>
-      <c r="C59" s="20"/>
+      <c r="C59" s="77"/>
       <c r="D59" s="11"/>
       <c r="E59" s="50"/>
       <c r="F59" s="50"/>
@@ -42798,7 +42851,7 @@
     <row r="60" spans="1:12" ht="14.65" customHeight="1">
       <c r="A60" s="32"/>
       <c r="B60" s="11"/>
-      <c r="C60" s="20"/>
+      <c r="C60" s="77"/>
       <c r="D60" s="11"/>
       <c r="E60" s="50"/>
       <c r="F60" s="50"/>
@@ -42815,7 +42868,7 @@
     <row r="61" spans="1:12" ht="14.65" customHeight="1">
       <c r="A61" s="32"/>
       <c r="B61" s="11"/>
-      <c r="C61" s="20"/>
+      <c r="C61" s="77"/>
       <c r="D61" s="11"/>
       <c r="E61" s="50"/>
       <c r="F61" s="50"/>
@@ -42832,7 +42885,7 @@
     <row r="62" spans="1:12" ht="14.65" customHeight="1">
       <c r="A62" s="32"/>
       <c r="B62" s="11"/>
-      <c r="C62" s="20"/>
+      <c r="C62" s="77"/>
       <c r="D62" s="11"/>
       <c r="E62" s="50"/>
       <c r="F62" s="50"/>
@@ -42849,7 +42902,7 @@
     <row r="63" spans="1:12" ht="14.65" customHeight="1">
       <c r="A63" s="32"/>
       <c r="B63" s="11"/>
-      <c r="C63" s="20"/>
+      <c r="C63" s="77"/>
       <c r="D63" s="11"/>
       <c r="E63" s="50"/>
       <c r="F63" s="50"/>
@@ -42866,7 +42919,7 @@
     <row r="64" spans="1:12" ht="14.65" customHeight="1">
       <c r="A64" s="32"/>
       <c r="B64" s="11"/>
-      <c r="C64" s="20"/>
+      <c r="C64" s="77"/>
       <c r="D64" s="11"/>
       <c r="E64" s="50"/>
       <c r="F64" s="50"/>
@@ -42883,7 +42936,7 @@
     <row r="65" spans="1:12" ht="14.65" customHeight="1">
       <c r="A65" s="32"/>
       <c r="B65" s="11"/>
-      <c r="C65" s="20"/>
+      <c r="C65" s="77"/>
       <c r="D65" s="11"/>
       <c r="E65" s="50"/>
       <c r="F65" s="50"/>
@@ -42900,7 +42953,7 @@
     <row r="66" spans="1:12" ht="14.65" customHeight="1">
       <c r="A66" s="32"/>
       <c r="B66" s="11"/>
-      <c r="C66" s="20"/>
+      <c r="C66" s="77"/>
       <c r="D66" s="11"/>
       <c r="E66" s="50"/>
       <c r="F66" s="50"/>
@@ -42917,7 +42970,7 @@
     <row r="67" spans="1:12" ht="14.65" customHeight="1">
       <c r="A67" s="32"/>
       <c r="B67" s="11"/>
-      <c r="C67" s="20"/>
+      <c r="C67" s="77"/>
       <c r="D67" s="11"/>
       <c r="E67" s="50"/>
       <c r="F67" s="50"/>
@@ -42934,7 +42987,7 @@
     <row r="68" spans="1:12" ht="14.65" customHeight="1">
       <c r="A68" s="32"/>
       <c r="B68" s="11"/>
-      <c r="C68" s="20"/>
+      <c r="C68" s="77"/>
       <c r="D68" s="11"/>
       <c r="E68" s="50"/>
       <c r="F68" s="50"/>
@@ -42951,7 +43004,7 @@
     <row r="69" spans="1:12" ht="14.65" customHeight="1">
       <c r="A69" s="32"/>
       <c r="B69" s="11"/>
-      <c r="C69" s="20"/>
+      <c r="C69" s="77"/>
       <c r="D69" s="11"/>
       <c r="E69" s="50"/>
       <c r="F69" s="50"/>
@@ -42968,7 +43021,7 @@
     <row r="70" spans="1:12" ht="14.65" customHeight="1">
       <c r="A70" s="32"/>
       <c r="B70" s="11"/>
-      <c r="C70" s="20"/>
+      <c r="C70" s="77"/>
       <c r="D70" s="11"/>
       <c r="E70" s="50"/>
       <c r="F70" s="50"/>
@@ -42985,7 +43038,7 @@
     <row r="71" spans="1:12" ht="14.65" customHeight="1">
       <c r="A71" s="32"/>
       <c r="B71" s="11"/>
-      <c r="C71" s="20"/>
+      <c r="C71" s="77"/>
       <c r="D71" s="11"/>
       <c r="E71" s="50"/>
       <c r="F71" s="50"/>
@@ -43002,7 +43055,7 @@
     <row r="72" spans="1:12" ht="14.65" customHeight="1">
       <c r="A72" s="32"/>
       <c r="B72" s="11"/>
-      <c r="C72" s="20"/>
+      <c r="C72" s="77"/>
       <c r="D72" s="11"/>
       <c r="E72" s="50"/>
       <c r="F72" s="50"/>
@@ -43019,7 +43072,7 @@
     <row r="73" spans="1:12" ht="14.65" customHeight="1">
       <c r="A73" s="32"/>
       <c r="B73" s="11"/>
-      <c r="C73" s="20"/>
+      <c r="C73" s="77"/>
       <c r="D73" s="11"/>
       <c r="E73" s="50"/>
       <c r="F73" s="50"/>
@@ -43036,7 +43089,7 @@
     <row r="74" spans="1:12" ht="14.65" customHeight="1">
       <c r="A74" s="32"/>
       <c r="B74" s="11"/>
-      <c r="C74" s="20"/>
+      <c r="C74" s="77"/>
       <c r="D74" s="11"/>
       <c r="E74" s="50"/>
       <c r="F74" s="50"/>
@@ -43053,7 +43106,7 @@
     <row r="75" spans="1:12" ht="14.65" customHeight="1">
       <c r="A75" s="32"/>
       <c r="B75" s="11"/>
-      <c r="C75" s="20"/>
+      <c r="C75" s="77"/>
       <c r="D75" s="11"/>
       <c r="E75" s="50"/>
       <c r="F75" s="50"/>
@@ -43070,7 +43123,7 @@
     <row r="76" spans="1:12" ht="14.65" customHeight="1">
       <c r="A76" s="32"/>
       <c r="B76" s="11"/>
-      <c r="C76" s="20"/>
+      <c r="C76" s="77"/>
       <c r="D76" s="11"/>
       <c r="E76" s="50"/>
       <c r="F76" s="50"/>
@@ -43087,7 +43140,7 @@
     <row r="77" spans="1:12" ht="14.65" customHeight="1">
       <c r="A77" s="32"/>
       <c r="B77" s="11"/>
-      <c r="C77" s="20"/>
+      <c r="C77" s="77"/>
       <c r="D77" s="11"/>
       <c r="E77" s="50"/>
       <c r="F77" s="50"/>
@@ -43104,7 +43157,7 @@
     <row r="78" spans="1:12" ht="14.65" customHeight="1">
       <c r="A78" s="32"/>
       <c r="B78" s="11"/>
-      <c r="C78" s="20"/>
+      <c r="C78" s="77"/>
       <c r="D78" s="11"/>
       <c r="E78" s="50"/>
       <c r="F78" s="50"/>
@@ -43121,7 +43174,7 @@
     <row r="79" spans="1:12" ht="14.65" customHeight="1">
       <c r="A79" s="32"/>
       <c r="B79" s="11"/>
-      <c r="C79" s="20"/>
+      <c r="C79" s="77"/>
       <c r="D79" s="11"/>
       <c r="E79" s="50"/>
       <c r="F79" s="50"/>
@@ -43138,7 +43191,7 @@
     <row r="80" spans="1:12" ht="14.65" customHeight="1">
       <c r="A80" s="32"/>
       <c r="B80" s="11"/>
-      <c r="C80" s="20"/>
+      <c r="C80" s="77"/>
       <c r="D80" s="11"/>
       <c r="E80" s="50"/>
       <c r="F80" s="50"/>
@@ -43155,7 +43208,7 @@
     <row r="81" spans="1:12" ht="14.65" customHeight="1">
       <c r="A81" s="32"/>
       <c r="B81" s="11"/>
-      <c r="C81" s="20"/>
+      <c r="C81" s="77"/>
       <c r="D81" s="11"/>
       <c r="E81" s="50"/>
       <c r="F81" s="50"/>
@@ -43172,7 +43225,7 @@
     <row r="82" spans="1:12" ht="14.65" customHeight="1">
       <c r="A82" s="32"/>
       <c r="B82" s="11"/>
-      <c r="C82" s="20"/>
+      <c r="C82" s="77"/>
       <c r="D82" s="11"/>
       <c r="E82" s="50"/>
       <c r="F82" s="50"/>
@@ -43189,7 +43242,7 @@
     <row r="83" spans="1:12" ht="14.65" customHeight="1">
       <c r="A83" s="32"/>
       <c r="B83" s="11"/>
-      <c r="C83" s="20"/>
+      <c r="C83" s="77"/>
       <c r="D83" s="11"/>
       <c r="E83" s="50"/>
       <c r="F83" s="50"/>
@@ -43206,7 +43259,7 @@
     <row r="84" spans="1:12" ht="14.65" customHeight="1">
       <c r="A84" s="32"/>
       <c r="B84" s="11"/>
-      <c r="C84" s="20"/>
+      <c r="C84" s="77"/>
       <c r="D84" s="11"/>
       <c r="E84" s="50"/>
       <c r="F84" s="50"/>
@@ -43223,7 +43276,7 @@
     <row r="85" spans="1:12" ht="14.65" customHeight="1">
       <c r="A85" s="32"/>
       <c r="B85" s="11"/>
-      <c r="C85" s="20"/>
+      <c r="C85" s="77"/>
       <c r="D85" s="11"/>
       <c r="E85" s="50"/>
       <c r="F85" s="50"/>
@@ -43240,7 +43293,7 @@
     <row r="86" spans="1:12" ht="14.65" customHeight="1">
       <c r="A86" s="32"/>
       <c r="B86" s="11"/>
-      <c r="C86" s="20"/>
+      <c r="C86" s="77"/>
       <c r="D86" s="11"/>
       <c r="E86" s="50"/>
       <c r="F86" s="50"/>
@@ -43257,7 +43310,7 @@
     <row r="87" spans="1:12" ht="14.65" customHeight="1">
       <c r="A87" s="32"/>
       <c r="B87" s="11"/>
-      <c r="C87" s="20"/>
+      <c r="C87" s="77"/>
       <c r="D87" s="11"/>
       <c r="E87" s="50"/>
       <c r="F87" s="50"/>
@@ -43274,7 +43327,7 @@
     <row r="88" spans="1:12" ht="14.65" customHeight="1">
       <c r="A88" s="32"/>
       <c r="B88" s="11"/>
-      <c r="C88" s="20"/>
+      <c r="C88" s="77"/>
       <c r="D88" s="11"/>
       <c r="E88" s="50"/>
       <c r="F88" s="50"/>
@@ -43291,7 +43344,7 @@
     <row r="89" spans="1:12" ht="14.65" customHeight="1">
       <c r="A89" s="32"/>
       <c r="B89" s="11"/>
-      <c r="C89" s="20"/>
+      <c r="C89" s="77"/>
       <c r="D89" s="11"/>
       <c r="E89" s="50"/>
       <c r="F89" s="50"/>
@@ -43308,7 +43361,7 @@
     <row r="90" spans="1:12" ht="14.65" customHeight="1">
       <c r="A90" s="32"/>
       <c r="B90" s="11"/>
-      <c r="C90" s="20"/>
+      <c r="C90" s="77"/>
       <c r="D90" s="11"/>
       <c r="E90" s="50"/>
       <c r="F90" s="50"/>
@@ -43325,7 +43378,7 @@
     <row r="91" spans="1:12" ht="14.65" customHeight="1">
       <c r="A91" s="32"/>
       <c r="B91" s="11"/>
-      <c r="C91" s="20"/>
+      <c r="C91" s="77"/>
       <c r="D91" s="11"/>
       <c r="E91" s="50"/>
       <c r="F91" s="50"/>
@@ -43342,7 +43395,7 @@
     <row r="92" spans="1:12" ht="14.65" customHeight="1">
       <c r="A92" s="32"/>
       <c r="B92" s="11"/>
-      <c r="C92" s="20"/>
+      <c r="C92" s="77"/>
       <c r="D92" s="11"/>
       <c r="E92" s="50"/>
       <c r="F92" s="50"/>
@@ -43359,7 +43412,7 @@
     <row r="93" spans="1:12" ht="14.65" customHeight="1">
       <c r="A93" s="32"/>
       <c r="B93" s="11"/>
-      <c r="C93" s="20"/>
+      <c r="C93" s="77"/>
       <c r="D93" s="11"/>
       <c r="E93" s="50"/>
       <c r="F93" s="50"/>
@@ -43376,7 +43429,7 @@
     <row r="94" spans="1:12" ht="14.65" customHeight="1">
       <c r="A94" s="32"/>
       <c r="B94" s="11"/>
-      <c r="C94" s="20"/>
+      <c r="C94" s="77"/>
       <c r="D94" s="11"/>
       <c r="E94" s="50"/>
       <c r="F94" s="50"/>
@@ -43393,7 +43446,7 @@
     <row r="95" spans="1:12" ht="14.65" customHeight="1">
       <c r="A95" s="32"/>
       <c r="B95" s="11"/>
-      <c r="C95" s="20"/>
+      <c r="C95" s="77"/>
       <c r="D95" s="11"/>
       <c r="E95" s="50"/>
       <c r="F95" s="50"/>
@@ -43410,7 +43463,7 @@
     <row r="96" spans="1:12" ht="14.65" customHeight="1">
       <c r="A96" s="32"/>
       <c r="B96" s="11"/>
-      <c r="C96" s="20"/>
+      <c r="C96" s="77"/>
       <c r="D96" s="11"/>
       <c r="E96" s="50"/>
       <c r="F96" s="50"/>
@@ -43427,7 +43480,7 @@
     <row r="97" spans="1:12" ht="14.65" customHeight="1">
       <c r="A97" s="32"/>
       <c r="B97" s="11"/>
-      <c r="C97" s="20"/>
+      <c r="C97" s="77"/>
       <c r="D97" s="11"/>
       <c r="E97" s="50"/>
       <c r="F97" s="50"/>
@@ -43444,7 +43497,7 @@
     <row r="98" spans="1:12" ht="14.65" customHeight="1">
       <c r="A98" s="32"/>
       <c r="B98" s="11"/>
-      <c r="C98" s="20"/>
+      <c r="C98" s="77"/>
       <c r="D98" s="11"/>
       <c r="E98" s="50"/>
       <c r="F98" s="50"/>
@@ -43461,7 +43514,7 @@
     <row r="99" spans="1:12" ht="14.65" customHeight="1">
       <c r="A99" s="32"/>
       <c r="B99" s="11"/>
-      <c r="C99" s="20"/>
+      <c r="C99" s="77"/>
       <c r="D99" s="11"/>
       <c r="E99" s="50"/>
       <c r="F99" s="50"/>
@@ -43478,7 +43531,7 @@
     <row r="100" spans="1:12" ht="14.65" customHeight="1">
       <c r="A100" s="32"/>
       <c r="B100" s="11"/>
-      <c r="C100" s="20"/>
+      <c r="C100" s="77"/>
       <c r="D100" s="11"/>
       <c r="E100" s="50"/>
       <c r="F100" s="50"/>
@@ -43495,7 +43548,7 @@
     <row r="101" spans="1:12" ht="14.65" customHeight="1">
       <c r="A101" s="32"/>
       <c r="B101" s="11"/>
-      <c r="C101" s="20"/>
+      <c r="C101" s="77"/>
       <c r="D101" s="11"/>
       <c r="E101" s="50"/>
       <c r="F101" s="50"/>
@@ -43512,7 +43565,7 @@
     <row r="102" spans="1:12" ht="14.65" customHeight="1">
       <c r="A102" s="32"/>
       <c r="B102" s="11"/>
-      <c r="C102" s="20"/>
+      <c r="C102" s="77"/>
       <c r="D102" s="11"/>
       <c r="E102" s="50"/>
       <c r="F102" s="50"/>
@@ -43529,7 +43582,7 @@
     <row r="103" spans="1:12" ht="14.65" customHeight="1">
       <c r="A103" s="32"/>
       <c r="B103" s="11"/>
-      <c r="C103" s="20"/>
+      <c r="C103" s="77"/>
       <c r="D103" s="11"/>
       <c r="E103" s="50"/>
       <c r="F103" s="50"/>
@@ -43546,7 +43599,7 @@
     <row r="104" spans="1:12" ht="14.65" customHeight="1">
       <c r="A104" s="32"/>
       <c r="B104" s="11"/>
-      <c r="C104" s="20"/>
+      <c r="C104" s="77"/>
       <c r="D104" s="11"/>
       <c r="E104" s="50"/>
       <c r="F104" s="50"/>
@@ -43563,7 +43616,7 @@
     <row r="105" spans="1:12" ht="14.65" customHeight="1">
       <c r="A105" s="33"/>
       <c r="B105" s="12"/>
-      <c r="C105" s="21"/>
+      <c r="C105" s="78"/>
       <c r="D105" s="12"/>
       <c r="E105" s="51"/>
       <c r="F105" s="51"/>
@@ -43675,40 +43728,40 @@
       <c r="N1" s="70"/>
     </row>
     <row r="2" spans="1:14" ht="17.399999999999999" customHeight="1">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
     </row>
     <row r="3" spans="1:14" ht="20" customHeight="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
     </row>
     <row r="5" spans="1:14" ht="28" customHeight="1">
       <c r="A5" s="1" t="s">

--- a/data/Template_Resmi_Database_SIRUMAH.xlsx
+++ b/data/Template_Resmi_Database_SIRUMAH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CB6B0F-9FAD-4678-B11B-54C031659249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F420E8-4E4D-4F74-A530-2B5B37DB0D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41911,9 +41911,7 @@
     <row r="6" spans="1:12" ht="14.65" customHeight="1">
       <c r="A6" s="31"/>
       <c r="B6" s="10"/>
-      <c r="C6" s="76">
-        <v>2026</v>
-      </c>
+      <c r="C6" s="76"/>
       <c r="D6" s="10" t="s">
         <v>921</v>
       </c>
@@ -42020,7 +42018,9 @@
       <c r="B11" s="11"/>
       <c r="C11" s="77"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="50"/>
+      <c r="E11" s="50">
+        <v>350000000</v>
+      </c>
       <c r="F11" s="50"/>
       <c r="G11" s="26" t="str">
         <f t="shared" si="0"/>

--- a/data/Template_Resmi_Database_SIRUMAH.xlsx
+++ b/data/Template_Resmi_Database_SIRUMAH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\inovasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16125139-A2DE-478E-8512-CB71557A328C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD98D161-FEF2-4B4A-9864-D8F70D61174F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42035,9 +42035,7 @@
       <c r="D6" s="79" t="s">
         <v>918</v>
       </c>
-      <c r="E6" s="82">
-        <v>350000000</v>
-      </c>
+      <c r="E6" s="82"/>
       <c r="F6" s="82">
         <v>15850000</v>
       </c>
@@ -42047,7 +42045,7 @@
       </c>
       <c r="H6" s="84">
         <f t="shared" ref="H6:H69" si="1">IF(A6="","",IFERROR(G6/E6,0))</f>
-        <v>4.5285714285714283E-2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="79" t="s">
         <v>930</v>
@@ -42072,9 +42070,7 @@
       <c r="D7" s="79" t="s">
         <v>919</v>
       </c>
-      <c r="E7" s="82">
-        <v>350000000</v>
-      </c>
+      <c r="E7" s="82"/>
       <c r="F7" s="82">
         <v>13675000</v>
       </c>
@@ -42084,7 +42080,7 @@
       </c>
       <c r="H7" s="84">
         <f t="shared" si="1"/>
-        <v>8.4357142857142853E-2</v>
+        <v>0</v>
       </c>
       <c r="I7" s="79" t="s">
         <v>930</v>
@@ -42107,9 +42103,7 @@
       <c r="D8" s="79" t="s">
         <v>920</v>
       </c>
-      <c r="E8" s="82">
-        <v>350000000</v>
-      </c>
+      <c r="E8" s="82"/>
       <c r="F8" s="82">
         <v>24950000</v>
       </c>
@@ -42119,7 +42113,7 @@
       </c>
       <c r="H8" s="84">
         <f t="shared" si="1"/>
-        <v>0.15564285714285714</v>
+        <v>0</v>
       </c>
       <c r="I8" s="79" t="s">
         <v>930</v>
@@ -42142,9 +42136,7 @@
       <c r="D9" s="79" t="s">
         <v>921</v>
       </c>
-      <c r="E9" s="82">
-        <v>350000000</v>
-      </c>
+      <c r="E9" s="82"/>
       <c r="F9" s="82">
         <v>32950000</v>
       </c>
@@ -42154,7 +42146,7 @@
       </c>
       <c r="H9" s="84">
         <f t="shared" si="1"/>
-        <v>0.24978571428571428</v>
+        <v>0</v>
       </c>
       <c r="I9" s="79" t="s">
         <v>930</v>
@@ -42177,9 +42169,7 @@
       <c r="D10" s="79" t="s">
         <v>922</v>
       </c>
-      <c r="E10" s="82">
-        <v>350000000</v>
-      </c>
+      <c r="E10" s="82"/>
       <c r="F10" s="82">
         <v>32950000</v>
       </c>
@@ -42189,7 +42179,7 @@
       </c>
       <c r="H10" s="84">
         <f t="shared" si="1"/>
-        <v>0.34392857142857142</v>
+        <v>0</v>
       </c>
       <c r="I10" s="79" t="s">
         <v>930</v>

--- a/data/Template_Resmi_Database_SIRUMAH.xlsx
+++ b/data/Template_Resmi_Database_SIRUMAH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F925EC14-A79B-4B2E-B2EB-500DA69917D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D5410C-C2FE-4FB3-B494-7432B8D3FF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PERUMAHAN" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4750" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5365" uniqueCount="976">
   <si>
     <t>TEMPLATE RESMI DATABASE SIRUMAH — DATA PERUMAHAN</t>
   </si>
@@ -2931,7 +2931,40 @@
     <t>Rusak Sedang</t>
   </si>
   <si>
-    <t>C</t>
+    <t>BLOK C</t>
+  </si>
+  <si>
+    <t>Atap dan talang</t>
+  </si>
+  <si>
+    <t>Air bersih</t>
+  </si>
+  <si>
+    <t>Listrik koridor</t>
+  </si>
+  <si>
+    <t>Drainase lingkungan</t>
+  </si>
+  <si>
+    <t>IPAL / septic tank</t>
+  </si>
+  <si>
+    <t>Tangga dan railing</t>
+  </si>
+  <si>
+    <t>Area parkir</t>
+  </si>
+  <si>
+    <t>Gangguan Ringan</t>
+  </si>
+  <si>
+    <t>Rendah</t>
+  </si>
+  <si>
+    <t>Sedang</t>
+  </si>
+  <si>
+    <t>BLOK D</t>
   </si>
 </sst>
 </file>
@@ -41539,13 +41572,25 @@
     </row>
     <row r="105" spans="1:14" ht="9.75" customHeight="1">
       <c r="A105" s="32"/>
-      <c r="B105" s="11"/>
-      <c r="C105" s="11"/>
-      <c r="D105" s="20"/>
-      <c r="E105" s="47"/>
+      <c r="B105" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D105" s="20" t="s">
+        <v>936</v>
+      </c>
+      <c r="E105" s="47" t="s">
+        <v>858</v>
+      </c>
       <c r="F105" s="6"/>
-      <c r="G105" s="11"/>
-      <c r="H105" s="11"/>
+      <c r="G105" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H105" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I105" s="6"/>
       <c r="J105" s="20"/>
       <c r="K105" s="11"/>
@@ -41555,13 +41600,25 @@
     </row>
     <row r="106" spans="1:14" ht="9.75" customHeight="1">
       <c r="A106" s="32"/>
-      <c r="B106" s="11"/>
-      <c r="C106" s="11"/>
-      <c r="D106" s="20"/>
-      <c r="E106" s="47"/>
+      <c r="B106" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D106" s="20" t="s">
+        <v>936</v>
+      </c>
+      <c r="E106" s="47" t="s">
+        <v>862</v>
+      </c>
       <c r="F106" s="6"/>
-      <c r="G106" s="11"/>
-      <c r="H106" s="11"/>
+      <c r="G106" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H106" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I106" s="6"/>
       <c r="J106" s="20"/>
       <c r="K106" s="11"/>
@@ -41571,13 +41628,25 @@
     </row>
     <row r="107" spans="1:14" ht="9.75" customHeight="1">
       <c r="A107" s="32"/>
-      <c r="B107" s="11"/>
-      <c r="C107" s="11"/>
-      <c r="D107" s="20"/>
-      <c r="E107" s="47"/>
+      <c r="B107" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D107" s="20" t="s">
+        <v>936</v>
+      </c>
+      <c r="E107" s="47" t="s">
+        <v>863</v>
+      </c>
       <c r="F107" s="6"/>
-      <c r="G107" s="11"/>
-      <c r="H107" s="11"/>
+      <c r="G107" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H107" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I107" s="6"/>
       <c r="J107" s="20"/>
       <c r="K107" s="11"/>
@@ -41587,13 +41656,25 @@
     </row>
     <row r="108" spans="1:14" ht="9.75" customHeight="1">
       <c r="A108" s="32"/>
-      <c r="B108" s="11"/>
-      <c r="C108" s="11"/>
-      <c r="D108" s="20"/>
-      <c r="E108" s="47"/>
+      <c r="B108" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D108" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E108" s="47" t="s">
+        <v>858</v>
+      </c>
       <c r="F108" s="6"/>
-      <c r="G108" s="11"/>
-      <c r="H108" s="11"/>
+      <c r="G108" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H108" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I108" s="6"/>
       <c r="J108" s="20"/>
       <c r="K108" s="11"/>
@@ -41603,13 +41684,25 @@
     </row>
     <row r="109" spans="1:14" ht="9.75" customHeight="1">
       <c r="A109" s="32"/>
-      <c r="B109" s="11"/>
-      <c r="C109" s="11"/>
-      <c r="D109" s="20"/>
-      <c r="E109" s="47"/>
+      <c r="B109" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D109" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E109" s="47" t="s">
+        <v>862</v>
+      </c>
       <c r="F109" s="6"/>
-      <c r="G109" s="11"/>
-      <c r="H109" s="11"/>
+      <c r="G109" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H109" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I109" s="6"/>
       <c r="J109" s="20"/>
       <c r="K109" s="11"/>
@@ -41619,13 +41712,25 @@
     </row>
     <row r="110" spans="1:14" ht="9.75" customHeight="1">
       <c r="A110" s="32"/>
-      <c r="B110" s="11"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="20"/>
-      <c r="E110" s="47"/>
+      <c r="B110" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D110" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E110" s="47" t="s">
+        <v>863</v>
+      </c>
       <c r="F110" s="6"/>
-      <c r="G110" s="11"/>
-      <c r="H110" s="11"/>
+      <c r="G110" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H110" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I110" s="6"/>
       <c r="J110" s="20"/>
       <c r="K110" s="11"/>
@@ -41635,13 +41740,25 @@
     </row>
     <row r="111" spans="1:14" ht="9.75" customHeight="1">
       <c r="A111" s="32"/>
-      <c r="B111" s="11"/>
-      <c r="C111" s="11"/>
-      <c r="D111" s="20"/>
-      <c r="E111" s="47"/>
+      <c r="B111" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D111" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E111" s="47" t="s">
+        <v>865</v>
+      </c>
       <c r="F111" s="6"/>
-      <c r="G111" s="11"/>
-      <c r="H111" s="11"/>
+      <c r="G111" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H111" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I111" s="6"/>
       <c r="J111" s="20"/>
       <c r="K111" s="11"/>
@@ -41651,13 +41768,25 @@
     </row>
     <row r="112" spans="1:14" ht="9.75" customHeight="1">
       <c r="A112" s="32"/>
-      <c r="B112" s="11"/>
-      <c r="C112" s="11"/>
-      <c r="D112" s="20"/>
-      <c r="E112" s="47"/>
+      <c r="B112" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D112" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E112" s="47" t="s">
+        <v>866</v>
+      </c>
       <c r="F112" s="6"/>
-      <c r="G112" s="11"/>
-      <c r="H112" s="11"/>
+      <c r="G112" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H112" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I112" s="6"/>
       <c r="J112" s="20"/>
       <c r="K112" s="11"/>
@@ -41667,13 +41796,25 @@
     </row>
     <row r="113" spans="1:14" ht="9.75" customHeight="1">
       <c r="A113" s="32"/>
-      <c r="B113" s="11"/>
-      <c r="C113" s="11"/>
-      <c r="D113" s="20"/>
-      <c r="E113" s="47"/>
+      <c r="B113" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D113" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E113" s="47" t="s">
+        <v>867</v>
+      </c>
       <c r="F113" s="6"/>
-      <c r="G113" s="11"/>
-      <c r="H113" s="11"/>
+      <c r="G113" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="H113" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I113" s="6"/>
       <c r="J113" s="20"/>
       <c r="K113" s="11"/>
@@ -41683,13 +41824,25 @@
     </row>
     <row r="114" spans="1:14" ht="9.75" customHeight="1">
       <c r="A114" s="32"/>
-      <c r="B114" s="11"/>
-      <c r="C114" s="11"/>
-      <c r="D114" s="20"/>
-      <c r="E114" s="47"/>
+      <c r="B114" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D114" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E114" s="47" t="s">
+        <v>868</v>
+      </c>
       <c r="F114" s="6"/>
-      <c r="G114" s="11"/>
-      <c r="H114" s="11"/>
+      <c r="G114" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H114" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I114" s="6"/>
       <c r="J114" s="20"/>
       <c r="K114" s="11"/>
@@ -41699,13 +41852,25 @@
     </row>
     <row r="115" spans="1:14" ht="9.75" customHeight="1">
       <c r="A115" s="32"/>
-      <c r="B115" s="11"/>
-      <c r="C115" s="11"/>
-      <c r="D115" s="20"/>
-      <c r="E115" s="47"/>
+      <c r="B115" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D115" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E115" s="47" t="s">
+        <v>869</v>
+      </c>
       <c r="F115" s="6"/>
-      <c r="G115" s="11"/>
-      <c r="H115" s="11"/>
+      <c r="G115" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H115" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I115" s="6"/>
       <c r="J115" s="20"/>
       <c r="K115" s="11"/>
@@ -41715,13 +41880,25 @@
     </row>
     <row r="116" spans="1:14" ht="9.75" customHeight="1">
       <c r="A116" s="32"/>
-      <c r="B116" s="11"/>
-      <c r="C116" s="11"/>
-      <c r="D116" s="20"/>
-      <c r="E116" s="47"/>
+      <c r="B116" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D116" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E116" s="47" t="s">
+        <v>938</v>
+      </c>
       <c r="F116" s="6"/>
-      <c r="G116" s="11"/>
-      <c r="H116" s="11"/>
+      <c r="G116" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H116" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I116" s="6"/>
       <c r="J116" s="20"/>
       <c r="K116" s="11"/>
@@ -41731,13 +41908,25 @@
     </row>
     <row r="117" spans="1:14" ht="9.75" customHeight="1">
       <c r="A117" s="32"/>
-      <c r="B117" s="11"/>
-      <c r="C117" s="11"/>
-      <c r="D117" s="20"/>
-      <c r="E117" s="47"/>
+      <c r="B117" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D117" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E117" s="47" t="s">
+        <v>939</v>
+      </c>
       <c r="F117" s="6"/>
-      <c r="G117" s="11"/>
-      <c r="H117" s="11"/>
+      <c r="G117" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H117" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I117" s="6"/>
       <c r="J117" s="20"/>
       <c r="K117" s="11"/>
@@ -41747,13 +41936,25 @@
     </row>
     <row r="118" spans="1:14" ht="9.75" customHeight="1">
       <c r="A118" s="32"/>
-      <c r="B118" s="11"/>
-      <c r="C118" s="11"/>
-      <c r="D118" s="20"/>
-      <c r="E118" s="47"/>
+      <c r="B118" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D118" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E118" s="47" t="s">
+        <v>940</v>
+      </c>
       <c r="F118" s="6"/>
-      <c r="G118" s="11"/>
-      <c r="H118" s="11"/>
+      <c r="G118" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H118" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I118" s="6"/>
       <c r="J118" s="20"/>
       <c r="K118" s="11"/>
@@ -41763,13 +41964,25 @@
     </row>
     <row r="119" spans="1:14" ht="9.75" customHeight="1">
       <c r="A119" s="32"/>
-      <c r="B119" s="11"/>
-      <c r="C119" s="11"/>
-      <c r="D119" s="20"/>
-      <c r="E119" s="47"/>
+      <c r="B119" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D119" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E119" s="47" t="s">
+        <v>941</v>
+      </c>
       <c r="F119" s="6"/>
-      <c r="G119" s="11"/>
-      <c r="H119" s="11"/>
+      <c r="G119" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H119" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I119" s="6"/>
       <c r="J119" s="20"/>
       <c r="K119" s="11"/>
@@ -41779,13 +41992,25 @@
     </row>
     <row r="120" spans="1:14" ht="9.75" customHeight="1">
       <c r="A120" s="32"/>
-      <c r="B120" s="11"/>
-      <c r="C120" s="11"/>
-      <c r="D120" s="20"/>
-      <c r="E120" s="47"/>
+      <c r="B120" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D120" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E120" s="47" t="s">
+        <v>942</v>
+      </c>
       <c r="F120" s="6"/>
-      <c r="G120" s="11"/>
-      <c r="H120" s="11"/>
+      <c r="G120" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="H120" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I120" s="6"/>
       <c r="J120" s="20"/>
       <c r="K120" s="11"/>
@@ -41795,13 +42020,25 @@
     </row>
     <row r="121" spans="1:14" ht="9.75" customHeight="1">
       <c r="A121" s="32"/>
-      <c r="B121" s="11"/>
-      <c r="C121" s="11"/>
-      <c r="D121" s="20"/>
-      <c r="E121" s="47"/>
+      <c r="B121" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D121" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E121" s="47" t="s">
+        <v>943</v>
+      </c>
       <c r="F121" s="6"/>
-      <c r="G121" s="11"/>
-      <c r="H121" s="11"/>
+      <c r="G121" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H121" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I121" s="6"/>
       <c r="J121" s="20"/>
       <c r="K121" s="11"/>
@@ -41811,13 +42048,25 @@
     </row>
     <row r="122" spans="1:14" ht="9.75" customHeight="1">
       <c r="A122" s="32"/>
-      <c r="B122" s="11"/>
-      <c r="C122" s="11"/>
-      <c r="D122" s="20"/>
-      <c r="E122" s="47"/>
+      <c r="B122" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D122" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E122" s="47" t="s">
+        <v>944</v>
+      </c>
       <c r="F122" s="6"/>
-      <c r="G122" s="11"/>
-      <c r="H122" s="11"/>
+      <c r="G122" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H122" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I122" s="6"/>
       <c r="J122" s="20"/>
       <c r="K122" s="11"/>
@@ -41827,13 +42076,25 @@
     </row>
     <row r="123" spans="1:14" ht="9.75" customHeight="1">
       <c r="A123" s="32"/>
-      <c r="B123" s="11"/>
-      <c r="C123" s="11"/>
-      <c r="D123" s="20"/>
-      <c r="E123" s="47"/>
+      <c r="B123" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C123" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D123" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E123" s="47" t="s">
+        <v>945</v>
+      </c>
       <c r="F123" s="6"/>
-      <c r="G123" s="11"/>
-      <c r="H123" s="11"/>
+      <c r="G123" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H123" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I123" s="6"/>
       <c r="J123" s="20"/>
       <c r="K123" s="11"/>
@@ -41843,13 +42104,25 @@
     </row>
     <row r="124" spans="1:14" ht="9.75" customHeight="1">
       <c r="A124" s="32"/>
-      <c r="B124" s="11"/>
-      <c r="C124" s="11"/>
-      <c r="D124" s="20"/>
-      <c r="E124" s="47"/>
+      <c r="B124" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D124" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E124" s="47" t="s">
+        <v>946</v>
+      </c>
       <c r="F124" s="6"/>
-      <c r="G124" s="11"/>
-      <c r="H124" s="11"/>
+      <c r="G124" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="H124" s="11" t="s">
+        <v>963</v>
+      </c>
       <c r="I124" s="6"/>
       <c r="J124" s="20"/>
       <c r="K124" s="11"/>
@@ -41859,13 +42132,25 @@
     </row>
     <row r="125" spans="1:14" ht="9.75" customHeight="1">
       <c r="A125" s="32"/>
-      <c r="B125" s="11"/>
-      <c r="C125" s="11"/>
-      <c r="D125" s="20"/>
-      <c r="E125" s="47"/>
+      <c r="B125" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C125" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D125" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E125" s="47" t="s">
+        <v>947</v>
+      </c>
       <c r="F125" s="6"/>
-      <c r="G125" s="11"/>
-      <c r="H125" s="11"/>
+      <c r="G125" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H125" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I125" s="6"/>
       <c r="J125" s="20"/>
       <c r="K125" s="11"/>
@@ -41875,13 +42160,25 @@
     </row>
     <row r="126" spans="1:14" ht="9.75" customHeight="1">
       <c r="A126" s="32"/>
-      <c r="B126" s="11"/>
-      <c r="C126" s="11"/>
-      <c r="D126" s="20"/>
-      <c r="E126" s="47"/>
+      <c r="B126" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C126" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D126" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E126" s="47" t="s">
+        <v>948</v>
+      </c>
       <c r="F126" s="6"/>
-      <c r="G126" s="11"/>
-      <c r="H126" s="11"/>
+      <c r="G126" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H126" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I126" s="6"/>
       <c r="J126" s="20"/>
       <c r="K126" s="11"/>
@@ -41891,13 +42188,25 @@
     </row>
     <row r="127" spans="1:14" ht="9.75" customHeight="1">
       <c r="A127" s="32"/>
-      <c r="B127" s="11"/>
-      <c r="C127" s="11"/>
-      <c r="D127" s="20"/>
-      <c r="E127" s="47"/>
+      <c r="B127" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D127" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E127" s="47" t="s">
+        <v>949</v>
+      </c>
       <c r="F127" s="6"/>
-      <c r="G127" s="11"/>
-      <c r="H127" s="11"/>
+      <c r="G127" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H127" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I127" s="6"/>
       <c r="J127" s="20"/>
       <c r="K127" s="11"/>
@@ -41907,13 +42216,25 @@
     </row>
     <row r="128" spans="1:14" ht="9.75" customHeight="1">
       <c r="A128" s="32"/>
-      <c r="B128" s="11"/>
-      <c r="C128" s="11"/>
-      <c r="D128" s="20"/>
-      <c r="E128" s="47"/>
+      <c r="B128" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D128" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E128" s="47" t="s">
+        <v>950</v>
+      </c>
       <c r="F128" s="6"/>
-      <c r="G128" s="11"/>
-      <c r="H128" s="11"/>
+      <c r="G128" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H128" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I128" s="6"/>
       <c r="J128" s="20"/>
       <c r="K128" s="11"/>
@@ -41923,13 +42244,25 @@
     </row>
     <row r="129" spans="1:14" ht="9.75" customHeight="1">
       <c r="A129" s="32"/>
-      <c r="B129" s="11"/>
-      <c r="C129" s="11"/>
-      <c r="D129" s="20"/>
-      <c r="E129" s="47"/>
+      <c r="B129" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D129" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E129" s="47" t="s">
+        <v>951</v>
+      </c>
       <c r="F129" s="6"/>
-      <c r="G129" s="11"/>
-      <c r="H129" s="11"/>
+      <c r="G129" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H129" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I129" s="6"/>
       <c r="J129" s="20"/>
       <c r="K129" s="11"/>
@@ -41939,13 +42272,25 @@
     </row>
     <row r="130" spans="1:14" ht="9.75" customHeight="1">
       <c r="A130" s="32"/>
-      <c r="B130" s="11"/>
-      <c r="C130" s="11"/>
-      <c r="D130" s="20"/>
-      <c r="E130" s="47"/>
+      <c r="B130" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D130" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E130" s="47" t="s">
+        <v>952</v>
+      </c>
       <c r="F130" s="6"/>
-      <c r="G130" s="11"/>
-      <c r="H130" s="11"/>
+      <c r="G130" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H130" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I130" s="6"/>
       <c r="J130" s="20"/>
       <c r="K130" s="11"/>
@@ -41955,13 +42300,25 @@
     </row>
     <row r="131" spans="1:14" ht="9.75" customHeight="1">
       <c r="A131" s="32"/>
-      <c r="B131" s="11"/>
-      <c r="C131" s="11"/>
-      <c r="D131" s="20"/>
-      <c r="E131" s="47"/>
+      <c r="B131" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D131" s="20" t="s">
+        <v>937</v>
+      </c>
+      <c r="E131" s="47" t="s">
+        <v>953</v>
+      </c>
       <c r="F131" s="6"/>
-      <c r="G131" s="11"/>
-      <c r="H131" s="11"/>
+      <c r="G131" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H131" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I131" s="6"/>
       <c r="J131" s="20"/>
       <c r="K131" s="11"/>
@@ -41971,13 +42328,25 @@
     </row>
     <row r="132" spans="1:14" ht="9.75" customHeight="1">
       <c r="A132" s="32"/>
-      <c r="B132" s="11"/>
-      <c r="C132" s="11"/>
-      <c r="D132" s="20"/>
-      <c r="E132" s="47"/>
+      <c r="B132" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D132" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E132" s="47" t="s">
+        <v>858</v>
+      </c>
       <c r="F132" s="6"/>
-      <c r="G132" s="11"/>
-      <c r="H132" s="11"/>
+      <c r="G132" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H132" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I132" s="6"/>
       <c r="J132" s="20"/>
       <c r="K132" s="11"/>
@@ -41987,13 +42356,25 @@
     </row>
     <row r="133" spans="1:14" ht="9.75" customHeight="1">
       <c r="A133" s="32"/>
-      <c r="B133" s="11"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="20"/>
-      <c r="E133" s="47"/>
+      <c r="B133" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C133" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D133" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E133" s="47" t="s">
+        <v>862</v>
+      </c>
       <c r="F133" s="6"/>
-      <c r="G133" s="11"/>
-      <c r="H133" s="11"/>
+      <c r="G133" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H133" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I133" s="6"/>
       <c r="J133" s="20"/>
       <c r="K133" s="11"/>
@@ -42003,13 +42384,25 @@
     </row>
     <row r="134" spans="1:14" ht="9.75" customHeight="1">
       <c r="A134" s="32"/>
-      <c r="B134" s="11"/>
-      <c r="C134" s="11"/>
-      <c r="D134" s="20"/>
-      <c r="E134" s="47"/>
+      <c r="B134" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D134" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E134" s="47" t="s">
+        <v>863</v>
+      </c>
       <c r="F134" s="6"/>
-      <c r="G134" s="11"/>
-      <c r="H134" s="11"/>
+      <c r="G134" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H134" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I134" s="6"/>
       <c r="J134" s="20"/>
       <c r="K134" s="11"/>
@@ -42019,13 +42412,25 @@
     </row>
     <row r="135" spans="1:14" ht="9.75" customHeight="1">
       <c r="A135" s="32"/>
-      <c r="B135" s="11"/>
-      <c r="C135" s="11"/>
-      <c r="D135" s="20"/>
-      <c r="E135" s="47"/>
+      <c r="B135" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C135" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D135" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E135" s="47" t="s">
+        <v>865</v>
+      </c>
       <c r="F135" s="6"/>
-      <c r="G135" s="11"/>
-      <c r="H135" s="11"/>
+      <c r="G135" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H135" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I135" s="6"/>
       <c r="J135" s="20"/>
       <c r="K135" s="11"/>
@@ -42035,13 +42440,25 @@
     </row>
     <row r="136" spans="1:14" ht="9.75" customHeight="1">
       <c r="A136" s="32"/>
-      <c r="B136" s="11"/>
-      <c r="C136" s="11"/>
-      <c r="D136" s="20"/>
-      <c r="E136" s="47"/>
+      <c r="B136" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C136" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D136" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E136" s="47" t="s">
+        <v>866</v>
+      </c>
       <c r="F136" s="6"/>
-      <c r="G136" s="11"/>
-      <c r="H136" s="11"/>
+      <c r="G136" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H136" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I136" s="6"/>
       <c r="J136" s="20"/>
       <c r="K136" s="11"/>
@@ -42051,13 +42468,25 @@
     </row>
     <row r="137" spans="1:14" ht="9.75" customHeight="1">
       <c r="A137" s="32"/>
-      <c r="B137" s="11"/>
-      <c r="C137" s="11"/>
-      <c r="D137" s="20"/>
-      <c r="E137" s="47"/>
+      <c r="B137" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C137" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D137" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E137" s="47" t="s">
+        <v>867</v>
+      </c>
       <c r="F137" s="6"/>
-      <c r="G137" s="11"/>
-      <c r="H137" s="11"/>
+      <c r="G137" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H137" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I137" s="6"/>
       <c r="J137" s="20"/>
       <c r="K137" s="11"/>
@@ -42067,13 +42496,25 @@
     </row>
     <row r="138" spans="1:14" ht="9.75" customHeight="1">
       <c r="A138" s="32"/>
-      <c r="B138" s="11"/>
-      <c r="C138" s="11"/>
-      <c r="D138" s="20"/>
-      <c r="E138" s="47"/>
+      <c r="B138" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D138" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E138" s="47" t="s">
+        <v>868</v>
+      </c>
       <c r="F138" s="6"/>
-      <c r="G138" s="11"/>
-      <c r="H138" s="11"/>
+      <c r="G138" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H138" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I138" s="6"/>
       <c r="J138" s="20"/>
       <c r="K138" s="11"/>
@@ -42083,13 +42524,25 @@
     </row>
     <row r="139" spans="1:14" ht="9.75" customHeight="1">
       <c r="A139" s="32"/>
-      <c r="B139" s="11"/>
-      <c r="C139" s="11"/>
-      <c r="D139" s="20"/>
-      <c r="E139" s="47"/>
+      <c r="B139" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D139" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E139" s="47" t="s">
+        <v>869</v>
+      </c>
       <c r="F139" s="6"/>
-      <c r="G139" s="11"/>
-      <c r="H139" s="11"/>
+      <c r="G139" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H139" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I139" s="6"/>
       <c r="J139" s="20"/>
       <c r="K139" s="11"/>
@@ -42099,13 +42552,25 @@
     </row>
     <row r="140" spans="1:14" ht="9.75" customHeight="1">
       <c r="A140" s="32"/>
-      <c r="B140" s="11"/>
-      <c r="C140" s="11"/>
-      <c r="D140" s="20"/>
-      <c r="E140" s="47"/>
+      <c r="B140" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D140" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E140" s="47" t="s">
+        <v>938</v>
+      </c>
       <c r="F140" s="6"/>
-      <c r="G140" s="11"/>
-      <c r="H140" s="11"/>
+      <c r="G140" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H140" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I140" s="6"/>
       <c r="J140" s="20"/>
       <c r="K140" s="11"/>
@@ -42115,13 +42580,25 @@
     </row>
     <row r="141" spans="1:14" ht="9.75" customHeight="1">
       <c r="A141" s="32"/>
-      <c r="B141" s="11"/>
-      <c r="C141" s="11"/>
-      <c r="D141" s="20"/>
-      <c r="E141" s="47"/>
+      <c r="B141" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D141" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E141" s="47" t="s">
+        <v>939</v>
+      </c>
       <c r="F141" s="6"/>
-      <c r="G141" s="11"/>
-      <c r="H141" s="11"/>
+      <c r="G141" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H141" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I141" s="6"/>
       <c r="J141" s="20"/>
       <c r="K141" s="11"/>
@@ -42131,13 +42608,25 @@
     </row>
     <row r="142" spans="1:14" ht="9.75" customHeight="1">
       <c r="A142" s="32"/>
-      <c r="B142" s="11"/>
-      <c r="C142" s="11"/>
-      <c r="D142" s="20"/>
-      <c r="E142" s="47"/>
+      <c r="B142" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D142" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E142" s="47" t="s">
+        <v>940</v>
+      </c>
       <c r="F142" s="6"/>
-      <c r="G142" s="11"/>
-      <c r="H142" s="11"/>
+      <c r="G142" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H142" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I142" s="6"/>
       <c r="J142" s="20"/>
       <c r="K142" s="11"/>
@@ -42147,13 +42636,25 @@
     </row>
     <row r="143" spans="1:14" ht="9.75" customHeight="1">
       <c r="A143" s="32"/>
-      <c r="B143" s="11"/>
-      <c r="C143" s="11"/>
-      <c r="D143" s="20"/>
-      <c r="E143" s="47"/>
+      <c r="B143" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D143" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E143" s="47" t="s">
+        <v>941</v>
+      </c>
       <c r="F143" s="6"/>
-      <c r="G143" s="11"/>
-      <c r="H143" s="11"/>
+      <c r="G143" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H143" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I143" s="6"/>
       <c r="J143" s="20"/>
       <c r="K143" s="11"/>
@@ -42163,13 +42664,25 @@
     </row>
     <row r="144" spans="1:14" ht="9.75" customHeight="1">
       <c r="A144" s="32"/>
-      <c r="B144" s="11"/>
-      <c r="C144" s="11"/>
-      <c r="D144" s="20"/>
-      <c r="E144" s="47"/>
+      <c r="B144" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D144" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E144" s="47" t="s">
+        <v>942</v>
+      </c>
       <c r="F144" s="6"/>
-      <c r="G144" s="11"/>
-      <c r="H144" s="11"/>
+      <c r="G144" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H144" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I144" s="6"/>
       <c r="J144" s="20"/>
       <c r="K144" s="11"/>
@@ -42179,13 +42692,25 @@
     </row>
     <row r="145" spans="1:14" ht="9.75" customHeight="1">
       <c r="A145" s="32"/>
-      <c r="B145" s="11"/>
-      <c r="C145" s="11"/>
-      <c r="D145" s="20"/>
-      <c r="E145" s="47"/>
+      <c r="B145" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D145" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E145" s="47" t="s">
+        <v>943</v>
+      </c>
       <c r="F145" s="6"/>
-      <c r="G145" s="11"/>
-      <c r="H145" s="11"/>
+      <c r="G145" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H145" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I145" s="6"/>
       <c r="J145" s="20"/>
       <c r="K145" s="11"/>
@@ -42195,13 +42720,25 @@
     </row>
     <row r="146" spans="1:14" ht="9.75" customHeight="1">
       <c r="A146" s="32"/>
-      <c r="B146" s="11"/>
-      <c r="C146" s="11"/>
-      <c r="D146" s="20"/>
-      <c r="E146" s="47"/>
+      <c r="B146" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D146" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E146" s="47" t="s">
+        <v>944</v>
+      </c>
       <c r="F146" s="6"/>
-      <c r="G146" s="11"/>
-      <c r="H146" s="11"/>
+      <c r="G146" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="H146" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I146" s="6"/>
       <c r="J146" s="20"/>
       <c r="K146" s="11"/>
@@ -42211,13 +42748,25 @@
     </row>
     <row r="147" spans="1:14" ht="9.75" customHeight="1">
       <c r="A147" s="32"/>
-      <c r="B147" s="11"/>
-      <c r="C147" s="11"/>
-      <c r="D147" s="20"/>
-      <c r="E147" s="47"/>
+      <c r="B147" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D147" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E147" s="47" t="s">
+        <v>945</v>
+      </c>
       <c r="F147" s="6"/>
-      <c r="G147" s="11"/>
-      <c r="H147" s="11"/>
+      <c r="G147" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="H147" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I147" s="6"/>
       <c r="J147" s="20"/>
       <c r="K147" s="11"/>
@@ -42227,13 +42776,25 @@
     </row>
     <row r="148" spans="1:14" ht="9.75" customHeight="1">
       <c r="A148" s="32"/>
-      <c r="B148" s="11"/>
-      <c r="C148" s="11"/>
-      <c r="D148" s="20"/>
-      <c r="E148" s="47"/>
+      <c r="B148" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D148" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E148" s="47" t="s">
+        <v>946</v>
+      </c>
       <c r="F148" s="6"/>
-      <c r="G148" s="11"/>
-      <c r="H148" s="11"/>
+      <c r="G148" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H148" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I148" s="6"/>
       <c r="J148" s="20"/>
       <c r="K148" s="11"/>
@@ -42243,13 +42804,25 @@
     </row>
     <row r="149" spans="1:14" ht="9.75" customHeight="1">
       <c r="A149" s="32"/>
-      <c r="B149" s="11"/>
-      <c r="C149" s="11"/>
-      <c r="D149" s="20"/>
-      <c r="E149" s="47"/>
+      <c r="B149" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D149" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E149" s="47" t="s">
+        <v>947</v>
+      </c>
       <c r="F149" s="6"/>
-      <c r="G149" s="11"/>
-      <c r="H149" s="11"/>
+      <c r="G149" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H149" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I149" s="6"/>
       <c r="J149" s="20"/>
       <c r="K149" s="11"/>
@@ -42259,13 +42832,25 @@
     </row>
     <row r="150" spans="1:14" ht="9.75" customHeight="1">
       <c r="A150" s="32"/>
-      <c r="B150" s="11"/>
-      <c r="C150" s="11"/>
-      <c r="D150" s="20"/>
-      <c r="E150" s="47"/>
+      <c r="B150" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D150" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E150" s="47" t="s">
+        <v>948</v>
+      </c>
       <c r="F150" s="6"/>
-      <c r="G150" s="11"/>
-      <c r="H150" s="11"/>
+      <c r="G150" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H150" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I150" s="6"/>
       <c r="J150" s="20"/>
       <c r="K150" s="11"/>
@@ -42275,13 +42860,25 @@
     </row>
     <row r="151" spans="1:14" ht="9.75" customHeight="1">
       <c r="A151" s="32"/>
-      <c r="B151" s="11"/>
-      <c r="C151" s="11"/>
-      <c r="D151" s="20"/>
-      <c r="E151" s="47"/>
+      <c r="B151" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D151" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E151" s="47" t="s">
+        <v>949</v>
+      </c>
       <c r="F151" s="6"/>
-      <c r="G151" s="11"/>
-      <c r="H151" s="11"/>
+      <c r="G151" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H151" s="11" t="s">
+        <v>963</v>
+      </c>
       <c r="I151" s="6"/>
       <c r="J151" s="20"/>
       <c r="K151" s="11"/>
@@ -42291,13 +42888,25 @@
     </row>
     <row r="152" spans="1:14" ht="9.75" customHeight="1">
       <c r="A152" s="32"/>
-      <c r="B152" s="11"/>
-      <c r="C152" s="11"/>
-      <c r="D152" s="20"/>
-      <c r="E152" s="47"/>
+      <c r="B152" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C152" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D152" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E152" s="47" t="s">
+        <v>950</v>
+      </c>
       <c r="F152" s="6"/>
-      <c r="G152" s="11"/>
-      <c r="H152" s="11"/>
+      <c r="G152" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H152" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I152" s="6"/>
       <c r="J152" s="20"/>
       <c r="K152" s="11"/>
@@ -42307,13 +42916,25 @@
     </row>
     <row r="153" spans="1:14" ht="9.75" customHeight="1">
       <c r="A153" s="32"/>
-      <c r="B153" s="11"/>
-      <c r="C153" s="11"/>
-      <c r="D153" s="20"/>
-      <c r="E153" s="47"/>
+      <c r="B153" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C153" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D153" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E153" s="47" t="s">
+        <v>951</v>
+      </c>
       <c r="F153" s="6"/>
-      <c r="G153" s="11"/>
-      <c r="H153" s="11"/>
+      <c r="G153" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H153" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I153" s="6"/>
       <c r="J153" s="20"/>
       <c r="K153" s="11"/>
@@ -42323,13 +42944,25 @@
     </row>
     <row r="154" spans="1:14" ht="9.75" customHeight="1">
       <c r="A154" s="32"/>
-      <c r="B154" s="11"/>
-      <c r="C154" s="11"/>
-      <c r="D154" s="20"/>
-      <c r="E154" s="47"/>
+      <c r="B154" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D154" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E154" s="47" t="s">
+        <v>952</v>
+      </c>
       <c r="F154" s="6"/>
-      <c r="G154" s="11"/>
-      <c r="H154" s="11"/>
+      <c r="G154" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H154" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I154" s="6"/>
       <c r="J154" s="20"/>
       <c r="K154" s="11"/>
@@ -42339,13 +42972,25 @@
     </row>
     <row r="155" spans="1:14" ht="9.75" customHeight="1">
       <c r="A155" s="32"/>
-      <c r="B155" s="11"/>
-      <c r="C155" s="11"/>
-      <c r="D155" s="20"/>
-      <c r="E155" s="47"/>
+      <c r="B155" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D155" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="E155" s="47" t="s">
+        <v>953</v>
+      </c>
       <c r="F155" s="6"/>
-      <c r="G155" s="11"/>
-      <c r="H155" s="11"/>
+      <c r="G155" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H155" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I155" s="6"/>
       <c r="J155" s="20"/>
       <c r="K155" s="11"/>
@@ -42355,13 +43000,25 @@
     </row>
     <row r="156" spans="1:14" ht="9.75" customHeight="1">
       <c r="A156" s="32"/>
-      <c r="B156" s="11"/>
-      <c r="C156" s="11"/>
-      <c r="D156" s="20"/>
-      <c r="E156" s="47"/>
+      <c r="B156" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C156" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D156" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E156" s="47" t="s">
+        <v>858</v>
+      </c>
       <c r="F156" s="6"/>
-      <c r="G156" s="11"/>
-      <c r="H156" s="11"/>
+      <c r="G156" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H156" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I156" s="6"/>
       <c r="J156" s="20"/>
       <c r="K156" s="11"/>
@@ -42371,13 +43028,25 @@
     </row>
     <row r="157" spans="1:14" ht="9.75" customHeight="1">
       <c r="A157" s="32"/>
-      <c r="B157" s="11"/>
-      <c r="C157" s="11"/>
-      <c r="D157" s="20"/>
-      <c r="E157" s="47"/>
+      <c r="B157" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D157" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E157" s="47" t="s">
+        <v>862</v>
+      </c>
       <c r="F157" s="6"/>
-      <c r="G157" s="11"/>
-      <c r="H157" s="11"/>
+      <c r="G157" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H157" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I157" s="6"/>
       <c r="J157" s="20"/>
       <c r="K157" s="11"/>
@@ -42387,13 +43056,25 @@
     </row>
     <row r="158" spans="1:14" ht="9.75" customHeight="1">
       <c r="A158" s="32"/>
-      <c r="B158" s="11"/>
-      <c r="C158" s="11"/>
-      <c r="D158" s="20"/>
-      <c r="E158" s="47"/>
+      <c r="B158" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D158" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E158" s="47" t="s">
+        <v>863</v>
+      </c>
       <c r="F158" s="6"/>
-      <c r="G158" s="11"/>
-      <c r="H158" s="11"/>
+      <c r="G158" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H158" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I158" s="6"/>
       <c r="J158" s="20"/>
       <c r="K158" s="11"/>
@@ -42403,13 +43084,25 @@
     </row>
     <row r="159" spans="1:14" ht="9.75" customHeight="1">
       <c r="A159" s="32"/>
-      <c r="B159" s="11"/>
-      <c r="C159" s="11"/>
-      <c r="D159" s="20"/>
-      <c r="E159" s="47"/>
+      <c r="B159" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C159" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D159" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E159" s="47" t="s">
+        <v>865</v>
+      </c>
       <c r="F159" s="6"/>
-      <c r="G159" s="11"/>
-      <c r="H159" s="11"/>
+      <c r="G159" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="H159" s="11" t="s">
+        <v>963</v>
+      </c>
       <c r="I159" s="6"/>
       <c r="J159" s="20"/>
       <c r="K159" s="11"/>
@@ -42419,13 +43112,25 @@
     </row>
     <row r="160" spans="1:14" ht="9.75" customHeight="1">
       <c r="A160" s="32"/>
-      <c r="B160" s="11"/>
-      <c r="C160" s="11"/>
-      <c r="D160" s="20"/>
-      <c r="E160" s="47"/>
+      <c r="B160" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C160" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D160" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E160" s="47" t="s">
+        <v>866</v>
+      </c>
       <c r="F160" s="6"/>
-      <c r="G160" s="11"/>
-      <c r="H160" s="11"/>
+      <c r="G160" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H160" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I160" s="6"/>
       <c r="J160" s="20"/>
       <c r="K160" s="11"/>
@@ -42435,13 +43140,25 @@
     </row>
     <row r="161" spans="1:14" ht="9.75" customHeight="1">
       <c r="A161" s="32"/>
-      <c r="B161" s="11"/>
-      <c r="C161" s="11"/>
-      <c r="D161" s="20"/>
-      <c r="E161" s="47"/>
+      <c r="B161" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C161" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D161" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E161" s="47" t="s">
+        <v>867</v>
+      </c>
       <c r="F161" s="6"/>
-      <c r="G161" s="11"/>
-      <c r="H161" s="11"/>
+      <c r="G161" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H161" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I161" s="6"/>
       <c r="J161" s="20"/>
       <c r="K161" s="11"/>
@@ -42451,13 +43168,25 @@
     </row>
     <row r="162" spans="1:14" ht="9.75" customHeight="1">
       <c r="A162" s="32"/>
-      <c r="B162" s="11"/>
-      <c r="C162" s="11"/>
-      <c r="D162" s="20"/>
-      <c r="E162" s="47"/>
+      <c r="B162" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C162" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D162" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E162" s="47" t="s">
+        <v>868</v>
+      </c>
       <c r="F162" s="6"/>
-      <c r="G162" s="11"/>
-      <c r="H162" s="11"/>
+      <c r="G162" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H162" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I162" s="6"/>
       <c r="J162" s="20"/>
       <c r="K162" s="11"/>
@@ -42467,13 +43196,25 @@
     </row>
     <row r="163" spans="1:14" ht="9.75" customHeight="1">
       <c r="A163" s="32"/>
-      <c r="B163" s="11"/>
-      <c r="C163" s="11"/>
-      <c r="D163" s="20"/>
-      <c r="E163" s="47"/>
+      <c r="B163" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C163" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D163" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E163" s="47" t="s">
+        <v>869</v>
+      </c>
       <c r="F163" s="6"/>
-      <c r="G163" s="11"/>
-      <c r="H163" s="11"/>
+      <c r="G163" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H163" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I163" s="6"/>
       <c r="J163" s="20"/>
       <c r="K163" s="11"/>
@@ -42483,13 +43224,25 @@
     </row>
     <row r="164" spans="1:14" ht="9.75" customHeight="1">
       <c r="A164" s="32"/>
-      <c r="B164" s="11"/>
-      <c r="C164" s="11"/>
-      <c r="D164" s="20"/>
-      <c r="E164" s="47"/>
+      <c r="B164" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D164" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E164" s="47" t="s">
+        <v>938</v>
+      </c>
       <c r="F164" s="6"/>
-      <c r="G164" s="11"/>
-      <c r="H164" s="11"/>
+      <c r="G164" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H164" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I164" s="6"/>
       <c r="J164" s="20"/>
       <c r="K164" s="11"/>
@@ -42499,13 +43252,25 @@
     </row>
     <row r="165" spans="1:14" ht="9.75" customHeight="1">
       <c r="A165" s="32"/>
-      <c r="B165" s="11"/>
-      <c r="C165" s="11"/>
-      <c r="D165" s="20"/>
-      <c r="E165" s="47"/>
+      <c r="B165" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C165" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D165" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E165" s="47" t="s">
+        <v>939</v>
+      </c>
       <c r="F165" s="6"/>
-      <c r="G165" s="11"/>
-      <c r="H165" s="11"/>
+      <c r="G165" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H165" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I165" s="6"/>
       <c r="J165" s="20"/>
       <c r="K165" s="11"/>
@@ -42515,13 +43280,25 @@
     </row>
     <row r="166" spans="1:14" ht="9.75" customHeight="1">
       <c r="A166" s="32"/>
-      <c r="B166" s="11"/>
-      <c r="C166" s="11"/>
-      <c r="D166" s="20"/>
-      <c r="E166" s="47"/>
+      <c r="B166" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C166" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D166" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E166" s="47" t="s">
+        <v>940</v>
+      </c>
       <c r="F166" s="6"/>
-      <c r="G166" s="11"/>
-      <c r="H166" s="11"/>
+      <c r="G166" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H166" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I166" s="6"/>
       <c r="J166" s="20"/>
       <c r="K166" s="11"/>
@@ -42531,13 +43308,25 @@
     </row>
     <row r="167" spans="1:14" ht="9.75" customHeight="1">
       <c r="A167" s="32"/>
-      <c r="B167" s="11"/>
-      <c r="C167" s="11"/>
-      <c r="D167" s="20"/>
-      <c r="E167" s="47"/>
+      <c r="B167" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C167" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D167" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E167" s="47" t="s">
+        <v>941</v>
+      </c>
       <c r="F167" s="6"/>
-      <c r="G167" s="11"/>
-      <c r="H167" s="11"/>
+      <c r="G167" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H167" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I167" s="6"/>
       <c r="J167" s="20"/>
       <c r="K167" s="11"/>
@@ -42547,13 +43336,25 @@
     </row>
     <row r="168" spans="1:14" ht="9.75" customHeight="1">
       <c r="A168" s="32"/>
-      <c r="B168" s="11"/>
-      <c r="C168" s="11"/>
-      <c r="D168" s="20"/>
-      <c r="E168" s="47"/>
+      <c r="B168" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D168" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E168" s="47" t="s">
+        <v>942</v>
+      </c>
       <c r="F168" s="6"/>
-      <c r="G168" s="11"/>
-      <c r="H168" s="11"/>
+      <c r="G168" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="H168" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I168" s="6"/>
       <c r="J168" s="20"/>
       <c r="K168" s="11"/>
@@ -42563,13 +43364,25 @@
     </row>
     <row r="169" spans="1:14" ht="9.75" customHeight="1">
       <c r="A169" s="32"/>
-      <c r="B169" s="11"/>
-      <c r="C169" s="11"/>
-      <c r="D169" s="20"/>
-      <c r="E169" s="47"/>
+      <c r="B169" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C169" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D169" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E169" s="47" t="s">
+        <v>943</v>
+      </c>
       <c r="F169" s="6"/>
-      <c r="G169" s="11"/>
-      <c r="H169" s="11"/>
+      <c r="G169" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H169" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I169" s="6"/>
       <c r="J169" s="20"/>
       <c r="K169" s="11"/>
@@ -42579,13 +43392,25 @@
     </row>
     <row r="170" spans="1:14" ht="9.75" customHeight="1">
       <c r="A170" s="32"/>
-      <c r="B170" s="11"/>
-      <c r="C170" s="11"/>
-      <c r="D170" s="20"/>
-      <c r="E170" s="47"/>
+      <c r="B170" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D170" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E170" s="47" t="s">
+        <v>944</v>
+      </c>
       <c r="F170" s="6"/>
-      <c r="G170" s="11"/>
-      <c r="H170" s="11"/>
+      <c r="G170" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H170" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I170" s="6"/>
       <c r="J170" s="20"/>
       <c r="K170" s="11"/>
@@ -42595,13 +43420,25 @@
     </row>
     <row r="171" spans="1:14" ht="9.75" customHeight="1">
       <c r="A171" s="32"/>
-      <c r="B171" s="11"/>
-      <c r="C171" s="11"/>
-      <c r="D171" s="20"/>
-      <c r="E171" s="47"/>
+      <c r="B171" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C171" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D171" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E171" s="47" t="s">
+        <v>945</v>
+      </c>
       <c r="F171" s="6"/>
-      <c r="G171" s="11"/>
-      <c r="H171" s="11"/>
+      <c r="G171" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H171" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I171" s="6"/>
       <c r="J171" s="20"/>
       <c r="K171" s="11"/>
@@ -42611,13 +43448,25 @@
     </row>
     <row r="172" spans="1:14" ht="9.75" customHeight="1">
       <c r="A172" s="32"/>
-      <c r="B172" s="11"/>
-      <c r="C172" s="11"/>
-      <c r="D172" s="20"/>
-      <c r="E172" s="47"/>
+      <c r="B172" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C172" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D172" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E172" s="47" t="s">
+        <v>946</v>
+      </c>
       <c r="F172" s="6"/>
-      <c r="G172" s="11"/>
-      <c r="H172" s="11"/>
+      <c r="G172" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H172" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I172" s="6"/>
       <c r="J172" s="20"/>
       <c r="K172" s="11"/>
@@ -42627,13 +43476,25 @@
     </row>
     <row r="173" spans="1:14" ht="9.75" customHeight="1">
       <c r="A173" s="32"/>
-      <c r="B173" s="11"/>
-      <c r="C173" s="11"/>
-      <c r="D173" s="20"/>
-      <c r="E173" s="47"/>
+      <c r="B173" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D173" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E173" s="47" t="s">
+        <v>947</v>
+      </c>
       <c r="F173" s="6"/>
-      <c r="G173" s="11"/>
-      <c r="H173" s="11"/>
+      <c r="G173" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H173" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I173" s="6"/>
       <c r="J173" s="20"/>
       <c r="K173" s="11"/>
@@ -42643,13 +43504,25 @@
     </row>
     <row r="174" spans="1:14" ht="9.75" customHeight="1">
       <c r="A174" s="32"/>
-      <c r="B174" s="11"/>
-      <c r="C174" s="11"/>
-      <c r="D174" s="20"/>
-      <c r="E174" s="47"/>
+      <c r="B174" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C174" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D174" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E174" s="47" t="s">
+        <v>948</v>
+      </c>
       <c r="F174" s="6"/>
-      <c r="G174" s="11"/>
-      <c r="H174" s="11"/>
+      <c r="G174" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H174" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I174" s="6"/>
       <c r="J174" s="20"/>
       <c r="K174" s="11"/>
@@ -42659,13 +43532,25 @@
     </row>
     <row r="175" spans="1:14" ht="9.75" customHeight="1">
       <c r="A175" s="32"/>
-      <c r="B175" s="11"/>
-      <c r="C175" s="11"/>
-      <c r="D175" s="20"/>
-      <c r="E175" s="47"/>
+      <c r="B175" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C175" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D175" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E175" s="47" t="s">
+        <v>949</v>
+      </c>
       <c r="F175" s="6"/>
-      <c r="G175" s="11"/>
-      <c r="H175" s="11"/>
+      <c r="G175" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H175" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I175" s="6"/>
       <c r="J175" s="20"/>
       <c r="K175" s="11"/>
@@ -42675,13 +43560,25 @@
     </row>
     <row r="176" spans="1:14" ht="9.75" customHeight="1">
       <c r="A176" s="32"/>
-      <c r="B176" s="11"/>
-      <c r="C176" s="11"/>
-      <c r="D176" s="20"/>
-      <c r="E176" s="47"/>
+      <c r="B176" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D176" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E176" s="47" t="s">
+        <v>950</v>
+      </c>
       <c r="F176" s="6"/>
-      <c r="G176" s="11"/>
-      <c r="H176" s="11"/>
+      <c r="G176" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H176" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I176" s="6"/>
       <c r="J176" s="20"/>
       <c r="K176" s="11"/>
@@ -42691,13 +43588,25 @@
     </row>
     <row r="177" spans="1:14" ht="9.75" customHeight="1">
       <c r="A177" s="32"/>
-      <c r="B177" s="11"/>
-      <c r="C177" s="11"/>
-      <c r="D177" s="20"/>
-      <c r="E177" s="47"/>
+      <c r="B177" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C177" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D177" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E177" s="47" t="s">
+        <v>951</v>
+      </c>
       <c r="F177" s="6"/>
-      <c r="G177" s="11"/>
-      <c r="H177" s="11"/>
+      <c r="G177" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="H177" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I177" s="6"/>
       <c r="J177" s="20"/>
       <c r="K177" s="11"/>
@@ -42707,13 +43616,25 @@
     </row>
     <row r="178" spans="1:14" ht="9.75" customHeight="1">
       <c r="A178" s="32"/>
-      <c r="B178" s="11"/>
-      <c r="C178" s="11"/>
-      <c r="D178" s="20"/>
-      <c r="E178" s="47"/>
+      <c r="B178" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C178" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D178" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E178" s="47" t="s">
+        <v>952</v>
+      </c>
       <c r="F178" s="6"/>
-      <c r="G178" s="11"/>
-      <c r="H178" s="11"/>
+      <c r="G178" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H178" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I178" s="6"/>
       <c r="J178" s="20"/>
       <c r="K178" s="11"/>
@@ -42723,13 +43644,25 @@
     </row>
     <row r="179" spans="1:14" ht="9.75" customHeight="1">
       <c r="A179" s="32"/>
-      <c r="B179" s="11"/>
-      <c r="C179" s="11"/>
-      <c r="D179" s="20"/>
-      <c r="E179" s="47"/>
+      <c r="B179" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C179" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D179" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="E179" s="47" t="s">
+        <v>953</v>
+      </c>
       <c r="F179" s="6"/>
-      <c r="G179" s="11"/>
-      <c r="H179" s="11"/>
+      <c r="G179" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H179" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I179" s="6"/>
       <c r="J179" s="20"/>
       <c r="K179" s="11"/>
@@ -42739,13 +43672,25 @@
     </row>
     <row r="180" spans="1:14" ht="9.75" customHeight="1">
       <c r="A180" s="32"/>
-      <c r="B180" s="11"/>
-      <c r="C180" s="11"/>
-      <c r="D180" s="20"/>
-      <c r="E180" s="47"/>
+      <c r="B180" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C180" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D180" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E180" s="47" t="s">
+        <v>858</v>
+      </c>
       <c r="F180" s="6"/>
-      <c r="G180" s="11"/>
-      <c r="H180" s="11"/>
+      <c r="G180" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="H180" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I180" s="6"/>
       <c r="J180" s="20"/>
       <c r="K180" s="11"/>
@@ -42755,13 +43700,25 @@
     </row>
     <row r="181" spans="1:14" ht="9.75" customHeight="1">
       <c r="A181" s="32"/>
-      <c r="B181" s="11"/>
-      <c r="C181" s="11"/>
-      <c r="D181" s="20"/>
-      <c r="E181" s="47"/>
+      <c r="B181" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C181" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D181" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E181" s="47" t="s">
+        <v>862</v>
+      </c>
       <c r="F181" s="6"/>
-      <c r="G181" s="11"/>
-      <c r="H181" s="11"/>
+      <c r="G181" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H181" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I181" s="6"/>
       <c r="J181" s="20"/>
       <c r="K181" s="11"/>
@@ -42771,13 +43728,25 @@
     </row>
     <row r="182" spans="1:14" ht="9.75" customHeight="1">
       <c r="A182" s="32"/>
-      <c r="B182" s="11"/>
-      <c r="C182" s="11"/>
-      <c r="D182" s="20"/>
-      <c r="E182" s="47"/>
+      <c r="B182" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C182" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D182" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E182" s="47" t="s">
+        <v>863</v>
+      </c>
       <c r="F182" s="6"/>
-      <c r="G182" s="11"/>
-      <c r="H182" s="11"/>
+      <c r="G182" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="H182" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I182" s="6"/>
       <c r="J182" s="20"/>
       <c r="K182" s="11"/>
@@ -42787,13 +43756,25 @@
     </row>
     <row r="183" spans="1:14" ht="9.75" customHeight="1">
       <c r="A183" s="32"/>
-      <c r="B183" s="11"/>
-      <c r="C183" s="11"/>
-      <c r="D183" s="20"/>
-      <c r="E183" s="47"/>
+      <c r="B183" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C183" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D183" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E183" s="47" t="s">
+        <v>865</v>
+      </c>
       <c r="F183" s="6"/>
-      <c r="G183" s="11"/>
-      <c r="H183" s="11"/>
+      <c r="G183" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H183" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I183" s="6"/>
       <c r="J183" s="20"/>
       <c r="K183" s="11"/>
@@ -42803,13 +43784,25 @@
     </row>
     <row r="184" spans="1:14" ht="9.75" customHeight="1">
       <c r="A184" s="32"/>
-      <c r="B184" s="11"/>
-      <c r="C184" s="11"/>
-      <c r="D184" s="20"/>
-      <c r="E184" s="47"/>
+      <c r="B184" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C184" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D184" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E184" s="47" t="s">
+        <v>866</v>
+      </c>
       <c r="F184" s="6"/>
-      <c r="G184" s="11"/>
-      <c r="H184" s="11"/>
+      <c r="G184" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H184" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I184" s="6"/>
       <c r="J184" s="20"/>
       <c r="K184" s="11"/>
@@ -42819,13 +43812,25 @@
     </row>
     <row r="185" spans="1:14" ht="9.75" customHeight="1">
       <c r="A185" s="32"/>
-      <c r="B185" s="11"/>
-      <c r="C185" s="11"/>
-      <c r="D185" s="20"/>
-      <c r="E185" s="47"/>
+      <c r="B185" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C185" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D185" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E185" s="47" t="s">
+        <v>867</v>
+      </c>
       <c r="F185" s="6"/>
-      <c r="G185" s="11"/>
-      <c r="H185" s="11"/>
+      <c r="G185" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H185" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I185" s="6"/>
       <c r="J185" s="20"/>
       <c r="K185" s="11"/>
@@ -42835,13 +43840,25 @@
     </row>
     <row r="186" spans="1:14" ht="9.75" customHeight="1">
       <c r="A186" s="32"/>
-      <c r="B186" s="11"/>
-      <c r="C186" s="11"/>
-      <c r="D186" s="20"/>
-      <c r="E186" s="47"/>
+      <c r="B186" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C186" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D186" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E186" s="47" t="s">
+        <v>868</v>
+      </c>
       <c r="F186" s="6"/>
-      <c r="G186" s="11"/>
-      <c r="H186" s="11"/>
+      <c r="G186" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H186" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I186" s="6"/>
       <c r="J186" s="20"/>
       <c r="K186" s="11"/>
@@ -42851,13 +43868,25 @@
     </row>
     <row r="187" spans="1:14" ht="9.75" customHeight="1">
       <c r="A187" s="32"/>
-      <c r="B187" s="11"/>
-      <c r="C187" s="11"/>
-      <c r="D187" s="20"/>
-      <c r="E187" s="47"/>
+      <c r="B187" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C187" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D187" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E187" s="47" t="s">
+        <v>869</v>
+      </c>
       <c r="F187" s="6"/>
-      <c r="G187" s="11"/>
-      <c r="H187" s="11"/>
+      <c r="G187" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H187" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I187" s="6"/>
       <c r="J187" s="20"/>
       <c r="K187" s="11"/>
@@ -42867,13 +43896,25 @@
     </row>
     <row r="188" spans="1:14" ht="9.75" customHeight="1">
       <c r="A188" s="32"/>
-      <c r="B188" s="11"/>
-      <c r="C188" s="11"/>
-      <c r="D188" s="20"/>
-      <c r="E188" s="47"/>
+      <c r="B188" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D188" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E188" s="47" t="s">
+        <v>938</v>
+      </c>
       <c r="F188" s="6"/>
-      <c r="G188" s="11"/>
-      <c r="H188" s="11"/>
+      <c r="G188" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H188" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I188" s="6"/>
       <c r="J188" s="20"/>
       <c r="K188" s="11"/>
@@ -42883,13 +43924,25 @@
     </row>
     <row r="189" spans="1:14" ht="9.75" customHeight="1">
       <c r="A189" s="32"/>
-      <c r="B189" s="11"/>
-      <c r="C189" s="11"/>
-      <c r="D189" s="20"/>
-      <c r="E189" s="47"/>
+      <c r="B189" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C189" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D189" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E189" s="47" t="s">
+        <v>939</v>
+      </c>
       <c r="F189" s="6"/>
-      <c r="G189" s="11"/>
-      <c r="H189" s="11"/>
+      <c r="G189" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H189" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I189" s="6"/>
       <c r="J189" s="20"/>
       <c r="K189" s="11"/>
@@ -42899,13 +43952,25 @@
     </row>
     <row r="190" spans="1:14" ht="9.75" customHeight="1">
       <c r="A190" s="32"/>
-      <c r="B190" s="11"/>
-      <c r="C190" s="11"/>
-      <c r="D190" s="20"/>
-      <c r="E190" s="47"/>
+      <c r="B190" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C190" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D190" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E190" s="47" t="s">
+        <v>940</v>
+      </c>
       <c r="F190" s="6"/>
-      <c r="G190" s="11"/>
-      <c r="H190" s="11"/>
+      <c r="G190" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="H190" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I190" s="6"/>
       <c r="J190" s="20"/>
       <c r="K190" s="11"/>
@@ -42915,13 +43980,25 @@
     </row>
     <row r="191" spans="1:14" ht="9.75" customHeight="1">
       <c r="A191" s="32"/>
-      <c r="B191" s="11"/>
-      <c r="C191" s="11"/>
-      <c r="D191" s="20"/>
-      <c r="E191" s="47"/>
+      <c r="B191" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C191" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D191" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E191" s="47" t="s">
+        <v>941</v>
+      </c>
       <c r="F191" s="6"/>
-      <c r="G191" s="11"/>
-      <c r="H191" s="11"/>
+      <c r="G191" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="H191" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I191" s="6"/>
       <c r="J191" s="20"/>
       <c r="K191" s="11"/>
@@ -42931,13 +44008,25 @@
     </row>
     <row r="192" spans="1:14" ht="9.75" customHeight="1">
       <c r="A192" s="32"/>
-      <c r="B192" s="11"/>
-      <c r="C192" s="11"/>
-      <c r="D192" s="20"/>
-      <c r="E192" s="47"/>
+      <c r="B192" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C192" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D192" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E192" s="47" t="s">
+        <v>942</v>
+      </c>
       <c r="F192" s="6"/>
-      <c r="G192" s="11"/>
-      <c r="H192" s="11"/>
+      <c r="G192" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H192" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I192" s="6"/>
       <c r="J192" s="20"/>
       <c r="K192" s="11"/>
@@ -42947,13 +44036,25 @@
     </row>
     <row r="193" spans="1:14" ht="9.75" customHeight="1">
       <c r="A193" s="32"/>
-      <c r="B193" s="11"/>
-      <c r="C193" s="11"/>
-      <c r="D193" s="20"/>
-      <c r="E193" s="47"/>
+      <c r="B193" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C193" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D193" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E193" s="47" t="s">
+        <v>943</v>
+      </c>
       <c r="F193" s="6"/>
-      <c r="G193" s="11"/>
-      <c r="H193" s="11"/>
+      <c r="G193" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H193" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I193" s="6"/>
       <c r="J193" s="20"/>
       <c r="K193" s="11"/>
@@ -42963,13 +44064,25 @@
     </row>
     <row r="194" spans="1:14" ht="9.75" customHeight="1">
       <c r="A194" s="32"/>
-      <c r="B194" s="11"/>
-      <c r="C194" s="11"/>
-      <c r="D194" s="20"/>
-      <c r="E194" s="47"/>
+      <c r="B194" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C194" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D194" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E194" s="47" t="s">
+        <v>944</v>
+      </c>
       <c r="F194" s="6"/>
-      <c r="G194" s="11"/>
-      <c r="H194" s="11"/>
+      <c r="G194" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H194" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I194" s="6"/>
       <c r="J194" s="20"/>
       <c r="K194" s="11"/>
@@ -42979,13 +44092,25 @@
     </row>
     <row r="195" spans="1:14" ht="9.75" customHeight="1">
       <c r="A195" s="32"/>
-      <c r="B195" s="11"/>
-      <c r="C195" s="11"/>
-      <c r="D195" s="20"/>
-      <c r="E195" s="47"/>
+      <c r="B195" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C195" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D195" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E195" s="47" t="s">
+        <v>945</v>
+      </c>
       <c r="F195" s="6"/>
-      <c r="G195" s="11"/>
-      <c r="H195" s="11"/>
+      <c r="G195" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H195" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I195" s="6"/>
       <c r="J195" s="20"/>
       <c r="K195" s="11"/>
@@ -42995,13 +44120,25 @@
     </row>
     <row r="196" spans="1:14" ht="9.75" customHeight="1">
       <c r="A196" s="32"/>
-      <c r="B196" s="11"/>
-      <c r="C196" s="11"/>
-      <c r="D196" s="20"/>
-      <c r="E196" s="47"/>
+      <c r="B196" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C196" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D196" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E196" s="47" t="s">
+        <v>946</v>
+      </c>
       <c r="F196" s="6"/>
-      <c r="G196" s="11"/>
-      <c r="H196" s="11"/>
+      <c r="G196" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="H196" s="11" t="s">
+        <v>960</v>
+      </c>
       <c r="I196" s="6"/>
       <c r="J196" s="20"/>
       <c r="K196" s="11"/>
@@ -43011,13 +44148,25 @@
     </row>
     <row r="197" spans="1:14" ht="9.75" customHeight="1">
       <c r="A197" s="32"/>
-      <c r="B197" s="11"/>
-      <c r="C197" s="11"/>
-      <c r="D197" s="20"/>
-      <c r="E197" s="47"/>
+      <c r="B197" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C197" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D197" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E197" s="47" t="s">
+        <v>947</v>
+      </c>
       <c r="F197" s="6"/>
-      <c r="G197" s="11"/>
-      <c r="H197" s="11"/>
+      <c r="G197" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H197" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I197" s="6"/>
       <c r="J197" s="20"/>
       <c r="K197" s="11"/>
@@ -43027,13 +44176,25 @@
     </row>
     <row r="198" spans="1:14" ht="9.75" customHeight="1">
       <c r="A198" s="32"/>
-      <c r="B198" s="11"/>
-      <c r="C198" s="11"/>
-      <c r="D198" s="20"/>
-      <c r="E198" s="47"/>
+      <c r="B198" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D198" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E198" s="47" t="s">
+        <v>948</v>
+      </c>
       <c r="F198" s="6"/>
-      <c r="G198" s="11"/>
-      <c r="H198" s="11"/>
+      <c r="G198" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H198" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I198" s="6"/>
       <c r="J198" s="20"/>
       <c r="K198" s="11"/>
@@ -43043,13 +44204,25 @@
     </row>
     <row r="199" spans="1:14" ht="9.75" customHeight="1">
       <c r="A199" s="32"/>
-      <c r="B199" s="11"/>
-      <c r="C199" s="11"/>
-      <c r="D199" s="20"/>
-      <c r="E199" s="47"/>
+      <c r="B199" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C199" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D199" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E199" s="47" t="s">
+        <v>949</v>
+      </c>
       <c r="F199" s="6"/>
-      <c r="G199" s="11"/>
-      <c r="H199" s="11"/>
+      <c r="G199" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H199" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I199" s="6"/>
       <c r="J199" s="20"/>
       <c r="K199" s="11"/>
@@ -43059,13 +44232,25 @@
     </row>
     <row r="200" spans="1:14" ht="9.75" customHeight="1">
       <c r="A200" s="32"/>
-      <c r="B200" s="11"/>
-      <c r="C200" s="11"/>
-      <c r="D200" s="20"/>
-      <c r="E200" s="47"/>
+      <c r="B200" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C200" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D200" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E200" s="47" t="s">
+        <v>950</v>
+      </c>
       <c r="F200" s="6"/>
-      <c r="G200" s="11"/>
-      <c r="H200" s="11"/>
+      <c r="G200" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H200" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I200" s="6"/>
       <c r="J200" s="20"/>
       <c r="K200" s="11"/>
@@ -43075,13 +44260,25 @@
     </row>
     <row r="201" spans="1:14" ht="9.75" customHeight="1">
       <c r="A201" s="32"/>
-      <c r="B201" s="11"/>
-      <c r="C201" s="11"/>
-      <c r="D201" s="20"/>
-      <c r="E201" s="47"/>
+      <c r="B201" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C201" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D201" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E201" s="47" t="s">
+        <v>951</v>
+      </c>
       <c r="F201" s="6"/>
-      <c r="G201" s="11"/>
-      <c r="H201" s="11"/>
+      <c r="G201" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H201" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I201" s="6"/>
       <c r="J201" s="20"/>
       <c r="K201" s="11"/>
@@ -43091,13 +44288,25 @@
     </row>
     <row r="202" spans="1:14" ht="9.75" customHeight="1">
       <c r="A202" s="32"/>
-      <c r="B202" s="11"/>
-      <c r="C202" s="11"/>
-      <c r="D202" s="20"/>
-      <c r="E202" s="47"/>
+      <c r="B202" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C202" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D202" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E202" s="47" t="s">
+        <v>952</v>
+      </c>
       <c r="F202" s="6"/>
-      <c r="G202" s="11"/>
-      <c r="H202" s="11"/>
+      <c r="G202" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="H202" s="11" t="s">
+        <v>958</v>
+      </c>
       <c r="I202" s="6"/>
       <c r="J202" s="20"/>
       <c r="K202" s="11"/>
@@ -43107,13 +44316,25 @@
     </row>
     <row r="203" spans="1:14" ht="9.75" customHeight="1">
       <c r="A203" s="32"/>
-      <c r="B203" s="11"/>
-      <c r="C203" s="11"/>
-      <c r="D203" s="20"/>
-      <c r="E203" s="47"/>
+      <c r="B203" s="69" t="s">
+        <v>914</v>
+      </c>
+      <c r="C203" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="D203" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="E203" s="47" t="s">
+        <v>953</v>
+      </c>
       <c r="F203" s="6"/>
-      <c r="G203" s="11"/>
-      <c r="H203" s="11"/>
+      <c r="G203" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="H203" s="11" t="s">
+        <v>962</v>
+      </c>
       <c r="I203" s="6"/>
       <c r="J203" s="20"/>
       <c r="K203" s="11"/>
@@ -45697,10 +46918,16 @@
     <row r="6" spans="1:14" ht="9.75" customHeight="1">
       <c r="A6" s="31"/>
       <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
+      <c r="C6" s="10" t="s">
+        <v>965</v>
+      </c>
       <c r="D6" s="4"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
+      <c r="E6" s="10" t="s">
+        <v>972</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>973</v>
+      </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
       <c r="I6" s="13"/>
@@ -45713,10 +46940,16 @@
     <row r="7" spans="1:14" ht="9.75" customHeight="1">
       <c r="A7" s="32"/>
       <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
+      <c r="C7" s="11" t="s">
+        <v>966</v>
+      </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
+      <c r="E7" s="11" t="s">
+        <v>958</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>973</v>
+      </c>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="14"/>
@@ -45729,10 +46962,16 @@
     <row r="8" spans="1:14" ht="9.75" customHeight="1">
       <c r="A8" s="32"/>
       <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
+      <c r="C8" s="11" t="s">
+        <v>967</v>
+      </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
+      <c r="E8" s="11" t="s">
+        <v>963</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>974</v>
+      </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="14"/>
@@ -45745,10 +46984,16 @@
     <row r="9" spans="1:14" ht="9.75" customHeight="1">
       <c r="A9" s="32"/>
       <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
+      <c r="C9" s="11" t="s">
+        <v>968</v>
+      </c>
       <c r="D9" s="6"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
+      <c r="E9" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>973</v>
+      </c>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="14"/>
@@ -45761,10 +47006,16 @@
     <row r="10" spans="1:14" ht="9.75" customHeight="1">
       <c r="A10" s="32"/>
       <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
+      <c r="C10" s="11" t="s">
+        <v>969</v>
+      </c>
       <c r="D10" s="6"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
+      <c r="E10" s="11" t="s">
+        <v>960</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>973</v>
+      </c>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="14"/>
@@ -45777,10 +47028,16 @@
     <row r="11" spans="1:14" ht="9.75" customHeight="1">
       <c r="A11" s="32"/>
       <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
+      <c r="C11" s="11" t="s">
+        <v>970</v>
+      </c>
       <c r="D11" s="6"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
+      <c r="E11" s="11" t="s">
+        <v>960</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>973</v>
+      </c>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="14"/>
@@ -45793,10 +47050,16 @@
     <row r="12" spans="1:14" ht="9.75" customHeight="1">
       <c r="A12" s="32"/>
       <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
+      <c r="C12" s="11" t="s">
+        <v>971</v>
+      </c>
       <c r="D12" s="6"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
+      <c r="E12" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>973</v>
+      </c>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="14"/>

--- a/data/Template_Resmi_Database_SIRUMAH.xlsx
+++ b/data/Template_Resmi_Database_SIRUMAH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D5410C-C2FE-4FB3-B494-7432B8D3FF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AABEEC-89F3-436C-9A7B-B0F08F567338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3291,7 +3291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3508,13 +3508,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3536,11 +3536,27 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3708,7 +3724,7 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="KOMPONEN*"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="LOKASI"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="KONDISI*"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="PRIORITAS*"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="PRIORITAS*" dataDxfId="0"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="TINDAK_LANJUT*"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="STATUS_TINDAK_LANJUT*"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="TANGGAL_PEMERIKSAAN*"/>
@@ -3927,74 +3943,74 @@
       <c r="W1" s="75"/>
       <c r="X1" s="75"/>
       <c r="Y1" s="75"/>
-      <c r="Z1" s="76"/>
-      <c r="AA1" s="76"/>
-      <c r="AB1" s="76"/>
-      <c r="AC1" s="76"/>
-      <c r="AD1" s="76"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
     </row>
     <row r="2" spans="1:30" ht="11.65" customHeight="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
-      <c r="W2" s="77"/>
-      <c r="X2" s="77"/>
-      <c r="Y2" s="77"/>
-      <c r="Z2" s="76"/>
-      <c r="AA2" s="76"/>
-      <c r="AB2" s="76"/>
-      <c r="AC2" s="76"/>
-      <c r="AD2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
+      <c r="W2" s="76"/>
+      <c r="X2" s="76"/>
+      <c r="Y2" s="76"/>
+      <c r="Z2" s="78"/>
+      <c r="AA2" s="78"/>
+      <c r="AB2" s="78"/>
+      <c r="AC2" s="78"/>
+      <c r="AD2" s="78"/>
     </row>
     <row r="3" spans="1:30" ht="16.899999999999999" customHeight="1">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="78"/>
-      <c r="T3" s="78"/>
-      <c r="U3" s="78"/>
-      <c r="V3" s="78"/>
-      <c r="W3" s="78"/>
-      <c r="X3" s="78"/>
-      <c r="Y3" s="78"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="77"/>
+      <c r="V3" s="77"/>
+      <c r="W3" s="77"/>
+      <c r="X3" s="77"/>
+      <c r="Y3" s="77"/>
       <c r="Z3" s="79"/>
       <c r="AA3" s="79"/>
       <c r="AB3" s="79"/>
@@ -29807,34 +29823,34 @@
       <c r="K1" s="75"/>
     </row>
     <row r="2" spans="1:11" ht="11.65" customHeight="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="76" t="s">
         <v>850</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
     </row>
     <row r="3" spans="1:11" ht="13.4" customHeight="1">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="77" t="s">
         <v>851</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
     </row>
     <row r="5" spans="1:11" ht="18.649999999999999" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -30733,34 +30749,34 @@
       <c r="K1" s="75"/>
     </row>
     <row r="2" spans="1:11" ht="11.65" customHeight="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="76" t="s">
         <v>872</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
     </row>
     <row r="3" spans="1:11" ht="13.4" customHeight="1">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="77" t="s">
         <v>851</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
     </row>
     <row r="5" spans="1:11" ht="18.649999999999999" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -31928,52 +31944,52 @@
       <c r="T1" s="75"/>
     </row>
     <row r="2" spans="1:20" ht="11.65" customHeight="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="76" t="s">
         <v>879</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
     </row>
     <row r="3" spans="1:20" ht="13.4" customHeight="1">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="77" t="s">
         <v>851</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="78"/>
-      <c r="T3" s="78"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
     </row>
     <row r="5" spans="1:20" ht="18.649999999999999" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -38719,40 +38735,40 @@
       <c r="N1" s="75"/>
     </row>
     <row r="2" spans="1:14" ht="11.65" customHeight="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="76" t="s">
         <v>894</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="76"/>
     </row>
     <row r="3" spans="1:14" ht="13.4" customHeight="1">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="77" t="s">
         <v>851</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
     </row>
     <row r="5" spans="1:14" ht="18.649999999999999" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -46806,7 +46822,7 @@
     <col min="2" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="6" max="6" width="14" style="89" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
@@ -46836,40 +46852,40 @@
       <c r="N1" s="75"/>
     </row>
     <row r="2" spans="1:14" ht="11.65" customHeight="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="76" t="s">
         <v>927</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="76"/>
     </row>
     <row r="3" spans="1:14" ht="13.4" customHeight="1">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="77" t="s">
         <v>851</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
     </row>
     <row r="5" spans="1:14" ht="18.649999999999999" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -46925,7 +46941,7 @@
       <c r="E6" s="10" t="s">
         <v>972</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="86" t="s">
         <v>973</v>
       </c>
       <c r="G6" s="10"/>
@@ -46947,7 +46963,7 @@
       <c r="E7" s="11" t="s">
         <v>958</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="87" t="s">
         <v>973</v>
       </c>
       <c r="G7" s="11"/>
@@ -46969,7 +46985,7 @@
       <c r="E8" s="11" t="s">
         <v>963</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="87" t="s">
         <v>974</v>
       </c>
       <c r="G8" s="11"/>
@@ -46991,7 +47007,7 @@
       <c r="E9" s="11" t="s">
         <v>972</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="87" t="s">
         <v>973</v>
       </c>
       <c r="G9" s="11"/>
@@ -47013,7 +47029,7 @@
       <c r="E10" s="11" t="s">
         <v>960</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="87" t="s">
         <v>973</v>
       </c>
       <c r="G10" s="11"/>
@@ -47035,7 +47051,7 @@
       <c r="E11" s="11" t="s">
         <v>960</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="87" t="s">
         <v>973</v>
       </c>
       <c r="G11" s="11"/>
@@ -47057,7 +47073,7 @@
       <c r="E12" s="11" t="s">
         <v>972</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="87" t="s">
         <v>973</v>
       </c>
       <c r="G12" s="11"/>
@@ -47075,7 +47091,7 @@
       <c r="C13" s="11"/>
       <c r="D13" s="6"/>
       <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
+      <c r="F13" s="87"/>
       <c r="G13" s="11"/>
       <c r="H13" s="11"/>
       <c r="I13" s="14"/>
@@ -47091,7 +47107,7 @@
       <c r="C14" s="11"/>
       <c r="D14" s="6"/>
       <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
+      <c r="F14" s="87"/>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
       <c r="I14" s="14"/>
@@ -47107,7 +47123,7 @@
       <c r="C15" s="11"/>
       <c r="D15" s="6"/>
       <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="F15" s="87"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="14"/>
@@ -47123,7 +47139,7 @@
       <c r="C16" s="11"/>
       <c r="D16" s="6"/>
       <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
+      <c r="F16" s="87"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
       <c r="I16" s="14"/>
@@ -47139,7 +47155,7 @@
       <c r="C17" s="11"/>
       <c r="D17" s="6"/>
       <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="F17" s="87"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="14"/>
@@ -47155,7 +47171,7 @@
       <c r="C18" s="11"/>
       <c r="D18" s="6"/>
       <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
+      <c r="F18" s="87"/>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="14"/>
@@ -47171,7 +47187,7 @@
       <c r="C19" s="11"/>
       <c r="D19" s="6"/>
       <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+      <c r="F19" s="87"/>
       <c r="G19" s="11"/>
       <c r="H19" s="11"/>
       <c r="I19" s="14"/>
@@ -47187,7 +47203,7 @@
       <c r="C20" s="11"/>
       <c r="D20" s="6"/>
       <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
+      <c r="F20" s="87"/>
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
       <c r="I20" s="14"/>
@@ -47203,7 +47219,7 @@
       <c r="C21" s="11"/>
       <c r="D21" s="6"/>
       <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
+      <c r="F21" s="87"/>
       <c r="G21" s="11"/>
       <c r="H21" s="11"/>
       <c r="I21" s="14"/>
@@ -47219,7 +47235,7 @@
       <c r="C22" s="11"/>
       <c r="D22" s="6"/>
       <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
+      <c r="F22" s="87"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="14"/>
@@ -47235,7 +47251,7 @@
       <c r="C23" s="11"/>
       <c r="D23" s="6"/>
       <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="F23" s="87"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="14"/>
@@ -47251,7 +47267,7 @@
       <c r="C24" s="11"/>
       <c r="D24" s="6"/>
       <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
+      <c r="F24" s="87"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="14"/>
@@ -47267,7 +47283,7 @@
       <c r="C25" s="11"/>
       <c r="D25" s="6"/>
       <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
+      <c r="F25" s="87"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
       <c r="I25" s="14"/>
@@ -47283,7 +47299,7 @@
       <c r="C26" s="11"/>
       <c r="D26" s="6"/>
       <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
+      <c r="F26" s="87"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
       <c r="I26" s="14"/>
@@ -47299,7 +47315,7 @@
       <c r="C27" s="11"/>
       <c r="D27" s="6"/>
       <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
+      <c r="F27" s="87"/>
       <c r="G27" s="11"/>
       <c r="H27" s="11"/>
       <c r="I27" s="14"/>
@@ -47315,7 +47331,7 @@
       <c r="C28" s="11"/>
       <c r="D28" s="6"/>
       <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
+      <c r="F28" s="87"/>
       <c r="G28" s="11"/>
       <c r="H28" s="11"/>
       <c r="I28" s="14"/>
@@ -47331,7 +47347,7 @@
       <c r="C29" s="11"/>
       <c r="D29" s="6"/>
       <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
+      <c r="F29" s="87"/>
       <c r="G29" s="11"/>
       <c r="H29" s="11"/>
       <c r="I29" s="14"/>
@@ -47347,7 +47363,7 @@
       <c r="C30" s="11"/>
       <c r="D30" s="6"/>
       <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
+      <c r="F30" s="87"/>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14"/>
@@ -47363,7 +47379,7 @@
       <c r="C31" s="11"/>
       <c r="D31" s="6"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
+      <c r="F31" s="87"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="14"/>
@@ -47379,7 +47395,7 @@
       <c r="C32" s="11"/>
       <c r="D32" s="6"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
+      <c r="F32" s="87"/>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
       <c r="I32" s="14"/>
@@ -47395,7 +47411,7 @@
       <c r="C33" s="11"/>
       <c r="D33" s="6"/>
       <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
+      <c r="F33" s="87"/>
       <c r="G33" s="11"/>
       <c r="H33" s="11"/>
       <c r="I33" s="14"/>
@@ -47411,7 +47427,7 @@
       <c r="C34" s="11"/>
       <c r="D34" s="6"/>
       <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
+      <c r="F34" s="87"/>
       <c r="G34" s="11"/>
       <c r="H34" s="11"/>
       <c r="I34" s="14"/>
@@ -47427,7 +47443,7 @@
       <c r="C35" s="11"/>
       <c r="D35" s="6"/>
       <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
+      <c r="F35" s="87"/>
       <c r="G35" s="11"/>
       <c r="H35" s="11"/>
       <c r="I35" s="14"/>
@@ -47443,7 +47459,7 @@
       <c r="C36" s="11"/>
       <c r="D36" s="6"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
+      <c r="F36" s="87"/>
       <c r="G36" s="11"/>
       <c r="H36" s="11"/>
       <c r="I36" s="14"/>
@@ -47459,7 +47475,7 @@
       <c r="C37" s="11"/>
       <c r="D37" s="6"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
+      <c r="F37" s="87"/>
       <c r="G37" s="11"/>
       <c r="H37" s="11"/>
       <c r="I37" s="14"/>
@@ -47475,7 +47491,7 @@
       <c r="C38" s="11"/>
       <c r="D38" s="6"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
+      <c r="F38" s="87"/>
       <c r="G38" s="11"/>
       <c r="H38" s="11"/>
       <c r="I38" s="14"/>
@@ -47491,7 +47507,7 @@
       <c r="C39" s="11"/>
       <c r="D39" s="6"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
+      <c r="F39" s="87"/>
       <c r="G39" s="11"/>
       <c r="H39" s="11"/>
       <c r="I39" s="14"/>
@@ -47507,7 +47523,7 @@
       <c r="C40" s="11"/>
       <c r="D40" s="6"/>
       <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
+      <c r="F40" s="87"/>
       <c r="G40" s="11"/>
       <c r="H40" s="11"/>
       <c r="I40" s="14"/>
@@ -47523,7 +47539,7 @@
       <c r="C41" s="11"/>
       <c r="D41" s="6"/>
       <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
+      <c r="F41" s="87"/>
       <c r="G41" s="11"/>
       <c r="H41" s="11"/>
       <c r="I41" s="14"/>
@@ -47539,7 +47555,7 @@
       <c r="C42" s="11"/>
       <c r="D42" s="6"/>
       <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
+      <c r="F42" s="87"/>
       <c r="G42" s="11"/>
       <c r="H42" s="11"/>
       <c r="I42" s="14"/>
@@ -47555,7 +47571,7 @@
       <c r="C43" s="11"/>
       <c r="D43" s="6"/>
       <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
+      <c r="F43" s="87"/>
       <c r="G43" s="11"/>
       <c r="H43" s="11"/>
       <c r="I43" s="14"/>
@@ -47571,7 +47587,7 @@
       <c r="C44" s="11"/>
       <c r="D44" s="6"/>
       <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
+      <c r="F44" s="87"/>
       <c r="G44" s="11"/>
       <c r="H44" s="11"/>
       <c r="I44" s="14"/>
@@ -47587,7 +47603,7 @@
       <c r="C45" s="11"/>
       <c r="D45" s="6"/>
       <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
+      <c r="F45" s="87"/>
       <c r="G45" s="11"/>
       <c r="H45" s="11"/>
       <c r="I45" s="14"/>
@@ -47603,7 +47619,7 @@
       <c r="C46" s="11"/>
       <c r="D46" s="6"/>
       <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
+      <c r="F46" s="87"/>
       <c r="G46" s="11"/>
       <c r="H46" s="11"/>
       <c r="I46" s="14"/>
@@ -47619,7 +47635,7 @@
       <c r="C47" s="11"/>
       <c r="D47" s="6"/>
       <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
+      <c r="F47" s="87"/>
       <c r="G47" s="11"/>
       <c r="H47" s="11"/>
       <c r="I47" s="14"/>
@@ -47635,7 +47651,7 @@
       <c r="C48" s="11"/>
       <c r="D48" s="6"/>
       <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
+      <c r="F48" s="87"/>
       <c r="G48" s="11"/>
       <c r="H48" s="11"/>
       <c r="I48" s="14"/>
@@ -47651,7 +47667,7 @@
       <c r="C49" s="11"/>
       <c r="D49" s="6"/>
       <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
+      <c r="F49" s="87"/>
       <c r="G49" s="11"/>
       <c r="H49" s="11"/>
       <c r="I49" s="14"/>
@@ -47667,7 +47683,7 @@
       <c r="C50" s="11"/>
       <c r="D50" s="6"/>
       <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
+      <c r="F50" s="87"/>
       <c r="G50" s="11"/>
       <c r="H50" s="11"/>
       <c r="I50" s="14"/>
@@ -47683,7 +47699,7 @@
       <c r="C51" s="11"/>
       <c r="D51" s="6"/>
       <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
+      <c r="F51" s="87"/>
       <c r="G51" s="11"/>
       <c r="H51" s="11"/>
       <c r="I51" s="14"/>
@@ -47699,7 +47715,7 @@
       <c r="C52" s="11"/>
       <c r="D52" s="6"/>
       <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
+      <c r="F52" s="87"/>
       <c r="G52" s="11"/>
       <c r="H52" s="11"/>
       <c r="I52" s="14"/>
@@ -47715,7 +47731,7 @@
       <c r="C53" s="11"/>
       <c r="D53" s="6"/>
       <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
+      <c r="F53" s="87"/>
       <c r="G53" s="11"/>
       <c r="H53" s="11"/>
       <c r="I53" s="14"/>
@@ -47731,7 +47747,7 @@
       <c r="C54" s="11"/>
       <c r="D54" s="6"/>
       <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
+      <c r="F54" s="87"/>
       <c r="G54" s="11"/>
       <c r="H54" s="11"/>
       <c r="I54" s="14"/>
@@ -47747,7 +47763,7 @@
       <c r="C55" s="11"/>
       <c r="D55" s="6"/>
       <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
+      <c r="F55" s="87"/>
       <c r="G55" s="11"/>
       <c r="H55" s="11"/>
       <c r="I55" s="14"/>
@@ -47763,7 +47779,7 @@
       <c r="C56" s="11"/>
       <c r="D56" s="6"/>
       <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
+      <c r="F56" s="87"/>
       <c r="G56" s="11"/>
       <c r="H56" s="11"/>
       <c r="I56" s="14"/>
@@ -47779,7 +47795,7 @@
       <c r="C57" s="11"/>
       <c r="D57" s="6"/>
       <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
+      <c r="F57" s="87"/>
       <c r="G57" s="11"/>
       <c r="H57" s="11"/>
       <c r="I57" s="14"/>
@@ -47795,7 +47811,7 @@
       <c r="C58" s="11"/>
       <c r="D58" s="6"/>
       <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
+      <c r="F58" s="87"/>
       <c r="G58" s="11"/>
       <c r="H58" s="11"/>
       <c r="I58" s="14"/>
@@ -47811,7 +47827,7 @@
       <c r="C59" s="11"/>
       <c r="D59" s="6"/>
       <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
+      <c r="F59" s="87"/>
       <c r="G59" s="11"/>
       <c r="H59" s="11"/>
       <c r="I59" s="14"/>
@@ -47827,7 +47843,7 @@
       <c r="C60" s="11"/>
       <c r="D60" s="6"/>
       <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
+      <c r="F60" s="87"/>
       <c r="G60" s="11"/>
       <c r="H60" s="11"/>
       <c r="I60" s="14"/>
@@ -47843,7 +47859,7 @@
       <c r="C61" s="11"/>
       <c r="D61" s="6"/>
       <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
+      <c r="F61" s="87"/>
       <c r="G61" s="11"/>
       <c r="H61" s="11"/>
       <c r="I61" s="14"/>
@@ -47859,7 +47875,7 @@
       <c r="C62" s="11"/>
       <c r="D62" s="6"/>
       <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
+      <c r="F62" s="87"/>
       <c r="G62" s="11"/>
       <c r="H62" s="11"/>
       <c r="I62" s="14"/>
@@ -47875,7 +47891,7 @@
       <c r="C63" s="11"/>
       <c r="D63" s="6"/>
       <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
+      <c r="F63" s="87"/>
       <c r="G63" s="11"/>
       <c r="H63" s="11"/>
       <c r="I63" s="14"/>
@@ -47891,7 +47907,7 @@
       <c r="C64" s="11"/>
       <c r="D64" s="6"/>
       <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
+      <c r="F64" s="87"/>
       <c r="G64" s="11"/>
       <c r="H64" s="11"/>
       <c r="I64" s="14"/>
@@ -47907,7 +47923,7 @@
       <c r="C65" s="11"/>
       <c r="D65" s="6"/>
       <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
+      <c r="F65" s="87"/>
       <c r="G65" s="11"/>
       <c r="H65" s="11"/>
       <c r="I65" s="14"/>
@@ -47923,7 +47939,7 @@
       <c r="C66" s="11"/>
       <c r="D66" s="6"/>
       <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
+      <c r="F66" s="87"/>
       <c r="G66" s="11"/>
       <c r="H66" s="11"/>
       <c r="I66" s="14"/>
@@ -47939,7 +47955,7 @@
       <c r="C67" s="11"/>
       <c r="D67" s="6"/>
       <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
+      <c r="F67" s="87"/>
       <c r="G67" s="11"/>
       <c r="H67" s="11"/>
       <c r="I67" s="14"/>
@@ -47955,7 +47971,7 @@
       <c r="C68" s="11"/>
       <c r="D68" s="6"/>
       <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
+      <c r="F68" s="87"/>
       <c r="G68" s="11"/>
       <c r="H68" s="11"/>
       <c r="I68" s="14"/>
@@ -47971,7 +47987,7 @@
       <c r="C69" s="11"/>
       <c r="D69" s="6"/>
       <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
+      <c r="F69" s="87"/>
       <c r="G69" s="11"/>
       <c r="H69" s="11"/>
       <c r="I69" s="14"/>
@@ -47987,7 +48003,7 @@
       <c r="C70" s="11"/>
       <c r="D70" s="6"/>
       <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
+      <c r="F70" s="87"/>
       <c r="G70" s="11"/>
       <c r="H70" s="11"/>
       <c r="I70" s="14"/>
@@ -48003,7 +48019,7 @@
       <c r="C71" s="11"/>
       <c r="D71" s="6"/>
       <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
+      <c r="F71" s="87"/>
       <c r="G71" s="11"/>
       <c r="H71" s="11"/>
       <c r="I71" s="14"/>
@@ -48019,7 +48035,7 @@
       <c r="C72" s="11"/>
       <c r="D72" s="6"/>
       <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
+      <c r="F72" s="87"/>
       <c r="G72" s="11"/>
       <c r="H72" s="11"/>
       <c r="I72" s="14"/>
@@ -48035,7 +48051,7 @@
       <c r="C73" s="11"/>
       <c r="D73" s="6"/>
       <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
+      <c r="F73" s="87"/>
       <c r="G73" s="11"/>
       <c r="H73" s="11"/>
       <c r="I73" s="14"/>
@@ -48051,7 +48067,7 @@
       <c r="C74" s="11"/>
       <c r="D74" s="6"/>
       <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
+      <c r="F74" s="87"/>
       <c r="G74" s="11"/>
       <c r="H74" s="11"/>
       <c r="I74" s="14"/>
@@ -48067,7 +48083,7 @@
       <c r="C75" s="11"/>
       <c r="D75" s="6"/>
       <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
+      <c r="F75" s="87"/>
       <c r="G75" s="11"/>
       <c r="H75" s="11"/>
       <c r="I75" s="14"/>
@@ -48083,7 +48099,7 @@
       <c r="C76" s="11"/>
       <c r="D76" s="6"/>
       <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
+      <c r="F76" s="87"/>
       <c r="G76" s="11"/>
       <c r="H76" s="11"/>
       <c r="I76" s="14"/>
@@ -48099,7 +48115,7 @@
       <c r="C77" s="11"/>
       <c r="D77" s="6"/>
       <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
+      <c r="F77" s="87"/>
       <c r="G77" s="11"/>
       <c r="H77" s="11"/>
       <c r="I77" s="14"/>
@@ -48115,7 +48131,7 @@
       <c r="C78" s="11"/>
       <c r="D78" s="6"/>
       <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
+      <c r="F78" s="87"/>
       <c r="G78" s="11"/>
       <c r="H78" s="11"/>
       <c r="I78" s="14"/>
@@ -48131,7 +48147,7 @@
       <c r="C79" s="11"/>
       <c r="D79" s="6"/>
       <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
+      <c r="F79" s="87"/>
       <c r="G79" s="11"/>
       <c r="H79" s="11"/>
       <c r="I79" s="14"/>
@@ -48147,7 +48163,7 @@
       <c r="C80" s="11"/>
       <c r="D80" s="6"/>
       <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
+      <c r="F80" s="87"/>
       <c r="G80" s="11"/>
       <c r="H80" s="11"/>
       <c r="I80" s="14"/>
@@ -48163,7 +48179,7 @@
       <c r="C81" s="11"/>
       <c r="D81" s="6"/>
       <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
+      <c r="F81" s="87"/>
       <c r="G81" s="11"/>
       <c r="H81" s="11"/>
       <c r="I81" s="14"/>
@@ -48179,7 +48195,7 @@
       <c r="C82" s="11"/>
       <c r="D82" s="6"/>
       <c r="E82" s="11"/>
-      <c r="F82" s="11"/>
+      <c r="F82" s="87"/>
       <c r="G82" s="11"/>
       <c r="H82" s="11"/>
       <c r="I82" s="14"/>
@@ -48195,7 +48211,7 @@
       <c r="C83" s="11"/>
       <c r="D83" s="6"/>
       <c r="E83" s="11"/>
-      <c r="F83" s="11"/>
+      <c r="F83" s="87"/>
       <c r="G83" s="11"/>
       <c r="H83" s="11"/>
       <c r="I83" s="14"/>
@@ -48211,7 +48227,7 @@
       <c r="C84" s="11"/>
       <c r="D84" s="6"/>
       <c r="E84" s="11"/>
-      <c r="F84" s="11"/>
+      <c r="F84" s="87"/>
       <c r="G84" s="11"/>
       <c r="H84" s="11"/>
       <c r="I84" s="14"/>
@@ -48227,7 +48243,7 @@
       <c r="C85" s="11"/>
       <c r="D85" s="6"/>
       <c r="E85" s="11"/>
-      <c r="F85" s="11"/>
+      <c r="F85" s="87"/>
       <c r="G85" s="11"/>
       <c r="H85" s="11"/>
       <c r="I85" s="14"/>
@@ -48243,7 +48259,7 @@
       <c r="C86" s="11"/>
       <c r="D86" s="6"/>
       <c r="E86" s="11"/>
-      <c r="F86" s="11"/>
+      <c r="F86" s="87"/>
       <c r="G86" s="11"/>
       <c r="H86" s="11"/>
       <c r="I86" s="14"/>
@@ -48259,7 +48275,7 @@
       <c r="C87" s="11"/>
       <c r="D87" s="6"/>
       <c r="E87" s="11"/>
-      <c r="F87" s="11"/>
+      <c r="F87" s="87"/>
       <c r="G87" s="11"/>
       <c r="H87" s="11"/>
       <c r="I87" s="14"/>
@@ -48275,7 +48291,7 @@
       <c r="C88" s="11"/>
       <c r="D88" s="6"/>
       <c r="E88" s="11"/>
-      <c r="F88" s="11"/>
+      <c r="F88" s="87"/>
       <c r="G88" s="11"/>
       <c r="H88" s="11"/>
       <c r="I88" s="14"/>
@@ -48291,7 +48307,7 @@
       <c r="C89" s="11"/>
       <c r="D89" s="6"/>
       <c r="E89" s="11"/>
-      <c r="F89" s="11"/>
+      <c r="F89" s="87"/>
       <c r="G89" s="11"/>
       <c r="H89" s="11"/>
       <c r="I89" s="14"/>
@@ -48307,7 +48323,7 @@
       <c r="C90" s="11"/>
       <c r="D90" s="6"/>
       <c r="E90" s="11"/>
-      <c r="F90" s="11"/>
+      <c r="F90" s="87"/>
       <c r="G90" s="11"/>
       <c r="H90" s="11"/>
       <c r="I90" s="14"/>
@@ -48323,7 +48339,7 @@
       <c r="C91" s="11"/>
       <c r="D91" s="6"/>
       <c r="E91" s="11"/>
-      <c r="F91" s="11"/>
+      <c r="F91" s="87"/>
       <c r="G91" s="11"/>
       <c r="H91" s="11"/>
       <c r="I91" s="14"/>
@@ -48339,7 +48355,7 @@
       <c r="C92" s="11"/>
       <c r="D92" s="6"/>
       <c r="E92" s="11"/>
-      <c r="F92" s="11"/>
+      <c r="F92" s="87"/>
       <c r="G92" s="11"/>
       <c r="H92" s="11"/>
       <c r="I92" s="14"/>
@@ -48355,7 +48371,7 @@
       <c r="C93" s="11"/>
       <c r="D93" s="6"/>
       <c r="E93" s="11"/>
-      <c r="F93" s="11"/>
+      <c r="F93" s="87"/>
       <c r="G93" s="11"/>
       <c r="H93" s="11"/>
       <c r="I93" s="14"/>
@@ -48371,7 +48387,7 @@
       <c r="C94" s="11"/>
       <c r="D94" s="6"/>
       <c r="E94" s="11"/>
-      <c r="F94" s="11"/>
+      <c r="F94" s="87"/>
       <c r="G94" s="11"/>
       <c r="H94" s="11"/>
       <c r="I94" s="14"/>
@@ -48387,7 +48403,7 @@
       <c r="C95" s="11"/>
       <c r="D95" s="6"/>
       <c r="E95" s="11"/>
-      <c r="F95" s="11"/>
+      <c r="F95" s="87"/>
       <c r="G95" s="11"/>
       <c r="H95" s="11"/>
       <c r="I95" s="14"/>
@@ -48403,7 +48419,7 @@
       <c r="C96" s="11"/>
       <c r="D96" s="6"/>
       <c r="E96" s="11"/>
-      <c r="F96" s="11"/>
+      <c r="F96" s="87"/>
       <c r="G96" s="11"/>
       <c r="H96" s="11"/>
       <c r="I96" s="14"/>
@@ -48419,7 +48435,7 @@
       <c r="C97" s="11"/>
       <c r="D97" s="6"/>
       <c r="E97" s="11"/>
-      <c r="F97" s="11"/>
+      <c r="F97" s="87"/>
       <c r="G97" s="11"/>
       <c r="H97" s="11"/>
       <c r="I97" s="14"/>
@@ -48435,7 +48451,7 @@
       <c r="C98" s="11"/>
       <c r="D98" s="6"/>
       <c r="E98" s="11"/>
-      <c r="F98" s="11"/>
+      <c r="F98" s="87"/>
       <c r="G98" s="11"/>
       <c r="H98" s="11"/>
       <c r="I98" s="14"/>
@@ -48451,7 +48467,7 @@
       <c r="C99" s="11"/>
       <c r="D99" s="6"/>
       <c r="E99" s="11"/>
-      <c r="F99" s="11"/>
+      <c r="F99" s="87"/>
       <c r="G99" s="11"/>
       <c r="H99" s="11"/>
       <c r="I99" s="14"/>
@@ -48467,7 +48483,7 @@
       <c r="C100" s="11"/>
       <c r="D100" s="6"/>
       <c r="E100" s="11"/>
-      <c r="F100" s="11"/>
+      <c r="F100" s="87"/>
       <c r="G100" s="11"/>
       <c r="H100" s="11"/>
       <c r="I100" s="14"/>
@@ -48483,7 +48499,7 @@
       <c r="C101" s="11"/>
       <c r="D101" s="6"/>
       <c r="E101" s="11"/>
-      <c r="F101" s="11"/>
+      <c r="F101" s="87"/>
       <c r="G101" s="11"/>
       <c r="H101" s="11"/>
       <c r="I101" s="14"/>
@@ -48499,7 +48515,7 @@
       <c r="C102" s="11"/>
       <c r="D102" s="6"/>
       <c r="E102" s="11"/>
-      <c r="F102" s="11"/>
+      <c r="F102" s="87"/>
       <c r="G102" s="11"/>
       <c r="H102" s="11"/>
       <c r="I102" s="14"/>
@@ -48515,7 +48531,7 @@
       <c r="C103" s="11"/>
       <c r="D103" s="6"/>
       <c r="E103" s="11"/>
-      <c r="F103" s="11"/>
+      <c r="F103" s="87"/>
       <c r="G103" s="11"/>
       <c r="H103" s="11"/>
       <c r="I103" s="14"/>
@@ -48531,7 +48547,7 @@
       <c r="C104" s="11"/>
       <c r="D104" s="6"/>
       <c r="E104" s="11"/>
-      <c r="F104" s="11"/>
+      <c r="F104" s="87"/>
       <c r="G104" s="11"/>
       <c r="H104" s="11"/>
       <c r="I104" s="14"/>
@@ -48547,7 +48563,7 @@
       <c r="C105" s="11"/>
       <c r="D105" s="6"/>
       <c r="E105" s="11"/>
-      <c r="F105" s="11"/>
+      <c r="F105" s="87"/>
       <c r="G105" s="11"/>
       <c r="H105" s="11"/>
       <c r="I105" s="14"/>
@@ -48563,7 +48579,7 @@
       <c r="C106" s="11"/>
       <c r="D106" s="6"/>
       <c r="E106" s="11"/>
-      <c r="F106" s="11"/>
+      <c r="F106" s="87"/>
       <c r="G106" s="11"/>
       <c r="H106" s="11"/>
       <c r="I106" s="14"/>
@@ -48579,7 +48595,7 @@
       <c r="C107" s="11"/>
       <c r="D107" s="6"/>
       <c r="E107" s="11"/>
-      <c r="F107" s="11"/>
+      <c r="F107" s="87"/>
       <c r="G107" s="11"/>
       <c r="H107" s="11"/>
       <c r="I107" s="14"/>
@@ -48595,7 +48611,7 @@
       <c r="C108" s="11"/>
       <c r="D108" s="6"/>
       <c r="E108" s="11"/>
-      <c r="F108" s="11"/>
+      <c r="F108" s="87"/>
       <c r="G108" s="11"/>
       <c r="H108" s="11"/>
       <c r="I108" s="14"/>
@@ -48611,7 +48627,7 @@
       <c r="C109" s="11"/>
       <c r="D109" s="6"/>
       <c r="E109" s="11"/>
-      <c r="F109" s="11"/>
+      <c r="F109" s="87"/>
       <c r="G109" s="11"/>
       <c r="H109" s="11"/>
       <c r="I109" s="14"/>
@@ -48627,7 +48643,7 @@
       <c r="C110" s="11"/>
       <c r="D110" s="6"/>
       <c r="E110" s="11"/>
-      <c r="F110" s="11"/>
+      <c r="F110" s="87"/>
       <c r="G110" s="11"/>
       <c r="H110" s="11"/>
       <c r="I110" s="14"/>
@@ -48643,7 +48659,7 @@
       <c r="C111" s="11"/>
       <c r="D111" s="6"/>
       <c r="E111" s="11"/>
-      <c r="F111" s="11"/>
+      <c r="F111" s="87"/>
       <c r="G111" s="11"/>
       <c r="H111" s="11"/>
       <c r="I111" s="14"/>
@@ -48659,7 +48675,7 @@
       <c r="C112" s="11"/>
       <c r="D112" s="6"/>
       <c r="E112" s="11"/>
-      <c r="F112" s="11"/>
+      <c r="F112" s="87"/>
       <c r="G112" s="11"/>
       <c r="H112" s="11"/>
       <c r="I112" s="14"/>
@@ -48675,7 +48691,7 @@
       <c r="C113" s="11"/>
       <c r="D113" s="6"/>
       <c r="E113" s="11"/>
-      <c r="F113" s="11"/>
+      <c r="F113" s="87"/>
       <c r="G113" s="11"/>
       <c r="H113" s="11"/>
       <c r="I113" s="14"/>
@@ -48691,7 +48707,7 @@
       <c r="C114" s="11"/>
       <c r="D114" s="6"/>
       <c r="E114" s="11"/>
-      <c r="F114" s="11"/>
+      <c r="F114" s="87"/>
       <c r="G114" s="11"/>
       <c r="H114" s="11"/>
       <c r="I114" s="14"/>
@@ -48707,7 +48723,7 @@
       <c r="C115" s="11"/>
       <c r="D115" s="6"/>
       <c r="E115" s="11"/>
-      <c r="F115" s="11"/>
+      <c r="F115" s="87"/>
       <c r="G115" s="11"/>
       <c r="H115" s="11"/>
       <c r="I115" s="14"/>
@@ -48723,7 +48739,7 @@
       <c r="C116" s="11"/>
       <c r="D116" s="6"/>
       <c r="E116" s="11"/>
-      <c r="F116" s="11"/>
+      <c r="F116" s="87"/>
       <c r="G116" s="11"/>
       <c r="H116" s="11"/>
       <c r="I116" s="14"/>
@@ -48739,7 +48755,7 @@
       <c r="C117" s="11"/>
       <c r="D117" s="6"/>
       <c r="E117" s="11"/>
-      <c r="F117" s="11"/>
+      <c r="F117" s="87"/>
       <c r="G117" s="11"/>
       <c r="H117" s="11"/>
       <c r="I117" s="14"/>
@@ -48755,7 +48771,7 @@
       <c r="C118" s="11"/>
       <c r="D118" s="6"/>
       <c r="E118" s="11"/>
-      <c r="F118" s="11"/>
+      <c r="F118" s="87"/>
       <c r="G118" s="11"/>
       <c r="H118" s="11"/>
       <c r="I118" s="14"/>
@@ -48771,7 +48787,7 @@
       <c r="C119" s="11"/>
       <c r="D119" s="6"/>
       <c r="E119" s="11"/>
-      <c r="F119" s="11"/>
+      <c r="F119" s="87"/>
       <c r="G119" s="11"/>
       <c r="H119" s="11"/>
       <c r="I119" s="14"/>
@@ -48787,7 +48803,7 @@
       <c r="C120" s="11"/>
       <c r="D120" s="6"/>
       <c r="E120" s="11"/>
-      <c r="F120" s="11"/>
+      <c r="F120" s="87"/>
       <c r="G120" s="11"/>
       <c r="H120" s="11"/>
       <c r="I120" s="14"/>
@@ -48803,7 +48819,7 @@
       <c r="C121" s="11"/>
       <c r="D121" s="6"/>
       <c r="E121" s="11"/>
-      <c r="F121" s="11"/>
+      <c r="F121" s="87"/>
       <c r="G121" s="11"/>
       <c r="H121" s="11"/>
       <c r="I121" s="14"/>
@@ -48819,7 +48835,7 @@
       <c r="C122" s="11"/>
       <c r="D122" s="6"/>
       <c r="E122" s="11"/>
-      <c r="F122" s="11"/>
+      <c r="F122" s="87"/>
       <c r="G122" s="11"/>
       <c r="H122" s="11"/>
       <c r="I122" s="14"/>
@@ -48835,7 +48851,7 @@
       <c r="C123" s="11"/>
       <c r="D123" s="6"/>
       <c r="E123" s="11"/>
-      <c r="F123" s="11"/>
+      <c r="F123" s="87"/>
       <c r="G123" s="11"/>
       <c r="H123" s="11"/>
       <c r="I123" s="14"/>
@@ -48851,7 +48867,7 @@
       <c r="C124" s="11"/>
       <c r="D124" s="6"/>
       <c r="E124" s="11"/>
-      <c r="F124" s="11"/>
+      <c r="F124" s="87"/>
       <c r="G124" s="11"/>
       <c r="H124" s="11"/>
       <c r="I124" s="14"/>
@@ -48867,7 +48883,7 @@
       <c r="C125" s="11"/>
       <c r="D125" s="6"/>
       <c r="E125" s="11"/>
-      <c r="F125" s="11"/>
+      <c r="F125" s="87"/>
       <c r="G125" s="11"/>
       <c r="H125" s="11"/>
       <c r="I125" s="14"/>
@@ -48883,7 +48899,7 @@
       <c r="C126" s="11"/>
       <c r="D126" s="6"/>
       <c r="E126" s="11"/>
-      <c r="F126" s="11"/>
+      <c r="F126" s="87"/>
       <c r="G126" s="11"/>
       <c r="H126" s="11"/>
       <c r="I126" s="14"/>
@@ -48899,7 +48915,7 @@
       <c r="C127" s="11"/>
       <c r="D127" s="6"/>
       <c r="E127" s="11"/>
-      <c r="F127" s="11"/>
+      <c r="F127" s="87"/>
       <c r="G127" s="11"/>
       <c r="H127" s="11"/>
       <c r="I127" s="14"/>
@@ -48915,7 +48931,7 @@
       <c r="C128" s="11"/>
       <c r="D128" s="6"/>
       <c r="E128" s="11"/>
-      <c r="F128" s="11"/>
+      <c r="F128" s="87"/>
       <c r="G128" s="11"/>
       <c r="H128" s="11"/>
       <c r="I128" s="14"/>
@@ -48931,7 +48947,7 @@
       <c r="C129" s="11"/>
       <c r="D129" s="6"/>
       <c r="E129" s="11"/>
-      <c r="F129" s="11"/>
+      <c r="F129" s="87"/>
       <c r="G129" s="11"/>
       <c r="H129" s="11"/>
       <c r="I129" s="14"/>
@@ -48947,7 +48963,7 @@
       <c r="C130" s="11"/>
       <c r="D130" s="6"/>
       <c r="E130" s="11"/>
-      <c r="F130" s="11"/>
+      <c r="F130" s="87"/>
       <c r="G130" s="11"/>
       <c r="H130" s="11"/>
       <c r="I130" s="14"/>
@@ -48963,7 +48979,7 @@
       <c r="C131" s="11"/>
       <c r="D131" s="6"/>
       <c r="E131" s="11"/>
-      <c r="F131" s="11"/>
+      <c r="F131" s="87"/>
       <c r="G131" s="11"/>
       <c r="H131" s="11"/>
       <c r="I131" s="14"/>
@@ -48979,7 +48995,7 @@
       <c r="C132" s="11"/>
       <c r="D132" s="6"/>
       <c r="E132" s="11"/>
-      <c r="F132" s="11"/>
+      <c r="F132" s="87"/>
       <c r="G132" s="11"/>
       <c r="H132" s="11"/>
       <c r="I132" s="14"/>
@@ -48995,7 +49011,7 @@
       <c r="C133" s="11"/>
       <c r="D133" s="6"/>
       <c r="E133" s="11"/>
-      <c r="F133" s="11"/>
+      <c r="F133" s="87"/>
       <c r="G133" s="11"/>
       <c r="H133" s="11"/>
       <c r="I133" s="14"/>
@@ -49011,7 +49027,7 @@
       <c r="C134" s="11"/>
       <c r="D134" s="6"/>
       <c r="E134" s="11"/>
-      <c r="F134" s="11"/>
+      <c r="F134" s="87"/>
       <c r="G134" s="11"/>
       <c r="H134" s="11"/>
       <c r="I134" s="14"/>
@@ -49027,7 +49043,7 @@
       <c r="C135" s="11"/>
       <c r="D135" s="6"/>
       <c r="E135" s="11"/>
-      <c r="F135" s="11"/>
+      <c r="F135" s="87"/>
       <c r="G135" s="11"/>
       <c r="H135" s="11"/>
       <c r="I135" s="14"/>
@@ -49043,7 +49059,7 @@
       <c r="C136" s="11"/>
       <c r="D136" s="6"/>
       <c r="E136" s="11"/>
-      <c r="F136" s="11"/>
+      <c r="F136" s="87"/>
       <c r="G136" s="11"/>
       <c r="H136" s="11"/>
       <c r="I136" s="14"/>
@@ -49059,7 +49075,7 @@
       <c r="C137" s="11"/>
       <c r="D137" s="6"/>
       <c r="E137" s="11"/>
-      <c r="F137" s="11"/>
+      <c r="F137" s="87"/>
       <c r="G137" s="11"/>
       <c r="H137" s="11"/>
       <c r="I137" s="14"/>
@@ -49075,7 +49091,7 @@
       <c r="C138" s="11"/>
       <c r="D138" s="6"/>
       <c r="E138" s="11"/>
-      <c r="F138" s="11"/>
+      <c r="F138" s="87"/>
       <c r="G138" s="11"/>
       <c r="H138" s="11"/>
       <c r="I138" s="14"/>
@@ -49091,7 +49107,7 @@
       <c r="C139" s="11"/>
       <c r="D139" s="6"/>
       <c r="E139" s="11"/>
-      <c r="F139" s="11"/>
+      <c r="F139" s="87"/>
       <c r="G139" s="11"/>
       <c r="H139" s="11"/>
       <c r="I139" s="14"/>
@@ -49107,7 +49123,7 @@
       <c r="C140" s="11"/>
       <c r="D140" s="6"/>
       <c r="E140" s="11"/>
-      <c r="F140" s="11"/>
+      <c r="F140" s="87"/>
       <c r="G140" s="11"/>
       <c r="H140" s="11"/>
       <c r="I140" s="14"/>
@@ -49123,7 +49139,7 @@
       <c r="C141" s="11"/>
       <c r="D141" s="6"/>
       <c r="E141" s="11"/>
-      <c r="F141" s="11"/>
+      <c r="F141" s="87"/>
       <c r="G141" s="11"/>
       <c r="H141" s="11"/>
       <c r="I141" s="14"/>
@@ -49139,7 +49155,7 @@
       <c r="C142" s="11"/>
       <c r="D142" s="6"/>
       <c r="E142" s="11"/>
-      <c r="F142" s="11"/>
+      <c r="F142" s="87"/>
       <c r="G142" s="11"/>
       <c r="H142" s="11"/>
       <c r="I142" s="14"/>
@@ -49155,7 +49171,7 @@
       <c r="C143" s="11"/>
       <c r="D143" s="6"/>
       <c r="E143" s="11"/>
-      <c r="F143" s="11"/>
+      <c r="F143" s="87"/>
       <c r="G143" s="11"/>
       <c r="H143" s="11"/>
       <c r="I143" s="14"/>
@@ -49171,7 +49187,7 @@
       <c r="C144" s="11"/>
       <c r="D144" s="6"/>
       <c r="E144" s="11"/>
-      <c r="F144" s="11"/>
+      <c r="F144" s="87"/>
       <c r="G144" s="11"/>
       <c r="H144" s="11"/>
       <c r="I144" s="14"/>
@@ -49187,7 +49203,7 @@
       <c r="C145" s="11"/>
       <c r="D145" s="6"/>
       <c r="E145" s="11"/>
-      <c r="F145" s="11"/>
+      <c r="F145" s="87"/>
       <c r="G145" s="11"/>
       <c r="H145" s="11"/>
       <c r="I145" s="14"/>
@@ -49203,7 +49219,7 @@
       <c r="C146" s="11"/>
       <c r="D146" s="6"/>
       <c r="E146" s="11"/>
-      <c r="F146" s="11"/>
+      <c r="F146" s="87"/>
       <c r="G146" s="11"/>
       <c r="H146" s="11"/>
       <c r="I146" s="14"/>
@@ -49219,7 +49235,7 @@
       <c r="C147" s="11"/>
       <c r="D147" s="6"/>
       <c r="E147" s="11"/>
-      <c r="F147" s="11"/>
+      <c r="F147" s="87"/>
       <c r="G147" s="11"/>
       <c r="H147" s="11"/>
       <c r="I147" s="14"/>
@@ -49235,7 +49251,7 @@
       <c r="C148" s="11"/>
       <c r="D148" s="6"/>
       <c r="E148" s="11"/>
-      <c r="F148" s="11"/>
+      <c r="F148" s="87"/>
       <c r="G148" s="11"/>
       <c r="H148" s="11"/>
       <c r="I148" s="14"/>
@@ -49251,7 +49267,7 @@
       <c r="C149" s="11"/>
       <c r="D149" s="6"/>
       <c r="E149" s="11"/>
-      <c r="F149" s="11"/>
+      <c r="F149" s="87"/>
       <c r="G149" s="11"/>
       <c r="H149" s="11"/>
       <c r="I149" s="14"/>
@@ -49267,7 +49283,7 @@
       <c r="C150" s="11"/>
       <c r="D150" s="6"/>
       <c r="E150" s="11"/>
-      <c r="F150" s="11"/>
+      <c r="F150" s="87"/>
       <c r="G150" s="11"/>
       <c r="H150" s="11"/>
       <c r="I150" s="14"/>
@@ -49283,7 +49299,7 @@
       <c r="C151" s="11"/>
       <c r="D151" s="6"/>
       <c r="E151" s="11"/>
-      <c r="F151" s="11"/>
+      <c r="F151" s="87"/>
       <c r="G151" s="11"/>
       <c r="H151" s="11"/>
       <c r="I151" s="14"/>
@@ -49299,7 +49315,7 @@
       <c r="C152" s="11"/>
       <c r="D152" s="6"/>
       <c r="E152" s="11"/>
-      <c r="F152" s="11"/>
+      <c r="F152" s="87"/>
       <c r="G152" s="11"/>
       <c r="H152" s="11"/>
       <c r="I152" s="14"/>
@@ -49315,7 +49331,7 @@
       <c r="C153" s="11"/>
       <c r="D153" s="6"/>
       <c r="E153" s="11"/>
-      <c r="F153" s="11"/>
+      <c r="F153" s="87"/>
       <c r="G153" s="11"/>
       <c r="H153" s="11"/>
       <c r="I153" s="14"/>
@@ -49331,7 +49347,7 @@
       <c r="C154" s="11"/>
       <c r="D154" s="6"/>
       <c r="E154" s="11"/>
-      <c r="F154" s="11"/>
+      <c r="F154" s="87"/>
       <c r="G154" s="11"/>
       <c r="H154" s="11"/>
       <c r="I154" s="14"/>
@@ -49347,7 +49363,7 @@
       <c r="C155" s="12"/>
       <c r="D155" s="8"/>
       <c r="E155" s="12"/>
-      <c r="F155" s="12"/>
+      <c r="F155" s="88"/>
       <c r="G155" s="12"/>
       <c r="H155" s="12"/>
       <c r="I155" s="15"/>

--- a/data/Template_Resmi_Database_SIRUMAH.xlsx
+++ b/data/Template_Resmi_Database_SIRUMAH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DAABA62-8451-404C-B362-BB45BCF3BBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392CF0BB-7058-4792-808A-700E453BEC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12781" uniqueCount="1954">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12780" uniqueCount="1954">
   <si>
     <t>TEMPLATE RESMI DATABASE SIRUMAH — DATA PERUMAHAN</t>
   </si>
@@ -5909,7 +5909,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
     <numFmt numFmtId="166" formatCode="[$Rp-421]\ #,##0"/>
-    <numFmt numFmtId="168" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="167" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -6539,6 +6539,17 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="6" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -6579,24 +6590,13 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="168" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
+      <numFmt numFmtId="167" formatCode="[$-421]dd\ mmmm\ yyyy;@"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="0.000000"/>
@@ -6996,111 +6996,111 @@
     <col min="21" max="21" width="32" customWidth="1"/>
     <col min="22" max="22" width="17.25" customWidth="1"/>
     <col min="23" max="26" width="18" customWidth="1"/>
-    <col min="27" max="27" width="18" style="101" customWidth="1"/>
+    <col min="27" max="27" width="18" style="87" customWidth="1"/>
     <col min="28" max="30" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="23">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="83"/>
-      <c r="T1" s="83"/>
-      <c r="U1" s="83"/>
-      <c r="V1" s="83"/>
-      <c r="W1" s="83"/>
-      <c r="X1" s="83"/>
-      <c r="Y1" s="83"/>
-      <c r="Z1" s="84"/>
-      <c r="AA1" s="84"/>
-      <c r="AB1" s="84"/>
-      <c r="AC1" s="84"/>
-      <c r="AD1" s="84"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
+      <c r="V1" s="88"/>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="88"/>
+      <c r="Z1" s="89"/>
+      <c r="AA1" s="89"/>
+      <c r="AB1" s="89"/>
+      <c r="AC1" s="89"/>
+      <c r="AD1" s="89"/>
     </row>
     <row r="2" spans="1:30">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="85"/>
-      <c r="S2" s="85"/>
-      <c r="T2" s="85"/>
-      <c r="U2" s="85"/>
-      <c r="V2" s="85"/>
-      <c r="W2" s="85"/>
-      <c r="X2" s="85"/>
-      <c r="Y2" s="85"/>
-      <c r="Z2" s="84"/>
-      <c r="AA2" s="84"/>
-      <c r="AB2" s="84"/>
-      <c r="AC2" s="84"/>
-      <c r="AD2" s="84"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
+      <c r="O2" s="90"/>
+      <c r="P2" s="90"/>
+      <c r="Q2" s="90"/>
+      <c r="R2" s="90"/>
+      <c r="S2" s="90"/>
+      <c r="T2" s="90"/>
+      <c r="U2" s="90"/>
+      <c r="V2" s="90"/>
+      <c r="W2" s="90"/>
+      <c r="X2" s="90"/>
+      <c r="Y2" s="90"/>
+      <c r="Z2" s="89"/>
+      <c r="AA2" s="89"/>
+      <c r="AB2" s="89"/>
+      <c r="AC2" s="89"/>
+      <c r="AD2" s="89"/>
     </row>
     <row r="3" spans="1:30">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
-      <c r="O3" s="86"/>
-      <c r="P3" s="86"/>
-      <c r="Q3" s="86"/>
-      <c r="R3" s="86"/>
-      <c r="S3" s="86"/>
-      <c r="T3" s="86"/>
-      <c r="U3" s="86"/>
-      <c r="V3" s="86"/>
-      <c r="W3" s="86"/>
-      <c r="X3" s="86"/>
-      <c r="Y3" s="86"/>
-      <c r="Z3" s="87"/>
-      <c r="AA3" s="87"/>
-      <c r="AB3" s="87"/>
-      <c r="AC3" s="87"/>
-      <c r="AD3" s="87"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
+      <c r="N3" s="91"/>
+      <c r="O3" s="91"/>
+      <c r="P3" s="91"/>
+      <c r="Q3" s="91"/>
+      <c r="R3" s="91"/>
+      <c r="S3" s="91"/>
+      <c r="T3" s="91"/>
+      <c r="U3" s="91"/>
+      <c r="V3" s="91"/>
+      <c r="W3" s="91"/>
+      <c r="X3" s="91"/>
+      <c r="Y3" s="91"/>
+      <c r="Z3" s="92"/>
+      <c r="AA3" s="92"/>
+      <c r="AB3" s="92"/>
+      <c r="AC3" s="92"/>
+      <c r="AD3" s="92"/>
     </row>
     <row r="5" spans="1:30" ht="39">
       <c r="A5" s="1" t="s">
@@ -7181,7 +7181,7 @@
       <c r="Z5" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="AA5" s="97" t="s">
+      <c r="AA5" s="83" t="s">
         <v>29</v>
       </c>
       <c r="AB5" s="46" t="s">
@@ -7263,7 +7263,7 @@
       <c r="Z6" s="44" t="s">
         <v>860</v>
       </c>
-      <c r="AA6" s="98">
+      <c r="AA6" s="84">
         <v>46220</v>
       </c>
       <c r="AB6" s="47"/>
@@ -7343,7 +7343,7 @@
       <c r="Z7" s="44" t="s">
         <v>860</v>
       </c>
-      <c r="AA7" s="98">
+      <c r="AA7" s="84">
         <v>46220</v>
       </c>
       <c r="AB7" s="48"/>
@@ -7423,7 +7423,7 @@
       <c r="Z8" s="44" t="s">
         <v>860</v>
       </c>
-      <c r="AA8" s="98">
+      <c r="AA8" s="84">
         <v>46220</v>
       </c>
       <c r="AB8" s="48"/>
@@ -7499,7 +7499,7 @@
       <c r="X9" s="55"/>
       <c r="Y9" s="29"/>
       <c r="Z9" s="45"/>
-      <c r="AA9" s="99"/>
+      <c r="AA9" s="85"/>
       <c r="AB9" s="48"/>
       <c r="AC9">
         <f t="shared" si="0"/>
@@ -7575,7 +7575,7 @@
       <c r="X10" s="55"/>
       <c r="Y10" s="29"/>
       <c r="Z10" s="45"/>
-      <c r="AA10" s="99"/>
+      <c r="AA10" s="85"/>
       <c r="AB10" s="48"/>
       <c r="AC10">
         <f t="shared" si="0"/>
@@ -7649,7 +7649,7 @@
       <c r="X11" s="55"/>
       <c r="Y11" s="29"/>
       <c r="Z11" s="45"/>
-      <c r="AA11" s="99"/>
+      <c r="AA11" s="85"/>
       <c r="AB11" s="48"/>
       <c r="AC11">
         <f t="shared" si="0"/>
@@ -7725,7 +7725,7 @@
       <c r="X12" s="55"/>
       <c r="Y12" s="29"/>
       <c r="Z12" s="45"/>
-      <c r="AA12" s="99"/>
+      <c r="AA12" s="85"/>
       <c r="AB12" s="48"/>
       <c r="AC12">
         <f t="shared" si="0"/>
@@ -7799,7 +7799,7 @@
       <c r="X13" s="55"/>
       <c r="Y13" s="29"/>
       <c r="Z13" s="45"/>
-      <c r="AA13" s="99"/>
+      <c r="AA13" s="85"/>
       <c r="AB13" s="48"/>
       <c r="AC13">
         <f t="shared" si="0"/>
@@ -7873,7 +7873,7 @@
       <c r="X14" s="55"/>
       <c r="Y14" s="29"/>
       <c r="Z14" s="45"/>
-      <c r="AA14" s="99"/>
+      <c r="AA14" s="85"/>
       <c r="AB14" s="48"/>
       <c r="AC14">
         <f t="shared" si="0"/>
@@ -7951,7 +7951,7 @@
       <c r="X15" s="55"/>
       <c r="Y15" s="29"/>
       <c r="Z15" s="45"/>
-      <c r="AA15" s="99"/>
+      <c r="AA15" s="85"/>
       <c r="AB15" s="48"/>
       <c r="AC15">
         <f t="shared" si="0"/>
@@ -8025,7 +8025,7 @@
       <c r="X16" s="55"/>
       <c r="Y16" s="29"/>
       <c r="Z16" s="45"/>
-      <c r="AA16" s="99"/>
+      <c r="AA16" s="85"/>
       <c r="AB16" s="48"/>
       <c r="AC16">
         <f t="shared" si="0"/>
@@ -8101,7 +8101,7 @@
       <c r="X17" s="55"/>
       <c r="Y17" s="29"/>
       <c r="Z17" s="45"/>
-      <c r="AA17" s="99"/>
+      <c r="AA17" s="85"/>
       <c r="AB17" s="48"/>
       <c r="AC17">
         <f t="shared" si="0"/>
@@ -8177,7 +8177,7 @@
       <c r="X18" s="55"/>
       <c r="Y18" s="29"/>
       <c r="Z18" s="45"/>
-      <c r="AA18" s="99"/>
+      <c r="AA18" s="85"/>
       <c r="AB18" s="48"/>
       <c r="AC18">
         <f t="shared" si="0"/>
@@ -8255,7 +8255,7 @@
       <c r="X19" s="55"/>
       <c r="Y19" s="29"/>
       <c r="Z19" s="45"/>
-      <c r="AA19" s="99"/>
+      <c r="AA19" s="85"/>
       <c r="AB19" s="48"/>
       <c r="AC19">
         <f t="shared" si="0"/>
@@ -8333,7 +8333,7 @@
       <c r="X20" s="55"/>
       <c r="Y20" s="29"/>
       <c r="Z20" s="45"/>
-      <c r="AA20" s="99"/>
+      <c r="AA20" s="85"/>
       <c r="AB20" s="48"/>
       <c r="AC20">
         <f t="shared" si="0"/>
@@ -8411,7 +8411,7 @@
       <c r="X21" s="55"/>
       <c r="Y21" s="29"/>
       <c r="Z21" s="45"/>
-      <c r="AA21" s="99"/>
+      <c r="AA21" s="85"/>
       <c r="AB21" s="48"/>
       <c r="AC21">
         <f t="shared" si="0"/>
@@ -8487,7 +8487,7 @@
       <c r="X22" s="55"/>
       <c r="Y22" s="29"/>
       <c r="Z22" s="45"/>
-      <c r="AA22" s="99"/>
+      <c r="AA22" s="85"/>
       <c r="AB22" s="48"/>
       <c r="AC22">
         <f t="shared" si="0"/>
@@ -8563,7 +8563,7 @@
       <c r="X23" s="55"/>
       <c r="Y23" s="29"/>
       <c r="Z23" s="45"/>
-      <c r="AA23" s="99"/>
+      <c r="AA23" s="85"/>
       <c r="AB23" s="48"/>
       <c r="AC23">
         <f t="shared" si="0"/>
@@ -8637,7 +8637,7 @@
       <c r="X24" s="55"/>
       <c r="Y24" s="29"/>
       <c r="Z24" s="45"/>
-      <c r="AA24" s="99"/>
+      <c r="AA24" s="85"/>
       <c r="AB24" s="48"/>
       <c r="AC24">
         <f t="shared" si="0"/>
@@ -8711,7 +8711,7 @@
       <c r="X25" s="55"/>
       <c r="Y25" s="29"/>
       <c r="Z25" s="45"/>
-      <c r="AA25" s="99"/>
+      <c r="AA25" s="85"/>
       <c r="AB25" s="48"/>
       <c r="AC25">
         <f t="shared" si="0"/>
@@ -8785,7 +8785,7 @@
       <c r="X26" s="55"/>
       <c r="Y26" s="29"/>
       <c r="Z26" s="45"/>
-      <c r="AA26" s="99"/>
+      <c r="AA26" s="85"/>
       <c r="AB26" s="48"/>
       <c r="AC26">
         <f t="shared" si="0"/>
@@ -8861,7 +8861,7 @@
       <c r="X27" s="55"/>
       <c r="Y27" s="29"/>
       <c r="Z27" s="45"/>
-      <c r="AA27" s="99"/>
+      <c r="AA27" s="85"/>
       <c r="AB27" s="48"/>
       <c r="AC27">
         <f t="shared" si="0"/>
@@ -8935,7 +8935,7 @@
       <c r="X28" s="55"/>
       <c r="Y28" s="29"/>
       <c r="Z28" s="45"/>
-      <c r="AA28" s="99"/>
+      <c r="AA28" s="85"/>
       <c r="AB28" s="48"/>
       <c r="AC28">
         <f t="shared" si="0"/>
@@ -9009,7 +9009,7 @@
       <c r="X29" s="55"/>
       <c r="Y29" s="29"/>
       <c r="Z29" s="45"/>
-      <c r="AA29" s="99"/>
+      <c r="AA29" s="85"/>
       <c r="AB29" s="48"/>
       <c r="AC29">
         <f t="shared" si="0"/>
@@ -9083,7 +9083,7 @@
       <c r="X30" s="55"/>
       <c r="Y30" s="29"/>
       <c r="Z30" s="45"/>
-      <c r="AA30" s="99"/>
+      <c r="AA30" s="85"/>
       <c r="AB30" s="48"/>
       <c r="AC30">
         <f t="shared" si="0"/>
@@ -9155,7 +9155,7 @@
       <c r="X31" s="55"/>
       <c r="Y31" s="29"/>
       <c r="Z31" s="45"/>
-      <c r="AA31" s="99"/>
+      <c r="AA31" s="85"/>
       <c r="AB31" s="48"/>
       <c r="AC31">
         <f t="shared" si="0"/>
@@ -9229,7 +9229,7 @@
       <c r="X32" s="55"/>
       <c r="Y32" s="29"/>
       <c r="Z32" s="45"/>
-      <c r="AA32" s="99"/>
+      <c r="AA32" s="85"/>
       <c r="AB32" s="48"/>
       <c r="AC32">
         <f t="shared" si="0"/>
@@ -9303,7 +9303,7 @@
       <c r="X33" s="55"/>
       <c r="Y33" s="29"/>
       <c r="Z33" s="45"/>
-      <c r="AA33" s="99"/>
+      <c r="AA33" s="85"/>
       <c r="AB33" s="48"/>
       <c r="AC33">
         <f t="shared" si="0"/>
@@ -9377,7 +9377,7 @@
       <c r="X34" s="55"/>
       <c r="Y34" s="29"/>
       <c r="Z34" s="45"/>
-      <c r="AA34" s="99"/>
+      <c r="AA34" s="85"/>
       <c r="AB34" s="48"/>
       <c r="AC34">
         <f t="shared" si="0"/>
@@ -9453,7 +9453,7 @@
       <c r="X35" s="55"/>
       <c r="Y35" s="29"/>
       <c r="Z35" s="45"/>
-      <c r="AA35" s="99"/>
+      <c r="AA35" s="85"/>
       <c r="AB35" s="48"/>
       <c r="AC35">
         <f t="shared" si="0"/>
@@ -9529,7 +9529,7 @@
       <c r="X36" s="55"/>
       <c r="Y36" s="29"/>
       <c r="Z36" s="45"/>
-      <c r="AA36" s="99"/>
+      <c r="AA36" s="85"/>
       <c r="AB36" s="48"/>
       <c r="AC36">
         <f t="shared" si="0"/>
@@ -9603,7 +9603,7 @@
       <c r="X37" s="55"/>
       <c r="Y37" s="29"/>
       <c r="Z37" s="45"/>
-      <c r="AA37" s="99"/>
+      <c r="AA37" s="85"/>
       <c r="AB37" s="48"/>
       <c r="AC37">
         <f t="shared" si="0"/>
@@ -9677,7 +9677,7 @@
       <c r="X38" s="55"/>
       <c r="Y38" s="29"/>
       <c r="Z38" s="45"/>
-      <c r="AA38" s="99"/>
+      <c r="AA38" s="85"/>
       <c r="AB38" s="48"/>
       <c r="AC38">
         <f t="shared" si="0"/>
@@ -9751,7 +9751,7 @@
       <c r="X39" s="55"/>
       <c r="Y39" s="29"/>
       <c r="Z39" s="45"/>
-      <c r="AA39" s="99"/>
+      <c r="AA39" s="85"/>
       <c r="AB39" s="48"/>
       <c r="AC39">
         <f t="shared" si="0"/>
@@ -9827,7 +9827,7 @@
       <c r="X40" s="55"/>
       <c r="Y40" s="29"/>
       <c r="Z40" s="45"/>
-      <c r="AA40" s="99"/>
+      <c r="AA40" s="85"/>
       <c r="AB40" s="48"/>
       <c r="AC40">
         <f t="shared" si="0"/>
@@ -9901,7 +9901,7 @@
       <c r="X41" s="55"/>
       <c r="Y41" s="29"/>
       <c r="Z41" s="45"/>
-      <c r="AA41" s="99"/>
+      <c r="AA41" s="85"/>
       <c r="AB41" s="48"/>
       <c r="AC41">
         <f t="shared" si="0"/>
@@ -9975,7 +9975,7 @@
       <c r="X42" s="55"/>
       <c r="Y42" s="29"/>
       <c r="Z42" s="45"/>
-      <c r="AA42" s="99"/>
+      <c r="AA42" s="85"/>
       <c r="AB42" s="48"/>
       <c r="AC42">
         <f t="shared" si="0"/>
@@ -10049,7 +10049,7 @@
       <c r="X43" s="55"/>
       <c r="Y43" s="29"/>
       <c r="Z43" s="45"/>
-      <c r="AA43" s="99"/>
+      <c r="AA43" s="85"/>
       <c r="AB43" s="48"/>
       <c r="AC43">
         <f t="shared" si="0"/>
@@ -10123,7 +10123,7 @@
       <c r="X44" s="55"/>
       <c r="Y44" s="29"/>
       <c r="Z44" s="45"/>
-      <c r="AA44" s="99"/>
+      <c r="AA44" s="85"/>
       <c r="AB44" s="48"/>
       <c r="AC44">
         <f t="shared" si="0"/>
@@ -10199,7 +10199,7 @@
       <c r="X45" s="55"/>
       <c r="Y45" s="29"/>
       <c r="Z45" s="45"/>
-      <c r="AA45" s="99"/>
+      <c r="AA45" s="85"/>
       <c r="AB45" s="48"/>
       <c r="AC45">
         <f t="shared" si="0"/>
@@ -10273,7 +10273,7 @@
       <c r="X46" s="55"/>
       <c r="Y46" s="29"/>
       <c r="Z46" s="45"/>
-      <c r="AA46" s="99"/>
+      <c r="AA46" s="85"/>
       <c r="AB46" s="48"/>
       <c r="AC46">
         <f t="shared" si="0"/>
@@ -10347,7 +10347,7 @@
       <c r="X47" s="55"/>
       <c r="Y47" s="29"/>
       <c r="Z47" s="45"/>
-      <c r="AA47" s="99"/>
+      <c r="AA47" s="85"/>
       <c r="AB47" s="48"/>
       <c r="AC47">
         <f t="shared" si="0"/>
@@ -10421,7 +10421,7 @@
       <c r="X48" s="55"/>
       <c r="Y48" s="29"/>
       <c r="Z48" s="45"/>
-      <c r="AA48" s="99"/>
+      <c r="AA48" s="85"/>
       <c r="AB48" s="48"/>
       <c r="AC48">
         <f t="shared" si="0"/>
@@ -10491,7 +10491,7 @@
       <c r="X49" s="55"/>
       <c r="Y49" s="29"/>
       <c r="Z49" s="45"/>
-      <c r="AA49" s="99"/>
+      <c r="AA49" s="85"/>
       <c r="AB49" s="48"/>
       <c r="AC49">
         <f t="shared" si="0"/>
@@ -10565,7 +10565,7 @@
       <c r="X50" s="55"/>
       <c r="Y50" s="29"/>
       <c r="Z50" s="45"/>
-      <c r="AA50" s="99"/>
+      <c r="AA50" s="85"/>
       <c r="AB50" s="48"/>
       <c r="AC50">
         <f t="shared" si="0"/>
@@ -10641,7 +10641,7 @@
       <c r="X51" s="55"/>
       <c r="Y51" s="29"/>
       <c r="Z51" s="45"/>
-      <c r="AA51" s="99"/>
+      <c r="AA51" s="85"/>
       <c r="AB51" s="48"/>
       <c r="AC51">
         <f t="shared" si="0"/>
@@ -10711,7 +10711,7 @@
       <c r="X52" s="55"/>
       <c r="Y52" s="67"/>
       <c r="Z52" s="45"/>
-      <c r="AA52" s="99"/>
+      <c r="AA52" s="85"/>
       <c r="AB52" s="78"/>
     </row>
     <row r="53" spans="1:30">
@@ -10779,7 +10779,7 @@
       <c r="X53" s="55"/>
       <c r="Y53" s="29"/>
       <c r="Z53" s="45"/>
-      <c r="AA53" s="99"/>
+      <c r="AA53" s="85"/>
       <c r="AB53" s="48"/>
       <c r="AC53">
         <f t="shared" ref="AC53:AC84" si="2">IF(A53="","",IFERROR(L53/K53,0))</f>
@@ -10855,7 +10855,7 @@
       <c r="X54" s="55"/>
       <c r="Y54" s="29"/>
       <c r="Z54" s="45"/>
-      <c r="AA54" s="99"/>
+      <c r="AA54" s="85"/>
       <c r="AB54" s="48"/>
       <c r="AC54">
         <f t="shared" si="2"/>
@@ -10933,7 +10933,7 @@
       <c r="X55" s="55"/>
       <c r="Y55" s="29"/>
       <c r="Z55" s="45"/>
-      <c r="AA55" s="99"/>
+      <c r="AA55" s="85"/>
       <c r="AB55" s="48"/>
       <c r="AC55">
         <f t="shared" si="2"/>
@@ -11011,7 +11011,7 @@
       <c r="X56" s="55"/>
       <c r="Y56" s="29"/>
       <c r="Z56" s="45"/>
-      <c r="AA56" s="99"/>
+      <c r="AA56" s="85"/>
       <c r="AB56" s="48"/>
       <c r="AC56">
         <f t="shared" si="2"/>
@@ -11085,7 +11085,7 @@
       <c r="X57" s="55"/>
       <c r="Y57" s="29"/>
       <c r="Z57" s="45"/>
-      <c r="AA57" s="99"/>
+      <c r="AA57" s="85"/>
       <c r="AB57" s="48"/>
       <c r="AC57">
         <f t="shared" si="2"/>
@@ -11159,7 +11159,7 @@
       <c r="X58" s="55"/>
       <c r="Y58" s="29"/>
       <c r="Z58" s="45"/>
-      <c r="AA58" s="99"/>
+      <c r="AA58" s="85"/>
       <c r="AB58" s="48"/>
       <c r="AC58">
         <f t="shared" si="2"/>
@@ -11233,7 +11233,7 @@
       <c r="X59" s="55"/>
       <c r="Y59" s="29"/>
       <c r="Z59" s="45"/>
-      <c r="AA59" s="99"/>
+      <c r="AA59" s="85"/>
       <c r="AB59" s="48"/>
       <c r="AC59">
         <f t="shared" si="2"/>
@@ -11307,7 +11307,7 @@
       <c r="X60" s="55"/>
       <c r="Y60" s="29"/>
       <c r="Z60" s="45"/>
-      <c r="AA60" s="99"/>
+      <c r="AA60" s="85"/>
       <c r="AB60" s="48"/>
       <c r="AC60">
         <f t="shared" si="2"/>
@@ -11381,7 +11381,7 @@
       <c r="X61" s="55"/>
       <c r="Y61" s="29"/>
       <c r="Z61" s="45"/>
-      <c r="AA61" s="99"/>
+      <c r="AA61" s="85"/>
       <c r="AB61" s="48"/>
       <c r="AC61">
         <f t="shared" si="2"/>
@@ -11455,7 +11455,7 @@
       <c r="X62" s="55"/>
       <c r="Y62" s="29"/>
       <c r="Z62" s="45"/>
-      <c r="AA62" s="99"/>
+      <c r="AA62" s="85"/>
       <c r="AB62" s="48"/>
       <c r="AC62">
         <f t="shared" si="2"/>
@@ -11525,7 +11525,7 @@
       <c r="X63" s="55"/>
       <c r="Y63" s="29"/>
       <c r="Z63" s="45"/>
-      <c r="AA63" s="99"/>
+      <c r="AA63" s="85"/>
       <c r="AB63" s="48"/>
       <c r="AC63">
         <f t="shared" si="2"/>
@@ -11601,7 +11601,7 @@
       <c r="X64" s="55"/>
       <c r="Y64" s="29"/>
       <c r="Z64" s="45"/>
-      <c r="AA64" s="99"/>
+      <c r="AA64" s="85"/>
       <c r="AB64" s="48"/>
       <c r="AC64">
         <f t="shared" si="2"/>
@@ -11675,7 +11675,7 @@
       <c r="X65" s="55"/>
       <c r="Y65" s="29"/>
       <c r="Z65" s="45"/>
-      <c r="AA65" s="99"/>
+      <c r="AA65" s="85"/>
       <c r="AB65" s="48"/>
       <c r="AC65">
         <f t="shared" si="2"/>
@@ -11749,7 +11749,7 @@
       <c r="X66" s="55"/>
       <c r="Y66" s="29"/>
       <c r="Z66" s="45"/>
-      <c r="AA66" s="99"/>
+      <c r="AA66" s="85"/>
       <c r="AB66" s="48"/>
       <c r="AC66">
         <f t="shared" si="2"/>
@@ -11823,7 +11823,7 @@
       <c r="X67" s="55"/>
       <c r="Y67" s="29"/>
       <c r="Z67" s="45"/>
-      <c r="AA67" s="99"/>
+      <c r="AA67" s="85"/>
       <c r="AB67" s="48"/>
       <c r="AC67">
         <f t="shared" si="2"/>
@@ -11899,7 +11899,7 @@
       <c r="X68" s="55"/>
       <c r="Y68" s="29"/>
       <c r="Z68" s="45"/>
-      <c r="AA68" s="99"/>
+      <c r="AA68" s="85"/>
       <c r="AB68" s="48"/>
       <c r="AC68">
         <f t="shared" si="2"/>
@@ -11975,7 +11975,7 @@
       <c r="X69" s="55"/>
       <c r="Y69" s="29"/>
       <c r="Z69" s="45"/>
-      <c r="AA69" s="99"/>
+      <c r="AA69" s="85"/>
       <c r="AB69" s="48"/>
       <c r="AC69">
         <f t="shared" si="2"/>
@@ -12051,7 +12051,7 @@
       <c r="X70" s="55"/>
       <c r="Y70" s="29"/>
       <c r="Z70" s="45"/>
-      <c r="AA70" s="99"/>
+      <c r="AA70" s="85"/>
       <c r="AB70" s="48"/>
       <c r="AC70">
         <f t="shared" si="2"/>
@@ -12127,7 +12127,7 @@
       <c r="X71" s="55"/>
       <c r="Y71" s="29"/>
       <c r="Z71" s="45"/>
-      <c r="AA71" s="99"/>
+      <c r="AA71" s="85"/>
       <c r="AB71" s="48"/>
       <c r="AC71">
         <f t="shared" si="2"/>
@@ -12203,7 +12203,7 @@
       <c r="X72" s="55"/>
       <c r="Y72" s="29"/>
       <c r="Z72" s="45"/>
-      <c r="AA72" s="99"/>
+      <c r="AA72" s="85"/>
       <c r="AB72" s="48"/>
       <c r="AC72">
         <f t="shared" si="2"/>
@@ -12279,7 +12279,7 @@
       <c r="X73" s="55"/>
       <c r="Y73" s="29"/>
       <c r="Z73" s="45"/>
-      <c r="AA73" s="99"/>
+      <c r="AA73" s="85"/>
       <c r="AB73" s="48"/>
       <c r="AC73">
         <f t="shared" si="2"/>
@@ -12355,7 +12355,7 @@
       <c r="X74" s="55"/>
       <c r="Y74" s="29"/>
       <c r="Z74" s="45"/>
-      <c r="AA74" s="99"/>
+      <c r="AA74" s="85"/>
       <c r="AB74" s="48"/>
       <c r="AC74">
         <f t="shared" si="2"/>
@@ -12429,7 +12429,7 @@
       <c r="X75" s="55"/>
       <c r="Y75" s="29"/>
       <c r="Z75" s="45"/>
-      <c r="AA75" s="99"/>
+      <c r="AA75" s="85"/>
       <c r="AB75" s="48"/>
       <c r="AC75">
         <f t="shared" si="2"/>
@@ -12503,7 +12503,7 @@
       <c r="X76" s="55"/>
       <c r="Y76" s="29"/>
       <c r="Z76" s="45"/>
-      <c r="AA76" s="99"/>
+      <c r="AA76" s="85"/>
       <c r="AB76" s="48"/>
       <c r="AC76">
         <f t="shared" si="2"/>
@@ -12577,7 +12577,7 @@
       <c r="X77" s="55"/>
       <c r="Y77" s="29"/>
       <c r="Z77" s="45"/>
-      <c r="AA77" s="99"/>
+      <c r="AA77" s="85"/>
       <c r="AB77" s="48"/>
       <c r="AC77">
         <f t="shared" si="2"/>
@@ -12651,7 +12651,7 @@
       <c r="X78" s="55"/>
       <c r="Y78" s="29"/>
       <c r="Z78" s="45"/>
-      <c r="AA78" s="99"/>
+      <c r="AA78" s="85"/>
       <c r="AB78" s="48"/>
       <c r="AC78">
         <f t="shared" si="2"/>
@@ -12725,7 +12725,7 @@
       <c r="X79" s="55"/>
       <c r="Y79" s="29"/>
       <c r="Z79" s="45"/>
-      <c r="AA79" s="99"/>
+      <c r="AA79" s="85"/>
       <c r="AB79" s="48"/>
       <c r="AC79">
         <f t="shared" si="2"/>
@@ -12799,7 +12799,7 @@
       <c r="X80" s="55"/>
       <c r="Y80" s="29"/>
       <c r="Z80" s="45"/>
-      <c r="AA80" s="99"/>
+      <c r="AA80" s="85"/>
       <c r="AB80" s="48"/>
       <c r="AC80">
         <f t="shared" si="2"/>
@@ -12873,7 +12873,7 @@
       <c r="X81" s="55"/>
       <c r="Y81" s="29"/>
       <c r="Z81" s="45"/>
-      <c r="AA81" s="99"/>
+      <c r="AA81" s="85"/>
       <c r="AB81" s="48"/>
       <c r="AC81">
         <f t="shared" si="2"/>
@@ -12947,7 +12947,7 @@
       <c r="X82" s="55"/>
       <c r="Y82" s="29"/>
       <c r="Z82" s="45"/>
-      <c r="AA82" s="99"/>
+      <c r="AA82" s="85"/>
       <c r="AB82" s="48"/>
       <c r="AC82">
         <f t="shared" si="2"/>
@@ -13021,7 +13021,7 @@
       <c r="X83" s="55"/>
       <c r="Y83" s="29"/>
       <c r="Z83" s="45"/>
-      <c r="AA83" s="99"/>
+      <c r="AA83" s="85"/>
       <c r="AB83" s="48"/>
       <c r="AC83">
         <f t="shared" si="2"/>
@@ -13097,7 +13097,7 @@
       <c r="X84" s="55"/>
       <c r="Y84" s="29"/>
       <c r="Z84" s="45"/>
-      <c r="AA84" s="99"/>
+      <c r="AA84" s="85"/>
       <c r="AB84" s="48"/>
       <c r="AC84">
         <f t="shared" si="2"/>
@@ -13171,7 +13171,7 @@
       <c r="X85" s="55"/>
       <c r="Y85" s="29"/>
       <c r="Z85" s="45"/>
-      <c r="AA85" s="99"/>
+      <c r="AA85" s="85"/>
       <c r="AB85" s="48"/>
       <c r="AC85">
         <f t="shared" ref="AC85:AC107" si="4">IF(A85="","",IFERROR(L85/K85,0))</f>
@@ -13245,7 +13245,7 @@
       <c r="X86" s="55"/>
       <c r="Y86" s="29"/>
       <c r="Z86" s="45"/>
-      <c r="AA86" s="99"/>
+      <c r="AA86" s="85"/>
       <c r="AB86" s="48"/>
       <c r="AC86">
         <f t="shared" si="4"/>
@@ -13321,7 +13321,7 @@
       <c r="X87" s="55"/>
       <c r="Y87" s="29"/>
       <c r="Z87" s="45"/>
-      <c r="AA87" s="99"/>
+      <c r="AA87" s="85"/>
       <c r="AB87" s="48"/>
       <c r="AC87">
         <f t="shared" si="4"/>
@@ -13391,7 +13391,7 @@
       <c r="X88" s="55"/>
       <c r="Y88" s="29"/>
       <c r="Z88" s="45"/>
-      <c r="AA88" s="99"/>
+      <c r="AA88" s="85"/>
       <c r="AB88" s="48"/>
       <c r="AC88">
         <f t="shared" si="4"/>
@@ -13465,7 +13465,7 @@
       <c r="X89" s="55"/>
       <c r="Y89" s="29"/>
       <c r="Z89" s="45"/>
-      <c r="AA89" s="99"/>
+      <c r="AA89" s="85"/>
       <c r="AB89" s="48"/>
       <c r="AC89">
         <f t="shared" si="4"/>
@@ -13539,7 +13539,7 @@
       <c r="X90" s="55"/>
       <c r="Y90" s="29"/>
       <c r="Z90" s="45"/>
-      <c r="AA90" s="99"/>
+      <c r="AA90" s="85"/>
       <c r="AB90" s="48"/>
       <c r="AC90">
         <f t="shared" si="4"/>
@@ -13613,7 +13613,7 @@
       <c r="X91" s="55"/>
       <c r="Y91" s="29"/>
       <c r="Z91" s="45"/>
-      <c r="AA91" s="99"/>
+      <c r="AA91" s="85"/>
       <c r="AB91" s="48"/>
       <c r="AC91">
         <f t="shared" si="4"/>
@@ -13687,7 +13687,7 @@
       <c r="X92" s="55"/>
       <c r="Y92" s="29"/>
       <c r="Z92" s="45"/>
-      <c r="AA92" s="99"/>
+      <c r="AA92" s="85"/>
       <c r="AB92" s="48"/>
       <c r="AC92">
         <f t="shared" si="4"/>
@@ -13763,7 +13763,7 @@
       <c r="X93" s="55"/>
       <c r="Y93" s="29"/>
       <c r="Z93" s="45"/>
-      <c r="AA93" s="99"/>
+      <c r="AA93" s="85"/>
       <c r="AB93" s="48"/>
       <c r="AC93">
         <f t="shared" si="4"/>
@@ -13841,7 +13841,7 @@
       <c r="X94" s="55"/>
       <c r="Y94" s="29"/>
       <c r="Z94" s="45"/>
-      <c r="AA94" s="99"/>
+      <c r="AA94" s="85"/>
       <c r="AB94" s="48"/>
       <c r="AC94">
         <f t="shared" si="4"/>
@@ -13917,7 +13917,7 @@
       <c r="X95" s="55"/>
       <c r="Y95" s="29"/>
       <c r="Z95" s="45"/>
-      <c r="AA95" s="99"/>
+      <c r="AA95" s="85"/>
       <c r="AB95" s="48"/>
       <c r="AC95">
         <f t="shared" si="4"/>
@@ -13991,7 +13991,7 @@
       <c r="X96" s="55"/>
       <c r="Y96" s="29"/>
       <c r="Z96" s="45"/>
-      <c r="AA96" s="99"/>
+      <c r="AA96" s="85"/>
       <c r="AB96" s="48"/>
       <c r="AC96">
         <f t="shared" si="4"/>
@@ -14065,7 +14065,7 @@
       <c r="X97" s="55"/>
       <c r="Y97" s="29"/>
       <c r="Z97" s="45"/>
-      <c r="AA97" s="99"/>
+      <c r="AA97" s="85"/>
       <c r="AB97" s="48"/>
       <c r="AC97">
         <f t="shared" si="4"/>
@@ -14139,7 +14139,7 @@
       <c r="X98" s="55"/>
       <c r="Y98" s="29"/>
       <c r="Z98" s="45"/>
-      <c r="AA98" s="99"/>
+      <c r="AA98" s="85"/>
       <c r="AB98" s="48"/>
       <c r="AC98">
         <f t="shared" si="4"/>
@@ -14217,7 +14217,7 @@
       <c r="X99" s="55"/>
       <c r="Y99" s="29"/>
       <c r="Z99" s="45"/>
-      <c r="AA99" s="99"/>
+      <c r="AA99" s="85"/>
       <c r="AB99" s="48"/>
       <c r="AC99">
         <f t="shared" si="4"/>
@@ -14295,7 +14295,7 @@
       <c r="X100" s="55"/>
       <c r="Y100" s="29"/>
       <c r="Z100" s="45"/>
-      <c r="AA100" s="99"/>
+      <c r="AA100" s="85"/>
       <c r="AB100" s="48"/>
       <c r="AC100">
         <f t="shared" si="4"/>
@@ -14371,7 +14371,7 @@
       <c r="X101" s="55"/>
       <c r="Y101" s="29"/>
       <c r="Z101" s="45"/>
-      <c r="AA101" s="99"/>
+      <c r="AA101" s="85"/>
       <c r="AB101" s="48"/>
       <c r="AC101">
         <f t="shared" si="4"/>
@@ -14447,7 +14447,7 @@
       <c r="X102" s="55"/>
       <c r="Y102" s="29"/>
       <c r="Z102" s="45"/>
-      <c r="AA102" s="99"/>
+      <c r="AA102" s="85"/>
       <c r="AB102" s="48"/>
       <c r="AC102">
         <f t="shared" si="4"/>
@@ -14521,7 +14521,7 @@
       <c r="X103" s="55"/>
       <c r="Y103" s="29"/>
       <c r="Z103" s="45"/>
-      <c r="AA103" s="99"/>
+      <c r="AA103" s="85"/>
       <c r="AB103" s="48"/>
       <c r="AC103">
         <f t="shared" si="4"/>
@@ -14595,7 +14595,7 @@
       <c r="X104" s="55"/>
       <c r="Y104" s="29"/>
       <c r="Z104" s="45"/>
-      <c r="AA104" s="99"/>
+      <c r="AA104" s="85"/>
       <c r="AB104" s="48"/>
       <c r="AC104">
         <f t="shared" si="4"/>
@@ -14669,7 +14669,7 @@
       <c r="X105" s="55"/>
       <c r="Y105" s="29"/>
       <c r="Z105" s="45"/>
-      <c r="AA105" s="99"/>
+      <c r="AA105" s="85"/>
       <c r="AB105" s="48"/>
       <c r="AC105">
         <f t="shared" si="4"/>
@@ -14745,7 +14745,7 @@
       <c r="X106" s="55"/>
       <c r="Y106" s="29"/>
       <c r="Z106" s="45"/>
-      <c r="AA106" s="99"/>
+      <c r="AA106" s="85"/>
       <c r="AB106" s="48"/>
       <c r="AC106">
         <f t="shared" si="4"/>
@@ -14821,7 +14821,7 @@
       <c r="X107" s="55"/>
       <c r="Y107" s="29"/>
       <c r="Z107" s="45"/>
-      <c r="AA107" s="99"/>
+      <c r="AA107" s="85"/>
       <c r="AB107" s="48"/>
       <c r="AC107">
         <f t="shared" si="4"/>
@@ -14897,7 +14897,7 @@
       <c r="X108" s="55"/>
       <c r="Y108" s="67"/>
       <c r="Z108" s="45"/>
-      <c r="AA108" s="99"/>
+      <c r="AA108" s="85"/>
       <c r="AB108" s="78"/>
     </row>
     <row r="109" spans="1:30" ht="25">
@@ -14963,7 +14963,7 @@
       <c r="X109" s="55"/>
       <c r="Y109" s="29"/>
       <c r="Z109" s="45"/>
-      <c r="AA109" s="99"/>
+      <c r="AA109" s="85"/>
       <c r="AB109" s="48"/>
       <c r="AC109">
         <f t="shared" ref="AC109:AC114" si="6">IF(A109="","",IFERROR(L109/K109,0))</f>
@@ -15037,7 +15037,7 @@
       <c r="X110" s="55"/>
       <c r="Y110" s="29"/>
       <c r="Z110" s="45"/>
-      <c r="AA110" s="99"/>
+      <c r="AA110" s="85"/>
       <c r="AB110" s="48"/>
       <c r="AC110">
         <f t="shared" si="6"/>
@@ -15111,7 +15111,7 @@
       <c r="X111" s="55"/>
       <c r="Y111" s="29"/>
       <c r="Z111" s="45"/>
-      <c r="AA111" s="99"/>
+      <c r="AA111" s="85"/>
       <c r="AB111" s="48"/>
       <c r="AC111">
         <f t="shared" si="6"/>
@@ -15185,7 +15185,7 @@
       <c r="X112" s="55"/>
       <c r="Y112" s="29"/>
       <c r="Z112" s="45"/>
-      <c r="AA112" s="99"/>
+      <c r="AA112" s="85"/>
       <c r="AB112" s="48"/>
       <c r="AC112">
         <f t="shared" si="6"/>
@@ -15261,7 +15261,7 @@
       <c r="X113" s="55"/>
       <c r="Y113" s="29"/>
       <c r="Z113" s="45"/>
-      <c r="AA113" s="99"/>
+      <c r="AA113" s="85"/>
       <c r="AB113" s="48"/>
       <c r="AC113">
         <f t="shared" si="6"/>
@@ -15335,7 +15335,7 @@
       <c r="X114" s="55"/>
       <c r="Y114" s="29"/>
       <c r="Z114" s="45"/>
-      <c r="AA114" s="99"/>
+      <c r="AA114" s="85"/>
       <c r="AB114" s="48"/>
       <c r="AC114">
         <f t="shared" si="6"/>
@@ -15407,7 +15407,7 @@
       <c r="X115" s="55"/>
       <c r="Y115" s="67"/>
       <c r="Z115" s="45"/>
-      <c r="AA115" s="99"/>
+      <c r="AA115" s="85"/>
       <c r="AB115" s="78"/>
     </row>
     <row r="116" spans="1:30" ht="25">
@@ -15475,7 +15475,7 @@
       <c r="X116" s="55"/>
       <c r="Y116" s="29"/>
       <c r="Z116" s="45"/>
-      <c r="AA116" s="99"/>
+      <c r="AA116" s="85"/>
       <c r="AB116" s="48"/>
       <c r="AC116">
         <f t="shared" ref="AC116:AC142" si="8">IF(A116="","",IFERROR(L116/K116,0))</f>
@@ -15551,7 +15551,7 @@
       <c r="X117" s="55"/>
       <c r="Y117" s="29"/>
       <c r="Z117" s="45"/>
-      <c r="AA117" s="99"/>
+      <c r="AA117" s="85"/>
       <c r="AB117" s="48"/>
       <c r="AC117">
         <f t="shared" si="8"/>
@@ -15625,7 +15625,7 @@
       <c r="X118" s="55"/>
       <c r="Y118" s="29"/>
       <c r="Z118" s="45"/>
-      <c r="AA118" s="99"/>
+      <c r="AA118" s="85"/>
       <c r="AB118" s="48"/>
       <c r="AC118">
         <f t="shared" si="8"/>
@@ -15699,7 +15699,7 @@
       <c r="X119" s="55"/>
       <c r="Y119" s="29"/>
       <c r="Z119" s="45"/>
-      <c r="AA119" s="99"/>
+      <c r="AA119" s="85"/>
       <c r="AB119" s="48"/>
       <c r="AC119">
         <f t="shared" si="8"/>
@@ -15773,7 +15773,7 @@
       <c r="X120" s="55"/>
       <c r="Y120" s="29"/>
       <c r="Z120" s="45"/>
-      <c r="AA120" s="99"/>
+      <c r="AA120" s="85"/>
       <c r="AB120" s="48"/>
       <c r="AC120">
         <f t="shared" si="8"/>
@@ -15847,7 +15847,7 @@
       <c r="X121" s="55"/>
       <c r="Y121" s="29"/>
       <c r="Z121" s="45"/>
-      <c r="AA121" s="99"/>
+      <c r="AA121" s="85"/>
       <c r="AB121" s="48"/>
       <c r="AC121">
         <f t="shared" si="8"/>
@@ -15921,7 +15921,7 @@
       <c r="X122" s="55"/>
       <c r="Y122" s="29"/>
       <c r="Z122" s="45"/>
-      <c r="AA122" s="99"/>
+      <c r="AA122" s="85"/>
       <c r="AB122" s="48"/>
       <c r="AC122">
         <f t="shared" si="8"/>
@@ -15995,7 +15995,7 @@
       <c r="X123" s="55"/>
       <c r="Y123" s="29"/>
       <c r="Z123" s="45"/>
-      <c r="AA123" s="99"/>
+      <c r="AA123" s="85"/>
       <c r="AB123" s="48"/>
       <c r="AC123">
         <f t="shared" si="8"/>
@@ -16071,7 +16071,7 @@
       <c r="X124" s="55"/>
       <c r="Y124" s="29"/>
       <c r="Z124" s="45"/>
-      <c r="AA124" s="99"/>
+      <c r="AA124" s="85"/>
       <c r="AB124" s="48"/>
       <c r="AC124">
         <f t="shared" si="8"/>
@@ -16147,7 +16147,7 @@
       <c r="X125" s="55"/>
       <c r="Y125" s="29"/>
       <c r="Z125" s="45"/>
-      <c r="AA125" s="99"/>
+      <c r="AA125" s="85"/>
       <c r="AB125" s="48"/>
       <c r="AC125">
         <f t="shared" si="8"/>
@@ -16223,7 +16223,7 @@
       <c r="X126" s="55"/>
       <c r="Y126" s="29"/>
       <c r="Z126" s="45"/>
-      <c r="AA126" s="99"/>
+      <c r="AA126" s="85"/>
       <c r="AB126" s="48"/>
       <c r="AC126">
         <f t="shared" si="8"/>
@@ -16299,7 +16299,7 @@
       <c r="X127" s="55"/>
       <c r="Y127" s="29"/>
       <c r="Z127" s="45"/>
-      <c r="AA127" s="99"/>
+      <c r="AA127" s="85"/>
       <c r="AB127" s="48"/>
       <c r="AC127">
         <f t="shared" si="8"/>
@@ -16369,7 +16369,7 @@
       <c r="X128" s="55"/>
       <c r="Y128" s="29"/>
       <c r="Z128" s="45"/>
-      <c r="AA128" s="99"/>
+      <c r="AA128" s="85"/>
       <c r="AB128" s="48"/>
       <c r="AC128">
         <f t="shared" si="8"/>
@@ -16443,7 +16443,7 @@
       <c r="X129" s="55"/>
       <c r="Y129" s="29"/>
       <c r="Z129" s="45"/>
-      <c r="AA129" s="99"/>
+      <c r="AA129" s="85"/>
       <c r="AB129" s="48"/>
       <c r="AC129">
         <f t="shared" si="8"/>
@@ -16517,7 +16517,7 @@
       <c r="X130" s="55"/>
       <c r="Y130" s="29"/>
       <c r="Z130" s="45"/>
-      <c r="AA130" s="99"/>
+      <c r="AA130" s="85"/>
       <c r="AB130" s="48"/>
       <c r="AC130">
         <f t="shared" si="8"/>
@@ -16593,7 +16593,7 @@
       <c r="X131" s="55"/>
       <c r="Y131" s="29"/>
       <c r="Z131" s="45"/>
-      <c r="AA131" s="99"/>
+      <c r="AA131" s="85"/>
       <c r="AB131" s="48"/>
       <c r="AC131">
         <f t="shared" si="8"/>
@@ -16669,7 +16669,7 @@
       <c r="X132" s="55"/>
       <c r="Y132" s="29"/>
       <c r="Z132" s="45"/>
-      <c r="AA132" s="99"/>
+      <c r="AA132" s="85"/>
       <c r="AB132" s="48"/>
       <c r="AC132">
         <f t="shared" si="8"/>
@@ -16743,7 +16743,7 @@
       <c r="X133" s="55"/>
       <c r="Y133" s="29"/>
       <c r="Z133" s="45"/>
-      <c r="AA133" s="99"/>
+      <c r="AA133" s="85"/>
       <c r="AB133" s="48"/>
       <c r="AC133">
         <f t="shared" si="8"/>
@@ -16819,7 +16819,7 @@
       <c r="X134" s="55"/>
       <c r="Y134" s="29"/>
       <c r="Z134" s="45"/>
-      <c r="AA134" s="99"/>
+      <c r="AA134" s="85"/>
       <c r="AB134" s="48"/>
       <c r="AC134">
         <f t="shared" si="8"/>
@@ -16891,7 +16891,7 @@
       <c r="X135" s="55"/>
       <c r="Y135" s="29"/>
       <c r="Z135" s="45"/>
-      <c r="AA135" s="99"/>
+      <c r="AA135" s="85"/>
       <c r="AB135" s="48"/>
       <c r="AC135">
         <f t="shared" si="8"/>
@@ -16967,7 +16967,7 @@
       <c r="X136" s="55"/>
       <c r="Y136" s="29"/>
       <c r="Z136" s="45"/>
-      <c r="AA136" s="99"/>
+      <c r="AA136" s="85"/>
       <c r="AB136" s="48"/>
       <c r="AC136">
         <f t="shared" si="8"/>
@@ -17043,7 +17043,7 @@
       <c r="X137" s="55"/>
       <c r="Y137" s="29"/>
       <c r="Z137" s="45"/>
-      <c r="AA137" s="99"/>
+      <c r="AA137" s="85"/>
       <c r="AB137" s="48"/>
       <c r="AC137">
         <f t="shared" si="8"/>
@@ -17121,7 +17121,7 @@
       <c r="X138" s="55"/>
       <c r="Y138" s="29"/>
       <c r="Z138" s="45"/>
-      <c r="AA138" s="99"/>
+      <c r="AA138" s="85"/>
       <c r="AB138" s="48"/>
       <c r="AC138">
         <f t="shared" si="8"/>
@@ -17199,7 +17199,7 @@
       <c r="X139" s="55"/>
       <c r="Y139" s="29"/>
       <c r="Z139" s="45"/>
-      <c r="AA139" s="99"/>
+      <c r="AA139" s="85"/>
       <c r="AB139" s="48"/>
       <c r="AC139">
         <f t="shared" si="8"/>
@@ -17275,7 +17275,7 @@
       <c r="X140" s="55"/>
       <c r="Y140" s="29"/>
       <c r="Z140" s="45"/>
-      <c r="AA140" s="99"/>
+      <c r="AA140" s="85"/>
       <c r="AB140" s="48"/>
       <c r="AC140">
         <f t="shared" si="8"/>
@@ -17351,7 +17351,7 @@
       <c r="X141" s="55"/>
       <c r="Y141" s="29"/>
       <c r="Z141" s="45"/>
-      <c r="AA141" s="99"/>
+      <c r="AA141" s="85"/>
       <c r="AB141" s="48"/>
       <c r="AC141">
         <f t="shared" si="8"/>
@@ -17427,7 +17427,7 @@
       <c r="X142" s="55"/>
       <c r="Y142" s="29"/>
       <c r="Z142" s="45"/>
-      <c r="AA142" s="99"/>
+      <c r="AA142" s="85"/>
       <c r="AB142" s="48"/>
       <c r="AC142">
         <f t="shared" si="8"/>
@@ -17501,7 +17501,7 @@
       <c r="X143" s="55"/>
       <c r="Y143" s="29"/>
       <c r="Z143" s="45"/>
-      <c r="AA143" s="99"/>
+      <c r="AA143" s="85"/>
       <c r="AB143" s="48"/>
       <c r="AC143">
         <f t="shared" ref="AC143:AC144" si="10">IF(A143="","",IFERROR(L143/K143,0))</f>
@@ -17573,7 +17573,7 @@
       <c r="X144" s="55"/>
       <c r="Y144" s="67"/>
       <c r="Z144" s="45"/>
-      <c r="AA144" s="99"/>
+      <c r="AA144" s="85"/>
       <c r="AB144" s="78"/>
       <c r="AC144">
         <f t="shared" si="10"/>
@@ -17649,7 +17649,7 @@
       <c r="X145" s="55"/>
       <c r="Y145" s="29"/>
       <c r="Z145" s="45"/>
-      <c r="AA145" s="99"/>
+      <c r="AA145" s="85"/>
       <c r="AB145" s="48"/>
       <c r="AC145">
         <f t="shared" ref="AC145:AC163" si="12">IF(A145="","",IFERROR(L145/K145,0))</f>
@@ -17723,7 +17723,7 @@
       <c r="X146" s="55"/>
       <c r="Y146" s="29"/>
       <c r="Z146" s="45"/>
-      <c r="AA146" s="99"/>
+      <c r="AA146" s="85"/>
       <c r="AB146" s="48"/>
       <c r="AC146">
         <f t="shared" si="12"/>
@@ -17795,7 +17795,7 @@
       <c r="X147" s="55"/>
       <c r="Y147" s="29"/>
       <c r="Z147" s="45"/>
-      <c r="AA147" s="99"/>
+      <c r="AA147" s="85"/>
       <c r="AB147" s="48"/>
       <c r="AC147">
         <f t="shared" si="12"/>
@@ -17869,7 +17869,7 @@
       <c r="X148" s="55"/>
       <c r="Y148" s="29"/>
       <c r="Z148" s="45"/>
-      <c r="AA148" s="99"/>
+      <c r="AA148" s="85"/>
       <c r="AB148" s="48"/>
       <c r="AC148">
         <f t="shared" si="12"/>
@@ -17943,7 +17943,7 @@
       <c r="X149" s="55"/>
       <c r="Y149" s="29"/>
       <c r="Z149" s="45"/>
-      <c r="AA149" s="99"/>
+      <c r="AA149" s="85"/>
       <c r="AB149" s="48"/>
       <c r="AC149">
         <f t="shared" si="12"/>
@@ -18015,7 +18015,7 @@
       <c r="X150" s="55"/>
       <c r="Y150" s="67"/>
       <c r="Z150" s="45"/>
-      <c r="AA150" s="99"/>
+      <c r="AA150" s="85"/>
       <c r="AB150" s="78"/>
     </row>
     <row r="151" spans="1:30">
@@ -18081,7 +18081,7 @@
       <c r="X151" s="55"/>
       <c r="Y151" s="29"/>
       <c r="Z151" s="45"/>
-      <c r="AA151" s="99"/>
+      <c r="AA151" s="85"/>
       <c r="AB151" s="48"/>
       <c r="AC151">
         <f t="shared" si="12"/>
@@ -18157,7 +18157,7 @@
       <c r="X152" s="55"/>
       <c r="Y152" s="29"/>
       <c r="Z152" s="45"/>
-      <c r="AA152" s="99"/>
+      <c r="AA152" s="85"/>
       <c r="AB152" s="48"/>
       <c r="AC152">
         <f t="shared" si="12"/>
@@ -18231,7 +18231,7 @@
       <c r="X153" s="55"/>
       <c r="Y153" s="29"/>
       <c r="Z153" s="45"/>
-      <c r="AA153" s="99"/>
+      <c r="AA153" s="85"/>
       <c r="AB153" s="48"/>
       <c r="AC153">
         <f t="shared" si="12"/>
@@ -18307,7 +18307,7 @@
       <c r="X154" s="55"/>
       <c r="Y154" s="29"/>
       <c r="Z154" s="45"/>
-      <c r="AA154" s="99"/>
+      <c r="AA154" s="85"/>
       <c r="AB154" s="48"/>
       <c r="AC154">
         <f t="shared" si="12"/>
@@ -18383,7 +18383,7 @@
       <c r="X155" s="55"/>
       <c r="Y155" s="29"/>
       <c r="Z155" s="45"/>
-      <c r="AA155" s="99"/>
+      <c r="AA155" s="85"/>
       <c r="AB155" s="48"/>
       <c r="AC155">
         <f t="shared" si="12"/>
@@ -18457,7 +18457,7 @@
       <c r="X156" s="55"/>
       <c r="Y156" s="29"/>
       <c r="Z156" s="45"/>
-      <c r="AA156" s="99"/>
+      <c r="AA156" s="85"/>
       <c r="AB156" s="48"/>
       <c r="AC156">
         <f t="shared" si="12"/>
@@ -18531,7 +18531,7 @@
       <c r="X157" s="55"/>
       <c r="Y157" s="29"/>
       <c r="Z157" s="45"/>
-      <c r="AA157" s="99"/>
+      <c r="AA157" s="85"/>
       <c r="AB157" s="48"/>
       <c r="AC157">
         <f t="shared" si="12"/>
@@ -18605,7 +18605,7 @@
       <c r="X158" s="55"/>
       <c r="Y158" s="29"/>
       <c r="Z158" s="45"/>
-      <c r="AA158" s="99"/>
+      <c r="AA158" s="85"/>
       <c r="AB158" s="48"/>
       <c r="AC158">
         <f t="shared" si="12"/>
@@ -18681,7 +18681,7 @@
       <c r="X159" s="55"/>
       <c r="Y159" s="29"/>
       <c r="Z159" s="45"/>
-      <c r="AA159" s="99"/>
+      <c r="AA159" s="85"/>
       <c r="AB159" s="48"/>
       <c r="AC159">
         <f t="shared" si="12"/>
@@ -18757,7 +18757,7 @@
       <c r="X160" s="55"/>
       <c r="Y160" s="29"/>
       <c r="Z160" s="45"/>
-      <c r="AA160" s="99"/>
+      <c r="AA160" s="85"/>
       <c r="AB160" s="48"/>
       <c r="AC160">
         <f t="shared" si="12"/>
@@ -18833,7 +18833,7 @@
       <c r="X161" s="55"/>
       <c r="Y161" s="29"/>
       <c r="Z161" s="45"/>
-      <c r="AA161" s="99"/>
+      <c r="AA161" s="85"/>
       <c r="AB161" s="48"/>
       <c r="AC161">
         <f t="shared" si="12"/>
@@ -18909,7 +18909,7 @@
       <c r="X162" s="55"/>
       <c r="Y162" s="29"/>
       <c r="Z162" s="45"/>
-      <c r="AA162" s="99"/>
+      <c r="AA162" s="85"/>
       <c r="AB162" s="48"/>
       <c r="AC162">
         <f t="shared" si="12"/>
@@ -18985,7 +18985,7 @@
       <c r="X163" s="55"/>
       <c r="Y163" s="29"/>
       <c r="Z163" s="45"/>
-      <c r="AA163" s="99"/>
+      <c r="AA163" s="85"/>
       <c r="AB163" s="48"/>
       <c r="AC163">
         <f t="shared" si="12"/>
@@ -19055,7 +19055,7 @@
       <c r="X164" s="55"/>
       <c r="Y164" s="67"/>
       <c r="Z164" s="45"/>
-      <c r="AA164" s="99"/>
+      <c r="AA164" s="85"/>
       <c r="AB164" s="78"/>
     </row>
     <row r="165" spans="1:30">
@@ -19123,7 +19123,7 @@
       <c r="X165" s="55"/>
       <c r="Y165" s="29"/>
       <c r="Z165" s="45"/>
-      <c r="AA165" s="99"/>
+      <c r="AA165" s="85"/>
       <c r="AB165" s="48"/>
       <c r="AC165">
         <f t="shared" ref="AC165:AC205" si="14">IF(A165="","",IFERROR(L165/K165,0))</f>
@@ -19193,7 +19193,7 @@
       <c r="X166" s="55"/>
       <c r="Y166" s="29"/>
       <c r="Z166" s="45"/>
-      <c r="AA166" s="99"/>
+      <c r="AA166" s="85"/>
       <c r="AB166" s="48"/>
       <c r="AC166">
         <f t="shared" si="14"/>
@@ -19269,7 +19269,7 @@
       <c r="X167" s="55"/>
       <c r="Y167" s="29"/>
       <c r="Z167" s="45"/>
-      <c r="AA167" s="99"/>
+      <c r="AA167" s="85"/>
       <c r="AB167" s="48"/>
       <c r="AC167">
         <f t="shared" si="14"/>
@@ -19343,7 +19343,7 @@
       <c r="X168" s="55"/>
       <c r="Y168" s="29"/>
       <c r="Z168" s="45"/>
-      <c r="AA168" s="99"/>
+      <c r="AA168" s="85"/>
       <c r="AB168" s="48"/>
       <c r="AC168">
         <f t="shared" si="14"/>
@@ -19404,9 +19404,7 @@
       <c r="Q169" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="R169" s="23" t="s">
-        <v>113</v>
-      </c>
+      <c r="R169" s="23"/>
       <c r="S169" s="20"/>
       <c r="T169" s="11"/>
       <c r="U169" s="11"/>
@@ -19419,7 +19417,7 @@
       <c r="X169" s="55"/>
       <c r="Y169" s="29"/>
       <c r="Z169" s="45"/>
-      <c r="AA169" s="99"/>
+      <c r="AA169" s="85"/>
       <c r="AB169" s="48"/>
       <c r="AC169">
         <f t="shared" si="14"/>
@@ -19497,7 +19495,7 @@
       <c r="X170" s="55"/>
       <c r="Y170" s="29"/>
       <c r="Z170" s="45"/>
-      <c r="AA170" s="99"/>
+      <c r="AA170" s="85"/>
       <c r="AB170" s="48"/>
       <c r="AC170">
         <f t="shared" si="14"/>
@@ -19573,7 +19571,7 @@
       <c r="X171" s="55"/>
       <c r="Y171" s="29"/>
       <c r="Z171" s="45"/>
-      <c r="AA171" s="99"/>
+      <c r="AA171" s="85"/>
       <c r="AB171" s="48"/>
       <c r="AC171">
         <f t="shared" si="14"/>
@@ -19649,7 +19647,7 @@
       <c r="X172" s="55"/>
       <c r="Y172" s="29"/>
       <c r="Z172" s="45"/>
-      <c r="AA172" s="99"/>
+      <c r="AA172" s="85"/>
       <c r="AB172" s="48"/>
       <c r="AC172">
         <f t="shared" si="14"/>
@@ -19725,7 +19723,7 @@
       <c r="X173" s="55"/>
       <c r="Y173" s="29"/>
       <c r="Z173" s="45"/>
-      <c r="AA173" s="99"/>
+      <c r="AA173" s="85"/>
       <c r="AB173" s="48"/>
       <c r="AC173">
         <f t="shared" si="14"/>
@@ -19801,7 +19799,7 @@
       <c r="X174" s="55"/>
       <c r="Y174" s="29"/>
       <c r="Z174" s="45"/>
-      <c r="AA174" s="99"/>
+      <c r="AA174" s="85"/>
       <c r="AB174" s="48"/>
       <c r="AC174">
         <f t="shared" si="14"/>
@@ -19881,7 +19879,7 @@
       <c r="X175" s="55"/>
       <c r="Y175" s="29"/>
       <c r="Z175" s="45"/>
-      <c r="AA175" s="99"/>
+      <c r="AA175" s="85"/>
       <c r="AB175" s="48"/>
       <c r="AC175">
         <f t="shared" si="14"/>
@@ -19957,7 +19955,7 @@
       <c r="X176" s="55"/>
       <c r="Y176" s="29"/>
       <c r="Z176" s="45"/>
-      <c r="AA176" s="99"/>
+      <c r="AA176" s="85"/>
       <c r="AB176" s="48"/>
       <c r="AC176">
         <f t="shared" si="14"/>
@@ -20033,7 +20031,7 @@
       <c r="X177" s="55"/>
       <c r="Y177" s="29"/>
       <c r="Z177" s="45"/>
-      <c r="AA177" s="99"/>
+      <c r="AA177" s="85"/>
       <c r="AB177" s="48"/>
       <c r="AC177">
         <f t="shared" si="14"/>
@@ -20111,7 +20109,7 @@
       <c r="X178" s="55"/>
       <c r="Y178" s="29"/>
       <c r="Z178" s="45"/>
-      <c r="AA178" s="99"/>
+      <c r="AA178" s="85"/>
       <c r="AB178" s="48"/>
       <c r="AC178">
         <f t="shared" si="14"/>
@@ -20187,7 +20185,7 @@
       <c r="X179" s="55"/>
       <c r="Y179" s="29"/>
       <c r="Z179" s="45"/>
-      <c r="AA179" s="99"/>
+      <c r="AA179" s="85"/>
       <c r="AB179" s="48"/>
       <c r="AC179">
         <f t="shared" si="14"/>
@@ -20263,7 +20261,7 @@
       <c r="X180" s="55"/>
       <c r="Y180" s="29"/>
       <c r="Z180" s="45"/>
-      <c r="AA180" s="99"/>
+      <c r="AA180" s="85"/>
       <c r="AB180" s="48"/>
       <c r="AC180">
         <f t="shared" si="14"/>
@@ -20339,7 +20337,7 @@
       <c r="X181" s="55"/>
       <c r="Y181" s="29"/>
       <c r="Z181" s="45"/>
-      <c r="AA181" s="99"/>
+      <c r="AA181" s="85"/>
       <c r="AB181" s="48"/>
       <c r="AC181">
         <f t="shared" si="14"/>
@@ -20413,7 +20411,7 @@
       <c r="X182" s="55"/>
       <c r="Y182" s="29"/>
       <c r="Z182" s="45"/>
-      <c r="AA182" s="99"/>
+      <c r="AA182" s="85"/>
       <c r="AB182" s="48"/>
       <c r="AC182">
         <f t="shared" si="14"/>
@@ -20489,7 +20487,7 @@
       <c r="X183" s="55"/>
       <c r="Y183" s="29"/>
       <c r="Z183" s="45"/>
-      <c r="AA183" s="99"/>
+      <c r="AA183" s="85"/>
       <c r="AB183" s="48"/>
       <c r="AC183">
         <f t="shared" si="14"/>
@@ -20563,7 +20561,7 @@
       <c r="X184" s="55"/>
       <c r="Y184" s="29"/>
       <c r="Z184" s="45"/>
-      <c r="AA184" s="99"/>
+      <c r="AA184" s="85"/>
       <c r="AB184" s="48"/>
       <c r="AC184">
         <f t="shared" si="14"/>
@@ -20637,7 +20635,7 @@
       <c r="X185" s="55"/>
       <c r="Y185" s="29"/>
       <c r="Z185" s="45"/>
-      <c r="AA185" s="99"/>
+      <c r="AA185" s="85"/>
       <c r="AB185" s="48"/>
       <c r="AC185">
         <f t="shared" si="14"/>
@@ -20713,7 +20711,7 @@
       <c r="X186" s="55"/>
       <c r="Y186" s="29"/>
       <c r="Z186" s="45"/>
-      <c r="AA186" s="99"/>
+      <c r="AA186" s="85"/>
       <c r="AB186" s="48"/>
       <c r="AC186">
         <f t="shared" si="14"/>
@@ -20789,7 +20787,7 @@
       <c r="X187" s="55"/>
       <c r="Y187" s="29"/>
       <c r="Z187" s="45"/>
-      <c r="AA187" s="99"/>
+      <c r="AA187" s="85"/>
       <c r="AB187" s="48"/>
       <c r="AC187">
         <f t="shared" si="14"/>
@@ -20865,7 +20863,7 @@
       <c r="X188" s="55"/>
       <c r="Y188" s="29"/>
       <c r="Z188" s="45"/>
-      <c r="AA188" s="99"/>
+      <c r="AA188" s="85"/>
       <c r="AB188" s="48"/>
       <c r="AC188">
         <f t="shared" si="14"/>
@@ -20939,7 +20937,7 @@
       <c r="X189" s="55"/>
       <c r="Y189" s="29"/>
       <c r="Z189" s="45"/>
-      <c r="AA189" s="99"/>
+      <c r="AA189" s="85"/>
       <c r="AB189" s="48"/>
       <c r="AC189">
         <f t="shared" si="14"/>
@@ -21013,7 +21011,7 @@
       <c r="X190" s="55"/>
       <c r="Y190" s="29"/>
       <c r="Z190" s="45"/>
-      <c r="AA190" s="99"/>
+      <c r="AA190" s="85"/>
       <c r="AB190" s="48"/>
       <c r="AC190">
         <f t="shared" si="14"/>
@@ -21087,7 +21085,7 @@
       <c r="X191" s="55"/>
       <c r="Y191" s="29"/>
       <c r="Z191" s="45"/>
-      <c r="AA191" s="99"/>
+      <c r="AA191" s="85"/>
       <c r="AB191" s="48"/>
       <c r="AC191">
         <f t="shared" si="14"/>
@@ -21163,7 +21161,7 @@
       <c r="X192" s="55"/>
       <c r="Y192" s="29"/>
       <c r="Z192" s="45"/>
-      <c r="AA192" s="99"/>
+      <c r="AA192" s="85"/>
       <c r="AB192" s="48"/>
       <c r="AC192">
         <f t="shared" si="14"/>
@@ -21237,7 +21235,7 @@
       <c r="X193" s="55"/>
       <c r="Y193" s="29"/>
       <c r="Z193" s="45"/>
-      <c r="AA193" s="99"/>
+      <c r="AA193" s="85"/>
       <c r="AB193" s="48"/>
       <c r="AC193">
         <f t="shared" si="14"/>
@@ -21311,7 +21309,7 @@
       <c r="X194" s="55"/>
       <c r="Y194" s="29"/>
       <c r="Z194" s="45"/>
-      <c r="AA194" s="99"/>
+      <c r="AA194" s="85"/>
       <c r="AB194" s="48"/>
       <c r="AC194">
         <f t="shared" si="14"/>
@@ -21387,7 +21385,7 @@
       <c r="X195" s="55"/>
       <c r="Y195" s="29"/>
       <c r="Z195" s="45"/>
-      <c r="AA195" s="99"/>
+      <c r="AA195" s="85"/>
       <c r="AB195" s="48"/>
       <c r="AC195">
         <f t="shared" si="14"/>
@@ -21461,7 +21459,7 @@
       <c r="X196" s="55"/>
       <c r="Y196" s="29"/>
       <c r="Z196" s="45"/>
-      <c r="AA196" s="99"/>
+      <c r="AA196" s="85"/>
       <c r="AB196" s="48"/>
       <c r="AC196">
         <f t="shared" si="14"/>
@@ -21535,7 +21533,7 @@
       <c r="X197" s="55"/>
       <c r="Y197" s="29"/>
       <c r="Z197" s="45"/>
-      <c r="AA197" s="99"/>
+      <c r="AA197" s="85"/>
       <c r="AB197" s="48"/>
       <c r="AC197">
         <f t="shared" si="14"/>
@@ -21609,7 +21607,7 @@
       <c r="X198" s="55"/>
       <c r="Y198" s="29"/>
       <c r="Z198" s="45"/>
-      <c r="AA198" s="99"/>
+      <c r="AA198" s="85"/>
       <c r="AB198" s="48"/>
       <c r="AC198">
         <f t="shared" si="14"/>
@@ -21685,7 +21683,7 @@
       <c r="X199" s="55"/>
       <c r="Y199" s="29"/>
       <c r="Z199" s="45"/>
-      <c r="AA199" s="99"/>
+      <c r="AA199" s="85"/>
       <c r="AB199" s="48"/>
       <c r="AC199">
         <f t="shared" si="14"/>
@@ -21763,7 +21761,7 @@
       <c r="X200" s="55"/>
       <c r="Y200" s="29"/>
       <c r="Z200" s="45"/>
-      <c r="AA200" s="99"/>
+      <c r="AA200" s="85"/>
       <c r="AB200" s="48"/>
       <c r="AC200">
         <f t="shared" si="14"/>
@@ -21837,7 +21835,7 @@
       <c r="X201" s="55"/>
       <c r="Y201" s="29"/>
       <c r="Z201" s="45"/>
-      <c r="AA201" s="99"/>
+      <c r="AA201" s="85"/>
       <c r="AB201" s="48"/>
       <c r="AC201">
         <f t="shared" si="14"/>
@@ -21911,7 +21909,7 @@
       <c r="X202" s="55"/>
       <c r="Y202" s="29"/>
       <c r="Z202" s="45"/>
-      <c r="AA202" s="99"/>
+      <c r="AA202" s="85"/>
       <c r="AB202" s="48"/>
       <c r="AC202">
         <f t="shared" si="14"/>
@@ -21989,7 +21987,7 @@
       <c r="X203" s="55"/>
       <c r="Y203" s="29"/>
       <c r="Z203" s="45"/>
-      <c r="AA203" s="99"/>
+      <c r="AA203" s="85"/>
       <c r="AB203" s="48"/>
       <c r="AC203">
         <f t="shared" si="14"/>
@@ -22067,7 +22065,7 @@
       <c r="X204" s="55"/>
       <c r="Y204" s="29"/>
       <c r="Z204" s="45"/>
-      <c r="AA204" s="99"/>
+      <c r="AA204" s="85"/>
       <c r="AB204" s="48"/>
       <c r="AC204">
         <f t="shared" si="14"/>
@@ -22141,7 +22139,7 @@
       <c r="X205" s="55"/>
       <c r="Y205" s="29"/>
       <c r="Z205" s="45"/>
-      <c r="AA205" s="99"/>
+      <c r="AA205" s="85"/>
       <c r="AB205" s="48"/>
       <c r="AC205">
         <f t="shared" si="14"/>
@@ -22213,7 +22211,7 @@
       <c r="X206" s="55"/>
       <c r="Y206" s="67"/>
       <c r="Z206" s="45"/>
-      <c r="AA206" s="99"/>
+      <c r="AA206" s="85"/>
       <c r="AB206" s="78"/>
     </row>
     <row r="207" spans="1:30">
@@ -22281,7 +22279,7 @@
       <c r="X207" s="55"/>
       <c r="Y207" s="29"/>
       <c r="Z207" s="45"/>
-      <c r="AA207" s="99"/>
+      <c r="AA207" s="85"/>
       <c r="AB207" s="48"/>
       <c r="AC207">
         <f>IF(A207="","",IFERROR(L207/K207,0))</f>
@@ -22355,7 +22353,7 @@
       <c r="X208" s="55"/>
       <c r="Y208" s="29"/>
       <c r="Z208" s="45"/>
-      <c r="AA208" s="99"/>
+      <c r="AA208" s="85"/>
       <c r="AB208" s="48"/>
       <c r="AC208">
         <f>IF(A208="","",IFERROR(L208/K208,0))</f>
@@ -22429,7 +22427,7 @@
       <c r="X209" s="55"/>
       <c r="Y209" s="29"/>
       <c r="Z209" s="45"/>
-      <c r="AA209" s="99"/>
+      <c r="AA209" s="85"/>
       <c r="AB209" s="48"/>
       <c r="AC209">
         <f>IF(A209="","",IFERROR(L209/K209,0))</f>
@@ -22503,7 +22501,7 @@
       <c r="X210" s="55"/>
       <c r="Y210" s="29"/>
       <c r="Z210" s="45"/>
-      <c r="AA210" s="99"/>
+      <c r="AA210" s="85"/>
       <c r="AB210" s="48"/>
       <c r="AC210">
         <f>IF(A210="","",IFERROR(L210/K210,0))</f>
@@ -22573,7 +22571,7 @@
       <c r="X211" s="55"/>
       <c r="Y211" s="67"/>
       <c r="Z211" s="45"/>
-      <c r="AA211" s="99"/>
+      <c r="AA211" s="85"/>
       <c r="AB211" s="78"/>
     </row>
     <row r="212" spans="1:30">
@@ -22635,7 +22633,7 @@
       <c r="X212" s="55"/>
       <c r="Y212" s="67"/>
       <c r="Z212" s="45"/>
-      <c r="AA212" s="99"/>
+      <c r="AA212" s="85"/>
       <c r="AB212" s="78"/>
     </row>
     <row r="213" spans="1:30">
@@ -22703,7 +22701,7 @@
       <c r="X213" s="55"/>
       <c r="Y213" s="29"/>
       <c r="Z213" s="45"/>
-      <c r="AA213" s="99"/>
+      <c r="AA213" s="85"/>
       <c r="AB213" s="48"/>
       <c r="AC213">
         <f t="shared" ref="AC213:AC244" si="16">IF(A213="","",IFERROR(L213/K213,0))</f>
@@ -22779,7 +22777,7 @@
       <c r="X214" s="56"/>
       <c r="Y214" s="30"/>
       <c r="Z214" s="45"/>
-      <c r="AA214" s="99"/>
+      <c r="AA214" s="85"/>
       <c r="AB214" s="49"/>
       <c r="AC214">
         <f t="shared" si="16"/>
@@ -22853,7 +22851,7 @@
       <c r="X215" s="52"/>
       <c r="Y215" s="52"/>
       <c r="Z215" s="50"/>
-      <c r="AA215" s="100"/>
+      <c r="AA215" s="86"/>
       <c r="AB215" s="52"/>
       <c r="AC215" s="53">
         <f t="shared" si="16"/>
@@ -22925,7 +22923,7 @@
       <c r="X216" s="52"/>
       <c r="Y216" s="52"/>
       <c r="Z216" s="50"/>
-      <c r="AA216" s="100"/>
+      <c r="AA216" s="86"/>
       <c r="AB216" s="52"/>
       <c r="AC216" s="53">
         <f t="shared" si="16"/>
@@ -22997,7 +22995,7 @@
       <c r="X217" s="52"/>
       <c r="Y217" s="52"/>
       <c r="Z217" s="50"/>
-      <c r="AA217" s="100"/>
+      <c r="AA217" s="86"/>
       <c r="AB217" s="52"/>
       <c r="AC217" s="53">
         <f t="shared" si="16"/>
@@ -23072,7 +23070,7 @@
       <c r="X218" s="52"/>
       <c r="Y218" s="52"/>
       <c r="Z218" s="50"/>
-      <c r="AA218" s="100"/>
+      <c r="AA218" s="86"/>
       <c r="AB218" s="52"/>
       <c r="AC218" s="53">
         <f t="shared" si="16"/>
@@ -23147,7 +23145,7 @@
       <c r="X219" s="52"/>
       <c r="Y219" s="52"/>
       <c r="Z219" s="50"/>
-      <c r="AA219" s="100"/>
+      <c r="AA219" s="86"/>
       <c r="AB219" s="52"/>
       <c r="AC219" s="53">
         <f t="shared" si="16"/>
@@ -23219,7 +23217,7 @@
       <c r="X220" s="52"/>
       <c r="Y220" s="52"/>
       <c r="Z220" s="50"/>
-      <c r="AA220" s="100"/>
+      <c r="AA220" s="86"/>
       <c r="AB220" s="52"/>
       <c r="AC220" s="53">
         <f t="shared" si="16"/>
@@ -23291,7 +23289,7 @@
       <c r="X221" s="52"/>
       <c r="Y221" s="52"/>
       <c r="Z221" s="50"/>
-      <c r="AA221" s="100"/>
+      <c r="AA221" s="86"/>
       <c r="AB221" s="52"/>
       <c r="AC221" s="53">
         <f t="shared" si="16"/>
@@ -23363,7 +23361,7 @@
       <c r="X222" s="52"/>
       <c r="Y222" s="52"/>
       <c r="Z222" s="50"/>
-      <c r="AA222" s="100"/>
+      <c r="AA222" s="86"/>
       <c r="AB222" s="52"/>
       <c r="AC222" s="53">
         <f t="shared" si="16"/>
@@ -23437,7 +23435,7 @@
       <c r="X223" s="52"/>
       <c r="Y223" s="52"/>
       <c r="Z223" s="50"/>
-      <c r="AA223" s="100"/>
+      <c r="AA223" s="86"/>
       <c r="AB223" s="52"/>
       <c r="AC223" s="53">
         <f t="shared" si="16"/>
@@ -23509,7 +23507,7 @@
       <c r="X224" s="52"/>
       <c r="Y224" s="52"/>
       <c r="Z224" s="50"/>
-      <c r="AA224" s="100"/>
+      <c r="AA224" s="86"/>
       <c r="AB224" s="52"/>
       <c r="AC224" s="53">
         <f t="shared" si="16"/>
@@ -23584,7 +23582,7 @@
       <c r="X225" s="52"/>
       <c r="Y225" s="52"/>
       <c r="Z225" s="50"/>
-      <c r="AA225" s="100"/>
+      <c r="AA225" s="86"/>
       <c r="AB225" s="52"/>
       <c r="AC225" s="53">
         <f t="shared" si="16"/>
@@ -23657,7 +23655,7 @@
       <c r="X226" s="52"/>
       <c r="Y226" s="52"/>
       <c r="Z226" s="50"/>
-      <c r="AA226" s="100"/>
+      <c r="AA226" s="86"/>
       <c r="AB226" s="52"/>
       <c r="AC226" s="53">
         <f t="shared" si="16"/>
@@ -23729,7 +23727,7 @@
       <c r="X227" s="52"/>
       <c r="Y227" s="52"/>
       <c r="Z227" s="50"/>
-      <c r="AA227" s="100"/>
+      <c r="AA227" s="86"/>
       <c r="AB227" s="52"/>
       <c r="AC227" s="53">
         <f t="shared" si="16"/>
@@ -23801,7 +23799,7 @@
       <c r="X228" s="52"/>
       <c r="Y228" s="52"/>
       <c r="Z228" s="50"/>
-      <c r="AA228" s="100"/>
+      <c r="AA228" s="86"/>
       <c r="AB228" s="52"/>
       <c r="AC228" s="53">
         <f t="shared" si="16"/>
@@ -23876,7 +23874,7 @@
       <c r="X229" s="52"/>
       <c r="Y229" s="52"/>
       <c r="Z229" s="50"/>
-      <c r="AA229" s="100"/>
+      <c r="AA229" s="86"/>
       <c r="AB229" s="52"/>
       <c r="AC229" s="53">
         <f t="shared" si="16"/>
@@ -23951,7 +23949,7 @@
       <c r="X230" s="52"/>
       <c r="Y230" s="52"/>
       <c r="Z230" s="50"/>
-      <c r="AA230" s="100"/>
+      <c r="AA230" s="86"/>
       <c r="AB230" s="52"/>
       <c r="AC230" s="53">
         <f t="shared" si="16"/>
@@ -24026,7 +24024,7 @@
       <c r="X231" s="52"/>
       <c r="Y231" s="52"/>
       <c r="Z231" s="50"/>
-      <c r="AA231" s="100"/>
+      <c r="AA231" s="86"/>
       <c r="AB231" s="52"/>
       <c r="AC231" s="53">
         <f t="shared" si="16"/>
@@ -24101,7 +24099,7 @@
       <c r="X232" s="52"/>
       <c r="Y232" s="52"/>
       <c r="Z232" s="50"/>
-      <c r="AA232" s="100"/>
+      <c r="AA232" s="86"/>
       <c r="AB232" s="52"/>
       <c r="AC232" s="53">
         <f t="shared" si="16"/>
@@ -24176,7 +24174,7 @@
       <c r="X233" s="52"/>
       <c r="Y233" s="52"/>
       <c r="Z233" s="50"/>
-      <c r="AA233" s="100"/>
+      <c r="AA233" s="86"/>
       <c r="AB233" s="52"/>
       <c r="AC233" s="53">
         <f t="shared" si="16"/>
@@ -24244,7 +24242,7 @@
       <c r="X234" s="52"/>
       <c r="Y234" s="52"/>
       <c r="Z234" s="50"/>
-      <c r="AA234" s="100"/>
+      <c r="AA234" s="86"/>
       <c r="AB234" s="52"/>
       <c r="AC234" s="53">
         <f t="shared" si="16"/>
@@ -24315,7 +24313,7 @@
       <c r="X235" s="52"/>
       <c r="Y235" s="52"/>
       <c r="Z235" s="50"/>
-      <c r="AA235" s="100"/>
+      <c r="AA235" s="86"/>
       <c r="AB235" s="52"/>
       <c r="AC235" s="53">
         <f t="shared" si="16"/>
@@ -24387,7 +24385,7 @@
       <c r="X236" s="52"/>
       <c r="Y236" s="52"/>
       <c r="Z236" s="50"/>
-      <c r="AA236" s="100"/>
+      <c r="AA236" s="86"/>
       <c r="AB236" s="52"/>
       <c r="AC236" s="53">
         <f t="shared" si="16"/>
@@ -24459,7 +24457,7 @@
       <c r="X237" s="52"/>
       <c r="Y237" s="52"/>
       <c r="Z237" s="50"/>
-      <c r="AA237" s="100"/>
+      <c r="AA237" s="86"/>
       <c r="AB237" s="52"/>
       <c r="AC237" s="53">
         <f t="shared" si="16"/>
@@ -24531,7 +24529,7 @@
       <c r="X238" s="52"/>
       <c r="Y238" s="52"/>
       <c r="Z238" s="50"/>
-      <c r="AA238" s="100"/>
+      <c r="AA238" s="86"/>
       <c r="AB238" s="52"/>
       <c r="AC238" s="53">
         <f t="shared" si="16"/>
@@ -24606,7 +24604,7 @@
       <c r="X239" s="52"/>
       <c r="Y239" s="52"/>
       <c r="Z239" s="50"/>
-      <c r="AA239" s="100"/>
+      <c r="AA239" s="86"/>
       <c r="AB239" s="52"/>
       <c r="AC239" s="53">
         <f t="shared" si="16"/>
@@ -24681,7 +24679,7 @@
       <c r="X240" s="52"/>
       <c r="Y240" s="52"/>
       <c r="Z240" s="50"/>
-      <c r="AA240" s="100"/>
+      <c r="AA240" s="86"/>
       <c r="AB240" s="52"/>
       <c r="AC240" s="53">
         <f t="shared" si="16"/>
@@ -24753,7 +24751,7 @@
       <c r="X241" s="52"/>
       <c r="Y241" s="52"/>
       <c r="Z241" s="50"/>
-      <c r="AA241" s="100"/>
+      <c r="AA241" s="86"/>
       <c r="AB241" s="52"/>
       <c r="AC241" s="53">
         <f t="shared" si="16"/>
@@ -24828,7 +24826,7 @@
       <c r="X242" s="52"/>
       <c r="Y242" s="52"/>
       <c r="Z242" s="50"/>
-      <c r="AA242" s="100"/>
+      <c r="AA242" s="86"/>
       <c r="AB242" s="52"/>
       <c r="AC242" s="53">
         <f t="shared" si="16"/>
@@ -24900,7 +24898,7 @@
       <c r="X243" s="52"/>
       <c r="Y243" s="52"/>
       <c r="Z243" s="50"/>
-      <c r="AA243" s="100"/>
+      <c r="AA243" s="86"/>
       <c r="AB243" s="52"/>
       <c r="AC243" s="53">
         <f t="shared" si="16"/>
@@ -24975,7 +24973,7 @@
       <c r="X244" s="52"/>
       <c r="Y244" s="52"/>
       <c r="Z244" s="50"/>
-      <c r="AA244" s="100"/>
+      <c r="AA244" s="86"/>
       <c r="AB244" s="52"/>
       <c r="AC244" s="53">
         <f t="shared" si="16"/>
@@ -25050,7 +25048,7 @@
       <c r="X245" s="52"/>
       <c r="Y245" s="52"/>
       <c r="Z245" s="50"/>
-      <c r="AA245" s="100"/>
+      <c r="AA245" s="86"/>
       <c r="AB245" s="52"/>
       <c r="AC245" s="53">
         <f t="shared" ref="AC245:AC276" si="18">IF(A245="","",IFERROR(L245/K245,0))</f>
@@ -25122,7 +25120,7 @@
       <c r="X246" s="52"/>
       <c r="Y246" s="52"/>
       <c r="Z246" s="50"/>
-      <c r="AA246" s="100"/>
+      <c r="AA246" s="86"/>
       <c r="AB246" s="52"/>
       <c r="AC246" s="53">
         <f t="shared" si="18"/>
@@ -25197,7 +25195,7 @@
       <c r="X247" s="52"/>
       <c r="Y247" s="52"/>
       <c r="Z247" s="50"/>
-      <c r="AA247" s="100"/>
+      <c r="AA247" s="86"/>
       <c r="AB247" s="52"/>
       <c r="AC247" s="53">
         <f t="shared" si="18"/>
@@ -25272,7 +25270,7 @@
       <c r="X248" s="52"/>
       <c r="Y248" s="52"/>
       <c r="Z248" s="50"/>
-      <c r="AA248" s="100"/>
+      <c r="AA248" s="86"/>
       <c r="AB248" s="52"/>
       <c r="AC248" s="53">
         <f t="shared" si="18"/>
@@ -25347,7 +25345,7 @@
       <c r="X249" s="52"/>
       <c r="Y249" s="52"/>
       <c r="Z249" s="50"/>
-      <c r="AA249" s="100"/>
+      <c r="AA249" s="86"/>
       <c r="AB249" s="52"/>
       <c r="AC249" s="53">
         <f t="shared" si="18"/>
@@ -25419,7 +25417,7 @@
       <c r="X250" s="52"/>
       <c r="Y250" s="52"/>
       <c r="Z250" s="50"/>
-      <c r="AA250" s="100"/>
+      <c r="AA250" s="86"/>
       <c r="AB250" s="52"/>
       <c r="AC250" s="53">
         <f t="shared" si="18"/>
@@ -25491,7 +25489,7 @@
       <c r="X251" s="52"/>
       <c r="Y251" s="52"/>
       <c r="Z251" s="50"/>
-      <c r="AA251" s="100"/>
+      <c r="AA251" s="86"/>
       <c r="AB251" s="52"/>
       <c r="AC251" s="53">
         <f t="shared" si="18"/>
@@ -25566,7 +25564,7 @@
       <c r="X252" s="52"/>
       <c r="Y252" s="52"/>
       <c r="Z252" s="50"/>
-      <c r="AA252" s="100"/>
+      <c r="AA252" s="86"/>
       <c r="AB252" s="52"/>
       <c r="AC252" s="53">
         <f t="shared" si="18"/>
@@ -25641,7 +25639,7 @@
       <c r="X253" s="52"/>
       <c r="Y253" s="52"/>
       <c r="Z253" s="50"/>
-      <c r="AA253" s="100"/>
+      <c r="AA253" s="86"/>
       <c r="AB253" s="52"/>
       <c r="AC253" s="53">
         <f t="shared" si="18"/>
@@ -25716,7 +25714,7 @@
       <c r="X254" s="52"/>
       <c r="Y254" s="52"/>
       <c r="Z254" s="50"/>
-      <c r="AA254" s="100"/>
+      <c r="AA254" s="86"/>
       <c r="AB254" s="52"/>
       <c r="AC254" s="53">
         <f t="shared" si="18"/>
@@ -25788,7 +25786,7 @@
       <c r="X255" s="52"/>
       <c r="Y255" s="52"/>
       <c r="Z255" s="50"/>
-      <c r="AA255" s="100"/>
+      <c r="AA255" s="86"/>
       <c r="AB255" s="52"/>
       <c r="AC255" s="53">
         <f t="shared" si="18"/>
@@ -25863,7 +25861,7 @@
       <c r="X256" s="52"/>
       <c r="Y256" s="52"/>
       <c r="Z256" s="50"/>
-      <c r="AA256" s="100"/>
+      <c r="AA256" s="86"/>
       <c r="AB256" s="52"/>
       <c r="AC256" s="53">
         <f t="shared" si="18"/>
@@ -25938,7 +25936,7 @@
       <c r="X257" s="52"/>
       <c r="Y257" s="52"/>
       <c r="Z257" s="50"/>
-      <c r="AA257" s="100"/>
+      <c r="AA257" s="86"/>
       <c r="AB257" s="52"/>
       <c r="AC257" s="53">
         <f t="shared" si="18"/>
@@ -26012,7 +26010,7 @@
       <c r="X258" s="52"/>
       <c r="Y258" s="52"/>
       <c r="Z258" s="50"/>
-      <c r="AA258" s="100"/>
+      <c r="AA258" s="86"/>
       <c r="AB258" s="52"/>
       <c r="AC258" s="53">
         <f t="shared" si="18"/>
@@ -26084,7 +26082,7 @@
       <c r="X259" s="52"/>
       <c r="Y259" s="52"/>
       <c r="Z259" s="50"/>
-      <c r="AA259" s="100"/>
+      <c r="AA259" s="86"/>
       <c r="AB259" s="52"/>
       <c r="AC259" s="53">
         <f t="shared" si="18"/>
@@ -26161,7 +26159,7 @@
       <c r="X260" s="52"/>
       <c r="Y260" s="52"/>
       <c r="Z260" s="50"/>
-      <c r="AA260" s="100"/>
+      <c r="AA260" s="86"/>
       <c r="AB260" s="52"/>
       <c r="AC260" s="53">
         <f t="shared" si="18"/>
@@ -26233,7 +26231,7 @@
       <c r="X261" s="52"/>
       <c r="Y261" s="52"/>
       <c r="Z261" s="50"/>
-      <c r="AA261" s="100"/>
+      <c r="AA261" s="86"/>
       <c r="AB261" s="52"/>
       <c r="AC261" s="53">
         <f t="shared" si="18"/>
@@ -26308,7 +26306,7 @@
       <c r="X262" s="52"/>
       <c r="Y262" s="52"/>
       <c r="Z262" s="50"/>
-      <c r="AA262" s="100"/>
+      <c r="AA262" s="86"/>
       <c r="AB262" s="52"/>
       <c r="AC262" s="53">
         <f t="shared" si="18"/>
@@ -26380,7 +26378,7 @@
       <c r="X263" s="52"/>
       <c r="Y263" s="52"/>
       <c r="Z263" s="50"/>
-      <c r="AA263" s="100"/>
+      <c r="AA263" s="86"/>
       <c r="AB263" s="52"/>
       <c r="AC263" s="53">
         <f t="shared" si="18"/>
@@ -26452,7 +26450,7 @@
       <c r="X264" s="52"/>
       <c r="Y264" s="52"/>
       <c r="Z264" s="50"/>
-      <c r="AA264" s="100"/>
+      <c r="AA264" s="86"/>
       <c r="AB264" s="52"/>
       <c r="AC264" s="53">
         <f t="shared" si="18"/>
@@ -26526,7 +26524,7 @@
       <c r="X265" s="52"/>
       <c r="Y265" s="52"/>
       <c r="Z265" s="50"/>
-      <c r="AA265" s="100"/>
+      <c r="AA265" s="86"/>
       <c r="AB265" s="52"/>
       <c r="AC265" s="53">
         <f t="shared" si="18"/>
@@ -26597,7 +26595,7 @@
       <c r="X266" s="52"/>
       <c r="Y266" s="52"/>
       <c r="Z266" s="50"/>
-      <c r="AA266" s="100"/>
+      <c r="AA266" s="86"/>
       <c r="AB266" s="52"/>
       <c r="AC266" s="53">
         <f t="shared" si="18"/>
@@ -26669,7 +26667,7 @@
       <c r="X267" s="52"/>
       <c r="Y267" s="52"/>
       <c r="Z267" s="50"/>
-      <c r="AA267" s="100"/>
+      <c r="AA267" s="86"/>
       <c r="AB267" s="52"/>
       <c r="AC267" s="53">
         <f t="shared" si="18"/>
@@ -26741,7 +26739,7 @@
       <c r="X268" s="52"/>
       <c r="Y268" s="52"/>
       <c r="Z268" s="50"/>
-      <c r="AA268" s="100"/>
+      <c r="AA268" s="86"/>
       <c r="AB268" s="52"/>
       <c r="AC268" s="53">
         <f t="shared" si="18"/>
@@ -26813,7 +26811,7 @@
       <c r="X269" s="52"/>
       <c r="Y269" s="52"/>
       <c r="Z269" s="50"/>
-      <c r="AA269" s="100"/>
+      <c r="AA269" s="86"/>
       <c r="AB269" s="52"/>
       <c r="AC269" s="53">
         <f t="shared" si="18"/>
@@ -26885,7 +26883,7 @@
       <c r="X270" s="52"/>
       <c r="Y270" s="52"/>
       <c r="Z270" s="50"/>
-      <c r="AA270" s="100"/>
+      <c r="AA270" s="86"/>
       <c r="AB270" s="52"/>
       <c r="AC270" s="53">
         <f t="shared" si="18"/>
@@ -26957,7 +26955,7 @@
       <c r="X271" s="52"/>
       <c r="Y271" s="52"/>
       <c r="Z271" s="50"/>
-      <c r="AA271" s="100"/>
+      <c r="AA271" s="86"/>
       <c r="AB271" s="52"/>
       <c r="AC271" s="53">
         <f t="shared" si="18"/>
@@ -27029,7 +27027,7 @@
       <c r="X272" s="52"/>
       <c r="Y272" s="52"/>
       <c r="Z272" s="50"/>
-      <c r="AA272" s="100"/>
+      <c r="AA272" s="86"/>
       <c r="AB272" s="52"/>
       <c r="AC272" s="53">
         <f t="shared" si="18"/>
@@ -27101,7 +27099,7 @@
       <c r="X273" s="52"/>
       <c r="Y273" s="52"/>
       <c r="Z273" s="50"/>
-      <c r="AA273" s="100"/>
+      <c r="AA273" s="86"/>
       <c r="AB273" s="52"/>
       <c r="AC273" s="53">
         <f t="shared" si="18"/>
@@ -27173,7 +27171,7 @@
       <c r="X274" s="52"/>
       <c r="Y274" s="52"/>
       <c r="Z274" s="50"/>
-      <c r="AA274" s="100"/>
+      <c r="AA274" s="86"/>
       <c r="AB274" s="52"/>
       <c r="AC274" s="53">
         <f t="shared" si="18"/>
@@ -27245,7 +27243,7 @@
       <c r="X275" s="52"/>
       <c r="Y275" s="52"/>
       <c r="Z275" s="50"/>
-      <c r="AA275" s="100"/>
+      <c r="AA275" s="86"/>
       <c r="AB275" s="52"/>
       <c r="AC275" s="53">
         <f t="shared" si="18"/>
@@ -27317,7 +27315,7 @@
       <c r="X276" s="52"/>
       <c r="Y276" s="52"/>
       <c r="Z276" s="50"/>
-      <c r="AA276" s="100"/>
+      <c r="AA276" s="86"/>
       <c r="AB276" s="52"/>
       <c r="AC276" s="53">
         <f t="shared" si="18"/>
@@ -27389,7 +27387,7 @@
       <c r="X277" s="52"/>
       <c r="Y277" s="52"/>
       <c r="Z277" s="50"/>
-      <c r="AA277" s="100"/>
+      <c r="AA277" s="86"/>
       <c r="AB277" s="52"/>
       <c r="AC277" s="53">
         <f t="shared" ref="AC277:AC308" si="20">IF(A277="","",IFERROR(L277/K277,0))</f>
@@ -27461,7 +27459,7 @@
       <c r="X278" s="52"/>
       <c r="Y278" s="52"/>
       <c r="Z278" s="50"/>
-      <c r="AA278" s="100"/>
+      <c r="AA278" s="86"/>
       <c r="AB278" s="52"/>
       <c r="AC278" s="53">
         <f t="shared" si="20"/>
@@ -27533,7 +27531,7 @@
       <c r="X279" s="52"/>
       <c r="Y279" s="52"/>
       <c r="Z279" s="50"/>
-      <c r="AA279" s="100"/>
+      <c r="AA279" s="86"/>
       <c r="AB279" s="52"/>
       <c r="AC279" s="53">
         <f t="shared" si="20"/>
@@ -27605,7 +27603,7 @@
       <c r="X280" s="52"/>
       <c r="Y280" s="52"/>
       <c r="Z280" s="50"/>
-      <c r="AA280" s="100"/>
+      <c r="AA280" s="86"/>
       <c r="AB280" s="52"/>
       <c r="AC280" s="53">
         <f t="shared" si="20"/>
@@ -27680,7 +27678,7 @@
       <c r="X281" s="52"/>
       <c r="Y281" s="52"/>
       <c r="Z281" s="50"/>
-      <c r="AA281" s="100"/>
+      <c r="AA281" s="86"/>
       <c r="AB281" s="52"/>
       <c r="AC281" s="53">
         <f t="shared" si="20"/>
@@ -27752,7 +27750,7 @@
       <c r="X282" s="52"/>
       <c r="Y282" s="52"/>
       <c r="Z282" s="50"/>
-      <c r="AA282" s="100"/>
+      <c r="AA282" s="86"/>
       <c r="AB282" s="52"/>
       <c r="AC282" s="53">
         <f t="shared" si="20"/>
@@ -27824,7 +27822,7 @@
       <c r="X283" s="52"/>
       <c r="Y283" s="52"/>
       <c r="Z283" s="50"/>
-      <c r="AA283" s="100"/>
+      <c r="AA283" s="86"/>
       <c r="AB283" s="52"/>
       <c r="AC283" s="53">
         <f t="shared" si="20"/>
@@ -27896,7 +27894,7 @@
       <c r="X284" s="52"/>
       <c r="Y284" s="52"/>
       <c r="Z284" s="50"/>
-      <c r="AA284" s="100"/>
+      <c r="AA284" s="86"/>
       <c r="AB284" s="52"/>
       <c r="AC284" s="53">
         <f t="shared" si="20"/>
@@ -27968,7 +27966,7 @@
       <c r="X285" s="52"/>
       <c r="Y285" s="52"/>
       <c r="Z285" s="50"/>
-      <c r="AA285" s="100"/>
+      <c r="AA285" s="86"/>
       <c r="AB285" s="52"/>
       <c r="AC285" s="53">
         <f t="shared" si="20"/>
@@ -28041,7 +28039,7 @@
       <c r="X286" s="52"/>
       <c r="Y286" s="52"/>
       <c r="Z286" s="50"/>
-      <c r="AA286" s="100"/>
+      <c r="AA286" s="86"/>
       <c r="AB286" s="52"/>
       <c r="AC286" s="53">
         <f t="shared" si="20"/>
@@ -28109,7 +28107,7 @@
       <c r="X287" s="52"/>
       <c r="Y287" s="52"/>
       <c r="Z287" s="50"/>
-      <c r="AA287" s="100"/>
+      <c r="AA287" s="86"/>
       <c r="AB287" s="52"/>
       <c r="AC287" s="53">
         <f t="shared" si="20"/>
@@ -28181,7 +28179,7 @@
       <c r="X288" s="52"/>
       <c r="Y288" s="52"/>
       <c r="Z288" s="50"/>
-      <c r="AA288" s="100"/>
+      <c r="AA288" s="86"/>
       <c r="AB288" s="52"/>
       <c r="AC288" s="53">
         <f t="shared" si="20"/>
@@ -28249,7 +28247,7 @@
       <c r="X289" s="52"/>
       <c r="Y289" s="52"/>
       <c r="Z289" s="50"/>
-      <c r="AA289" s="100"/>
+      <c r="AA289" s="86"/>
       <c r="AB289" s="52"/>
       <c r="AC289" s="53">
         <f t="shared" si="20"/>
@@ -28324,7 +28322,7 @@
       <c r="X290" s="52"/>
       <c r="Y290" s="52"/>
       <c r="Z290" s="50"/>
-      <c r="AA290" s="100"/>
+      <c r="AA290" s="86"/>
       <c r="AB290" s="52"/>
       <c r="AC290" s="53">
         <f t="shared" si="20"/>
@@ -28399,7 +28397,7 @@
       <c r="X291" s="52"/>
       <c r="Y291" s="52"/>
       <c r="Z291" s="50"/>
-      <c r="AA291" s="100"/>
+      <c r="AA291" s="86"/>
       <c r="AB291" s="52"/>
       <c r="AC291" s="53">
         <f t="shared" si="20"/>
@@ -28474,7 +28472,7 @@
       <c r="X292" s="52"/>
       <c r="Y292" s="52"/>
       <c r="Z292" s="50"/>
-      <c r="AA292" s="100"/>
+      <c r="AA292" s="86"/>
       <c r="AB292" s="52"/>
       <c r="AC292" s="53">
         <f t="shared" si="20"/>
@@ -28546,7 +28544,7 @@
       <c r="X293" s="52"/>
       <c r="Y293" s="52"/>
       <c r="Z293" s="50"/>
-      <c r="AA293" s="100"/>
+      <c r="AA293" s="86"/>
       <c r="AB293" s="52"/>
       <c r="AC293" s="53">
         <f t="shared" si="20"/>
@@ -28621,7 +28619,7 @@
       <c r="X294" s="52"/>
       <c r="Y294" s="52"/>
       <c r="Z294" s="50"/>
-      <c r="AA294" s="100"/>
+      <c r="AA294" s="86"/>
       <c r="AB294" s="52"/>
       <c r="AC294" s="53">
         <f t="shared" si="20"/>
@@ -28693,7 +28691,7 @@
       <c r="X295" s="52"/>
       <c r="Y295" s="52"/>
       <c r="Z295" s="50"/>
-      <c r="AA295" s="100"/>
+      <c r="AA295" s="86"/>
       <c r="AB295" s="52"/>
       <c r="AC295" s="53">
         <f t="shared" si="20"/>
@@ -28765,7 +28763,7 @@
       <c r="X296" s="52"/>
       <c r="Y296" s="52"/>
       <c r="Z296" s="50"/>
-      <c r="AA296" s="100"/>
+      <c r="AA296" s="86"/>
       <c r="AB296" s="52"/>
       <c r="AC296" s="53">
         <f t="shared" si="20"/>
@@ -28840,7 +28838,7 @@
       <c r="X297" s="52"/>
       <c r="Y297" s="52"/>
       <c r="Z297" s="50"/>
-      <c r="AA297" s="100"/>
+      <c r="AA297" s="86"/>
       <c r="AB297" s="52"/>
       <c r="AC297" s="53">
         <f t="shared" si="20"/>
@@ -28915,7 +28913,7 @@
       <c r="X298" s="52"/>
       <c r="Y298" s="52"/>
       <c r="Z298" s="50"/>
-      <c r="AA298" s="100"/>
+      <c r="AA298" s="86"/>
       <c r="AB298" s="52"/>
       <c r="AC298" s="53">
         <f t="shared" si="20"/>
@@ -28990,7 +28988,7 @@
       <c r="X299" s="52"/>
       <c r="Y299" s="52"/>
       <c r="Z299" s="50"/>
-      <c r="AA299" s="100"/>
+      <c r="AA299" s="86"/>
       <c r="AB299" s="52"/>
       <c r="AC299" s="53">
         <f t="shared" si="20"/>
@@ -29065,7 +29063,7 @@
       <c r="X300" s="52"/>
       <c r="Y300" s="52"/>
       <c r="Z300" s="50"/>
-      <c r="AA300" s="100"/>
+      <c r="AA300" s="86"/>
       <c r="AB300" s="52"/>
       <c r="AC300" s="53">
         <f t="shared" si="20"/>
@@ -29140,7 +29138,7 @@
       <c r="X301" s="52"/>
       <c r="Y301" s="52"/>
       <c r="Z301" s="50"/>
-      <c r="AA301" s="100"/>
+      <c r="AA301" s="86"/>
       <c r="AB301" s="52"/>
       <c r="AC301" s="53">
         <f t="shared" si="20"/>
@@ -29215,7 +29213,7 @@
       <c r="X302" s="52"/>
       <c r="Y302" s="52"/>
       <c r="Z302" s="50"/>
-      <c r="AA302" s="100"/>
+      <c r="AA302" s="86"/>
       <c r="AB302" s="52"/>
       <c r="AC302" s="53">
         <f t="shared" si="20"/>
@@ -29290,7 +29288,7 @@
       <c r="X303" s="52"/>
       <c r="Y303" s="52"/>
       <c r="Z303" s="50"/>
-      <c r="AA303" s="100"/>
+      <c r="AA303" s="86"/>
       <c r="AB303" s="52"/>
       <c r="AC303" s="53">
         <f t="shared" si="20"/>
@@ -29365,7 +29363,7 @@
       <c r="X304" s="52"/>
       <c r="Y304" s="52"/>
       <c r="Z304" s="50"/>
-      <c r="AA304" s="100"/>
+      <c r="AA304" s="86"/>
       <c r="AB304" s="52"/>
       <c r="AC304" s="53">
         <f t="shared" si="20"/>
@@ -29440,7 +29438,7 @@
       <c r="X305" s="52"/>
       <c r="Y305" s="52"/>
       <c r="Z305" s="50"/>
-      <c r="AA305" s="100"/>
+      <c r="AA305" s="86"/>
       <c r="AB305" s="52"/>
       <c r="AC305" s="53">
         <f t="shared" si="20"/>
@@ -29512,7 +29510,7 @@
       <c r="X306" s="52"/>
       <c r="Y306" s="52"/>
       <c r="Z306" s="50"/>
-      <c r="AA306" s="100"/>
+      <c r="AA306" s="86"/>
       <c r="AB306" s="52"/>
       <c r="AC306" s="53">
         <f t="shared" si="20"/>
@@ -29587,7 +29585,7 @@
       <c r="X307" s="52"/>
       <c r="Y307" s="52"/>
       <c r="Z307" s="50"/>
-      <c r="AA307" s="100"/>
+      <c r="AA307" s="86"/>
       <c r="AB307" s="52"/>
       <c r="AC307" s="53">
         <f t="shared" si="20"/>
@@ -29659,7 +29657,7 @@
       <c r="X308" s="52"/>
       <c r="Y308" s="52"/>
       <c r="Z308" s="50"/>
-      <c r="AA308" s="100"/>
+      <c r="AA308" s="86"/>
       <c r="AB308" s="52"/>
       <c r="AC308" s="53">
         <f t="shared" si="20"/>
@@ -29730,7 +29728,7 @@
       <c r="X309" s="52"/>
       <c r="Y309" s="52"/>
       <c r="Z309" s="50"/>
-      <c r="AA309" s="100"/>
+      <c r="AA309" s="86"/>
       <c r="AB309" s="52"/>
       <c r="AC309" s="53">
         <f t="shared" ref="AC309:AC340" si="22">IF(A309="","",IFERROR(L309/K309,0))</f>
@@ -29805,7 +29803,7 @@
       <c r="X310" s="52"/>
       <c r="Y310" s="52"/>
       <c r="Z310" s="50"/>
-      <c r="AA310" s="100"/>
+      <c r="AA310" s="86"/>
       <c r="AB310" s="52"/>
       <c r="AC310" s="53">
         <f t="shared" si="22"/>
@@ -29877,7 +29875,7 @@
       <c r="X311" s="52"/>
       <c r="Y311" s="52"/>
       <c r="Z311" s="50"/>
-      <c r="AA311" s="100"/>
+      <c r="AA311" s="86"/>
       <c r="AB311" s="52"/>
       <c r="AC311" s="53">
         <f t="shared" si="22"/>
@@ -29952,7 +29950,7 @@
       <c r="X312" s="52"/>
       <c r="Y312" s="52"/>
       <c r="Z312" s="50"/>
-      <c r="AA312" s="100"/>
+      <c r="AA312" s="86"/>
       <c r="AB312" s="52"/>
       <c r="AC312" s="53">
         <f t="shared" si="22"/>
@@ -30027,7 +30025,7 @@
       <c r="X313" s="52"/>
       <c r="Y313" s="52"/>
       <c r="Z313" s="50"/>
-      <c r="AA313" s="100"/>
+      <c r="AA313" s="86"/>
       <c r="AB313" s="52"/>
       <c r="AC313" s="53">
         <f t="shared" si="22"/>
@@ -30099,7 +30097,7 @@
       <c r="X314" s="52"/>
       <c r="Y314" s="52"/>
       <c r="Z314" s="50"/>
-      <c r="AA314" s="100"/>
+      <c r="AA314" s="86"/>
       <c r="AB314" s="52"/>
       <c r="AC314" s="53">
         <f t="shared" si="22"/>
@@ -30171,7 +30169,7 @@
       <c r="X315" s="52"/>
       <c r="Y315" s="52"/>
       <c r="Z315" s="50"/>
-      <c r="AA315" s="100"/>
+      <c r="AA315" s="86"/>
       <c r="AB315" s="52"/>
       <c r="AC315" s="53">
         <f t="shared" si="22"/>
@@ -30239,7 +30237,7 @@
       <c r="X316" s="52"/>
       <c r="Y316" s="52"/>
       <c r="Z316" s="50"/>
-      <c r="AA316" s="100"/>
+      <c r="AA316" s="86"/>
       <c r="AB316" s="52"/>
       <c r="AC316" s="53">
         <f t="shared" si="22"/>
@@ -30310,7 +30308,7 @@
       <c r="X317" s="52"/>
       <c r="Y317" s="52"/>
       <c r="Z317" s="50"/>
-      <c r="AA317" s="100"/>
+      <c r="AA317" s="86"/>
       <c r="AB317" s="52"/>
       <c r="AC317" s="53">
         <f t="shared" si="22"/>
@@ -30382,7 +30380,7 @@
       <c r="X318" s="52"/>
       <c r="Y318" s="52"/>
       <c r="Z318" s="50"/>
-      <c r="AA318" s="100"/>
+      <c r="AA318" s="86"/>
       <c r="AB318" s="52"/>
       <c r="AC318" s="53">
         <f t="shared" si="22"/>
@@ -30454,7 +30452,7 @@
       <c r="X319" s="52"/>
       <c r="Y319" s="52"/>
       <c r="Z319" s="50"/>
-      <c r="AA319" s="100"/>
+      <c r="AA319" s="86"/>
       <c r="AB319" s="52"/>
       <c r="AC319" s="53">
         <f t="shared" si="22"/>
@@ -30529,7 +30527,7 @@
       <c r="X320" s="52"/>
       <c r="Y320" s="52"/>
       <c r="Z320" s="50"/>
-      <c r="AA320" s="100"/>
+      <c r="AA320" s="86"/>
       <c r="AB320" s="52"/>
       <c r="AC320" s="53">
         <f t="shared" si="22"/>
@@ -30597,7 +30595,7 @@
       <c r="X321" s="52"/>
       <c r="Y321" s="52"/>
       <c r="Z321" s="50"/>
-      <c r="AA321" s="100"/>
+      <c r="AA321" s="86"/>
       <c r="AB321" s="52"/>
       <c r="AC321" s="53">
         <f t="shared" si="22"/>
@@ -30672,7 +30670,7 @@
       <c r="X322" s="52"/>
       <c r="Y322" s="52"/>
       <c r="Z322" s="50"/>
-      <c r="AA322" s="100"/>
+      <c r="AA322" s="86"/>
       <c r="AB322" s="52"/>
       <c r="AC322" s="53">
         <f t="shared" si="22"/>
@@ -30743,7 +30741,7 @@
       <c r="X323" s="52"/>
       <c r="Y323" s="52"/>
       <c r="Z323" s="50"/>
-      <c r="AA323" s="100"/>
+      <c r="AA323" s="86"/>
       <c r="AB323" s="52"/>
       <c r="AC323" s="53">
         <f t="shared" si="22"/>
@@ -30815,7 +30813,7 @@
       <c r="X324" s="52"/>
       <c r="Y324" s="52"/>
       <c r="Z324" s="50"/>
-      <c r="AA324" s="100"/>
+      <c r="AA324" s="86"/>
       <c r="AB324" s="52"/>
       <c r="AC324" s="53">
         <f t="shared" si="22"/>
@@ -30889,7 +30887,7 @@
       <c r="X325" s="52"/>
       <c r="Y325" s="52"/>
       <c r="Z325" s="50"/>
-      <c r="AA325" s="100"/>
+      <c r="AA325" s="86"/>
       <c r="AB325" s="52"/>
       <c r="AC325" s="53">
         <f t="shared" si="22"/>
@@ -30961,7 +30959,7 @@
       <c r="X326" s="52"/>
       <c r="Y326" s="52"/>
       <c r="Z326" s="50"/>
-      <c r="AA326" s="100"/>
+      <c r="AA326" s="86"/>
       <c r="AB326" s="52"/>
       <c r="AC326" s="53">
         <f t="shared" si="22"/>
@@ -31033,7 +31031,7 @@
       <c r="X327" s="52"/>
       <c r="Y327" s="52"/>
       <c r="Z327" s="50"/>
-      <c r="AA327" s="100"/>
+      <c r="AA327" s="86"/>
       <c r="AB327" s="52"/>
       <c r="AC327" s="53">
         <f t="shared" si="22"/>
@@ -31104,7 +31102,7 @@
       <c r="X328" s="52"/>
       <c r="Y328" s="52"/>
       <c r="Z328" s="50"/>
-      <c r="AA328" s="100"/>
+      <c r="AA328" s="86"/>
       <c r="AB328" s="52"/>
       <c r="AC328" s="53">
         <f t="shared" si="22"/>
@@ -31179,7 +31177,7 @@
       <c r="X329" s="52"/>
       <c r="Y329" s="52"/>
       <c r="Z329" s="50"/>
-      <c r="AA329" s="100"/>
+      <c r="AA329" s="86"/>
       <c r="AB329" s="52"/>
       <c r="AC329" s="53">
         <f t="shared" si="22"/>
@@ -31254,7 +31252,7 @@
       <c r="X330" s="52"/>
       <c r="Y330" s="52"/>
       <c r="Z330" s="50"/>
-      <c r="AA330" s="100"/>
+      <c r="AA330" s="86"/>
       <c r="AB330" s="52"/>
       <c r="AC330" s="53">
         <f t="shared" si="22"/>
@@ -31322,7 +31320,7 @@
       <c r="X331" s="52"/>
       <c r="Y331" s="52"/>
       <c r="Z331" s="50"/>
-      <c r="AA331" s="100"/>
+      <c r="AA331" s="86"/>
       <c r="AB331" s="52"/>
       <c r="AC331" s="53">
         <f t="shared" si="22"/>
@@ -31393,7 +31391,7 @@
       <c r="X332" s="52"/>
       <c r="Y332" s="52"/>
       <c r="Z332" s="50"/>
-      <c r="AA332" s="100"/>
+      <c r="AA332" s="86"/>
       <c r="AB332" s="52"/>
       <c r="AC332" s="53">
         <f t="shared" si="22"/>
@@ -31464,7 +31462,7 @@
       <c r="X333" s="52"/>
       <c r="Y333" s="52"/>
       <c r="Z333" s="50"/>
-      <c r="AA333" s="100"/>
+      <c r="AA333" s="86"/>
       <c r="AB333" s="52"/>
       <c r="AC333" s="53">
         <f t="shared" si="22"/>
@@ -31539,7 +31537,7 @@
       <c r="X334" s="52"/>
       <c r="Y334" s="52"/>
       <c r="Z334" s="50"/>
-      <c r="AA334" s="100"/>
+      <c r="AA334" s="86"/>
       <c r="AB334" s="52"/>
       <c r="AC334" s="53">
         <f t="shared" si="22"/>
@@ -31614,7 +31612,7 @@
       <c r="X335" s="52"/>
       <c r="Y335" s="52"/>
       <c r="Z335" s="50"/>
-      <c r="AA335" s="100"/>
+      <c r="AA335" s="86"/>
       <c r="AB335" s="52"/>
       <c r="AC335" s="53">
         <f t="shared" si="22"/>
@@ -31682,7 +31680,7 @@
       <c r="X336" s="52"/>
       <c r="Y336" s="52"/>
       <c r="Z336" s="50"/>
-      <c r="AA336" s="100"/>
+      <c r="AA336" s="86"/>
       <c r="AB336" s="52"/>
       <c r="AC336" s="53">
         <f t="shared" si="22"/>
@@ -31757,7 +31755,7 @@
       <c r="X337" s="52"/>
       <c r="Y337" s="52"/>
       <c r="Z337" s="50"/>
-      <c r="AA337" s="100"/>
+      <c r="AA337" s="86"/>
       <c r="AB337" s="52"/>
       <c r="AC337" s="53">
         <f t="shared" si="22"/>
@@ -31829,7 +31827,7 @@
       <c r="X338" s="52"/>
       <c r="Y338" s="52"/>
       <c r="Z338" s="50"/>
-      <c r="AA338" s="100"/>
+      <c r="AA338" s="86"/>
       <c r="AB338" s="52"/>
       <c r="AC338" s="53">
         <f t="shared" si="22"/>
@@ -31904,7 +31902,7 @@
       <c r="X339" s="52"/>
       <c r="Y339" s="52"/>
       <c r="Z339" s="50"/>
-      <c r="AA339" s="100"/>
+      <c r="AA339" s="86"/>
       <c r="AB339" s="52"/>
       <c r="AC339" s="53">
         <f t="shared" si="22"/>
@@ -31976,7 +31974,7 @@
       <c r="X340" s="52"/>
       <c r="Y340" s="52"/>
       <c r="Z340" s="50"/>
-      <c r="AA340" s="100"/>
+      <c r="AA340" s="86"/>
       <c r="AB340" s="52"/>
       <c r="AC340" s="53">
         <f t="shared" si="22"/>
@@ -32048,7 +32046,7 @@
       <c r="X341" s="52"/>
       <c r="Y341" s="52"/>
       <c r="Z341" s="50"/>
-      <c r="AA341" s="100"/>
+      <c r="AA341" s="86"/>
       <c r="AB341" s="52"/>
       <c r="AC341" s="53">
         <f t="shared" ref="AC341:AC348" si="24">IF(A341="","",IFERROR(L341/K341,0))</f>
@@ -32120,7 +32118,7 @@
       <c r="X342" s="52"/>
       <c r="Y342" s="52"/>
       <c r="Z342" s="50"/>
-      <c r="AA342" s="100"/>
+      <c r="AA342" s="86"/>
       <c r="AB342" s="52"/>
       <c r="AC342" s="53">
         <f t="shared" si="24"/>
@@ -32192,7 +32190,7 @@
       <c r="X343" s="52"/>
       <c r="Y343" s="52"/>
       <c r="Z343" s="50"/>
-      <c r="AA343" s="100"/>
+      <c r="AA343" s="86"/>
       <c r="AB343" s="52"/>
       <c r="AC343" s="53">
         <f t="shared" si="24"/>
@@ -32264,7 +32262,7 @@
       <c r="X344" s="52"/>
       <c r="Y344" s="52"/>
       <c r="Z344" s="50"/>
-      <c r="AA344" s="100"/>
+      <c r="AA344" s="86"/>
       <c r="AB344" s="52"/>
       <c r="AC344" s="53">
         <f t="shared" si="24"/>
@@ -32332,7 +32330,7 @@
       <c r="X345" s="52"/>
       <c r="Y345" s="52"/>
       <c r="Z345" s="50"/>
-      <c r="AA345" s="100"/>
+      <c r="AA345" s="86"/>
       <c r="AB345" s="52"/>
       <c r="AC345" s="53">
         <f t="shared" si="24"/>
@@ -32404,7 +32402,7 @@
       <c r="X346" s="52"/>
       <c r="Y346" s="52"/>
       <c r="Z346" s="50"/>
-      <c r="AA346" s="100"/>
+      <c r="AA346" s="86"/>
       <c r="AB346" s="52"/>
       <c r="AC346" s="53">
         <f t="shared" si="24"/>
@@ -32476,7 +32474,7 @@
       <c r="X347" s="52"/>
       <c r="Y347" s="52"/>
       <c r="Z347" s="50"/>
-      <c r="AA347" s="100"/>
+      <c r="AA347" s="86"/>
       <c r="AB347" s="52"/>
       <c r="AC347" s="53">
         <f t="shared" si="24"/>
@@ -32551,7 +32549,7 @@
       <c r="X348" s="52"/>
       <c r="Y348" s="52"/>
       <c r="Z348" s="50"/>
-      <c r="AA348" s="100"/>
+      <c r="AA348" s="86"/>
       <c r="AB348" s="52"/>
       <c r="AC348" s="53">
         <f t="shared" si="24"/>
@@ -32622,7 +32620,7 @@
       <c r="X349" s="52"/>
       <c r="Y349" s="52"/>
       <c r="Z349" s="50"/>
-      <c r="AA349" s="100"/>
+      <c r="AA349" s="86"/>
       <c r="AB349" s="52"/>
       <c r="AC349" s="53"/>
       <c r="AD349" s="53"/>
@@ -32691,7 +32689,7 @@
       <c r="X350" s="52"/>
       <c r="Y350" s="52"/>
       <c r="Z350" s="50"/>
-      <c r="AA350" s="100"/>
+      <c r="AA350" s="86"/>
       <c r="AB350" s="52"/>
       <c r="AC350" s="53">
         <f t="shared" ref="AC350:AC361" si="26">IF(A350="","",IFERROR(L350/K350,0))</f>
@@ -32766,7 +32764,7 @@
       <c r="X351" s="52"/>
       <c r="Y351" s="52"/>
       <c r="Z351" s="50"/>
-      <c r="AA351" s="100"/>
+      <c r="AA351" s="86"/>
       <c r="AB351" s="52"/>
       <c r="AC351" s="53">
         <f t="shared" si="26"/>
@@ -32841,7 +32839,7 @@
       <c r="X352" s="52"/>
       <c r="Y352" s="52"/>
       <c r="Z352" s="50"/>
-      <c r="AA352" s="100"/>
+      <c r="AA352" s="86"/>
       <c r="AB352" s="52"/>
       <c r="AC352" s="53">
         <f t="shared" si="26"/>
@@ -32913,7 +32911,7 @@
       <c r="X353" s="52"/>
       <c r="Y353" s="52"/>
       <c r="Z353" s="50"/>
-      <c r="AA353" s="100"/>
+      <c r="AA353" s="86"/>
       <c r="AB353" s="52"/>
       <c r="AC353" s="53">
         <f t="shared" si="26"/>
@@ -32988,7 +32986,7 @@
       <c r="X354" s="52"/>
       <c r="Y354" s="52"/>
       <c r="Z354" s="50"/>
-      <c r="AA354" s="100"/>
+      <c r="AA354" s="86"/>
       <c r="AB354" s="52"/>
       <c r="AC354" s="53">
         <f t="shared" si="26"/>
@@ -33060,7 +33058,7 @@
       <c r="X355" s="52"/>
       <c r="Y355" s="52"/>
       <c r="Z355" s="50"/>
-      <c r="AA355" s="100"/>
+      <c r="AA355" s="86"/>
       <c r="AB355" s="52"/>
       <c r="AC355" s="53">
         <f t="shared" si="26"/>
@@ -33135,7 +33133,7 @@
       <c r="X356" s="52"/>
       <c r="Y356" s="52"/>
       <c r="Z356" s="50"/>
-      <c r="AA356" s="100"/>
+      <c r="AA356" s="86"/>
       <c r="AB356" s="52"/>
       <c r="AC356" s="53">
         <f t="shared" si="26"/>
@@ -33207,7 +33205,7 @@
       <c r="X357" s="52"/>
       <c r="Y357" s="52"/>
       <c r="Z357" s="50"/>
-      <c r="AA357" s="100"/>
+      <c r="AA357" s="86"/>
       <c r="AB357" s="52"/>
       <c r="AC357" s="53">
         <f t="shared" si="26"/>
@@ -33279,7 +33277,7 @@
       <c r="X358" s="52"/>
       <c r="Y358" s="52"/>
       <c r="Z358" s="50"/>
-      <c r="AA358" s="100"/>
+      <c r="AA358" s="86"/>
       <c r="AB358" s="52"/>
       <c r="AC358" s="53">
         <f t="shared" si="26"/>
@@ -33351,7 +33349,7 @@
       <c r="X359" s="52"/>
       <c r="Y359" s="52"/>
       <c r="Z359" s="50"/>
-      <c r="AA359" s="100"/>
+      <c r="AA359" s="86"/>
       <c r="AB359" s="52"/>
       <c r="AC359" s="53">
         <f t="shared" si="26"/>
@@ -33423,7 +33421,7 @@
       <c r="X360" s="52"/>
       <c r="Y360" s="52"/>
       <c r="Z360" s="50"/>
-      <c r="AA360" s="100"/>
+      <c r="AA360" s="86"/>
       <c r="AB360" s="52"/>
       <c r="AC360" s="53">
         <f t="shared" si="26"/>
@@ -33495,7 +33493,7 @@
       <c r="X361" s="52"/>
       <c r="Y361" s="52"/>
       <c r="Z361" s="50"/>
-      <c r="AA361" s="100"/>
+      <c r="AA361" s="86"/>
       <c r="AB361" s="52"/>
       <c r="AC361" s="53">
         <f t="shared" si="26"/>
@@ -33623,49 +33621,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="88" t="s">
         <v>848</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="90" t="s">
         <v>849</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="91" t="s">
         <v>850</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
     </row>
     <row r="5" spans="1:11" ht="26">
       <c r="A5" s="1" t="s">
@@ -34563,49 +34561,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="88" t="s">
         <v>870</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="90" t="s">
         <v>871</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="91" t="s">
         <v>850</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
     </row>
     <row r="5" spans="1:11" ht="26">
       <c r="A5" s="1" t="s">
@@ -35787,66 +35785,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:77">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="93" t="s">
         <v>1165</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
-      <c r="R1" s="88"/>
-      <c r="S1" s="88"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="88"/>
-      <c r="V1" s="88"/>
-      <c r="W1" s="88"/>
-      <c r="X1" s="88"/>
-      <c r="Y1" s="88"/>
-      <c r="Z1" s="88"/>
-      <c r="AA1" s="88"/>
-      <c r="AB1" s="88"/>
-      <c r="AC1" s="88"/>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="88"/>
-      <c r="AF1" s="88"/>
-      <c r="AG1" s="88"/>
-      <c r="AH1" s="88"/>
-      <c r="AI1" s="88"/>
-      <c r="AJ1" s="88"/>
-      <c r="AK1" s="88"/>
-      <c r="AL1" s="88"/>
-      <c r="AM1" s="88"/>
-      <c r="AN1" s="88"/>
-      <c r="AO1" s="88"/>
-      <c r="AP1" s="88"/>
-      <c r="AQ1" s="88"/>
-      <c r="AR1" s="88"/>
-      <c r="AS1" s="88"/>
-      <c r="AT1" s="88"/>
-      <c r="AU1" s="88"/>
-      <c r="AV1" s="88"/>
-      <c r="AW1" s="88"/>
-      <c r="AX1" s="88"/>
-      <c r="AY1" s="88"/>
-      <c r="AZ1" s="88"/>
-      <c r="BA1" s="88"/>
-      <c r="BB1" s="88"/>
-      <c r="BC1" s="88"/>
-      <c r="BD1" s="88"/>
-      <c r="BE1" s="88"/>
-      <c r="BF1" s="88"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="93"/>
+      <c r="L1" s="93"/>
+      <c r="M1" s="93"/>
+      <c r="N1" s="93"/>
+      <c r="O1" s="93"/>
+      <c r="P1" s="93"/>
+      <c r="Q1" s="93"/>
+      <c r="R1" s="93"/>
+      <c r="S1" s="93"/>
+      <c r="T1" s="93"/>
+      <c r="U1" s="93"/>
+      <c r="V1" s="93"/>
+      <c r="W1" s="93"/>
+      <c r="X1" s="93"/>
+      <c r="Y1" s="93"/>
+      <c r="Z1" s="93"/>
+      <c r="AA1" s="93"/>
+      <c r="AB1" s="93"/>
+      <c r="AC1" s="93"/>
+      <c r="AD1" s="93"/>
+      <c r="AE1" s="93"/>
+      <c r="AF1" s="93"/>
+      <c r="AG1" s="93"/>
+      <c r="AH1" s="93"/>
+      <c r="AI1" s="93"/>
+      <c r="AJ1" s="93"/>
+      <c r="AK1" s="93"/>
+      <c r="AL1" s="93"/>
+      <c r="AM1" s="93"/>
+      <c r="AN1" s="93"/>
+      <c r="AO1" s="93"/>
+      <c r="AP1" s="93"/>
+      <c r="AQ1" s="93"/>
+      <c r="AR1" s="93"/>
+      <c r="AS1" s="93"/>
+      <c r="AT1" s="93"/>
+      <c r="AU1" s="93"/>
+      <c r="AV1" s="93"/>
+      <c r="AW1" s="93"/>
+      <c r="AX1" s="93"/>
+      <c r="AY1" s="93"/>
+      <c r="AZ1" s="93"/>
+      <c r="BA1" s="93"/>
+      <c r="BB1" s="93"/>
+      <c r="BC1" s="93"/>
+      <c r="BD1" s="93"/>
+      <c r="BE1" s="93"/>
+      <c r="BF1" s="93"/>
       <c r="BH1" s="73" t="s">
         <v>1166</v>
       </c>
@@ -35903,66 +35901,66 @@
       </c>
     </row>
     <row r="2" spans="1:77" ht="14.5">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="94" t="s">
         <v>1184</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
-      <c r="R2" s="89"/>
-      <c r="S2" s="89"/>
-      <c r="T2" s="89"/>
-      <c r="U2" s="89"/>
-      <c r="V2" s="89"/>
-      <c r="W2" s="89"/>
-      <c r="X2" s="89"/>
-      <c r="Y2" s="89"/>
-      <c r="Z2" s="89"/>
-      <c r="AA2" s="89"/>
-      <c r="AB2" s="89"/>
-      <c r="AC2" s="89"/>
-      <c r="AD2" s="89"/>
-      <c r="AE2" s="89"/>
-      <c r="AF2" s="89"/>
-      <c r="AG2" s="89"/>
-      <c r="AH2" s="89"/>
-      <c r="AI2" s="89"/>
-      <c r="AJ2" s="89"/>
-      <c r="AK2" s="89"/>
-      <c r="AL2" s="89"/>
-      <c r="AM2" s="89"/>
-      <c r="AN2" s="89"/>
-      <c r="AO2" s="89"/>
-      <c r="AP2" s="89"/>
-      <c r="AQ2" s="89"/>
-      <c r="AR2" s="89"/>
-      <c r="AS2" s="89"/>
-      <c r="AT2" s="89"/>
-      <c r="AU2" s="89"/>
-      <c r="AV2" s="89"/>
-      <c r="AW2" s="89"/>
-      <c r="AX2" s="89"/>
-      <c r="AY2" s="89"/>
-      <c r="AZ2" s="89"/>
-      <c r="BA2" s="89"/>
-      <c r="BB2" s="89"/>
-      <c r="BC2" s="89"/>
-      <c r="BD2" s="89"/>
-      <c r="BE2" s="89"/>
-      <c r="BF2" s="89"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="94"/>
+      <c r="O2" s="94"/>
+      <c r="P2" s="94"/>
+      <c r="Q2" s="94"/>
+      <c r="R2" s="94"/>
+      <c r="S2" s="94"/>
+      <c r="T2" s="94"/>
+      <c r="U2" s="94"/>
+      <c r="V2" s="94"/>
+      <c r="W2" s="94"/>
+      <c r="X2" s="94"/>
+      <c r="Y2" s="94"/>
+      <c r="Z2" s="94"/>
+      <c r="AA2" s="94"/>
+      <c r="AB2" s="94"/>
+      <c r="AC2" s="94"/>
+      <c r="AD2" s="94"/>
+      <c r="AE2" s="94"/>
+      <c r="AF2" s="94"/>
+      <c r="AG2" s="94"/>
+      <c r="AH2" s="94"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="94"/>
+      <c r="AK2" s="94"/>
+      <c r="AL2" s="94"/>
+      <c r="AM2" s="94"/>
+      <c r="AN2" s="94"/>
+      <c r="AO2" s="94"/>
+      <c r="AP2" s="94"/>
+      <c r="AQ2" s="94"/>
+      <c r="AR2" s="94"/>
+      <c r="AS2" s="94"/>
+      <c r="AT2" s="94"/>
+      <c r="AU2" s="94"/>
+      <c r="AV2" s="94"/>
+      <c r="AW2" s="94"/>
+      <c r="AX2" s="94"/>
+      <c r="AY2" s="94"/>
+      <c r="AZ2" s="94"/>
+      <c r="BA2" s="94"/>
+      <c r="BB2" s="94"/>
+      <c r="BC2" s="94"/>
+      <c r="BD2" s="94"/>
+      <c r="BE2" s="94"/>
+      <c r="BF2" s="94"/>
       <c r="BH2" t="s">
         <v>81</v>
       </c>
@@ -36019,66 +36017,66 @@
       </c>
     </row>
     <row r="3" spans="1:77">
-      <c r="A3" s="90" t="s">
+      <c r="A3" s="95" t="s">
         <v>1198</v>
       </c>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
-      <c r="L3" s="90"/>
-      <c r="M3" s="90"/>
-      <c r="N3" s="90"/>
-      <c r="O3" s="90"/>
-      <c r="P3" s="90"/>
-      <c r="Q3" s="90"/>
-      <c r="R3" s="90"/>
-      <c r="S3" s="90"/>
-      <c r="T3" s="90"/>
-      <c r="U3" s="90"/>
-      <c r="V3" s="90"/>
-      <c r="W3" s="90"/>
-      <c r="X3" s="90"/>
-      <c r="Y3" s="90"/>
-      <c r="Z3" s="90"/>
-      <c r="AA3" s="90"/>
-      <c r="AB3" s="90"/>
-      <c r="AC3" s="90"/>
-      <c r="AD3" s="90"/>
-      <c r="AE3" s="90"/>
-      <c r="AF3" s="90"/>
-      <c r="AG3" s="90"/>
-      <c r="AH3" s="90"/>
-      <c r="AI3" s="90"/>
-      <c r="AJ3" s="90"/>
-      <c r="AK3" s="90"/>
-      <c r="AL3" s="90"/>
-      <c r="AM3" s="90"/>
-      <c r="AN3" s="90"/>
-      <c r="AO3" s="90"/>
-      <c r="AP3" s="90"/>
-      <c r="AQ3" s="90"/>
-      <c r="AR3" s="90"/>
-      <c r="AS3" s="90"/>
-      <c r="AT3" s="90"/>
-      <c r="AU3" s="90"/>
-      <c r="AV3" s="90"/>
-      <c r="AW3" s="90"/>
-      <c r="AX3" s="90"/>
-      <c r="AY3" s="90"/>
-      <c r="AZ3" s="90"/>
-      <c r="BA3" s="90"/>
-      <c r="BB3" s="90"/>
-      <c r="BC3" s="90"/>
-      <c r="BD3" s="90"/>
-      <c r="BE3" s="90"/>
-      <c r="BF3" s="90"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="95"/>
+      <c r="N3" s="95"/>
+      <c r="O3" s="95"/>
+      <c r="P3" s="95"/>
+      <c r="Q3" s="95"/>
+      <c r="R3" s="95"/>
+      <c r="S3" s="95"/>
+      <c r="T3" s="95"/>
+      <c r="U3" s="95"/>
+      <c r="V3" s="95"/>
+      <c r="W3" s="95"/>
+      <c r="X3" s="95"/>
+      <c r="Y3" s="95"/>
+      <c r="Z3" s="95"/>
+      <c r="AA3" s="95"/>
+      <c r="AB3" s="95"/>
+      <c r="AC3" s="95"/>
+      <c r="AD3" s="95"/>
+      <c r="AE3" s="95"/>
+      <c r="AF3" s="95"/>
+      <c r="AG3" s="95"/>
+      <c r="AH3" s="95"/>
+      <c r="AI3" s="95"/>
+      <c r="AJ3" s="95"/>
+      <c r="AK3" s="95"/>
+      <c r="AL3" s="95"/>
+      <c r="AM3" s="95"/>
+      <c r="AN3" s="95"/>
+      <c r="AO3" s="95"/>
+      <c r="AP3" s="95"/>
+      <c r="AQ3" s="95"/>
+      <c r="AR3" s="95"/>
+      <c r="AS3" s="95"/>
+      <c r="AT3" s="95"/>
+      <c r="AU3" s="95"/>
+      <c r="AV3" s="95"/>
+      <c r="AW3" s="95"/>
+      <c r="AX3" s="95"/>
+      <c r="AY3" s="95"/>
+      <c r="AZ3" s="95"/>
+      <c r="BA3" s="95"/>
+      <c r="BB3" s="95"/>
+      <c r="BC3" s="95"/>
+      <c r="BD3" s="95"/>
+      <c r="BE3" s="95"/>
+      <c r="BF3" s="95"/>
       <c r="BH3" t="s">
         <v>60</v>
       </c>
@@ -71775,58 +71773,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="23">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="88" t="s">
         <v>877</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="90" t="s">
         <v>878</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="91" t="s">
         <v>850</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
+      <c r="N3" s="91"/>
     </row>
     <row r="5" spans="1:14" ht="26">
       <c r="A5" s="1" t="s">
@@ -77889,55 +77887,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="20">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="96" t="s">
         <v>918</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="92"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="97"/>
     </row>
     <row r="2" spans="1:13" ht="14.5">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="98" t="s">
         <v>919</v>
       </c>
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="94"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="99"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="95" t="s">
+      <c r="A3" s="100" t="s">
         <v>920</v>
       </c>
-      <c r="B3" s="95"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="96"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="101"/>
     </row>
     <row r="5" spans="1:13" ht="26">
       <c r="A5" s="57" t="s">
@@ -80316,58 +80314,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="23">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="88" t="s">
         <v>940</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="90" t="s">
         <v>941</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="90"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="91" t="s">
         <v>850</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="86"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
+      <c r="N3" s="91"/>
     </row>
     <row r="5" spans="1:14" ht="26">
       <c r="A5" s="1" t="s">

--- a/data/Template_Resmi_Database_SIRUMAH.xlsx
+++ b/data/Template_Resmi_Database_SIRUMAH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEGION\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C3446A-B8D0-43BE-A2CE-47B43492BD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E31319-FC7F-4A36-8A15-D61B619364C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12058" uniqueCount="1952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12058" uniqueCount="1953">
   <si>
     <t>TEMPLATE RESMI DATABASE SIRUMAH — DATA PERUMAHAN</t>
   </si>
@@ -5893,6 +5893,9 @@
   </si>
   <si>
     <t>Jl. Yos Sudarso</t>
+  </si>
+  <si>
+    <t>Selesai Ditangani</t>
   </si>
 </sst>
 </file>
@@ -36932,7 +36935,7 @@
         <v>1208</v>
       </c>
       <c r="AW8" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX8" s="69" t="s">
         <v>1210</v>
@@ -37479,7 +37482,7 @@
         <v>1208</v>
       </c>
       <c r="AW11" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX11" s="69" t="s">
         <v>1210</v>
@@ -39004,7 +39007,7 @@
         <v>1208</v>
       </c>
       <c r="AW20" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX20" s="69" t="s">
         <v>1272</v>
@@ -41864,7 +41867,7 @@
         <v>1208</v>
       </c>
       <c r="AW37" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX37" s="69" t="s">
         <v>1210</v>
@@ -42372,7 +42375,7 @@
         <v>1208</v>
       </c>
       <c r="AW40" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX40" s="69" t="s">
         <v>1272</v>
@@ -42544,7 +42547,7 @@
         <v>1208</v>
       </c>
       <c r="AW41" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX41" s="69" t="s">
         <v>1210</v>
@@ -42716,7 +42719,7 @@
         <v>1208</v>
       </c>
       <c r="AW42" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX42" s="69" t="s">
         <v>1272</v>
@@ -42888,7 +42891,7 @@
         <v>1208</v>
       </c>
       <c r="AW43" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX43" s="69" t="s">
         <v>1272</v>
@@ -43060,7 +43063,7 @@
         <v>1208</v>
       </c>
       <c r="AW44" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX44" s="69" t="s">
         <v>1272</v>
@@ -43232,7 +43235,7 @@
         <v>1208</v>
       </c>
       <c r="AW45" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX45" s="69" t="s">
         <v>1210</v>
@@ -43404,7 +43407,7 @@
         <v>1208</v>
       </c>
       <c r="AW46" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX46" s="69" t="s">
         <v>1272</v>
@@ -43744,7 +43747,7 @@
         <v>1208</v>
       </c>
       <c r="AW48" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX48" s="69" t="s">
         <v>1272</v>
@@ -43916,7 +43919,7 @@
         <v>1208</v>
       </c>
       <c r="AW49" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX49" s="69" t="s">
         <v>1272</v>
@@ -44088,7 +44091,7 @@
         <v>1208</v>
       </c>
       <c r="AW50" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX50" s="69" t="s">
         <v>1272</v>
@@ -44260,7 +44263,7 @@
         <v>1208</v>
       </c>
       <c r="AW51" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX51" s="69" t="s">
         <v>1221</v>
@@ -44432,7 +44435,7 @@
         <v>1208</v>
       </c>
       <c r="AW52" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX52" s="69" t="s">
         <v>1210</v>
@@ -44604,7 +44607,7 @@
         <v>1208</v>
       </c>
       <c r="AW53" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX53" s="69" t="s">
         <v>1221</v>
@@ -44774,7 +44777,7 @@
         <v>1208</v>
       </c>
       <c r="AW54" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX54" s="69" t="s">
         <v>1210</v>
@@ -46290,7 +46293,7 @@
         <v>1208</v>
       </c>
       <c r="AW63" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX63" s="69" t="s">
         <v>1210</v>
@@ -47639,7 +47642,7 @@
         <v>1208</v>
       </c>
       <c r="AW71" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX71" s="69" t="s">
         <v>1210</v>
@@ -48483,7 +48486,7 @@
         <v>1208</v>
       </c>
       <c r="AW76" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX76" s="69" t="s">
         <v>1210</v>
@@ -49831,7 +49834,7 @@
         <v>1208</v>
       </c>
       <c r="AW84" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX84" s="69" t="s">
         <v>1287</v>
@@ -50339,7 +50342,7 @@
         <v>1208</v>
       </c>
       <c r="AW87" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX87" s="69" t="s">
         <v>1221</v>
@@ -50679,7 +50682,7 @@
         <v>1208</v>
       </c>
       <c r="AW89" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX89" s="69" t="s">
         <v>1210</v>
@@ -50851,7 +50854,7 @@
         <v>1208</v>
       </c>
       <c r="AW90" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX90" s="69" t="s">
         <v>1210</v>
@@ -51023,7 +51026,7 @@
         <v>1208</v>
       </c>
       <c r="AW91" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX91" s="69" t="s">
         <v>1210</v>
@@ -52371,7 +52374,7 @@
         <v>1208</v>
       </c>
       <c r="AW99" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX99" s="69" t="s">
         <v>1221</v>
@@ -52711,7 +52714,7 @@
         <v>1208</v>
       </c>
       <c r="AW101" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX101" s="69" t="s">
         <v>1210</v>
@@ -53051,7 +53054,7 @@
         <v>1208</v>
       </c>
       <c r="AW103" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX103" s="69" t="s">
         <v>1210</v>
@@ -53223,7 +53226,7 @@
         <v>1208</v>
       </c>
       <c r="AW104" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX104" s="69" t="s">
         <v>1210</v>
@@ -53395,7 +53398,7 @@
         <v>1208</v>
       </c>
       <c r="AW105" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX105" s="69" t="s">
         <v>1210</v>
@@ -54239,7 +54242,7 @@
         <v>1208</v>
       </c>
       <c r="AW110" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX110" s="69" t="s">
         <v>1221</v>
@@ -55083,7 +55086,7 @@
         <v>1208</v>
       </c>
       <c r="AW115" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX115" s="69" t="s">
         <v>1210</v>
@@ -55591,7 +55594,7 @@
         <v>1208</v>
       </c>
       <c r="AW118" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX118" s="69" t="s">
         <v>1210</v>
@@ -55763,7 +55766,7 @@
         <v>1208</v>
       </c>
       <c r="AW119" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX119" s="69" t="s">
         <v>1210</v>
@@ -55935,7 +55938,7 @@
         <v>1208</v>
       </c>
       <c r="AW120" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX120" s="69" t="s">
         <v>1210</v>
@@ -56107,7 +56110,7 @@
         <v>1208</v>
       </c>
       <c r="AW121" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX121" s="69" t="s">
         <v>1210</v>
@@ -56447,7 +56450,7 @@
         <v>1208</v>
       </c>
       <c r="AW123" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX123" s="69" t="s">
         <v>1210</v>
@@ -56619,7 +56622,7 @@
         <v>1208</v>
       </c>
       <c r="AW124" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX124" s="69" t="s">
         <v>1210</v>
@@ -56791,7 +56794,7 @@
         <v>1208</v>
       </c>
       <c r="AW125" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX125" s="69" t="s">
         <v>1210</v>
@@ -58139,7 +58142,7 @@
         <v>1208</v>
       </c>
       <c r="AW133" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX133" s="69" t="s">
         <v>1221</v>
@@ -59656,7 +59659,7 @@
         <v>1208</v>
       </c>
       <c r="AW142" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX142" s="69" t="s">
         <v>1210</v>
@@ -59828,7 +59831,7 @@
         <v>1208</v>
       </c>
       <c r="AW143" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX143" s="69" t="s">
         <v>1210</v>
@@ -60000,7 +60003,7 @@
         <v>1208</v>
       </c>
       <c r="AW144" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX144" s="69" t="s">
         <v>1210</v>
@@ -60172,7 +60175,7 @@
         <v>1208</v>
       </c>
       <c r="AW145" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX145" s="69" t="s">
         <v>1210</v>
@@ -60848,7 +60851,7 @@
         <v>1208</v>
       </c>
       <c r="AW149" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX149" s="69" t="s">
         <v>1210</v>
@@ -61020,7 +61023,7 @@
         <v>1208</v>
       </c>
       <c r="AW150" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX150" s="69" t="s">
         <v>1210</v>
@@ -61864,7 +61867,7 @@
         <v>1208</v>
       </c>
       <c r="AW155" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX155" s="69" t="s">
         <v>1210</v>
@@ -62036,7 +62039,7 @@
         <v>1208</v>
       </c>
       <c r="AW156" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX156" s="69" t="s">
         <v>1210</v>
@@ -62544,7 +62547,7 @@
         <v>1208</v>
       </c>
       <c r="AW159" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX159" s="69" t="s">
         <v>1210</v>
@@ -62714,7 +62717,7 @@
         <v>1208</v>
       </c>
       <c r="AW160" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX160" s="69" t="s">
         <v>1210</v>
@@ -63220,7 +63223,7 @@
         <v>1208</v>
       </c>
       <c r="AW163" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX163" s="69" t="s">
         <v>1287</v>
@@ -63390,7 +63393,7 @@
         <v>1208</v>
       </c>
       <c r="AW164" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX164" s="69" t="s">
         <v>1210</v>
@@ -63898,7 +63901,7 @@
         <v>1208</v>
       </c>
       <c r="AW167" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX167" s="69" t="s">
         <v>1210</v>
@@ -64070,7 +64073,7 @@
         <v>1208</v>
       </c>
       <c r="AW168" s="69" t="s">
-        <v>1271</v>
+        <v>1952</v>
       </c>
       <c r="AX168" s="69" t="s">
         <v>1210</v>
